--- a/lyre-viz/historique_perf.xlsx
+++ b/lyre-viz/historique_perf.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O112"/>
+  <dimension ref="A1:O224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -6906,6 +6906,6530 @@
         </is>
       </c>
     </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e +modifs</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>7a. Aberration chromatique codee, coupee (atlas R32F garde)</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=0</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>defaut / public</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="H113" s="4">
+        <f>IF(G113&gt;0,1000/G113,"")</f>
+        <v/>
+      </c>
+      <c r="I113" s="3" t="n">
+        <v>7.13</v>
+      </c>
+      <c r="J113" s="3" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="K113" s="3" t="n">
+        <v>1.679</v>
+      </c>
+      <c r="L113" s="3" t="n">
+        <v>2.075</v>
+      </c>
+      <c r="M113" s="3" t="n"/>
+      <c r="N113" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>ca_v5_format_B0, ca_v5_format_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e +modifs</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>7a. Aberration chromatique codee, coupee (atlas R32F garde)</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=0</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>defaut / scene</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="n">
+        <v>8.734999999999999</v>
+      </c>
+      <c r="H114" s="4">
+        <f>IF(G114&gt;0,1000/G114,"")</f>
+        <v/>
+      </c>
+      <c r="I114" s="3" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="J114" s="3" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="K114" s="3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="L114" s="3" t="n">
+        <v>2.003</v>
+      </c>
+      <c r="M114" s="3" t="n"/>
+      <c r="N114" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>ca_v5_format_B0, ca_v5_format_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e +modifs</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>7a. Aberration chromatique codee, coupee (atlas R32F garde)</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=0</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>defaut / sous les trusses</t>
+        </is>
+      </c>
+      <c r="G115" s="3" t="n">
+        <v>7.93</v>
+      </c>
+      <c r="H115" s="4">
+        <f>IF(G115&gt;0,1000/G115,"")</f>
+        <v/>
+      </c>
+      <c r="I115" s="3" t="n">
+        <v>6.585</v>
+      </c>
+      <c r="J115" s="3" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="K115" s="3" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="L115" s="3" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="M115" s="3" t="n"/>
+      <c r="N115" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>ca_v5_format_B0, ca_v5_format_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e +modifs</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>7a. Aberration chromatique codee, coupee (atlas R32F garde)</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=0</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>gobo + prisme 8 + zoom 25 / public</t>
+        </is>
+      </c>
+      <c r="G116" s="3" t="n">
+        <v>20.54</v>
+      </c>
+      <c r="H116" s="4">
+        <f>IF(G116&gt;0,1000/G116,"")</f>
+        <v/>
+      </c>
+      <c r="I116" s="3" t="n">
+        <v>19.51</v>
+      </c>
+      <c r="J116" s="3" t="n">
+        <v>19.24</v>
+      </c>
+      <c r="K116" s="3" t="n">
+        <v>6.647</v>
+      </c>
+      <c r="L116" s="3" t="n">
+        <v>7.519</v>
+      </c>
+      <c r="M116" s="3" t="n"/>
+      <c r="N116" s="2" t="n">
+        <v>282</v>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>ca_v5_format_B0, ca_v5_format_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e +modifs</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>7a. Aberration chromatique codee, coupee (atlas R32F garde)</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=0</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>gobo + prisme 8 + zoom 25 / scene</t>
+        </is>
+      </c>
+      <c r="G117" s="3" t="n">
+        <v>19.82</v>
+      </c>
+      <c r="H117" s="4">
+        <f>IF(G117&gt;0,1000/G117,"")</f>
+        <v/>
+      </c>
+      <c r="I117" s="3" t="n">
+        <v>18.635</v>
+      </c>
+      <c r="J117" s="3" t="n">
+        <v>18.46</v>
+      </c>
+      <c r="K117" s="3" t="n">
+        <v>5.921</v>
+      </c>
+      <c r="L117" s="3" t="n">
+        <v>7.033</v>
+      </c>
+      <c r="M117" s="3" t="n"/>
+      <c r="N117" s="2" t="n">
+        <v>282</v>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>ca_v5_format_B0, ca_v5_format_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e +modifs</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>7a. Aberration chromatique codee, coupee (atlas R32F garde)</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=0</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>gobo + prisme 8 + zoom 25 / sous les trusses</t>
+        </is>
+      </c>
+      <c r="G118" s="3" t="n">
+        <v>14.855</v>
+      </c>
+      <c r="H118" s="4">
+        <f>IF(G118&gt;0,1000/G118,"")</f>
+        <v/>
+      </c>
+      <c r="I118" s="3" t="n">
+        <v>13.725</v>
+      </c>
+      <c r="J118" s="3" t="n">
+        <v>13.665</v>
+      </c>
+      <c r="K118" s="3" t="n">
+        <v>3.681</v>
+      </c>
+      <c r="L118" s="3" t="n">
+        <v>4.184</v>
+      </c>
+      <c r="M118" s="3" t="n"/>
+      <c r="N118" s="2" t="n">
+        <v>282</v>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>ca_v5_format_B0, ca_v5_format_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e +modifs</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>7a. Aberration chromatique codee, coupee (atlas R32F garde)</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=0</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>zoom 45 + frost 0.6 / public</t>
+        </is>
+      </c>
+      <c r="G119" s="3" t="n">
+        <v>12.85</v>
+      </c>
+      <c r="H119" s="4">
+        <f>IF(G119&gt;0,1000/G119,"")</f>
+        <v/>
+      </c>
+      <c r="I119" s="3" t="n">
+        <v>11.385</v>
+      </c>
+      <c r="J119" s="3" t="n">
+        <v>10.74</v>
+      </c>
+      <c r="K119" s="3" t="n">
+        <v>3.487</v>
+      </c>
+      <c r="L119" s="3" t="n">
+        <v>4.241</v>
+      </c>
+      <c r="M119" s="3" t="n"/>
+      <c r="N119" s="2" t="n">
+        <v>941</v>
+      </c>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>ca_v5_format_B0, ca_v5_format_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e +modifs</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>7a. Aberration chromatique codee, coupee (atlas R32F garde)</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=0</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>zoom 45 + frost 0.6 / scene</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="n">
+        <v>12.68</v>
+      </c>
+      <c r="H120" s="4">
+        <f>IF(G120&gt;0,1000/G120,"")</f>
+        <v/>
+      </c>
+      <c r="I120" s="3" t="n">
+        <v>11.27</v>
+      </c>
+      <c r="J120" s="3" t="n">
+        <v>10.855</v>
+      </c>
+      <c r="K120" s="3" t="n">
+        <v>3.348</v>
+      </c>
+      <c r="L120" s="3" t="n">
+        <v>4.163</v>
+      </c>
+      <c r="M120" s="3" t="n"/>
+      <c r="N120" s="2" t="n">
+        <v>941</v>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>ca_v5_format_B0, ca_v5_format_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e +modifs</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>7a. Aberration chromatique codee, coupee (atlas R32F garde)</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=0</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>zoom 45 + frost 0.6 / sous les trusses</t>
+        </is>
+      </c>
+      <c r="G121" s="3" t="n">
+        <v>10.015</v>
+      </c>
+      <c r="H121" s="4">
+        <f>IF(G121&gt;0,1000/G121,"")</f>
+        <v/>
+      </c>
+      <c r="I121" s="3" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="J121" s="3" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="K121" s="3" t="n">
+        <v>1.651</v>
+      </c>
+      <c r="L121" s="3" t="n">
+        <v>3.517</v>
+      </c>
+      <c r="M121" s="3" t="n"/>
+      <c r="N121" s="2" t="n">
+        <v>941</v>
+      </c>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>ca_v5_format_B0, ca_v5_format_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e +modifs</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>7a. Aberration chromatique codee, coupee (atlas R32F garde)</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=0</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>sans rebonds (GI)</t>
+        </is>
+      </c>
+      <c r="G122" s="3" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="H122" s="4">
+        <f>IF(G122&gt;0,1000/G122,"")</f>
+        <v/>
+      </c>
+      <c r="I122" s="3" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="J122" s="3" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="K122" s="3" t="n">
+        <v>1.442</v>
+      </c>
+      <c r="L122" s="3" t="n">
+        <v>1.613</v>
+      </c>
+      <c r="M122" s="3" t="n"/>
+      <c r="N122" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>ca_v5_format_B0, ca_v5_format_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e +modifs</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>7a. Aberration chromatique codee, coupee (atlas R32F garde)</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=0</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>sans fumee volumetrique</t>
+        </is>
+      </c>
+      <c r="G123" s="3" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="H123" s="4">
+        <f>IF(G123&gt;0,1000/G123,"")</f>
+        <v/>
+      </c>
+      <c r="I123" s="3" t="n">
+        <v>4.365</v>
+      </c>
+      <c r="J123" s="3" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="K123" s="3" t="n">
+        <v>1.681</v>
+      </c>
+      <c r="L123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" s="3" t="n"/>
+      <c r="N123" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>ca_v5_format_B0, ca_v5_format_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e +modifs</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>7a. Aberration chromatique codee, coupee (atlas R32F garde)</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=0</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>sans taches sur surfaces</t>
+        </is>
+      </c>
+      <c r="G124" s="3" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="H124" s="4">
+        <f>IF(G124&gt;0,1000/G124,"")</f>
+        <v/>
+      </c>
+      <c r="I124" s="3" t="n">
+        <v>6.425</v>
+      </c>
+      <c r="J124" s="3" t="n">
+        <v>5.925</v>
+      </c>
+      <c r="K124" s="3" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="L124" s="3" t="n">
+        <v>2.141</v>
+      </c>
+      <c r="M124" s="3" t="n"/>
+      <c r="N124" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>ca_v5_format_B0, ca_v5_format_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e +modifs</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>7a. Aberration chromatique codee, coupee (atlas R32F garde)</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=0</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>sans reflets</t>
+        </is>
+      </c>
+      <c r="G125" s="3" t="n">
+        <v>9.175000000000001</v>
+      </c>
+      <c r="H125" s="4">
+        <f>IF(G125&gt;0,1000/G125,"")</f>
+        <v/>
+      </c>
+      <c r="I125" s="3" t="n">
+        <v>7.305</v>
+      </c>
+      <c r="J125" s="3" t="n">
+        <v>6.845</v>
+      </c>
+      <c r="K125" s="3" t="n">
+        <v>1.725</v>
+      </c>
+      <c r="L125" s="3" t="n">
+        <v>2.123</v>
+      </c>
+      <c r="M125" s="3" t="n"/>
+      <c r="N125" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>ca_v5_format_B0, ca_v5_format_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e +modifs</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>7a. Aberration chromatique codee, coupee (atlas R32F garde)</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=0</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>sans bloom</t>
+        </is>
+      </c>
+      <c r="G126" s="3" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="H126" s="4">
+        <f>IF(G126&gt;0,1000/G126,"")</f>
+        <v/>
+      </c>
+      <c r="I126" s="3" t="n">
+        <v>7.115</v>
+      </c>
+      <c r="J126" s="3" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="K126" s="3" t="n">
+        <v>1.749</v>
+      </c>
+      <c r="L126" s="3" t="n">
+        <v>2.171</v>
+      </c>
+      <c r="M126" s="3" t="n"/>
+      <c r="N126" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>ca_v5_format_B0, ca_v5_format_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e +modifs</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>7a. Aberration chromatique codee, coupee (atlas R32F garde)</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=0</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>sol mouille / public</t>
+        </is>
+      </c>
+      <c r="G127" s="3" t="n">
+        <v>10.615</v>
+      </c>
+      <c r="H127" s="4">
+        <f>IF(G127&gt;0,1000/G127,"")</f>
+        <v/>
+      </c>
+      <c r="I127" s="3" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="J127" s="3" t="n">
+        <v>8.885</v>
+      </c>
+      <c r="K127" s="3" t="n">
+        <v>1.806</v>
+      </c>
+      <c r="L127" s="3" t="n">
+        <v>2.148</v>
+      </c>
+      <c r="M127" s="3" t="n">
+        <v>1.073</v>
+      </c>
+      <c r="N127" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>ca_v5_format_B0, ca_v5_format_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e +modifs</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>7a. Aberration chromatique codee, coupee (atlas R32F garde)</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=0</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>sol mouille + gobo + prisme 8 / scene</t>
+        </is>
+      </c>
+      <c r="G128" s="3" t="n">
+        <v>24.54</v>
+      </c>
+      <c r="H128" s="4">
+        <f>IF(G128&gt;0,1000/G128,"")</f>
+        <v/>
+      </c>
+      <c r="I128" s="3" t="n">
+        <v>23.73</v>
+      </c>
+      <c r="J128" s="3" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="K128" s="3" t="n">
+        <v>5.886</v>
+      </c>
+      <c r="L128" s="3" t="n">
+        <v>7.014</v>
+      </c>
+      <c r="M128" s="3" t="n">
+        <v>4.896</v>
+      </c>
+      <c r="N128" s="2" t="n">
+        <v>282</v>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>ca_v5_format_B0, ca_v5_format_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e +modifs</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>7b. Aberration chromatique coupee (banc rapide)</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide (--fast), chroma=0</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>defaut / public</t>
+        </is>
+      </c>
+      <c r="G129" s="3" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="H129" s="4">
+        <f>IF(G129&gt;0,1000/G129,"")</f>
+        <v/>
+      </c>
+      <c r="I129" s="3" t="n">
+        <v>6.875</v>
+      </c>
+      <c r="J129" s="3" t="n">
+        <v>6.305</v>
+      </c>
+      <c r="K129" s="3" t="n">
+        <v>1.636</v>
+      </c>
+      <c r="L129" s="3" t="n">
+        <v>1.973</v>
+      </c>
+      <c r="M129" s="3" t="n"/>
+      <c r="N129" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>ca_v5_A0, ca_v5_A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e +modifs</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>7b. Aberration chromatique coupee (banc rapide)</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide (--fast), chroma=0</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>defaut / scene</t>
+        </is>
+      </c>
+      <c r="G130" s="3" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="H130" s="4">
+        <f>IF(G130&gt;0,1000/G130,"")</f>
+        <v/>
+      </c>
+      <c r="I130" s="3" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="J130" s="3" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="K130" s="3" t="n">
+        <v>1.583</v>
+      </c>
+      <c r="L130" s="3" t="n">
+        <v>1.945</v>
+      </c>
+      <c r="M130" s="3" t="n"/>
+      <c r="N130" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>ca_v5_A0, ca_v5_A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e +modifs</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>7b. Aberration chromatique coupee (banc rapide)</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide (--fast), chroma=0</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>defaut / sous les trusses</t>
+        </is>
+      </c>
+      <c r="G131" s="3" t="n">
+        <v>7.59</v>
+      </c>
+      <c r="H131" s="4">
+        <f>IF(G131&gt;0,1000/G131,"")</f>
+        <v/>
+      </c>
+      <c r="I131" s="3" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="J131" s="3" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="K131" s="3" t="n">
+        <v>1.163</v>
+      </c>
+      <c r="L131" s="3" t="n">
+        <v>1.679</v>
+      </c>
+      <c r="M131" s="3" t="n"/>
+      <c r="N131" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>ca_v5_A0, ca_v5_A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e +modifs</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>7b. Aberration chromatique coupee (banc rapide)</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide (--fast), chroma=0</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>gobo + prisme 8 + zoom 25 / public</t>
+        </is>
+      </c>
+      <c r="G132" s="3" t="n">
+        <v>19.265</v>
+      </c>
+      <c r="H132" s="4">
+        <f>IF(G132&gt;0,1000/G132,"")</f>
+        <v/>
+      </c>
+      <c r="I132" s="3" t="n">
+        <v>18.405</v>
+      </c>
+      <c r="J132" s="3" t="n">
+        <v>18.225</v>
+      </c>
+      <c r="K132" s="3" t="n">
+        <v>6.259</v>
+      </c>
+      <c r="L132" s="3" t="n">
+        <v>7.221</v>
+      </c>
+      <c r="M132" s="3" t="n"/>
+      <c r="N132" s="2" t="n">
+        <v>273</v>
+      </c>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>ca_v5_A0, ca_v5_A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e +modifs</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>7b. Aberration chromatique coupee (banc rapide)</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide (--fast), chroma=0</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>gobo + prisme 8 + zoom 25 / scene</t>
+        </is>
+      </c>
+      <c r="G133" s="3" t="n">
+        <v>17.23</v>
+      </c>
+      <c r="H133" s="4">
+        <f>IF(G133&gt;0,1000/G133,"")</f>
+        <v/>
+      </c>
+      <c r="I133" s="3" t="n">
+        <v>16.365</v>
+      </c>
+      <c r="J133" s="3" t="n">
+        <v>16.21</v>
+      </c>
+      <c r="K133" s="3" t="n">
+        <v>5.069</v>
+      </c>
+      <c r="L133" s="3" t="n">
+        <v>6.412</v>
+      </c>
+      <c r="M133" s="3" t="n"/>
+      <c r="N133" s="2" t="n">
+        <v>273</v>
+      </c>
+      <c r="O133" s="2" t="inlineStr">
+        <is>
+          <t>ca_v5_A0, ca_v5_A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e +modifs</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>7b. Aberration chromatique coupee (banc rapide)</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide (--fast), chroma=0</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>gobo + prisme 8 + zoom 25 / sous les trusses</t>
+        </is>
+      </c>
+      <c r="G134" s="3" t="n">
+        <v>13.28</v>
+      </c>
+      <c r="H134" s="4">
+        <f>IF(G134&gt;0,1000/G134,"")</f>
+        <v/>
+      </c>
+      <c r="I134" s="3" t="n">
+        <v>12.345</v>
+      </c>
+      <c r="J134" s="3" t="n">
+        <v>12.225</v>
+      </c>
+      <c r="K134" s="3" t="n">
+        <v>3.351</v>
+      </c>
+      <c r="L134" s="3" t="n">
+        <v>3.978</v>
+      </c>
+      <c r="M134" s="3" t="n"/>
+      <c r="N134" s="2" t="n">
+        <v>273</v>
+      </c>
+      <c r="O134" s="2" t="inlineStr">
+        <is>
+          <t>ca_v5_A0, ca_v5_A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e +modifs</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>7b. Aberration chromatique coupee (banc rapide)</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide (--fast), chroma=0</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>zoom 45 + frost 0.6 / public</t>
+        </is>
+      </c>
+      <c r="G135" s="3" t="n">
+        <v>12.385</v>
+      </c>
+      <c r="H135" s="4">
+        <f>IF(G135&gt;0,1000/G135,"")</f>
+        <v/>
+      </c>
+      <c r="I135" s="3" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="J135" s="3" t="n">
+        <v>10.57</v>
+      </c>
+      <c r="K135" s="3" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="L135" s="3" t="n">
+        <v>3.979</v>
+      </c>
+      <c r="M135" s="3" t="n"/>
+      <c r="N135" s="2" t="n">
+        <v>885</v>
+      </c>
+      <c r="O135" s="2" t="inlineStr">
+        <is>
+          <t>ca_v5_A0, ca_v5_A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e +modifs</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>7b. Aberration chromatique coupee (banc rapide)</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide (--fast), chroma=0</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>zoom 45 + frost 0.6 / scene</t>
+        </is>
+      </c>
+      <c r="G136" s="3" t="n">
+        <v>12.075</v>
+      </c>
+      <c r="H136" s="4">
+        <f>IF(G136&gt;0,1000/G136,"")</f>
+        <v/>
+      </c>
+      <c r="I136" s="3" t="n">
+        <v>10.785</v>
+      </c>
+      <c r="J136" s="3" t="n">
+        <v>10.015</v>
+      </c>
+      <c r="K136" s="3" t="n">
+        <v>3.031</v>
+      </c>
+      <c r="L136" s="3" t="n">
+        <v>4.049</v>
+      </c>
+      <c r="M136" s="3" t="n"/>
+      <c r="N136" s="2" t="n">
+        <v>885</v>
+      </c>
+      <c r="O136" s="2" t="inlineStr">
+        <is>
+          <t>ca_v5_A0, ca_v5_A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e +modifs</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>7b. Aberration chromatique coupee (banc rapide)</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide (--fast), chroma=0</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>zoom 45 + frost 0.6 / sous les trusses</t>
+        </is>
+      </c>
+      <c r="G137" s="3" t="n">
+        <v>9.335000000000001</v>
+      </c>
+      <c r="H137" s="4">
+        <f>IF(G137&gt;0,1000/G137,"")</f>
+        <v/>
+      </c>
+      <c r="I137" s="3" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="J137" s="3" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="K137" s="3" t="n">
+        <v>1.502</v>
+      </c>
+      <c r="L137" s="3" t="n">
+        <v>2.924</v>
+      </c>
+      <c r="M137" s="3" t="n"/>
+      <c r="N137" s="2" t="n">
+        <v>885</v>
+      </c>
+      <c r="O137" s="2" t="inlineStr">
+        <is>
+          <t>ca_v5_A0, ca_v5_A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e +modifs</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>7b. Aberration chromatique coupee (banc rapide)</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide (--fast), chroma=0</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>sans rebonds (GI)</t>
+        </is>
+      </c>
+      <c r="G138" s="3" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="H138" s="4">
+        <f>IF(G138&gt;0,1000/G138,"")</f>
+        <v/>
+      </c>
+      <c r="I138" s="3" t="n">
+        <v>6.335</v>
+      </c>
+      <c r="J138" s="3" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="K138" s="3" t="n">
+        <v>1.383</v>
+      </c>
+      <c r="L138" s="3" t="n">
+        <v>1.522</v>
+      </c>
+      <c r="M138" s="3" t="n"/>
+      <c r="N138" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O138" s="2" t="inlineStr">
+        <is>
+          <t>ca_v5_A0, ca_v5_A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e +modifs</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>7b. Aberration chromatique coupee (banc rapide)</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide (--fast), chroma=0</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>sans fumee volumetrique</t>
+        </is>
+      </c>
+      <c r="G139" s="3" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="H139" s="4">
+        <f>IF(G139&gt;0,1000/G139,"")</f>
+        <v/>
+      </c>
+      <c r="I139" s="3" t="n">
+        <v>4.125</v>
+      </c>
+      <c r="J139" s="3" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="K139" s="3" t="n">
+        <v>1.651</v>
+      </c>
+      <c r="L139" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" s="3" t="n"/>
+      <c r="N139" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O139" s="2" t="inlineStr">
+        <is>
+          <t>ca_v5_A0, ca_v5_A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e +modifs</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>7b. Aberration chromatique coupee (banc rapide)</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide (--fast), chroma=0</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>sans taches sur surfaces</t>
+        </is>
+      </c>
+      <c r="G140" s="3" t="n">
+        <v>7.525</v>
+      </c>
+      <c r="H140" s="4">
+        <f>IF(G140&gt;0,1000/G140,"")</f>
+        <v/>
+      </c>
+      <c r="I140" s="3" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="J140" s="3" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="K140" s="3" t="n">
+        <v>0.796</v>
+      </c>
+      <c r="L140" s="3" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="M140" s="3" t="n"/>
+      <c r="N140" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O140" s="2" t="inlineStr">
+        <is>
+          <t>ca_v5_A0, ca_v5_A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e +modifs</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>7b. Aberration chromatique coupee (banc rapide)</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide (--fast), chroma=0</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>sans reflets</t>
+        </is>
+      </c>
+      <c r="G141" s="3" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="H141" s="4">
+        <f>IF(G141&gt;0,1000/G141,"")</f>
+        <v/>
+      </c>
+      <c r="I141" s="3" t="n">
+        <v>7.385</v>
+      </c>
+      <c r="J141" s="3" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="K141" s="3" t="n">
+        <v>1.666</v>
+      </c>
+      <c r="L141" s="3" t="n">
+        <v>2.089</v>
+      </c>
+      <c r="M141" s="3" t="n"/>
+      <c r="N141" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O141" s="2" t="inlineStr">
+        <is>
+          <t>ca_v5_A0, ca_v5_A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e +modifs</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>7b. Aberration chromatique coupee (banc rapide)</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide (--fast), chroma=0</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>sans bloom</t>
+        </is>
+      </c>
+      <c r="G142" s="3" t="n">
+        <v>7.875</v>
+      </c>
+      <c r="H142" s="4">
+        <f>IF(G142&gt;0,1000/G142,"")</f>
+        <v/>
+      </c>
+      <c r="I142" s="3" t="n">
+        <v>6.785</v>
+      </c>
+      <c r="J142" s="3" t="n">
+        <v>6.255</v>
+      </c>
+      <c r="K142" s="3" t="n">
+        <v>1.673</v>
+      </c>
+      <c r="L142" s="3" t="n">
+        <v>2.036</v>
+      </c>
+      <c r="M142" s="3" t="n"/>
+      <c r="N142" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O142" s="2" t="inlineStr">
+        <is>
+          <t>ca_v5_A0, ca_v5_A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e +modifs</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>7b. Aberration chromatique coupee (banc rapide)</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide (--fast), chroma=0</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>sol mouille / public</t>
+        </is>
+      </c>
+      <c r="G143" s="3" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="H143" s="4">
+        <f>IF(G143&gt;0,1000/G143,"")</f>
+        <v/>
+      </c>
+      <c r="I143" s="3" t="n">
+        <v>9.185</v>
+      </c>
+      <c r="J143" s="3" t="n">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="K143" s="3" t="n">
+        <v>1.736</v>
+      </c>
+      <c r="L143" s="3" t="n">
+        <v>2.024</v>
+      </c>
+      <c r="M143" s="3" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="N143" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O143" s="2" t="inlineStr">
+        <is>
+          <t>ca_v5_A0, ca_v5_A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e +modifs</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>7b. Aberration chromatique coupee (banc rapide)</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide (--fast), chroma=0</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>sol mouille + gobo + prisme 8 / scene</t>
+        </is>
+      </c>
+      <c r="G144" s="3" t="n">
+        <v>22.755</v>
+      </c>
+      <c r="H144" s="4">
+        <f>IF(G144&gt;0,1000/G144,"")</f>
+        <v/>
+      </c>
+      <c r="I144" s="3" t="n">
+        <v>21.95</v>
+      </c>
+      <c r="J144" s="3" t="n">
+        <v>21.615</v>
+      </c>
+      <c r="K144" s="3" t="n">
+        <v>5.541</v>
+      </c>
+      <c r="L144" s="3" t="n">
+        <v>6.549</v>
+      </c>
+      <c r="M144" s="3" t="n">
+        <v>4.114</v>
+      </c>
+      <c r="N144" s="2" t="n">
+        <v>273</v>
+      </c>
+      <c r="O144" s="2" t="inlineStr">
+        <is>
+          <t>ca_v5_A0, ca_v5_A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e +modifs</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>7c. Aberration chromatique active (banc rapide)</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide (--fast), chroma=1</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>defaut / public</t>
+        </is>
+      </c>
+      <c r="G145" s="3" t="n">
+        <v>8.215</v>
+      </c>
+      <c r="H145" s="4">
+        <f>IF(G145&gt;0,1000/G145,"")</f>
+        <v/>
+      </c>
+      <c r="I145" s="3" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="J145" s="3" t="n">
+        <v>6.455</v>
+      </c>
+      <c r="K145" s="3" t="n">
+        <v>1.686</v>
+      </c>
+      <c r="L145" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M145" s="3" t="n"/>
+      <c r="N145" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O145" s="2" t="inlineStr">
+        <is>
+          <t>ca_v5_B0, ca_v5_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e +modifs</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>7c. Aberration chromatique active (banc rapide)</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide (--fast), chroma=1</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>defaut / scene</t>
+        </is>
+      </c>
+      <c r="G146" s="3" t="n">
+        <v>8.385</v>
+      </c>
+      <c r="H146" s="4">
+        <f>IF(G146&gt;0,1000/G146,"")</f>
+        <v/>
+      </c>
+      <c r="I146" s="3" t="n">
+        <v>7.095</v>
+      </c>
+      <c r="J146" s="3" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="K146" s="3" t="n">
+        <v>1.646</v>
+      </c>
+      <c r="L146" s="3" t="n">
+        <v>1.957</v>
+      </c>
+      <c r="M146" s="3" t="n"/>
+      <c r="N146" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O146" s="2" t="inlineStr">
+        <is>
+          <t>ca_v5_B0, ca_v5_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e +modifs</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>7c. Aberration chromatique active (banc rapide)</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide (--fast), chroma=1</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>defaut / sous les trusses</t>
+        </is>
+      </c>
+      <c r="G147" s="3" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="H147" s="4">
+        <f>IF(G147&gt;0,1000/G147,"")</f>
+        <v/>
+      </c>
+      <c r="I147" s="3" t="n">
+        <v>6.735</v>
+      </c>
+      <c r="J147" s="3" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="K147" s="3" t="n">
+        <v>1.201</v>
+      </c>
+      <c r="L147" s="3" t="n">
+        <v>1.715</v>
+      </c>
+      <c r="M147" s="3" t="n"/>
+      <c r="N147" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O147" s="2" t="inlineStr">
+        <is>
+          <t>ca_v5_B0, ca_v5_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e +modifs</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>7c. Aberration chromatique active (banc rapide)</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide (--fast), chroma=1</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>gobo + prisme 8 + zoom 25 / public</t>
+        </is>
+      </c>
+      <c r="G148" s="3" t="n">
+        <v>20.07</v>
+      </c>
+      <c r="H148" s="4">
+        <f>IF(G148&gt;0,1000/G148,"")</f>
+        <v/>
+      </c>
+      <c r="I148" s="3" t="n">
+        <v>19.215</v>
+      </c>
+      <c r="J148" s="3" t="n">
+        <v>18.955</v>
+      </c>
+      <c r="K148" s="3" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="L148" s="3" t="n">
+        <v>7.327</v>
+      </c>
+      <c r="M148" s="3" t="n"/>
+      <c r="N148" s="2" t="n">
+        <v>273</v>
+      </c>
+      <c r="O148" s="2" t="inlineStr">
+        <is>
+          <t>ca_v5_B0, ca_v5_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e +modifs</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>7c. Aberration chromatique active (banc rapide)</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide (--fast), chroma=1</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>gobo + prisme 8 + zoom 25 / scene</t>
+        </is>
+      </c>
+      <c r="G149" s="3" t="n">
+        <v>18.23</v>
+      </c>
+      <c r="H149" s="4">
+        <f>IF(G149&gt;0,1000/G149,"")</f>
+        <v/>
+      </c>
+      <c r="I149" s="3" t="n">
+        <v>17.17</v>
+      </c>
+      <c r="J149" s="3" t="n">
+        <v>17.09</v>
+      </c>
+      <c r="K149" s="3" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="L149" s="3" t="n">
+        <v>6.613</v>
+      </c>
+      <c r="M149" s="3" t="n"/>
+      <c r="N149" s="2" t="n">
+        <v>273</v>
+      </c>
+      <c r="O149" s="2" t="inlineStr">
+        <is>
+          <t>ca_v5_B0, ca_v5_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e +modifs</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>7c. Aberration chromatique active (banc rapide)</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide (--fast), chroma=1</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>gobo + prisme 8 + zoom 25 / sous les trusses</t>
+        </is>
+      </c>
+      <c r="G150" s="3" t="n">
+        <v>13.855</v>
+      </c>
+      <c r="H150" s="4">
+        <f>IF(G150&gt;0,1000/G150,"")</f>
+        <v/>
+      </c>
+      <c r="I150" s="3" t="n">
+        <v>12.88</v>
+      </c>
+      <c r="J150" s="3" t="n">
+        <v>12.865</v>
+      </c>
+      <c r="K150" s="3" t="n">
+        <v>3.624</v>
+      </c>
+      <c r="L150" s="3" t="n">
+        <v>4.152</v>
+      </c>
+      <c r="M150" s="3" t="n"/>
+      <c r="N150" s="2" t="n">
+        <v>273</v>
+      </c>
+      <c r="O150" s="2" t="inlineStr">
+        <is>
+          <t>ca_v5_B0, ca_v5_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e +modifs</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>7c. Aberration chromatique active (banc rapide)</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide (--fast), chroma=1</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>zoom 45 + frost 0.6 / public</t>
+        </is>
+      </c>
+      <c r="G151" s="3" t="n">
+        <v>12.055</v>
+      </c>
+      <c r="H151" s="4">
+        <f>IF(G151&gt;0,1000/G151,"")</f>
+        <v/>
+      </c>
+      <c r="I151" s="3" t="n">
+        <v>10.93</v>
+      </c>
+      <c r="J151" s="3" t="n">
+        <v>10.63</v>
+      </c>
+      <c r="K151" s="3" t="n">
+        <v>3.529</v>
+      </c>
+      <c r="L151" s="3" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="M151" s="3" t="n"/>
+      <c r="N151" s="2" t="n">
+        <v>885</v>
+      </c>
+      <c r="O151" s="2" t="inlineStr">
+        <is>
+          <t>ca_v5_B0, ca_v5_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e +modifs</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>7c. Aberration chromatique active (banc rapide)</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide (--fast), chroma=1</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>zoom 45 + frost 0.6 / scene</t>
+        </is>
+      </c>
+      <c r="G152" s="3" t="n">
+        <v>12.28</v>
+      </c>
+      <c r="H152" s="4">
+        <f>IF(G152&gt;0,1000/G152,"")</f>
+        <v/>
+      </c>
+      <c r="I152" s="3" t="n">
+        <v>11.05</v>
+      </c>
+      <c r="J152" s="3" t="n">
+        <v>10.135</v>
+      </c>
+      <c r="K152" s="3" t="n">
+        <v>3.045</v>
+      </c>
+      <c r="L152" s="3" t="n">
+        <v>4.088</v>
+      </c>
+      <c r="M152" s="3" t="n"/>
+      <c r="N152" s="2" t="n">
+        <v>885</v>
+      </c>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>ca_v5_B0, ca_v5_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e +modifs</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>7c. Aberration chromatique active (banc rapide)</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide (--fast), chroma=1</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>zoom 45 + frost 0.6 / sous les trusses</t>
+        </is>
+      </c>
+      <c r="G153" s="3" t="n">
+        <v>9.945</v>
+      </c>
+      <c r="H153" s="4">
+        <f>IF(G153&gt;0,1000/G153,"")</f>
+        <v/>
+      </c>
+      <c r="I153" s="3" t="n">
+        <v>7.685</v>
+      </c>
+      <c r="J153" s="3" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="K153" s="3" t="n">
+        <v>1.591</v>
+      </c>
+      <c r="L153" s="3" t="n">
+        <v>2.997</v>
+      </c>
+      <c r="M153" s="3" t="n"/>
+      <c r="N153" s="2" t="n">
+        <v>885</v>
+      </c>
+      <c r="O153" s="2" t="inlineStr">
+        <is>
+          <t>ca_v5_B0, ca_v5_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e +modifs</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>7c. Aberration chromatique active (banc rapide)</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide (--fast), chroma=1</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>sans rebonds (GI)</t>
+        </is>
+      </c>
+      <c r="G154" s="3" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="H154" s="4">
+        <f>IF(G154&gt;0,1000/G154,"")</f>
+        <v/>
+      </c>
+      <c r="I154" s="3" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="J154" s="3" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="K154" s="3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="L154" s="3" t="n">
+        <v>1.521</v>
+      </c>
+      <c r="M154" s="3" t="n"/>
+      <c r="N154" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O154" s="2" t="inlineStr">
+        <is>
+          <t>ca_v5_B0, ca_v5_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e +modifs</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>7c. Aberration chromatique active (banc rapide)</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide (--fast), chroma=1</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>sans fumee volumetrique</t>
+        </is>
+      </c>
+      <c r="G155" s="3" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="H155" s="4">
+        <f>IF(G155&gt;0,1000/G155,"")</f>
+        <v/>
+      </c>
+      <c r="I155" s="3" t="n">
+        <v>3.915</v>
+      </c>
+      <c r="J155" s="3" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="K155" s="3" t="n">
+        <v>1.702</v>
+      </c>
+      <c r="L155" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M155" s="3" t="n"/>
+      <c r="N155" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O155" s="2" t="inlineStr">
+        <is>
+          <t>ca_v5_B0, ca_v5_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e +modifs</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>7c. Aberration chromatique active (banc rapide)</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide (--fast), chroma=1</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>sans taches sur surfaces</t>
+        </is>
+      </c>
+      <c r="G156" s="3" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="H156" s="4">
+        <f>IF(G156&gt;0,1000/G156,"")</f>
+        <v/>
+      </c>
+      <c r="I156" s="3" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="J156" s="3" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="K156" s="3" t="n">
+        <v>0.806</v>
+      </c>
+      <c r="L156" s="3" t="n">
+        <v>2.079</v>
+      </c>
+      <c r="M156" s="3" t="n"/>
+      <c r="N156" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O156" s="2" t="inlineStr">
+        <is>
+          <t>ca_v5_B0, ca_v5_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e +modifs</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>7c. Aberration chromatique active (banc rapide)</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide (--fast), chroma=1</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>sans reflets</t>
+        </is>
+      </c>
+      <c r="G157" s="3" t="n">
+        <v>8.865</v>
+      </c>
+      <c r="H157" s="4">
+        <f>IF(G157&gt;0,1000/G157,"")</f>
+        <v/>
+      </c>
+      <c r="I157" s="3" t="n">
+        <v>7.53</v>
+      </c>
+      <c r="J157" s="3" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="K157" s="3" t="n">
+        <v>1.772</v>
+      </c>
+      <c r="L157" s="3" t="n">
+        <v>2.071</v>
+      </c>
+      <c r="M157" s="3" t="n"/>
+      <c r="N157" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O157" s="2" t="inlineStr">
+        <is>
+          <t>ca_v5_B0, ca_v5_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e +modifs</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>7c. Aberration chromatique active (banc rapide)</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide (--fast), chroma=1</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>sans bloom</t>
+        </is>
+      </c>
+      <c r="G158" s="3" t="n">
+        <v>8.975</v>
+      </c>
+      <c r="H158" s="4">
+        <f>IF(G158&gt;0,1000/G158,"")</f>
+        <v/>
+      </c>
+      <c r="I158" s="3" t="n">
+        <v>7.235</v>
+      </c>
+      <c r="J158" s="3" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="K158" s="3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="L158" s="3" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="M158" s="3" t="n"/>
+      <c r="N158" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O158" s="2" t="inlineStr">
+        <is>
+          <t>ca_v5_B0, ca_v5_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e +modifs</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>7c. Aberration chromatique active (banc rapide)</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide (--fast), chroma=1</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>sol mouille / public</t>
+        </is>
+      </c>
+      <c r="G159" s="3" t="n">
+        <v>10.425</v>
+      </c>
+      <c r="H159" s="4">
+        <f>IF(G159&gt;0,1000/G159,"")</f>
+        <v/>
+      </c>
+      <c r="I159" s="3" t="n">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="J159" s="3" t="n">
+        <v>8.904999999999999</v>
+      </c>
+      <c r="K159" s="3" t="n">
+        <v>1.837</v>
+      </c>
+      <c r="L159" s="3" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="M159" s="3" t="n">
+        <v>1.067</v>
+      </c>
+      <c r="N159" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O159" s="2" t="inlineStr">
+        <is>
+          <t>ca_v5_B0, ca_v5_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e +modifs</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>7c. Aberration chromatique active (banc rapide)</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide (--fast), chroma=1</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>sol mouille + gobo + prisme 8 / scene</t>
+        </is>
+      </c>
+      <c r="G160" s="3" t="n">
+        <v>25.985</v>
+      </c>
+      <c r="H160" s="4">
+        <f>IF(G160&gt;0,1000/G160,"")</f>
+        <v/>
+      </c>
+      <c r="I160" s="3" t="n">
+        <v>24.975</v>
+      </c>
+      <c r="J160" s="3" t="n">
+        <v>24.615</v>
+      </c>
+      <c r="K160" s="3" t="n">
+        <v>6.646</v>
+      </c>
+      <c r="L160" s="3" t="n">
+        <v>6.51</v>
+      </c>
+      <c r="M160" s="3" t="n">
+        <v>5.163</v>
+      </c>
+      <c r="N160" s="2" t="n">
+        <v>273</v>
+      </c>
+      <c r="O160" s="2" t="inlineStr">
+        <is>
+          <t>ca_v5_B0, ca_v5_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>7e0. Essai v0 : aberration, enveloppe +2 %, chroma=1</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=1</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>defaut / public</t>
+        </is>
+      </c>
+      <c r="G161" s="3" t="n">
+        <v>9.365</v>
+      </c>
+      <c r="H161" s="4">
+        <f>IF(G161&gt;0,1000/G161,"")</f>
+        <v/>
+      </c>
+      <c r="I161" s="3" t="n">
+        <v>7.385</v>
+      </c>
+      <c r="J161" s="3" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="K161" s="3" t="n">
+        <v>1.767</v>
+      </c>
+      <c r="L161" s="3" t="n">
+        <v>2.106</v>
+      </c>
+      <c r="M161" s="3" t="n"/>
+      <c r="N161" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O161" s="2" t="inlineStr">
+        <is>
+          <t>ca_cout_B0, ca_cout_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>7e0. Essai v0 : aberration, enveloppe +2 %, chroma=1</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=1</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>defaut / scene</t>
+        </is>
+      </c>
+      <c r="G162" s="3" t="n">
+        <v>9.27</v>
+      </c>
+      <c r="H162" s="4">
+        <f>IF(G162&gt;0,1000/G162,"")</f>
+        <v/>
+      </c>
+      <c r="I162" s="3" t="n">
+        <v>7.295</v>
+      </c>
+      <c r="J162" s="3" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="K162" s="3" t="n">
+        <v>1.691</v>
+      </c>
+      <c r="L162" s="3" t="n">
+        <v>2.008</v>
+      </c>
+      <c r="M162" s="3" t="n"/>
+      <c r="N162" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O162" s="2" t="inlineStr">
+        <is>
+          <t>ca_cout_B0, ca_cout_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>7e0. Essai v0 : aberration, enveloppe +2 %, chroma=1</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=1</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>defaut / sous les trusses</t>
+        </is>
+      </c>
+      <c r="G163" s="3" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="H163" s="4">
+        <f>IF(G163&gt;0,1000/G163,"")</f>
+        <v/>
+      </c>
+      <c r="I163" s="3" t="n">
+        <v>6.745</v>
+      </c>
+      <c r="J163" s="3" t="n">
+        <v>6.265</v>
+      </c>
+      <c r="K163" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L163" s="3" t="n">
+        <v>1.774</v>
+      </c>
+      <c r="M163" s="3" t="n"/>
+      <c r="N163" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O163" s="2" t="inlineStr">
+        <is>
+          <t>ca_cout_B0, ca_cout_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>7e0. Essai v0 : aberration, enveloppe +2 %, chroma=1</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=1</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>gobo + prisme 8 + zoom 25 / public</t>
+        </is>
+      </c>
+      <c r="G164" s="3" t="n">
+        <v>22.045</v>
+      </c>
+      <c r="H164" s="4">
+        <f>IF(G164&gt;0,1000/G164,"")</f>
+        <v/>
+      </c>
+      <c r="I164" s="3" t="n">
+        <v>21.165</v>
+      </c>
+      <c r="J164" s="3" t="n">
+        <v>21.005</v>
+      </c>
+      <c r="K164" s="3" t="n">
+        <v>7.812</v>
+      </c>
+      <c r="L164" s="3" t="n">
+        <v>7.533</v>
+      </c>
+      <c r="M164" s="3" t="n"/>
+      <c r="N164" s="2" t="n">
+        <v>286</v>
+      </c>
+      <c r="O164" s="2" t="inlineStr">
+        <is>
+          <t>ca_cout_B0, ca_cout_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>7e0. Essai v0 : aberration, enveloppe +2 %, chroma=1</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=1</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>gobo + prisme 8 + zoom 25 / scene</t>
+        </is>
+      </c>
+      <c r="G165" s="3" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="H165" s="4">
+        <f>IF(G165&gt;0,1000/G165,"")</f>
+        <v/>
+      </c>
+      <c r="I165" s="3" t="n">
+        <v>19.795</v>
+      </c>
+      <c r="J165" s="3" t="n">
+        <v>19.705</v>
+      </c>
+      <c r="K165" s="3" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="L165" s="3" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="M165" s="3" t="n"/>
+      <c r="N165" s="2" t="n">
+        <v>286</v>
+      </c>
+      <c r="O165" s="2" t="inlineStr">
+        <is>
+          <t>ca_cout_B0, ca_cout_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>7e0. Essai v0 : aberration, enveloppe +2 %, chroma=1</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=1</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>gobo + prisme 8 + zoom 25 / sous les trusses</t>
+        </is>
+      </c>
+      <c r="G166" s="3" t="n">
+        <v>15.34</v>
+      </c>
+      <c r="H166" s="4">
+        <f>IF(G166&gt;0,1000/G166,"")</f>
+        <v/>
+      </c>
+      <c r="I166" s="3" t="n">
+        <v>14.44</v>
+      </c>
+      <c r="J166" s="3" t="n">
+        <v>14.46</v>
+      </c>
+      <c r="K166" s="3" t="n">
+        <v>3.778</v>
+      </c>
+      <c r="L166" s="3" t="n">
+        <v>4.096</v>
+      </c>
+      <c r="M166" s="3" t="n"/>
+      <c r="N166" s="2" t="n">
+        <v>286</v>
+      </c>
+      <c r="O166" s="2" t="inlineStr">
+        <is>
+          <t>ca_cout_B0, ca_cout_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>7e0. Essai v0 : aberration, enveloppe +2 %, chroma=1</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=1</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>zoom 45 + frost 0.6 / public</t>
+        </is>
+      </c>
+      <c r="G167" s="3" t="n">
+        <v>13.035</v>
+      </c>
+      <c r="H167" s="4">
+        <f>IF(G167&gt;0,1000/G167,"")</f>
+        <v/>
+      </c>
+      <c r="I167" s="3" t="n">
+        <v>11.785</v>
+      </c>
+      <c r="J167" s="3" t="n">
+        <v>11.125</v>
+      </c>
+      <c r="K167" s="3" t="n">
+        <v>3.569</v>
+      </c>
+      <c r="L167" s="3" t="n">
+        <v>4.225</v>
+      </c>
+      <c r="M167" s="3" t="n"/>
+      <c r="N167" s="2" t="n">
+        <v>944</v>
+      </c>
+      <c r="O167" s="2" t="inlineStr">
+        <is>
+          <t>ca_cout_B0, ca_cout_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>7e0. Essai v0 : aberration, enveloppe +2 %, chroma=1</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=1</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>zoom 45 + frost 0.6 / scene</t>
+        </is>
+      </c>
+      <c r="G168" s="3" t="n">
+        <v>13.07</v>
+      </c>
+      <c r="H168" s="4">
+        <f>IF(G168&gt;0,1000/G168,"")</f>
+        <v/>
+      </c>
+      <c r="I168" s="3" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="J168" s="3" t="n">
+        <v>11.435</v>
+      </c>
+      <c r="K168" s="3" t="n">
+        <v>3.567</v>
+      </c>
+      <c r="L168" s="3" t="n">
+        <v>4.223</v>
+      </c>
+      <c r="M168" s="3" t="n"/>
+      <c r="N168" s="2" t="n">
+        <v>944</v>
+      </c>
+      <c r="O168" s="2" t="inlineStr">
+        <is>
+          <t>ca_cout_B0, ca_cout_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>7e0. Essai v0 : aberration, enveloppe +2 %, chroma=1</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=1</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>zoom 45 + frost 0.6 / sous les trusses</t>
+        </is>
+      </c>
+      <c r="G169" s="3" t="n">
+        <v>10.39</v>
+      </c>
+      <c r="H169" s="4">
+        <f>IF(G169&gt;0,1000/G169,"")</f>
+        <v/>
+      </c>
+      <c r="I169" s="3" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="J169" s="3" t="n">
+        <v>8.085000000000001</v>
+      </c>
+      <c r="K169" s="3" t="n">
+        <v>1.794</v>
+      </c>
+      <c r="L169" s="3" t="n">
+        <v>3.615</v>
+      </c>
+      <c r="M169" s="3" t="n"/>
+      <c r="N169" s="2" t="n">
+        <v>944</v>
+      </c>
+      <c r="O169" s="2" t="inlineStr">
+        <is>
+          <t>ca_cout_B0, ca_cout_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>7e0. Essai v0 : aberration, enveloppe +2 %, chroma=1</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=1</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>sans rebonds (GI)</t>
+        </is>
+      </c>
+      <c r="G170" s="3" t="n">
+        <v>8.19</v>
+      </c>
+      <c r="H170" s="4">
+        <f>IF(G170&gt;0,1000/G170,"")</f>
+        <v/>
+      </c>
+      <c r="I170" s="3" t="n">
+        <v>6.945</v>
+      </c>
+      <c r="J170" s="3" t="n">
+        <v>6.215</v>
+      </c>
+      <c r="K170" s="3" t="n">
+        <v>1.519</v>
+      </c>
+      <c r="L170" s="3" t="n">
+        <v>1.672</v>
+      </c>
+      <c r="M170" s="3" t="n"/>
+      <c r="N170" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>ca_cout_B0, ca_cout_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>7e0. Essai v0 : aberration, enveloppe +2 %, chroma=1</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=1</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>sans fumee volumetrique</t>
+        </is>
+      </c>
+      <c r="G171" s="3" t="n">
+        <v>5.605</v>
+      </c>
+      <c r="H171" s="4">
+        <f>IF(G171&gt;0,1000/G171,"")</f>
+        <v/>
+      </c>
+      <c r="I171" s="3" t="n">
+        <v>4.485</v>
+      </c>
+      <c r="J171" s="3" t="n">
+        <v>3.365</v>
+      </c>
+      <c r="K171" s="3" t="n">
+        <v>1.723</v>
+      </c>
+      <c r="L171" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M171" s="3" t="n"/>
+      <c r="N171" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
+        <is>
+          <t>ca_cout_B0, ca_cout_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>7e0. Essai v0 : aberration, enveloppe +2 %, chroma=1</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=1</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>sans taches sur surfaces</t>
+        </is>
+      </c>
+      <c r="G172" s="3" t="n">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="H172" s="4">
+        <f>IF(G172&gt;0,1000/G172,"")</f>
+        <v/>
+      </c>
+      <c r="I172" s="3" t="n">
+        <v>6.525</v>
+      </c>
+      <c r="J172" s="3" t="n">
+        <v>5.895</v>
+      </c>
+      <c r="K172" s="3" t="n">
+        <v>0.788</v>
+      </c>
+      <c r="L172" s="3" t="n">
+        <v>2.116</v>
+      </c>
+      <c r="M172" s="3" t="n"/>
+      <c r="N172" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O172" s="2" t="inlineStr">
+        <is>
+          <t>ca_cout_B0, ca_cout_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>7e0. Essai v0 : aberration, enveloppe +2 %, chroma=1</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=1</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>sans reflets</t>
+        </is>
+      </c>
+      <c r="G173" s="3" t="n">
+        <v>9.635</v>
+      </c>
+      <c r="H173" s="4">
+        <f>IF(G173&gt;0,1000/G173,"")</f>
+        <v/>
+      </c>
+      <c r="I173" s="3" t="n">
+        <v>7.745</v>
+      </c>
+      <c r="J173" s="3" t="n">
+        <v>7.165</v>
+      </c>
+      <c r="K173" s="3" t="n">
+        <v>1.797</v>
+      </c>
+      <c r="L173" s="3" t="n">
+        <v>2.115</v>
+      </c>
+      <c r="M173" s="3" t="n"/>
+      <c r="N173" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
+        <is>
+          <t>ca_cout_B0, ca_cout_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>7e0. Essai v0 : aberration, enveloppe +2 %, chroma=1</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=1</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>sans bloom</t>
+        </is>
+      </c>
+      <c r="G174" s="3" t="n">
+        <v>8.744999999999999</v>
+      </c>
+      <c r="H174" s="4">
+        <f>IF(G174&gt;0,1000/G174,"")</f>
+        <v/>
+      </c>
+      <c r="I174" s="3" t="n">
+        <v>7.405</v>
+      </c>
+      <c r="J174" s="3" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="K174" s="3" t="n">
+        <v>1.789</v>
+      </c>
+      <c r="L174" s="3" t="n">
+        <v>2.113</v>
+      </c>
+      <c r="M174" s="3" t="n"/>
+      <c r="N174" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O174" s="2" t="inlineStr">
+        <is>
+          <t>ca_cout_B0, ca_cout_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>7e0. Essai v0 : aberration, enveloppe +2 %, chroma=1</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=1</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>sol mouille / public</t>
+        </is>
+      </c>
+      <c r="G175" s="3" t="n">
+        <v>10.655</v>
+      </c>
+      <c r="H175" s="4">
+        <f>IF(G175&gt;0,1000/G175,"")</f>
+        <v/>
+      </c>
+      <c r="I175" s="3" t="n">
+        <v>9.81</v>
+      </c>
+      <c r="J175" s="3" t="n">
+        <v>9.734999999999999</v>
+      </c>
+      <c r="K175" s="3" t="n">
+        <v>1.793</v>
+      </c>
+      <c r="L175" s="3" t="n">
+        <v>2.111</v>
+      </c>
+      <c r="M175" s="3" t="n">
+        <v>1.075</v>
+      </c>
+      <c r="N175" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
+        <is>
+          <t>ca_cout_B0, ca_cout_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>7e0. Essai v0 : aberration, enveloppe +2 %, chroma=1</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=1</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>sol mouille + gobo + prisme 8 / scene</t>
+        </is>
+      </c>
+      <c r="G176" s="3" t="n">
+        <v>26.52</v>
+      </c>
+      <c r="H176" s="4">
+        <f>IF(G176&gt;0,1000/G176,"")</f>
+        <v/>
+      </c>
+      <c r="I176" s="3" t="n">
+        <v>25.775</v>
+      </c>
+      <c r="J176" s="3" t="n">
+        <v>25.445</v>
+      </c>
+      <c r="K176" s="3" t="n">
+        <v>6.899</v>
+      </c>
+      <c r="L176" s="3" t="n">
+        <v>7.161</v>
+      </c>
+      <c r="M176" s="3" t="n">
+        <v>5.662</v>
+      </c>
+      <c r="N176" s="2" t="n">
+        <v>286</v>
+      </c>
+      <c r="O176" s="2" t="inlineStr">
+        <is>
+          <t>ca_cout_B0, ca_cout_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>7e1. Essai v1 : enveloppe inchangee, flou par couleur, chroma=1</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=1</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>defaut / public</t>
+        </is>
+      </c>
+      <c r="G177" s="3" t="n">
+        <v>9.115</v>
+      </c>
+      <c r="H177" s="4">
+        <f>IF(G177&gt;0,1000/G177,"")</f>
+        <v/>
+      </c>
+      <c r="I177" s="3" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="J177" s="3" t="n">
+        <v>6.615</v>
+      </c>
+      <c r="K177" s="3" t="n">
+        <v>1.816</v>
+      </c>
+      <c r="L177" s="3" t="n">
+        <v>2.059</v>
+      </c>
+      <c r="M177" s="3" t="n"/>
+      <c r="N177" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O177" s="2" t="inlineStr">
+        <is>
+          <t>ca_v1_B0, ca_v1_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>7e1. Essai v1 : enveloppe inchangee, flou par couleur, chroma=1</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=1</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>defaut / scene</t>
+        </is>
+      </c>
+      <c r="G178" s="3" t="n">
+        <v>9.324999999999999</v>
+      </c>
+      <c r="H178" s="4">
+        <f>IF(G178&gt;0,1000/G178,"")</f>
+        <v/>
+      </c>
+      <c r="I178" s="3" t="n">
+        <v>7.525</v>
+      </c>
+      <c r="J178" s="3" t="n">
+        <v>6.895</v>
+      </c>
+      <c r="K178" s="3" t="n">
+        <v>1.777</v>
+      </c>
+      <c r="L178" s="3" t="n">
+        <v>2.025</v>
+      </c>
+      <c r="M178" s="3" t="n"/>
+      <c r="N178" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O178" s="2" t="inlineStr">
+        <is>
+          <t>ca_v1_B0, ca_v1_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>7e1. Essai v1 : enveloppe inchangee, flou par couleur, chroma=1</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=1</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>defaut / sous les trusses</t>
+        </is>
+      </c>
+      <c r="G179" s="3" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="H179" s="4">
+        <f>IF(G179&gt;0,1000/G179,"")</f>
+        <v/>
+      </c>
+      <c r="I179" s="3" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="J179" s="3" t="n">
+        <v>6.295</v>
+      </c>
+      <c r="K179" s="3" t="n">
+        <v>1.277</v>
+      </c>
+      <c r="L179" s="3" t="n">
+        <v>1.789</v>
+      </c>
+      <c r="M179" s="3" t="n"/>
+      <c r="N179" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O179" s="2" t="inlineStr">
+        <is>
+          <t>ca_v1_B0, ca_v1_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>7e1. Essai v1 : enveloppe inchangee, flou par couleur, chroma=1</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=1</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>gobo + prisme 8 + zoom 25 / public</t>
+        </is>
+      </c>
+      <c r="G180" s="3" t="n">
+        <v>21.865</v>
+      </c>
+      <c r="H180" s="4">
+        <f>IF(G180&gt;0,1000/G180,"")</f>
+        <v/>
+      </c>
+      <c r="I180" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="J180" s="3" t="n">
+        <v>20.85</v>
+      </c>
+      <c r="K180" s="3" t="n">
+        <v>7.755</v>
+      </c>
+      <c r="L180" s="3" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="M180" s="3" t="n"/>
+      <c r="N180" s="2" t="n">
+        <v>282</v>
+      </c>
+      <c r="O180" s="2" t="inlineStr">
+        <is>
+          <t>ca_v1_B0, ca_v1_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>7e1. Essai v1 : enveloppe inchangee, flou par couleur, chroma=1</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=1</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>gobo + prisme 8 + zoom 25 / scene</t>
+        </is>
+      </c>
+      <c r="G181" s="3" t="n">
+        <v>21.005</v>
+      </c>
+      <c r="H181" s="4">
+        <f>IF(G181&gt;0,1000/G181,"")</f>
+        <v/>
+      </c>
+      <c r="I181" s="3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="J181" s="3" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="K181" s="3" t="n">
+        <v>6.271</v>
+      </c>
+      <c r="L181" s="3" t="n">
+        <v>6.933</v>
+      </c>
+      <c r="M181" s="3" t="n"/>
+      <c r="N181" s="2" t="n">
+        <v>282</v>
+      </c>
+      <c r="O181" s="2" t="inlineStr">
+        <is>
+          <t>ca_v1_B0, ca_v1_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>7e1. Essai v1 : enveloppe inchangee, flou par couleur, chroma=1</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=1</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>gobo + prisme 8 + zoom 25 / sous les trusses</t>
+        </is>
+      </c>
+      <c r="G182" s="3" t="n">
+        <v>15.51</v>
+      </c>
+      <c r="H182" s="4">
+        <f>IF(G182&gt;0,1000/G182,"")</f>
+        <v/>
+      </c>
+      <c r="I182" s="3" t="n">
+        <v>14.585</v>
+      </c>
+      <c r="J182" s="3" t="n">
+        <v>14.64</v>
+      </c>
+      <c r="K182" s="3" t="n">
+        <v>3.854</v>
+      </c>
+      <c r="L182" s="3" t="n">
+        <v>4.145</v>
+      </c>
+      <c r="M182" s="3" t="n"/>
+      <c r="N182" s="2" t="n">
+        <v>282</v>
+      </c>
+      <c r="O182" s="2" t="inlineStr">
+        <is>
+          <t>ca_v1_B0, ca_v1_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>7e1. Essai v1 : enveloppe inchangee, flou par couleur, chroma=1</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=1</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>zoom 45 + frost 0.6 / public</t>
+        </is>
+      </c>
+      <c r="G183" s="3" t="n">
+        <v>13.155</v>
+      </c>
+      <c r="H183" s="4">
+        <f>IF(G183&gt;0,1000/G183,"")</f>
+        <v/>
+      </c>
+      <c r="I183" s="3" t="n">
+        <v>11.795</v>
+      </c>
+      <c r="J183" s="3" t="n">
+        <v>11.345</v>
+      </c>
+      <c r="K183" s="3" t="n">
+        <v>3.662</v>
+      </c>
+      <c r="L183" s="3" t="n">
+        <v>4.267</v>
+      </c>
+      <c r="M183" s="3" t="n"/>
+      <c r="N183" s="2" t="n">
+        <v>941</v>
+      </c>
+      <c r="O183" s="2" t="inlineStr">
+        <is>
+          <t>ca_v1_B0, ca_v1_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>7e1. Essai v1 : enveloppe inchangee, flou par couleur, chroma=1</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=1</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>zoom 45 + frost 0.6 / scene</t>
+        </is>
+      </c>
+      <c r="G184" s="3" t="n">
+        <v>13.055</v>
+      </c>
+      <c r="H184" s="4">
+        <f>IF(G184&gt;0,1000/G184,"")</f>
+        <v/>
+      </c>
+      <c r="I184" s="3" t="n">
+        <v>11.79</v>
+      </c>
+      <c r="J184" s="3" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="K184" s="3" t="n">
+        <v>3.701</v>
+      </c>
+      <c r="L184" s="3" t="n">
+        <v>4.197</v>
+      </c>
+      <c r="M184" s="3" t="n"/>
+      <c r="N184" s="2" t="n">
+        <v>941</v>
+      </c>
+      <c r="O184" s="2" t="inlineStr">
+        <is>
+          <t>ca_v1_B0, ca_v1_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>7e1. Essai v1 : enveloppe inchangee, flou par couleur, chroma=1</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=1</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>zoom 45 + frost 0.6 / sous les trusses</t>
+        </is>
+      </c>
+      <c r="G185" s="3" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="H185" s="4">
+        <f>IF(G185&gt;0,1000/G185,"")</f>
+        <v/>
+      </c>
+      <c r="I185" s="3" t="n">
+        <v>8.715</v>
+      </c>
+      <c r="J185" s="3" t="n">
+        <v>8.115</v>
+      </c>
+      <c r="K185" s="3" t="n">
+        <v>1.766</v>
+      </c>
+      <c r="L185" s="3" t="n">
+        <v>3.565</v>
+      </c>
+      <c r="M185" s="3" t="n"/>
+      <c r="N185" s="2" t="n">
+        <v>941</v>
+      </c>
+      <c r="O185" s="2" t="inlineStr">
+        <is>
+          <t>ca_v1_B0, ca_v1_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>7e1. Essai v1 : enveloppe inchangee, flou par couleur, chroma=1</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=1</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>sans rebonds (GI)</t>
+        </is>
+      </c>
+      <c r="G186" s="3" t="n">
+        <v>8.164999999999999</v>
+      </c>
+      <c r="H186" s="4">
+        <f>IF(G186&gt;0,1000/G186,"")</f>
+        <v/>
+      </c>
+      <c r="I186" s="3" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="J186" s="3" t="n">
+        <v>6.365</v>
+      </c>
+      <c r="K186" s="3" t="n">
+        <v>1.555</v>
+      </c>
+      <c r="L186" s="3" t="n">
+        <v>1.605</v>
+      </c>
+      <c r="M186" s="3" t="n"/>
+      <c r="N186" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O186" s="2" t="inlineStr">
+        <is>
+          <t>ca_v1_B0, ca_v1_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>7e1. Essai v1 : enveloppe inchangee, flou par couleur, chroma=1</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=1</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>sans fumee volumetrique</t>
+        </is>
+      </c>
+      <c r="G187" s="3" t="n">
+        <v>5.495</v>
+      </c>
+      <c r="H187" s="4">
+        <f>IF(G187&gt;0,1000/G187,"")</f>
+        <v/>
+      </c>
+      <c r="I187" s="3" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="J187" s="3" t="n">
+        <v>3.595</v>
+      </c>
+      <c r="K187" s="3" t="n">
+        <v>1.803</v>
+      </c>
+      <c r="L187" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M187" s="3" t="n"/>
+      <c r="N187" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O187" s="2" t="inlineStr">
+        <is>
+          <t>ca_v1_B0, ca_v1_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>7e1. Essai v1 : enveloppe inchangee, flou par couleur, chroma=1</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=1</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>sans taches sur surfaces</t>
+        </is>
+      </c>
+      <c r="G188" s="3" t="n">
+        <v>8.175000000000001</v>
+      </c>
+      <c r="H188" s="4">
+        <f>IF(G188&gt;0,1000/G188,"")</f>
+        <v/>
+      </c>
+      <c r="I188" s="3" t="n">
+        <v>6.555</v>
+      </c>
+      <c r="J188" s="3" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="K188" s="3" t="n">
+        <v>0.831</v>
+      </c>
+      <c r="L188" s="3" t="n">
+        <v>2.166</v>
+      </c>
+      <c r="M188" s="3" t="n"/>
+      <c r="N188" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O188" s="2" t="inlineStr">
+        <is>
+          <t>ca_v1_B0, ca_v1_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>7e1. Essai v1 : enveloppe inchangee, flou par couleur, chroma=1</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=1</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>sans reflets</t>
+        </is>
+      </c>
+      <c r="G189" s="3" t="n">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="H189" s="4">
+        <f>IF(G189&gt;0,1000/G189,"")</f>
+        <v/>
+      </c>
+      <c r="I189" s="3" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="J189" s="3" t="n">
+        <v>7.125</v>
+      </c>
+      <c r="K189" s="3" t="n">
+        <v>1.886</v>
+      </c>
+      <c r="L189" s="3" t="n">
+        <v>2.117</v>
+      </c>
+      <c r="M189" s="3" t="n"/>
+      <c r="N189" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O189" s="2" t="inlineStr">
+        <is>
+          <t>ca_v1_B0, ca_v1_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>7e1. Essai v1 : enveloppe inchangee, flou par couleur, chroma=1</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=1</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>sans bloom</t>
+        </is>
+      </c>
+      <c r="G190" s="3" t="n">
+        <v>8.555</v>
+      </c>
+      <c r="H190" s="4">
+        <f>IF(G190&gt;0,1000/G190,"")</f>
+        <v/>
+      </c>
+      <c r="I190" s="3" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="J190" s="3" t="n">
+        <v>6.945</v>
+      </c>
+      <c r="K190" s="3" t="n">
+        <v>1.865</v>
+      </c>
+      <c r="L190" s="3" t="n">
+        <v>2.118</v>
+      </c>
+      <c r="M190" s="3" t="n"/>
+      <c r="N190" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O190" s="2" t="inlineStr">
+        <is>
+          <t>ca_v1_B0, ca_v1_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>7e1. Essai v1 : enveloppe inchangee, flou par couleur, chroma=1</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=1</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>sol mouille / public</t>
+        </is>
+      </c>
+      <c r="G191" s="3" t="n">
+        <v>10.765</v>
+      </c>
+      <c r="H191" s="4">
+        <f>IF(G191&gt;0,1000/G191,"")</f>
+        <v/>
+      </c>
+      <c r="I191" s="3" t="n">
+        <v>9.785</v>
+      </c>
+      <c r="J191" s="3" t="n">
+        <v>9.275</v>
+      </c>
+      <c r="K191" s="3" t="n">
+        <v>1.938</v>
+      </c>
+      <c r="L191" s="3" t="n">
+        <v>2.131</v>
+      </c>
+      <c r="M191" s="3" t="n">
+        <v>1.112</v>
+      </c>
+      <c r="N191" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O191" s="2" t="inlineStr">
+        <is>
+          <t>ca_v1_B0, ca_v1_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>7e1. Essai v1 : enveloppe inchangee, flou par couleur, chroma=1</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=1</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>sol mouille + gobo + prisme 8 / scene</t>
+        </is>
+      </c>
+      <c r="G192" s="3" t="n">
+        <v>25.72</v>
+      </c>
+      <c r="H192" s="4">
+        <f>IF(G192&gt;0,1000/G192,"")</f>
+        <v/>
+      </c>
+      <c r="I192" s="3" t="n">
+        <v>24.985</v>
+      </c>
+      <c r="J192" s="3" t="n">
+        <v>24.835</v>
+      </c>
+      <c r="K192" s="3" t="n">
+        <v>6.906</v>
+      </c>
+      <c r="L192" s="3" t="n">
+        <v>6.982</v>
+      </c>
+      <c r="M192" s="3" t="n">
+        <v>5.362</v>
+      </c>
+      <c r="N192" s="2" t="n">
+        <v>282</v>
+      </c>
+      <c r="O192" s="2" t="inlineStr">
+        <is>
+          <t>ca_v1_B0, ca_v1_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>7e3. Essai v3 : cache pour toutes les lyres, chroma=1</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=1</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>defaut / public</t>
+        </is>
+      </c>
+      <c r="G193" s="3" t="n">
+        <v>9.945</v>
+      </c>
+      <c r="H193" s="4">
+        <f>IF(G193&gt;0,1000/G193,"")</f>
+        <v/>
+      </c>
+      <c r="I193" s="3" t="n">
+        <v>7.885</v>
+      </c>
+      <c r="J193" s="3" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="K193" s="3" t="n">
+        <v>1.752</v>
+      </c>
+      <c r="L193" s="3" t="n">
+        <v>2.069</v>
+      </c>
+      <c r="M193" s="3" t="n"/>
+      <c r="N193" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O193" s="2" t="inlineStr">
+        <is>
+          <t>ca_fin_B0, ca_fin_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>7e3. Essai v3 : cache pour toutes les lyres, chroma=1</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=1</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>defaut / scene</t>
+        </is>
+      </c>
+      <c r="G194" s="3" t="n">
+        <v>9.460000000000001</v>
+      </c>
+      <c r="H194" s="4">
+        <f>IF(G194&gt;0,1000/G194,"")</f>
+        <v/>
+      </c>
+      <c r="I194" s="3" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="J194" s="3" t="n">
+        <v>7.745</v>
+      </c>
+      <c r="K194" s="3" t="n">
+        <v>1.729</v>
+      </c>
+      <c r="L194" s="3" t="n">
+        <v>2.015</v>
+      </c>
+      <c r="M194" s="3" t="n"/>
+      <c r="N194" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O194" s="2" t="inlineStr">
+        <is>
+          <t>ca_fin_B0, ca_fin_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>7e3. Essai v3 : cache pour toutes les lyres, chroma=1</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=1</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>defaut / sous les trusses</t>
+        </is>
+      </c>
+      <c r="G195" s="3" t="n">
+        <v>8.345000000000001</v>
+      </c>
+      <c r="H195" s="4">
+        <f>IF(G195&gt;0,1000/G195,"")</f>
+        <v/>
+      </c>
+      <c r="I195" s="3" t="n">
+        <v>7.245</v>
+      </c>
+      <c r="J195" s="3" t="n">
+        <v>7.205</v>
+      </c>
+      <c r="K195" s="3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="L195" s="3" t="n">
+        <v>1.828</v>
+      </c>
+      <c r="M195" s="3" t="n"/>
+      <c r="N195" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O195" s="2" t="inlineStr">
+        <is>
+          <t>ca_fin_B0, ca_fin_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>7e3. Essai v3 : cache pour toutes les lyres, chroma=1</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=1</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>gobo + prisme 8 + zoom 25 / public</t>
+        </is>
+      </c>
+      <c r="G196" s="3" t="n">
+        <v>22.965</v>
+      </c>
+      <c r="H196" s="4">
+        <f>IF(G196&gt;0,1000/G196,"")</f>
+        <v/>
+      </c>
+      <c r="I196" s="3" t="n">
+        <v>21.82</v>
+      </c>
+      <c r="J196" s="3" t="n">
+        <v>21.71</v>
+      </c>
+      <c r="K196" s="3" t="n">
+        <v>8.452999999999999</v>
+      </c>
+      <c r="L196" s="3" t="n">
+        <v>7.398</v>
+      </c>
+      <c r="M196" s="3" t="n"/>
+      <c r="N196" s="2" t="n">
+        <v>282</v>
+      </c>
+      <c r="O196" s="2" t="inlineStr">
+        <is>
+          <t>ca_fin_B0, ca_fin_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>7e3. Essai v3 : cache pour toutes les lyres, chroma=1</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=1</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>gobo + prisme 8 + zoom 25 / scene</t>
+        </is>
+      </c>
+      <c r="G197" s="3" t="n">
+        <v>21.27</v>
+      </c>
+      <c r="H197" s="4">
+        <f>IF(G197&gt;0,1000/G197,"")</f>
+        <v/>
+      </c>
+      <c r="I197" s="3" t="n">
+        <v>20.18</v>
+      </c>
+      <c r="J197" s="3" t="n">
+        <v>19.96</v>
+      </c>
+      <c r="K197" s="3" t="n">
+        <v>7.303</v>
+      </c>
+      <c r="L197" s="3" t="n">
+        <v>6.979</v>
+      </c>
+      <c r="M197" s="3" t="n"/>
+      <c r="N197" s="2" t="n">
+        <v>282</v>
+      </c>
+      <c r="O197" s="2" t="inlineStr">
+        <is>
+          <t>ca_fin_B0, ca_fin_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>7e3. Essai v3 : cache pour toutes les lyres, chroma=1</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=1</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>gobo + prisme 8 + zoom 25 / sous les trusses</t>
+        </is>
+      </c>
+      <c r="G198" s="3" t="n">
+        <v>15.835</v>
+      </c>
+      <c r="H198" s="4">
+        <f>IF(G198&gt;0,1000/G198,"")</f>
+        <v/>
+      </c>
+      <c r="I198" s="3" t="n">
+        <v>14.825</v>
+      </c>
+      <c r="J198" s="3" t="n">
+        <v>14.555</v>
+      </c>
+      <c r="K198" s="3" t="n">
+        <v>4.024</v>
+      </c>
+      <c r="L198" s="3" t="n">
+        <v>4.178</v>
+      </c>
+      <c r="M198" s="3" t="n"/>
+      <c r="N198" s="2" t="n">
+        <v>282</v>
+      </c>
+      <c r="O198" s="2" t="inlineStr">
+        <is>
+          <t>ca_fin_B0, ca_fin_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>7e3. Essai v3 : cache pour toutes les lyres, chroma=1</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=1</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>zoom 45 + frost 0.6 / public</t>
+        </is>
+      </c>
+      <c r="G199" s="3" t="n">
+        <v>13.285</v>
+      </c>
+      <c r="H199" s="4">
+        <f>IF(G199&gt;0,1000/G199,"")</f>
+        <v/>
+      </c>
+      <c r="I199" s="3" t="n">
+        <v>12.23</v>
+      </c>
+      <c r="J199" s="3" t="n">
+        <v>11.98</v>
+      </c>
+      <c r="K199" s="3" t="n">
+        <v>3.484</v>
+      </c>
+      <c r="L199" s="3" t="n">
+        <v>4.375</v>
+      </c>
+      <c r="M199" s="3" t="n"/>
+      <c r="N199" s="2" t="n">
+        <v>941</v>
+      </c>
+      <c r="O199" s="2" t="inlineStr">
+        <is>
+          <t>ca_fin_B0, ca_fin_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>7e3. Essai v3 : cache pour toutes les lyres, chroma=1</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=1</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>zoom 45 + frost 0.6 / scene</t>
+        </is>
+      </c>
+      <c r="G200" s="3" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="H200" s="4">
+        <f>IF(G200&gt;0,1000/G200,"")</f>
+        <v/>
+      </c>
+      <c r="I200" s="3" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="J200" s="3" t="n">
+        <v>12.035</v>
+      </c>
+      <c r="K200" s="3" t="n">
+        <v>3.445</v>
+      </c>
+      <c r="L200" s="3" t="n">
+        <v>4.417</v>
+      </c>
+      <c r="M200" s="3" t="n"/>
+      <c r="N200" s="2" t="n">
+        <v>941</v>
+      </c>
+      <c r="O200" s="2" t="inlineStr">
+        <is>
+          <t>ca_fin_B0, ca_fin_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>7e3. Essai v3 : cache pour toutes les lyres, chroma=1</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=1</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>zoom 45 + frost 0.6 / sous les trusses</t>
+        </is>
+      </c>
+      <c r="G201" s="3" t="n">
+        <v>10.435</v>
+      </c>
+      <c r="H201" s="4">
+        <f>IF(G201&gt;0,1000/G201,"")</f>
+        <v/>
+      </c>
+      <c r="I201" s="3" t="n">
+        <v>8.695</v>
+      </c>
+      <c r="J201" s="3" t="n">
+        <v>8.164999999999999</v>
+      </c>
+      <c r="K201" s="3" t="n">
+        <v>1.651</v>
+      </c>
+      <c r="L201" s="3" t="n">
+        <v>3.597</v>
+      </c>
+      <c r="M201" s="3" t="n"/>
+      <c r="N201" s="2" t="n">
+        <v>941</v>
+      </c>
+      <c r="O201" s="2" t="inlineStr">
+        <is>
+          <t>ca_fin_B0, ca_fin_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>7e3. Essai v3 : cache pour toutes les lyres, chroma=1</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=1</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>sans rebonds (GI)</t>
+        </is>
+      </c>
+      <c r="G202" s="3" t="n">
+        <v>8.145</v>
+      </c>
+      <c r="H202" s="4">
+        <f>IF(G202&gt;0,1000/G202,"")</f>
+        <v/>
+      </c>
+      <c r="I202" s="3" t="n">
+        <v>7.025</v>
+      </c>
+      <c r="J202" s="3" t="n">
+        <v>6.955</v>
+      </c>
+      <c r="K202" s="3" t="n">
+        <v>1.504</v>
+      </c>
+      <c r="L202" s="3" t="n">
+        <v>1.597</v>
+      </c>
+      <c r="M202" s="3" t="n"/>
+      <c r="N202" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O202" s="2" t="inlineStr">
+        <is>
+          <t>ca_fin_B0, ca_fin_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>7e3. Essai v3 : cache pour toutes les lyres, chroma=1</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=1</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>sans fumee volumetrique</t>
+        </is>
+      </c>
+      <c r="G203" s="3" t="n">
+        <v>5.235</v>
+      </c>
+      <c r="H203" s="4">
+        <f>IF(G203&gt;0,1000/G203,"")</f>
+        <v/>
+      </c>
+      <c r="I203" s="3" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="J203" s="3" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="K203" s="3" t="n">
+        <v>1.791</v>
+      </c>
+      <c r="L203" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M203" s="3" t="n"/>
+      <c r="N203" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O203" s="2" t="inlineStr">
+        <is>
+          <t>ca_fin_B0, ca_fin_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>7e3. Essai v3 : cache pour toutes les lyres, chroma=1</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=1</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>sans taches sur surfaces</t>
+        </is>
+      </c>
+      <c r="G204" s="3" t="n">
+        <v>8.015000000000001</v>
+      </c>
+      <c r="H204" s="4">
+        <f>IF(G204&gt;0,1000/G204,"")</f>
+        <v/>
+      </c>
+      <c r="I204" s="3" t="n">
+        <v>6.745</v>
+      </c>
+      <c r="J204" s="3" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="K204" s="3" t="n">
+        <v>0.845</v>
+      </c>
+      <c r="L204" s="3" t="n">
+        <v>2.186</v>
+      </c>
+      <c r="M204" s="3" t="n"/>
+      <c r="N204" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O204" s="2" t="inlineStr">
+        <is>
+          <t>ca_fin_B0, ca_fin_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>7e3. Essai v3 : cache pour toutes les lyres, chroma=1</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=1</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>sans reflets</t>
+        </is>
+      </c>
+      <c r="G205" s="3" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="H205" s="4">
+        <f>IF(G205&gt;0,1000/G205,"")</f>
+        <v/>
+      </c>
+      <c r="I205" s="3" t="n">
+        <v>7.96</v>
+      </c>
+      <c r="J205" s="3" t="n">
+        <v>7.915</v>
+      </c>
+      <c r="K205" s="3" t="n">
+        <v>1.805</v>
+      </c>
+      <c r="L205" s="3" t="n">
+        <v>2.127</v>
+      </c>
+      <c r="M205" s="3" t="n"/>
+      <c r="N205" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O205" s="2" t="inlineStr">
+        <is>
+          <t>ca_fin_B0, ca_fin_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>7e3. Essai v3 : cache pour toutes les lyres, chroma=1</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=1</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>sans bloom</t>
+        </is>
+      </c>
+      <c r="G206" s="3" t="n">
+        <v>9.07</v>
+      </c>
+      <c r="H206" s="4">
+        <f>IF(G206&gt;0,1000/G206,"")</f>
+        <v/>
+      </c>
+      <c r="I206" s="3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J206" s="3" t="n">
+        <v>7.475</v>
+      </c>
+      <c r="K206" s="3" t="n">
+        <v>1.814</v>
+      </c>
+      <c r="L206" s="3" t="n">
+        <v>2.135</v>
+      </c>
+      <c r="M206" s="3" t="n"/>
+      <c r="N206" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O206" s="2" t="inlineStr">
+        <is>
+          <t>ca_fin_B0, ca_fin_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>7e3. Essai v3 : cache pour toutes les lyres, chroma=1</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=1</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>sol mouille / public</t>
+        </is>
+      </c>
+      <c r="G207" s="3" t="n">
+        <v>10.81</v>
+      </c>
+      <c r="H207" s="4">
+        <f>IF(G207&gt;0,1000/G207,"")</f>
+        <v/>
+      </c>
+      <c r="I207" s="3" t="n">
+        <v>10.035</v>
+      </c>
+      <c r="J207" s="3" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="K207" s="3" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="L207" s="3" t="n">
+        <v>2.123</v>
+      </c>
+      <c r="M207" s="3" t="n">
+        <v>1.082</v>
+      </c>
+      <c r="N207" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O207" s="2" t="inlineStr">
+        <is>
+          <t>ca_fin_B0, ca_fin_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>7e3. Essai v3 : cache pour toutes les lyres, chroma=1</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, chroma=1</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>sol mouille + gobo + prisme 8 / scene</t>
+        </is>
+      </c>
+      <c r="G208" s="3" t="n">
+        <v>27.015</v>
+      </c>
+      <c r="H208" s="4">
+        <f>IF(G208&gt;0,1000/G208,"")</f>
+        <v/>
+      </c>
+      <c r="I208" s="3" t="n">
+        <v>26.185</v>
+      </c>
+      <c r="J208" s="3" t="n">
+        <v>26.01</v>
+      </c>
+      <c r="K208" s="3" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="L208" s="3" t="n">
+        <v>6.981</v>
+      </c>
+      <c r="M208" s="3" t="n">
+        <v>5.412</v>
+      </c>
+      <c r="N208" s="2" t="n">
+        <v>282</v>
+      </c>
+      <c r="O208" s="2" t="inlineStr">
+        <is>
+          <t>ca_fin_B0, ca_fin_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>7e4. Essai v4 : cache recalcule s'il change (RGBA16F), chroma=1</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide (--fast), chroma=1</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>defaut / public</t>
+        </is>
+      </c>
+      <c r="G209" s="3" t="n">
+        <v>8.625</v>
+      </c>
+      <c r="H209" s="4">
+        <f>IF(G209&gt;0,1000/G209,"")</f>
+        <v/>
+      </c>
+      <c r="I209" s="3" t="n">
+        <v>7.255</v>
+      </c>
+      <c r="J209" s="3" t="n">
+        <v>6.695</v>
+      </c>
+      <c r="K209" s="3" t="n">
+        <v>1.744</v>
+      </c>
+      <c r="L209" s="3" t="n">
+        <v>1.984</v>
+      </c>
+      <c r="M209" s="3" t="n"/>
+      <c r="N209" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O209" s="2" t="inlineStr">
+        <is>
+          <t>ca_v4_B0, ca_v4_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>7e4. Essai v4 : cache recalcule s'il change (RGBA16F), chroma=1</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide (--fast), chroma=1</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>defaut / scene</t>
+        </is>
+      </c>
+      <c r="G210" s="3" t="n">
+        <v>8.445</v>
+      </c>
+      <c r="H210" s="4">
+        <f>IF(G210&gt;0,1000/G210,"")</f>
+        <v/>
+      </c>
+      <c r="I210" s="3" t="n">
+        <v>6.865</v>
+      </c>
+      <c r="J210" s="3" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="K210" s="3" t="n">
+        <v>1.692</v>
+      </c>
+      <c r="L210" s="3" t="n">
+        <v>1.914</v>
+      </c>
+      <c r="M210" s="3" t="n"/>
+      <c r="N210" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O210" s="2" t="inlineStr">
+        <is>
+          <t>ca_v4_B0, ca_v4_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>7e4. Essai v4 : cache recalcule s'il change (RGBA16F), chroma=1</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide (--fast), chroma=1</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>defaut / sous les trusses</t>
+        </is>
+      </c>
+      <c r="G211" s="3" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="H211" s="4">
+        <f>IF(G211&gt;0,1000/G211,"")</f>
+        <v/>
+      </c>
+      <c r="I211" s="3" t="n">
+        <v>6.525</v>
+      </c>
+      <c r="J211" s="3" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="K211" s="3" t="n">
+        <v>1.163</v>
+      </c>
+      <c r="L211" s="3" t="n">
+        <v>1.679</v>
+      </c>
+      <c r="M211" s="3" t="n"/>
+      <c r="N211" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O211" s="2" t="inlineStr">
+        <is>
+          <t>ca_v4_B0, ca_v4_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>7e4. Essai v4 : cache recalcule s'il change (RGBA16F), chroma=1</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide (--fast), chroma=1</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>gobo + prisme 8 + zoom 25 / public</t>
+        </is>
+      </c>
+      <c r="G212" s="3" t="n">
+        <v>19.425</v>
+      </c>
+      <c r="H212" s="4">
+        <f>IF(G212&gt;0,1000/G212,"")</f>
+        <v/>
+      </c>
+      <c r="I212" s="3" t="n">
+        <v>18.71</v>
+      </c>
+      <c r="J212" s="3" t="n">
+        <v>18.62</v>
+      </c>
+      <c r="K212" s="3" t="n">
+        <v>6.532</v>
+      </c>
+      <c r="L212" s="3" t="n">
+        <v>7.099</v>
+      </c>
+      <c r="M212" s="3" t="n"/>
+      <c r="N212" s="2" t="n">
+        <v>273</v>
+      </c>
+      <c r="O212" s="2" t="inlineStr">
+        <is>
+          <t>ca_v4_B0, ca_v4_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>7e4. Essai v4 : cache recalcule s'il change (RGBA16F), chroma=1</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide (--fast), chroma=1</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>gobo + prisme 8 + zoom 25 / scene</t>
+        </is>
+      </c>
+      <c r="G213" s="3" t="n">
+        <v>17.705</v>
+      </c>
+      <c r="H213" s="4">
+        <f>IF(G213&gt;0,1000/G213,"")</f>
+        <v/>
+      </c>
+      <c r="I213" s="3" t="n">
+        <v>16.755</v>
+      </c>
+      <c r="J213" s="3" t="n">
+        <v>16.655</v>
+      </c>
+      <c r="K213" s="3" t="n">
+        <v>5.286</v>
+      </c>
+      <c r="L213" s="3" t="n">
+        <v>6.304</v>
+      </c>
+      <c r="M213" s="3" t="n"/>
+      <c r="N213" s="2" t="n">
+        <v>273</v>
+      </c>
+      <c r="O213" s="2" t="inlineStr">
+        <is>
+          <t>ca_v4_B0, ca_v4_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>7e4. Essai v4 : cache recalcule s'il change (RGBA16F), chroma=1</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide (--fast), chroma=1</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>gobo + prisme 8 + zoom 25 / sous les trusses</t>
+        </is>
+      </c>
+      <c r="G214" s="3" t="n">
+        <v>13.675</v>
+      </c>
+      <c r="H214" s="4">
+        <f>IF(G214&gt;0,1000/G214,"")</f>
+        <v/>
+      </c>
+      <c r="I214" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="J214" s="3" t="n">
+        <v>12.68</v>
+      </c>
+      <c r="K214" s="3" t="n">
+        <v>3.585</v>
+      </c>
+      <c r="L214" s="3" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="M214" s="3" t="n"/>
+      <c r="N214" s="2" t="n">
+        <v>273</v>
+      </c>
+      <c r="O214" s="2" t="inlineStr">
+        <is>
+          <t>ca_v4_B0, ca_v4_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>7e4. Essai v4 : cache recalcule s'il change (RGBA16F), chroma=1</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide (--fast), chroma=1</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>zoom 45 + frost 0.6 / public</t>
+        </is>
+      </c>
+      <c r="G215" s="3" t="n">
+        <v>12.105</v>
+      </c>
+      <c r="H215" s="4">
+        <f>IF(G215&gt;0,1000/G215,"")</f>
+        <v/>
+      </c>
+      <c r="I215" s="3" t="n">
+        <v>10.955</v>
+      </c>
+      <c r="J215" s="3" t="n">
+        <v>10.37</v>
+      </c>
+      <c r="K215" s="3" t="n">
+        <v>3.449</v>
+      </c>
+      <c r="L215" s="3" t="n">
+        <v>3.964</v>
+      </c>
+      <c r="M215" s="3" t="n"/>
+      <c r="N215" s="2" t="n">
+        <v>885</v>
+      </c>
+      <c r="O215" s="2" t="inlineStr">
+        <is>
+          <t>ca_v4_B0, ca_v4_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>7e4. Essai v4 : cache recalcule s'il change (RGBA16F), chroma=1</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide (--fast), chroma=1</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t>zoom 45 + frost 0.6 / scene</t>
+        </is>
+      </c>
+      <c r="G216" s="3" t="n">
+        <v>12.515</v>
+      </c>
+      <c r="H216" s="4">
+        <f>IF(G216&gt;0,1000/G216,"")</f>
+        <v/>
+      </c>
+      <c r="I216" s="3" t="n">
+        <v>11.085</v>
+      </c>
+      <c r="J216" s="3" t="n">
+        <v>10.15</v>
+      </c>
+      <c r="K216" s="3" t="n">
+        <v>3.092</v>
+      </c>
+      <c r="L216" s="3" t="n">
+        <v>4.059</v>
+      </c>
+      <c r="M216" s="3" t="n"/>
+      <c r="N216" s="2" t="n">
+        <v>885</v>
+      </c>
+      <c r="O216" s="2" t="inlineStr">
+        <is>
+          <t>ca_v4_B0, ca_v4_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>7e4. Essai v4 : cache recalcule s'il change (RGBA16F), chroma=1</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide (--fast), chroma=1</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F217" s="2" t="inlineStr">
+        <is>
+          <t>zoom 45 + frost 0.6 / sous les trusses</t>
+        </is>
+      </c>
+      <c r="G217" s="3" t="n">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="H217" s="4">
+        <f>IF(G217&gt;0,1000/G217,"")</f>
+        <v/>
+      </c>
+      <c r="I217" s="3" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="J217" s="3" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="K217" s="3" t="n">
+        <v>1.534</v>
+      </c>
+      <c r="L217" s="3" t="n">
+        <v>2.901</v>
+      </c>
+      <c r="M217" s="3" t="n"/>
+      <c r="N217" s="2" t="n">
+        <v>885</v>
+      </c>
+      <c r="O217" s="2" t="inlineStr">
+        <is>
+          <t>ca_v4_B0, ca_v4_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>7e4. Essai v4 : cache recalcule s'il change (RGBA16F), chroma=1</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide (--fast), chroma=1</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t>sans rebonds (GI)</t>
+        </is>
+      </c>
+      <c r="G218" s="3" t="n">
+        <v>7.51</v>
+      </c>
+      <c r="H218" s="4">
+        <f>IF(G218&gt;0,1000/G218,"")</f>
+        <v/>
+      </c>
+      <c r="I218" s="3" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="J218" s="3" t="n">
+        <v>5.985</v>
+      </c>
+      <c r="K218" s="3" t="n">
+        <v>1.478</v>
+      </c>
+      <c r="L218" s="3" t="n">
+        <v>1.515</v>
+      </c>
+      <c r="M218" s="3" t="n"/>
+      <c r="N218" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O218" s="2" t="inlineStr">
+        <is>
+          <t>ca_v4_B0, ca_v4_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>7e4. Essai v4 : cache recalcule s'il change (RGBA16F), chroma=1</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide (--fast), chroma=1</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F219" s="2" t="inlineStr">
+        <is>
+          <t>sans fumee volumetrique</t>
+        </is>
+      </c>
+      <c r="G219" s="3" t="n">
+        <v>5.595</v>
+      </c>
+      <c r="H219" s="4">
+        <f>IF(G219&gt;0,1000/G219,"")</f>
+        <v/>
+      </c>
+      <c r="I219" s="3" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="J219" s="3" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="K219" s="3" t="n">
+        <v>1.763</v>
+      </c>
+      <c r="L219" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M219" s="3" t="n"/>
+      <c r="N219" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O219" s="2" t="inlineStr">
+        <is>
+          <t>ca_v4_B0, ca_v4_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>7e4. Essai v4 : cache recalcule s'il change (RGBA16F), chroma=1</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide (--fast), chroma=1</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t>sans taches sur surfaces</t>
+        </is>
+      </c>
+      <c r="G220" s="3" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="H220" s="4">
+        <f>IF(G220&gt;0,1000/G220,"")</f>
+        <v/>
+      </c>
+      <c r="I220" s="3" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="J220" s="3" t="n">
+        <v>5.685</v>
+      </c>
+      <c r="K220" s="3" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="L220" s="3" t="n">
+        <v>2.006</v>
+      </c>
+      <c r="M220" s="3" t="n"/>
+      <c r="N220" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O220" s="2" t="inlineStr">
+        <is>
+          <t>ca_v4_B0, ca_v4_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>7e4. Essai v4 : cache recalcule s'il change (RGBA16F), chroma=1</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide (--fast), chroma=1</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t>sans reflets</t>
+        </is>
+      </c>
+      <c r="G221" s="3" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="H221" s="4">
+        <f>IF(G221&gt;0,1000/G221,"")</f>
+        <v/>
+      </c>
+      <c r="I221" s="3" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="J221" s="3" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="K221" s="3" t="n">
+        <v>1.762</v>
+      </c>
+      <c r="L221" s="3" t="n">
+        <v>1.987</v>
+      </c>
+      <c r="M221" s="3" t="n"/>
+      <c r="N221" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O221" s="2" t="inlineStr">
+        <is>
+          <t>ca_v4_B0, ca_v4_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>7e4. Essai v4 : cache recalcule s'il change (RGBA16F), chroma=1</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide (--fast), chroma=1</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>sans bloom</t>
+        </is>
+      </c>
+      <c r="G222" s="3" t="n">
+        <v>8.095000000000001</v>
+      </c>
+      <c r="H222" s="4">
+        <f>IF(G222&gt;0,1000/G222,"")</f>
+        <v/>
+      </c>
+      <c r="I222" s="3" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="J222" s="3" t="n">
+        <v>6.285</v>
+      </c>
+      <c r="K222" s="3" t="n">
+        <v>1.762</v>
+      </c>
+      <c r="L222" s="3" t="n">
+        <v>1.997</v>
+      </c>
+      <c r="M222" s="3" t="n"/>
+      <c r="N222" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O222" s="2" t="inlineStr">
+        <is>
+          <t>ca_v4_B0, ca_v4_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>7e4. Essai v4 : cache recalcule s'il change (RGBA16F), chroma=1</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide (--fast), chroma=1</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t>sol mouille / public</t>
+        </is>
+      </c>
+      <c r="G223" s="3" t="n">
+        <v>10.31</v>
+      </c>
+      <c r="H223" s="4">
+        <f>IF(G223&gt;0,1000/G223,"")</f>
+        <v/>
+      </c>
+      <c r="I223" s="3" t="n">
+        <v>8.885</v>
+      </c>
+      <c r="J223" s="3" t="n">
+        <v>8.215</v>
+      </c>
+      <c r="K223" s="3" t="n">
+        <v>1.853</v>
+      </c>
+      <c r="L223" s="3" t="n">
+        <v>2.007</v>
+      </c>
+      <c r="M223" s="3" t="n">
+        <v>1.048</v>
+      </c>
+      <c r="N223" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O223" s="2" t="inlineStr">
+        <is>
+          <t>ca_v4_B0, ca_v4_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:34</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>da54e7e+essai</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>7e4. Essai v4 : cache recalcule s'il change (RGBA16F), chroma=1</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide (--fast), chroma=1</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t>sol mouille + gobo + prisme 8 / scene</t>
+        </is>
+      </c>
+      <c r="G224" s="3" t="n">
+        <v>22.18</v>
+      </c>
+      <c r="H224" s="4">
+        <f>IF(G224&gt;0,1000/G224,"")</f>
+        <v/>
+      </c>
+      <c r="I224" s="3" t="n">
+        <v>21.48</v>
+      </c>
+      <c r="J224" s="3" t="n">
+        <v>21.07</v>
+      </c>
+      <c r="K224" s="3" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="L224" s="3" t="n">
+        <v>6.526</v>
+      </c>
+      <c r="M224" s="3" t="n">
+        <v>3.807</v>
+      </c>
+      <c r="N224" s="2" t="n">
+        <v>273</v>
+      </c>
+      <c r="O224" s="2" t="inlineStr">
+        <is>
+          <t>ca_v4_B0, ca_v4_B1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6917,7 +13441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:P37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6929,6 +13453,13 @@
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6984,6 +13515,41 @@
           <t>6b. Ombres + penombre sur surfaces (shadows=1)</t>
         </is>
       </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>7a. Aberration chromatique codee, coupee (atlas R32F garde)</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>7b. Aberration chromatique coupee (banc rapide)</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>7c. Aberration chromatique active (banc rapide)</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>7e0. Essai v0 : aberration, enveloppe +2 %, chroma=1</t>
+        </is>
+      </c>
+      <c r="N2" s="1" t="inlineStr">
+        <is>
+          <t>7e1. Essai v1 : enveloppe inchangee, flou par couleur, chroma=1</t>
+        </is>
+      </c>
+      <c r="O2" s="1" t="inlineStr">
+        <is>
+          <t>7e3. Essai v3 : cache pour toutes les lyres, chroma=1</t>
+        </is>
+      </c>
+      <c r="P2" s="1" t="inlineStr">
+        <is>
+          <t>7e4. Essai v4 : cache recalcule s'il change (RGBA16F), chroma=1</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -7023,6 +13589,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A3,Mesures!$C:$C,I$2),"")</f>
         <v/>
       </c>
+      <c r="J3" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A3,Mesures!$C:$C,J$2),"")</f>
+        <v/>
+      </c>
+      <c r="K3" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A3,Mesures!$C:$C,K$2),"")</f>
+        <v/>
+      </c>
+      <c r="L3" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A3,Mesures!$C:$C,L$2),"")</f>
+        <v/>
+      </c>
+      <c r="M3" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A3,Mesures!$C:$C,M$2),"")</f>
+        <v/>
+      </c>
+      <c r="N3" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A3,Mesures!$C:$C,N$2),"")</f>
+        <v/>
+      </c>
+      <c r="O3" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A3,Mesures!$C:$C,O$2),"")</f>
+        <v/>
+      </c>
+      <c r="P3" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A3,Mesures!$C:$C,P$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -7062,6 +13656,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A4,Mesures!$C:$C,I$2),"")</f>
         <v/>
       </c>
+      <c r="J4" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A4,Mesures!$C:$C,J$2),"")</f>
+        <v/>
+      </c>
+      <c r="K4" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A4,Mesures!$C:$C,K$2),"")</f>
+        <v/>
+      </c>
+      <c r="L4" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A4,Mesures!$C:$C,L$2),"")</f>
+        <v/>
+      </c>
+      <c r="M4" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A4,Mesures!$C:$C,M$2),"")</f>
+        <v/>
+      </c>
+      <c r="N4" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A4,Mesures!$C:$C,N$2),"")</f>
+        <v/>
+      </c>
+      <c r="O4" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A4,Mesures!$C:$C,O$2),"")</f>
+        <v/>
+      </c>
+      <c r="P4" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A4,Mesures!$C:$C,P$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -7101,6 +13723,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A5,Mesures!$C:$C,I$2),"")</f>
         <v/>
       </c>
+      <c r="J5" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A5,Mesures!$C:$C,J$2),"")</f>
+        <v/>
+      </c>
+      <c r="K5" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A5,Mesures!$C:$C,K$2),"")</f>
+        <v/>
+      </c>
+      <c r="L5" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A5,Mesures!$C:$C,L$2),"")</f>
+        <v/>
+      </c>
+      <c r="M5" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A5,Mesures!$C:$C,M$2),"")</f>
+        <v/>
+      </c>
+      <c r="N5" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A5,Mesures!$C:$C,N$2),"")</f>
+        <v/>
+      </c>
+      <c r="O5" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A5,Mesures!$C:$C,O$2),"")</f>
+        <v/>
+      </c>
+      <c r="P5" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A5,Mesures!$C:$C,P$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -7140,6 +13790,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A6,Mesures!$C:$C,I$2),"")</f>
         <v/>
       </c>
+      <c r="J6" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A6,Mesures!$C:$C,J$2),"")</f>
+        <v/>
+      </c>
+      <c r="K6" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A6,Mesures!$C:$C,K$2),"")</f>
+        <v/>
+      </c>
+      <c r="L6" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A6,Mesures!$C:$C,L$2),"")</f>
+        <v/>
+      </c>
+      <c r="M6" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A6,Mesures!$C:$C,M$2),"")</f>
+        <v/>
+      </c>
+      <c r="N6" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A6,Mesures!$C:$C,N$2),"")</f>
+        <v/>
+      </c>
+      <c r="O6" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A6,Mesures!$C:$C,O$2),"")</f>
+        <v/>
+      </c>
+      <c r="P6" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A6,Mesures!$C:$C,P$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -7179,6 +13857,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A7,Mesures!$C:$C,I$2),"")</f>
         <v/>
       </c>
+      <c r="J7" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A7,Mesures!$C:$C,J$2),"")</f>
+        <v/>
+      </c>
+      <c r="K7" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A7,Mesures!$C:$C,K$2),"")</f>
+        <v/>
+      </c>
+      <c r="L7" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A7,Mesures!$C:$C,L$2),"")</f>
+        <v/>
+      </c>
+      <c r="M7" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A7,Mesures!$C:$C,M$2),"")</f>
+        <v/>
+      </c>
+      <c r="N7" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A7,Mesures!$C:$C,N$2),"")</f>
+        <v/>
+      </c>
+      <c r="O7" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A7,Mesures!$C:$C,O$2),"")</f>
+        <v/>
+      </c>
+      <c r="P7" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A7,Mesures!$C:$C,P$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -7218,6 +13924,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A8,Mesures!$C:$C,I$2),"")</f>
         <v/>
       </c>
+      <c r="J8" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A8,Mesures!$C:$C,J$2),"")</f>
+        <v/>
+      </c>
+      <c r="K8" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A8,Mesures!$C:$C,K$2),"")</f>
+        <v/>
+      </c>
+      <c r="L8" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A8,Mesures!$C:$C,L$2),"")</f>
+        <v/>
+      </c>
+      <c r="M8" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A8,Mesures!$C:$C,M$2),"")</f>
+        <v/>
+      </c>
+      <c r="N8" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A8,Mesures!$C:$C,N$2),"")</f>
+        <v/>
+      </c>
+      <c r="O8" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A8,Mesures!$C:$C,O$2),"")</f>
+        <v/>
+      </c>
+      <c r="P8" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A8,Mesures!$C:$C,P$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -7257,6 +13991,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A9,Mesures!$C:$C,I$2),"")</f>
         <v/>
       </c>
+      <c r="J9" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A9,Mesures!$C:$C,J$2),"")</f>
+        <v/>
+      </c>
+      <c r="K9" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A9,Mesures!$C:$C,K$2),"")</f>
+        <v/>
+      </c>
+      <c r="L9" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A9,Mesures!$C:$C,L$2),"")</f>
+        <v/>
+      </c>
+      <c r="M9" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A9,Mesures!$C:$C,M$2),"")</f>
+        <v/>
+      </c>
+      <c r="N9" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A9,Mesures!$C:$C,N$2),"")</f>
+        <v/>
+      </c>
+      <c r="O9" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A9,Mesures!$C:$C,O$2),"")</f>
+        <v/>
+      </c>
+      <c r="P9" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A9,Mesures!$C:$C,P$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -7296,6 +14058,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A10,Mesures!$C:$C,I$2),"")</f>
         <v/>
       </c>
+      <c r="J10" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A10,Mesures!$C:$C,J$2),"")</f>
+        <v/>
+      </c>
+      <c r="K10" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A10,Mesures!$C:$C,K$2),"")</f>
+        <v/>
+      </c>
+      <c r="L10" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A10,Mesures!$C:$C,L$2),"")</f>
+        <v/>
+      </c>
+      <c r="M10" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A10,Mesures!$C:$C,M$2),"")</f>
+        <v/>
+      </c>
+      <c r="N10" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A10,Mesures!$C:$C,N$2),"")</f>
+        <v/>
+      </c>
+      <c r="O10" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A10,Mesures!$C:$C,O$2),"")</f>
+        <v/>
+      </c>
+      <c r="P10" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A10,Mesures!$C:$C,P$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -7335,6 +14125,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A11,Mesures!$C:$C,I$2),"")</f>
         <v/>
       </c>
+      <c r="J11" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A11,Mesures!$C:$C,J$2),"")</f>
+        <v/>
+      </c>
+      <c r="K11" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A11,Mesures!$C:$C,K$2),"")</f>
+        <v/>
+      </c>
+      <c r="L11" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A11,Mesures!$C:$C,L$2),"")</f>
+        <v/>
+      </c>
+      <c r="M11" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A11,Mesures!$C:$C,M$2),"")</f>
+        <v/>
+      </c>
+      <c r="N11" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A11,Mesures!$C:$C,N$2),"")</f>
+        <v/>
+      </c>
+      <c r="O11" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A11,Mesures!$C:$C,O$2),"")</f>
+        <v/>
+      </c>
+      <c r="P11" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A11,Mesures!$C:$C,P$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -7374,6 +14192,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A12,Mesures!$C:$C,I$2),"")</f>
         <v/>
       </c>
+      <c r="J12" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A12,Mesures!$C:$C,J$2),"")</f>
+        <v/>
+      </c>
+      <c r="K12" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A12,Mesures!$C:$C,K$2),"")</f>
+        <v/>
+      </c>
+      <c r="L12" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A12,Mesures!$C:$C,L$2),"")</f>
+        <v/>
+      </c>
+      <c r="M12" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A12,Mesures!$C:$C,M$2),"")</f>
+        <v/>
+      </c>
+      <c r="N12" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A12,Mesures!$C:$C,N$2),"")</f>
+        <v/>
+      </c>
+      <c r="O12" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A12,Mesures!$C:$C,O$2),"")</f>
+        <v/>
+      </c>
+      <c r="P12" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A12,Mesures!$C:$C,P$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -7413,6 +14259,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A13,Mesures!$C:$C,I$2),"")</f>
         <v/>
       </c>
+      <c r="J13" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A13,Mesures!$C:$C,J$2),"")</f>
+        <v/>
+      </c>
+      <c r="K13" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A13,Mesures!$C:$C,K$2),"")</f>
+        <v/>
+      </c>
+      <c r="L13" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A13,Mesures!$C:$C,L$2),"")</f>
+        <v/>
+      </c>
+      <c r="M13" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A13,Mesures!$C:$C,M$2),"")</f>
+        <v/>
+      </c>
+      <c r="N13" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A13,Mesures!$C:$C,N$2),"")</f>
+        <v/>
+      </c>
+      <c r="O13" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A13,Mesures!$C:$C,O$2),"")</f>
+        <v/>
+      </c>
+      <c r="P13" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A13,Mesures!$C:$C,P$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -7452,6 +14326,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A14,Mesures!$C:$C,I$2),"")</f>
         <v/>
       </c>
+      <c r="J14" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A14,Mesures!$C:$C,J$2),"")</f>
+        <v/>
+      </c>
+      <c r="K14" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A14,Mesures!$C:$C,K$2),"")</f>
+        <v/>
+      </c>
+      <c r="L14" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A14,Mesures!$C:$C,L$2),"")</f>
+        <v/>
+      </c>
+      <c r="M14" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A14,Mesures!$C:$C,M$2),"")</f>
+        <v/>
+      </c>
+      <c r="N14" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A14,Mesures!$C:$C,N$2),"")</f>
+        <v/>
+      </c>
+      <c r="O14" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A14,Mesures!$C:$C,O$2),"")</f>
+        <v/>
+      </c>
+      <c r="P14" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A14,Mesures!$C:$C,P$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -7491,6 +14393,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A15,Mesures!$C:$C,I$2),"")</f>
         <v/>
       </c>
+      <c r="J15" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A15,Mesures!$C:$C,J$2),"")</f>
+        <v/>
+      </c>
+      <c r="K15" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A15,Mesures!$C:$C,K$2),"")</f>
+        <v/>
+      </c>
+      <c r="L15" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A15,Mesures!$C:$C,L$2),"")</f>
+        <v/>
+      </c>
+      <c r="M15" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A15,Mesures!$C:$C,M$2),"")</f>
+        <v/>
+      </c>
+      <c r="N15" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A15,Mesures!$C:$C,N$2),"")</f>
+        <v/>
+      </c>
+      <c r="O15" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A15,Mesures!$C:$C,O$2),"")</f>
+        <v/>
+      </c>
+      <c r="P15" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A15,Mesures!$C:$C,P$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -7530,6 +14460,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A16,Mesures!$C:$C,I$2),"")</f>
         <v/>
       </c>
+      <c r="J16" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A16,Mesures!$C:$C,J$2),"")</f>
+        <v/>
+      </c>
+      <c r="K16" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A16,Mesures!$C:$C,K$2),"")</f>
+        <v/>
+      </c>
+      <c r="L16" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A16,Mesures!$C:$C,L$2),"")</f>
+        <v/>
+      </c>
+      <c r="M16" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A16,Mesures!$C:$C,M$2),"")</f>
+        <v/>
+      </c>
+      <c r="N16" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A16,Mesures!$C:$C,N$2),"")</f>
+        <v/>
+      </c>
+      <c r="O16" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A16,Mesures!$C:$C,O$2),"")</f>
+        <v/>
+      </c>
+      <c r="P16" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A16,Mesures!$C:$C,P$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -7569,6 +14527,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A17,Mesures!$C:$C,I$2),"")</f>
         <v/>
       </c>
+      <c r="J17" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A17,Mesures!$C:$C,J$2),"")</f>
+        <v/>
+      </c>
+      <c r="K17" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A17,Mesures!$C:$C,K$2),"")</f>
+        <v/>
+      </c>
+      <c r="L17" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A17,Mesures!$C:$C,L$2),"")</f>
+        <v/>
+      </c>
+      <c r="M17" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A17,Mesures!$C:$C,M$2),"")</f>
+        <v/>
+      </c>
+      <c r="N17" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A17,Mesures!$C:$C,N$2),"")</f>
+        <v/>
+      </c>
+      <c r="O17" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A17,Mesures!$C:$C,O$2),"")</f>
+        <v/>
+      </c>
+      <c r="P17" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A17,Mesures!$C:$C,P$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -7608,6 +14594,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A18,Mesures!$C:$C,I$2),"")</f>
         <v/>
       </c>
+      <c r="J18" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A18,Mesures!$C:$C,J$2),"")</f>
+        <v/>
+      </c>
+      <c r="K18" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A18,Mesures!$C:$C,K$2),"")</f>
+        <v/>
+      </c>
+      <c r="L18" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A18,Mesures!$C:$C,L$2),"")</f>
+        <v/>
+      </c>
+      <c r="M18" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A18,Mesures!$C:$C,M$2),"")</f>
+        <v/>
+      </c>
+      <c r="N18" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A18,Mesures!$C:$C,N$2),"")</f>
+        <v/>
+      </c>
+      <c r="O18" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A18,Mesures!$C:$C,O$2),"")</f>
+        <v/>
+      </c>
+      <c r="P18" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A18,Mesures!$C:$C,P$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -7662,6 +14676,41 @@
           <t>6b. Ombres + penombre sur surfaces (shadows=1)</t>
         </is>
       </c>
+      <c r="J21" s="1" t="inlineStr">
+        <is>
+          <t>7a. Aberration chromatique codee, coupee (atlas R32F garde)</t>
+        </is>
+      </c>
+      <c r="K21" s="1" t="inlineStr">
+        <is>
+          <t>7b. Aberration chromatique coupee (banc rapide)</t>
+        </is>
+      </c>
+      <c r="L21" s="1" t="inlineStr">
+        <is>
+          <t>7c. Aberration chromatique active (banc rapide)</t>
+        </is>
+      </c>
+      <c r="M21" s="1" t="inlineStr">
+        <is>
+          <t>7e0. Essai v0 : aberration, enveloppe +2 %, chroma=1</t>
+        </is>
+      </c>
+      <c r="N21" s="1" t="inlineStr">
+        <is>
+          <t>7e1. Essai v1 : enveloppe inchangee, flou par couleur, chroma=1</t>
+        </is>
+      </c>
+      <c r="O21" s="1" t="inlineStr">
+        <is>
+          <t>7e3. Essai v3 : cache pour toutes les lyres, chroma=1</t>
+        </is>
+      </c>
+      <c r="P21" s="1" t="inlineStr">
+        <is>
+          <t>7e4. Essai v4 : cache recalcule s'il change (RGBA16F), chroma=1</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -7701,6 +14750,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A22,Mesures!$C:$C,I$21),"")</f>
         <v/>
       </c>
+      <c r="J22" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A22,Mesures!$C:$C,J$21),"")</f>
+        <v/>
+      </c>
+      <c r="K22" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A22,Mesures!$C:$C,K$21),"")</f>
+        <v/>
+      </c>
+      <c r="L22" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A22,Mesures!$C:$C,L$21),"")</f>
+        <v/>
+      </c>
+      <c r="M22" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A22,Mesures!$C:$C,M$21),"")</f>
+        <v/>
+      </c>
+      <c r="N22" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A22,Mesures!$C:$C,N$21),"")</f>
+        <v/>
+      </c>
+      <c r="O22" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A22,Mesures!$C:$C,O$21),"")</f>
+        <v/>
+      </c>
+      <c r="P22" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A22,Mesures!$C:$C,P$21),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -7740,6 +14817,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A23,Mesures!$C:$C,I$21),"")</f>
         <v/>
       </c>
+      <c r="J23" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A23,Mesures!$C:$C,J$21),"")</f>
+        <v/>
+      </c>
+      <c r="K23" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A23,Mesures!$C:$C,K$21),"")</f>
+        <v/>
+      </c>
+      <c r="L23" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A23,Mesures!$C:$C,L$21),"")</f>
+        <v/>
+      </c>
+      <c r="M23" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A23,Mesures!$C:$C,M$21),"")</f>
+        <v/>
+      </c>
+      <c r="N23" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A23,Mesures!$C:$C,N$21),"")</f>
+        <v/>
+      </c>
+      <c r="O23" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A23,Mesures!$C:$C,O$21),"")</f>
+        <v/>
+      </c>
+      <c r="P23" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A23,Mesures!$C:$C,P$21),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -7779,6 +14884,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A24,Mesures!$C:$C,I$21),"")</f>
         <v/>
       </c>
+      <c r="J24" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A24,Mesures!$C:$C,J$21),"")</f>
+        <v/>
+      </c>
+      <c r="K24" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A24,Mesures!$C:$C,K$21),"")</f>
+        <v/>
+      </c>
+      <c r="L24" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A24,Mesures!$C:$C,L$21),"")</f>
+        <v/>
+      </c>
+      <c r="M24" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A24,Mesures!$C:$C,M$21),"")</f>
+        <v/>
+      </c>
+      <c r="N24" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A24,Mesures!$C:$C,N$21),"")</f>
+        <v/>
+      </c>
+      <c r="O24" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A24,Mesures!$C:$C,O$21),"")</f>
+        <v/>
+      </c>
+      <c r="P24" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A24,Mesures!$C:$C,P$21),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -7818,6 +14951,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A25,Mesures!$C:$C,I$21),"")</f>
         <v/>
       </c>
+      <c r="J25" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A25,Mesures!$C:$C,J$21),"")</f>
+        <v/>
+      </c>
+      <c r="K25" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A25,Mesures!$C:$C,K$21),"")</f>
+        <v/>
+      </c>
+      <c r="L25" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A25,Mesures!$C:$C,L$21),"")</f>
+        <v/>
+      </c>
+      <c r="M25" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A25,Mesures!$C:$C,M$21),"")</f>
+        <v/>
+      </c>
+      <c r="N25" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A25,Mesures!$C:$C,N$21),"")</f>
+        <v/>
+      </c>
+      <c r="O25" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A25,Mesures!$C:$C,O$21),"")</f>
+        <v/>
+      </c>
+      <c r="P25" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A25,Mesures!$C:$C,P$21),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -7857,6 +15018,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A26,Mesures!$C:$C,I$21),"")</f>
         <v/>
       </c>
+      <c r="J26" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A26,Mesures!$C:$C,J$21),"")</f>
+        <v/>
+      </c>
+      <c r="K26" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A26,Mesures!$C:$C,K$21),"")</f>
+        <v/>
+      </c>
+      <c r="L26" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A26,Mesures!$C:$C,L$21),"")</f>
+        <v/>
+      </c>
+      <c r="M26" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A26,Mesures!$C:$C,M$21),"")</f>
+        <v/>
+      </c>
+      <c r="N26" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A26,Mesures!$C:$C,N$21),"")</f>
+        <v/>
+      </c>
+      <c r="O26" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A26,Mesures!$C:$C,O$21),"")</f>
+        <v/>
+      </c>
+      <c r="P26" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A26,Mesures!$C:$C,P$21),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -7896,6 +15085,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A27,Mesures!$C:$C,I$21),"")</f>
         <v/>
       </c>
+      <c r="J27" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A27,Mesures!$C:$C,J$21),"")</f>
+        <v/>
+      </c>
+      <c r="K27" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A27,Mesures!$C:$C,K$21),"")</f>
+        <v/>
+      </c>
+      <c r="L27" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A27,Mesures!$C:$C,L$21),"")</f>
+        <v/>
+      </c>
+      <c r="M27" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A27,Mesures!$C:$C,M$21),"")</f>
+        <v/>
+      </c>
+      <c r="N27" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A27,Mesures!$C:$C,N$21),"")</f>
+        <v/>
+      </c>
+      <c r="O27" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A27,Mesures!$C:$C,O$21),"")</f>
+        <v/>
+      </c>
+      <c r="P27" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A27,Mesures!$C:$C,P$21),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -7935,6 +15152,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A28,Mesures!$C:$C,I$21),"")</f>
         <v/>
       </c>
+      <c r="J28" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A28,Mesures!$C:$C,J$21),"")</f>
+        <v/>
+      </c>
+      <c r="K28" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A28,Mesures!$C:$C,K$21),"")</f>
+        <v/>
+      </c>
+      <c r="L28" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A28,Mesures!$C:$C,L$21),"")</f>
+        <v/>
+      </c>
+      <c r="M28" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A28,Mesures!$C:$C,M$21),"")</f>
+        <v/>
+      </c>
+      <c r="N28" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A28,Mesures!$C:$C,N$21),"")</f>
+        <v/>
+      </c>
+      <c r="O28" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A28,Mesures!$C:$C,O$21),"")</f>
+        <v/>
+      </c>
+      <c r="P28" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A28,Mesures!$C:$C,P$21),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -7974,6 +15219,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A29,Mesures!$C:$C,I$21),"")</f>
         <v/>
       </c>
+      <c r="J29" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A29,Mesures!$C:$C,J$21),"")</f>
+        <v/>
+      </c>
+      <c r="K29" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A29,Mesures!$C:$C,K$21),"")</f>
+        <v/>
+      </c>
+      <c r="L29" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A29,Mesures!$C:$C,L$21),"")</f>
+        <v/>
+      </c>
+      <c r="M29" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A29,Mesures!$C:$C,M$21),"")</f>
+        <v/>
+      </c>
+      <c r="N29" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A29,Mesures!$C:$C,N$21),"")</f>
+        <v/>
+      </c>
+      <c r="O29" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A29,Mesures!$C:$C,O$21),"")</f>
+        <v/>
+      </c>
+      <c r="P29" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A29,Mesures!$C:$C,P$21),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -8013,6 +15286,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A30,Mesures!$C:$C,I$21),"")</f>
         <v/>
       </c>
+      <c r="J30" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A30,Mesures!$C:$C,J$21),"")</f>
+        <v/>
+      </c>
+      <c r="K30" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A30,Mesures!$C:$C,K$21),"")</f>
+        <v/>
+      </c>
+      <c r="L30" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A30,Mesures!$C:$C,L$21),"")</f>
+        <v/>
+      </c>
+      <c r="M30" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A30,Mesures!$C:$C,M$21),"")</f>
+        <v/>
+      </c>
+      <c r="N30" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A30,Mesures!$C:$C,N$21),"")</f>
+        <v/>
+      </c>
+      <c r="O30" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A30,Mesures!$C:$C,O$21),"")</f>
+        <v/>
+      </c>
+      <c r="P30" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A30,Mesures!$C:$C,P$21),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -8052,6 +15353,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A31,Mesures!$C:$C,I$21),"")</f>
         <v/>
       </c>
+      <c r="J31" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A31,Mesures!$C:$C,J$21),"")</f>
+        <v/>
+      </c>
+      <c r="K31" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A31,Mesures!$C:$C,K$21),"")</f>
+        <v/>
+      </c>
+      <c r="L31" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A31,Mesures!$C:$C,L$21),"")</f>
+        <v/>
+      </c>
+      <c r="M31" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A31,Mesures!$C:$C,M$21),"")</f>
+        <v/>
+      </c>
+      <c r="N31" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A31,Mesures!$C:$C,N$21),"")</f>
+        <v/>
+      </c>
+      <c r="O31" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A31,Mesures!$C:$C,O$21),"")</f>
+        <v/>
+      </c>
+      <c r="P31" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A31,Mesures!$C:$C,P$21),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -8091,6 +15420,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A32,Mesures!$C:$C,I$21),"")</f>
         <v/>
       </c>
+      <c r="J32" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A32,Mesures!$C:$C,J$21),"")</f>
+        <v/>
+      </c>
+      <c r="K32" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A32,Mesures!$C:$C,K$21),"")</f>
+        <v/>
+      </c>
+      <c r="L32" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A32,Mesures!$C:$C,L$21),"")</f>
+        <v/>
+      </c>
+      <c r="M32" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A32,Mesures!$C:$C,M$21),"")</f>
+        <v/>
+      </c>
+      <c r="N32" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A32,Mesures!$C:$C,N$21),"")</f>
+        <v/>
+      </c>
+      <c r="O32" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A32,Mesures!$C:$C,O$21),"")</f>
+        <v/>
+      </c>
+      <c r="P32" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A32,Mesures!$C:$C,P$21),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -8130,6 +15487,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A33,Mesures!$C:$C,I$21),"")</f>
         <v/>
       </c>
+      <c r="J33" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A33,Mesures!$C:$C,J$21),"")</f>
+        <v/>
+      </c>
+      <c r="K33" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A33,Mesures!$C:$C,K$21),"")</f>
+        <v/>
+      </c>
+      <c r="L33" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A33,Mesures!$C:$C,L$21),"")</f>
+        <v/>
+      </c>
+      <c r="M33" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A33,Mesures!$C:$C,M$21),"")</f>
+        <v/>
+      </c>
+      <c r="N33" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A33,Mesures!$C:$C,N$21),"")</f>
+        <v/>
+      </c>
+      <c r="O33" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A33,Mesures!$C:$C,O$21),"")</f>
+        <v/>
+      </c>
+      <c r="P33" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A33,Mesures!$C:$C,P$21),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -8169,6 +15554,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A34,Mesures!$C:$C,I$21),"")</f>
         <v/>
       </c>
+      <c r="J34" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A34,Mesures!$C:$C,J$21),"")</f>
+        <v/>
+      </c>
+      <c r="K34" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A34,Mesures!$C:$C,K$21),"")</f>
+        <v/>
+      </c>
+      <c r="L34" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A34,Mesures!$C:$C,L$21),"")</f>
+        <v/>
+      </c>
+      <c r="M34" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A34,Mesures!$C:$C,M$21),"")</f>
+        <v/>
+      </c>
+      <c r="N34" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A34,Mesures!$C:$C,N$21),"")</f>
+        <v/>
+      </c>
+      <c r="O34" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A34,Mesures!$C:$C,O$21),"")</f>
+        <v/>
+      </c>
+      <c r="P34" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A34,Mesures!$C:$C,P$21),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -8208,6 +15621,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A35,Mesures!$C:$C,I$21),"")</f>
         <v/>
       </c>
+      <c r="J35" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A35,Mesures!$C:$C,J$21),"")</f>
+        <v/>
+      </c>
+      <c r="K35" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A35,Mesures!$C:$C,K$21),"")</f>
+        <v/>
+      </c>
+      <c r="L35" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A35,Mesures!$C:$C,L$21),"")</f>
+        <v/>
+      </c>
+      <c r="M35" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A35,Mesures!$C:$C,M$21),"")</f>
+        <v/>
+      </c>
+      <c r="N35" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A35,Mesures!$C:$C,N$21),"")</f>
+        <v/>
+      </c>
+      <c r="O35" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A35,Mesures!$C:$C,O$21),"")</f>
+        <v/>
+      </c>
+      <c r="P35" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A35,Mesures!$C:$C,P$21),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -8247,6 +15688,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A36,Mesures!$C:$C,I$21),"")</f>
         <v/>
       </c>
+      <c r="J36" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A36,Mesures!$C:$C,J$21),"")</f>
+        <v/>
+      </c>
+      <c r="K36" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A36,Mesures!$C:$C,K$21),"")</f>
+        <v/>
+      </c>
+      <c r="L36" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A36,Mesures!$C:$C,L$21),"")</f>
+        <v/>
+      </c>
+      <c r="M36" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A36,Mesures!$C:$C,M$21),"")</f>
+        <v/>
+      </c>
+      <c r="N36" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A36,Mesures!$C:$C,N$21),"")</f>
+        <v/>
+      </c>
+      <c r="O36" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A36,Mesures!$C:$C,O$21),"")</f>
+        <v/>
+      </c>
+      <c r="P36" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A36,Mesures!$C:$C,P$21),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -8284,6 +15753,34 @@
       </c>
       <c r="I37" s="3">
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A37,Mesures!$C:$C,I$21),"")</f>
+        <v/>
+      </c>
+      <c r="J37" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A37,Mesures!$C:$C,J$21),"")</f>
+        <v/>
+      </c>
+      <c r="K37" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A37,Mesures!$C:$C,K$21),"")</f>
+        <v/>
+      </c>
+      <c r="L37" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A37,Mesures!$C:$C,L$21),"")</f>
+        <v/>
+      </c>
+      <c r="M37" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A37,Mesures!$C:$C,M$21),"")</f>
+        <v/>
+      </c>
+      <c r="N37" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A37,Mesures!$C:$C,N$21),"")</f>
+        <v/>
+      </c>
+      <c r="O37" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A37,Mesures!$C:$C,O$21),"")</f>
+        <v/>
+      </c>
+      <c r="P37" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A37,Mesures!$C:$C,P$21),"")</f>
         <v/>
       </c>
     </row>

--- a/lyre-viz/historique_perf.xlsx
+++ b/lyre-viz/historique_perf.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O224"/>
+  <dimension ref="A1:O240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -13430,6 +13430,938 @@
         </is>
       </c>
     </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:58</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>403cbd3 +modifs</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>8. Longueur exacte des faisceaux arretes par le sol (bout des taches rasantes)</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide (--fast)</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F225" s="2" t="inlineStr">
+        <is>
+          <t>defaut / public</t>
+        </is>
+      </c>
+      <c r="G225" s="3" t="n">
+        <v>8.535</v>
+      </c>
+      <c r="H225" s="4">
+        <f>IF(G225&gt;0,1000/G225,"")</f>
+        <v/>
+      </c>
+      <c r="I225" s="3" t="n">
+        <v>7.16</v>
+      </c>
+      <c r="J225" s="3" t="n">
+        <v>6.985</v>
+      </c>
+      <c r="K225" s="3" t="n">
+        <v>1.621</v>
+      </c>
+      <c r="L225" s="3" t="n">
+        <v>1.946</v>
+      </c>
+      <c r="M225" s="3" t="n"/>
+      <c r="N225" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="O225" s="2" t="inlineStr">
+        <is>
+          <t>longueur2_B0, longueur2_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:58</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>403cbd3 +modifs</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>8. Longueur exacte des faisceaux arretes par le sol (bout des taches rasantes)</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide (--fast)</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t>defaut / scene</t>
+        </is>
+      </c>
+      <c r="G226" s="3" t="n">
+        <v>8.025</v>
+      </c>
+      <c r="H226" s="4">
+        <f>IF(G226&gt;0,1000/G226,"")</f>
+        <v/>
+      </c>
+      <c r="I226" s="3" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="J226" s="3" t="n">
+        <v>6.835</v>
+      </c>
+      <c r="K226" s="3" t="n">
+        <v>1.601</v>
+      </c>
+      <c r="L226" s="3" t="n">
+        <v>1.861</v>
+      </c>
+      <c r="M226" s="3" t="n"/>
+      <c r="N226" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="O226" s="2" t="inlineStr">
+        <is>
+          <t>longueur2_B0, longueur2_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:58</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>403cbd3 +modifs</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>8. Longueur exacte des faisceaux arretes par le sol (bout des taches rasantes)</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide (--fast)</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F227" s="2" t="inlineStr">
+        <is>
+          <t>defaut / sous les trusses</t>
+        </is>
+      </c>
+      <c r="G227" s="3" t="n">
+        <v>7.745</v>
+      </c>
+      <c r="H227" s="4">
+        <f>IF(G227&gt;0,1000/G227,"")</f>
+        <v/>
+      </c>
+      <c r="I227" s="3" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="J227" s="3" t="n">
+        <v>5.625</v>
+      </c>
+      <c r="K227" s="3" t="n">
+        <v>1.106</v>
+      </c>
+      <c r="L227" s="3" t="n">
+        <v>1.542</v>
+      </c>
+      <c r="M227" s="3" t="n"/>
+      <c r="N227" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="O227" s="2" t="inlineStr">
+        <is>
+          <t>longueur2_B0, longueur2_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:58</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>403cbd3 +modifs</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>8. Longueur exacte des faisceaux arretes par le sol (bout des taches rasantes)</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide (--fast)</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F228" s="2" t="inlineStr">
+        <is>
+          <t>gobo + prisme 8 + zoom 25 / public</t>
+        </is>
+      </c>
+      <c r="G228" s="3" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="H228" s="4">
+        <f>IF(G228&gt;0,1000/G228,"")</f>
+        <v/>
+      </c>
+      <c r="I228" s="3" t="n">
+        <v>18.445</v>
+      </c>
+      <c r="J228" s="3" t="n">
+        <v>18.495</v>
+      </c>
+      <c r="K228" s="3" t="n">
+        <v>6.735</v>
+      </c>
+      <c r="L228" s="3" t="n">
+        <v>6.984</v>
+      </c>
+      <c r="M228" s="3" t="n"/>
+      <c r="N228" s="2" t="n">
+        <v>280</v>
+      </c>
+      <c r="O228" s="2" t="inlineStr">
+        <is>
+          <t>longueur2_B0, longueur2_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:58</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>403cbd3 +modifs</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>8. Longueur exacte des faisceaux arretes par le sol (bout des taches rasantes)</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide (--fast)</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F229" s="2" t="inlineStr">
+        <is>
+          <t>gobo + prisme 8 + zoom 25 / scene</t>
+        </is>
+      </c>
+      <c r="G229" s="3" t="n">
+        <v>18.335</v>
+      </c>
+      <c r="H229" s="4">
+        <f>IF(G229&gt;0,1000/G229,"")</f>
+        <v/>
+      </c>
+      <c r="I229" s="3" t="n">
+        <v>17.475</v>
+      </c>
+      <c r="J229" s="3" t="n">
+        <v>17.125</v>
+      </c>
+      <c r="K229" s="3" t="n">
+        <v>6.085</v>
+      </c>
+      <c r="L229" s="3" t="n">
+        <v>6.376</v>
+      </c>
+      <c r="M229" s="3" t="n"/>
+      <c r="N229" s="2" t="n">
+        <v>280</v>
+      </c>
+      <c r="O229" s="2" t="inlineStr">
+        <is>
+          <t>longueur2_B0, longueur2_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:58</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>403cbd3 +modifs</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>8. Longueur exacte des faisceaux arretes par le sol (bout des taches rasantes)</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide (--fast)</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
+          <t>gobo + prisme 8 + zoom 25 / sous les trusses</t>
+        </is>
+      </c>
+      <c r="G230" s="3" t="n">
+        <v>13.695</v>
+      </c>
+      <c r="H230" s="4">
+        <f>IF(G230&gt;0,1000/G230,"")</f>
+        <v/>
+      </c>
+      <c r="I230" s="3" t="n">
+        <v>13.005</v>
+      </c>
+      <c r="J230" s="3" t="n">
+        <v>13.095</v>
+      </c>
+      <c r="K230" s="3" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="L230" s="3" t="n">
+        <v>4.087</v>
+      </c>
+      <c r="M230" s="3" t="n"/>
+      <c r="N230" s="2" t="n">
+        <v>280</v>
+      </c>
+      <c r="O230" s="2" t="inlineStr">
+        <is>
+          <t>longueur2_B0, longueur2_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:58</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>403cbd3 +modifs</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>8. Longueur exacte des faisceaux arretes par le sol (bout des taches rasantes)</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide (--fast)</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F231" s="2" t="inlineStr">
+        <is>
+          <t>zoom 45 + frost 0.6 / public</t>
+        </is>
+      </c>
+      <c r="G231" s="3" t="n">
+        <v>11.775</v>
+      </c>
+      <c r="H231" s="4">
+        <f>IF(G231&gt;0,1000/G231,"")</f>
+        <v/>
+      </c>
+      <c r="I231" s="3" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="J231" s="3" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="K231" s="3" t="n">
+        <v>3.396</v>
+      </c>
+      <c r="L231" s="3" t="n">
+        <v>4.079</v>
+      </c>
+      <c r="M231" s="3" t="n"/>
+      <c r="N231" s="2" t="n">
+        <v>887</v>
+      </c>
+      <c r="O231" s="2" t="inlineStr">
+        <is>
+          <t>longueur2_B0, longueur2_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:58</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>403cbd3 +modifs</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>8. Longueur exacte des faisceaux arretes par le sol (bout des taches rasantes)</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide (--fast)</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t>zoom 45 + frost 0.6 / scene</t>
+        </is>
+      </c>
+      <c r="G232" s="3" t="n">
+        <v>11.81</v>
+      </c>
+      <c r="H232" s="4">
+        <f>IF(G232&gt;0,1000/G232,"")</f>
+        <v/>
+      </c>
+      <c r="I232" s="3" t="n">
+        <v>10.975</v>
+      </c>
+      <c r="J232" s="3" t="n">
+        <v>10.725</v>
+      </c>
+      <c r="K232" s="3" t="n">
+        <v>2.983</v>
+      </c>
+      <c r="L232" s="3" t="n">
+        <v>4.072</v>
+      </c>
+      <c r="M232" s="3" t="n"/>
+      <c r="N232" s="2" t="n">
+        <v>887</v>
+      </c>
+      <c r="O232" s="2" t="inlineStr">
+        <is>
+          <t>longueur2_B0, longueur2_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:58</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>403cbd3 +modifs</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>8. Longueur exacte des faisceaux arretes par le sol (bout des taches rasantes)</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide (--fast)</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F233" s="2" t="inlineStr">
+        <is>
+          <t>zoom 45 + frost 0.6 / sous les trusses</t>
+        </is>
+      </c>
+      <c r="G233" s="3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H233" s="4">
+        <f>IF(G233&gt;0,1000/G233,"")</f>
+        <v/>
+      </c>
+      <c r="I233" s="3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J233" s="3" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="K233" s="3" t="n">
+        <v>1.511</v>
+      </c>
+      <c r="L233" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="M233" s="3" t="n"/>
+      <c r="N233" s="2" t="n">
+        <v>887</v>
+      </c>
+      <c r="O233" s="2" t="inlineStr">
+        <is>
+          <t>longueur2_B0, longueur2_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:58</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>403cbd3 +modifs</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>8. Longueur exacte des faisceaux arretes par le sol (bout des taches rasantes)</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide (--fast)</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t>sans rebonds (GI)</t>
+        </is>
+      </c>
+      <c r="G234" s="3" t="n">
+        <v>7.815</v>
+      </c>
+      <c r="H234" s="4">
+        <f>IF(G234&gt;0,1000/G234,"")</f>
+        <v/>
+      </c>
+      <c r="I234" s="3" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="J234" s="3" t="n">
+        <v>5.995</v>
+      </c>
+      <c r="K234" s="3" t="n">
+        <v>1.422</v>
+      </c>
+      <c r="L234" s="3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M234" s="3" t="n"/>
+      <c r="N234" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="O234" s="2" t="inlineStr">
+        <is>
+          <t>longueur2_B0, longueur2_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:58</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>403cbd3 +modifs</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>8. Longueur exacte des faisceaux arretes par le sol (bout des taches rasantes)</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide (--fast)</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F235" s="2" t="inlineStr">
+        <is>
+          <t>sans fumee volumetrique</t>
+        </is>
+      </c>
+      <c r="G235" s="3" t="n">
+        <v>5.155</v>
+      </c>
+      <c r="H235" s="4">
+        <f>IF(G235&gt;0,1000/G235,"")</f>
+        <v/>
+      </c>
+      <c r="I235" s="3" t="n">
+        <v>3.375</v>
+      </c>
+      <c r="J235" s="3" t="n">
+        <v>2.985</v>
+      </c>
+      <c r="K235" s="3" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="L235" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M235" s="3" t="n"/>
+      <c r="N235" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="O235" s="2" t="inlineStr">
+        <is>
+          <t>longueur2_B0, longueur2_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:58</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>403cbd3 +modifs</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>8. Longueur exacte des faisceaux arretes par le sol (bout des taches rasantes)</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide (--fast)</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F236" s="2" t="inlineStr">
+        <is>
+          <t>sans taches sur surfaces</t>
+        </is>
+      </c>
+      <c r="G236" s="3" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="H236" s="4">
+        <f>IF(G236&gt;0,1000/G236,"")</f>
+        <v/>
+      </c>
+      <c r="I236" s="3" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="J236" s="3" t="n">
+        <v>5.905</v>
+      </c>
+      <c r="K236" s="3" t="n">
+        <v>0.699</v>
+      </c>
+      <c r="L236" s="3" t="n">
+        <v>1.922</v>
+      </c>
+      <c r="M236" s="3" t="n"/>
+      <c r="N236" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="O236" s="2" t="inlineStr">
+        <is>
+          <t>longueur2_B0, longueur2_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:58</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>403cbd3 +modifs</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>8. Longueur exacte des faisceaux arretes par le sol (bout des taches rasantes)</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide (--fast)</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F237" s="2" t="inlineStr">
+        <is>
+          <t>sans reflets</t>
+        </is>
+      </c>
+      <c r="G237" s="3" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="H237" s="4">
+        <f>IF(G237&gt;0,1000/G237,"")</f>
+        <v/>
+      </c>
+      <c r="I237" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J237" s="3" t="n">
+        <v>6.835</v>
+      </c>
+      <c r="K237" s="3" t="n">
+        <v>1.619</v>
+      </c>
+      <c r="L237" s="3" t="n">
+        <v>1.971</v>
+      </c>
+      <c r="M237" s="3" t="n"/>
+      <c r="N237" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="O237" s="2" t="inlineStr">
+        <is>
+          <t>longueur2_B0, longueur2_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:58</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>403cbd3 +modifs</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>8. Longueur exacte des faisceaux arretes par le sol (bout des taches rasantes)</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide (--fast)</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F238" s="2" t="inlineStr">
+        <is>
+          <t>sans bloom</t>
+        </is>
+      </c>
+      <c r="G238" s="3" t="n">
+        <v>7.785</v>
+      </c>
+      <c r="H238" s="4">
+        <f>IF(G238&gt;0,1000/G238,"")</f>
+        <v/>
+      </c>
+      <c r="I238" s="3" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="J238" s="3" t="n">
+        <v>6.155</v>
+      </c>
+      <c r="K238" s="3" t="n">
+        <v>1.607</v>
+      </c>
+      <c r="L238" s="3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M238" s="3" t="n"/>
+      <c r="N238" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="O238" s="2" t="inlineStr">
+        <is>
+          <t>longueur2_B0, longueur2_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:58</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>403cbd3 +modifs</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>8. Longueur exacte des faisceaux arretes par le sol (bout des taches rasantes)</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide (--fast)</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F239" s="2" t="inlineStr">
+        <is>
+          <t>sol mouille / public</t>
+        </is>
+      </c>
+      <c r="G239" s="3" t="n">
+        <v>10.135</v>
+      </c>
+      <c r="H239" s="4">
+        <f>IF(G239&gt;0,1000/G239,"")</f>
+        <v/>
+      </c>
+      <c r="I239" s="3" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="J239" s="3" t="n">
+        <v>9.215</v>
+      </c>
+      <c r="K239" s="3" t="n">
+        <v>1.773</v>
+      </c>
+      <c r="L239" s="3" t="n">
+        <v>2.058</v>
+      </c>
+      <c r="M239" s="3" t="n">
+        <v>1.046</v>
+      </c>
+      <c r="N239" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="O239" s="2" t="inlineStr">
+        <is>
+          <t>longueur2_B0, longueur2_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:58</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>403cbd3 +modifs</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>8. Longueur exacte des faisceaux arretes par le sol (bout des taches rasantes)</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide (--fast)</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F240" s="2" t="inlineStr">
+        <is>
+          <t>sol mouille + gobo + prisme 8 / scene</t>
+        </is>
+      </c>
+      <c r="G240" s="3" t="n">
+        <v>22.755</v>
+      </c>
+      <c r="H240" s="4">
+        <f>IF(G240&gt;0,1000/G240,"")</f>
+        <v/>
+      </c>
+      <c r="I240" s="3" t="n">
+        <v>22.225</v>
+      </c>
+      <c r="J240" s="3" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="K240" s="3" t="n">
+        <v>5.387</v>
+      </c>
+      <c r="L240" s="3" t="n">
+        <v>6.576</v>
+      </c>
+      <c r="M240" s="3" t="n">
+        <v>3.983</v>
+      </c>
+      <c r="N240" s="2" t="n">
+        <v>280</v>
+      </c>
+      <c r="O240" s="2" t="inlineStr">
+        <is>
+          <t>longueur2_B0, longueur2_B1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13441,7 +14373,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P37"/>
+  <dimension ref="A1:Q37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -13460,6 +14392,7 @@
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
     <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13550,6 +14483,11 @@
           <t>7e4. Essai v4 : cache recalcule s'il change (RGBA16F), chroma=1</t>
         </is>
       </c>
+      <c r="Q2" s="1" t="inlineStr">
+        <is>
+          <t>8. Longueur exacte des faisceaux arretes par le sol (bout des taches rasantes)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -13617,6 +14555,10 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A3,Mesures!$C:$C,P$2),"")</f>
         <v/>
       </c>
+      <c r="Q3" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A3,Mesures!$C:$C,Q$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -13684,6 +14626,10 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A4,Mesures!$C:$C,P$2),"")</f>
         <v/>
       </c>
+      <c r="Q4" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A4,Mesures!$C:$C,Q$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -13751,6 +14697,10 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A5,Mesures!$C:$C,P$2),"")</f>
         <v/>
       </c>
+      <c r="Q5" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A5,Mesures!$C:$C,Q$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -13818,6 +14768,10 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A6,Mesures!$C:$C,P$2),"")</f>
         <v/>
       </c>
+      <c r="Q6" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A6,Mesures!$C:$C,Q$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -13885,6 +14839,10 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A7,Mesures!$C:$C,P$2),"")</f>
         <v/>
       </c>
+      <c r="Q7" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A7,Mesures!$C:$C,Q$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -13952,6 +14910,10 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A8,Mesures!$C:$C,P$2),"")</f>
         <v/>
       </c>
+      <c r="Q8" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A8,Mesures!$C:$C,Q$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -14019,6 +14981,10 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A9,Mesures!$C:$C,P$2),"")</f>
         <v/>
       </c>
+      <c r="Q9" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A9,Mesures!$C:$C,Q$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -14086,6 +15052,10 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A10,Mesures!$C:$C,P$2),"")</f>
         <v/>
       </c>
+      <c r="Q10" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A10,Mesures!$C:$C,Q$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -14153,6 +15123,10 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A11,Mesures!$C:$C,P$2),"")</f>
         <v/>
       </c>
+      <c r="Q11" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A11,Mesures!$C:$C,Q$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -14220,6 +15194,10 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A12,Mesures!$C:$C,P$2),"")</f>
         <v/>
       </c>
+      <c r="Q12" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A12,Mesures!$C:$C,Q$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -14287,6 +15265,10 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A13,Mesures!$C:$C,P$2),"")</f>
         <v/>
       </c>
+      <c r="Q13" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A13,Mesures!$C:$C,Q$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -14354,6 +15336,10 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A14,Mesures!$C:$C,P$2),"")</f>
         <v/>
       </c>
+      <c r="Q14" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A14,Mesures!$C:$C,Q$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -14421,6 +15407,10 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A15,Mesures!$C:$C,P$2),"")</f>
         <v/>
       </c>
+      <c r="Q15" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A15,Mesures!$C:$C,Q$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -14488,6 +15478,10 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A16,Mesures!$C:$C,P$2),"")</f>
         <v/>
       </c>
+      <c r="Q16" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A16,Mesures!$C:$C,Q$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -14555,6 +15549,10 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A17,Mesures!$C:$C,P$2),"")</f>
         <v/>
       </c>
+      <c r="Q17" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A17,Mesures!$C:$C,Q$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -14622,6 +15620,10 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A18,Mesures!$C:$C,P$2),"")</f>
         <v/>
       </c>
+      <c r="Q18" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A18,Mesures!$C:$C,Q$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -14711,6 +15713,11 @@
           <t>7e4. Essai v4 : cache recalcule s'il change (RGBA16F), chroma=1</t>
         </is>
       </c>
+      <c r="Q21" s="1" t="inlineStr">
+        <is>
+          <t>8. Longueur exacte des faisceaux arretes par le sol (bout des taches rasantes)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -14778,6 +15785,10 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A22,Mesures!$C:$C,P$21),"")</f>
         <v/>
       </c>
+      <c r="Q22" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A22,Mesures!$C:$C,Q$21),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -14845,6 +15856,10 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A23,Mesures!$C:$C,P$21),"")</f>
         <v/>
       </c>
+      <c r="Q23" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A23,Mesures!$C:$C,Q$21),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -14912,6 +15927,10 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A24,Mesures!$C:$C,P$21),"")</f>
         <v/>
       </c>
+      <c r="Q24" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A24,Mesures!$C:$C,Q$21),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -14979,6 +15998,10 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A25,Mesures!$C:$C,P$21),"")</f>
         <v/>
       </c>
+      <c r="Q25" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A25,Mesures!$C:$C,Q$21),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -15046,6 +16069,10 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A26,Mesures!$C:$C,P$21),"")</f>
         <v/>
       </c>
+      <c r="Q26" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A26,Mesures!$C:$C,Q$21),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -15113,6 +16140,10 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A27,Mesures!$C:$C,P$21),"")</f>
         <v/>
       </c>
+      <c r="Q27" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A27,Mesures!$C:$C,Q$21),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -15180,6 +16211,10 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A28,Mesures!$C:$C,P$21),"")</f>
         <v/>
       </c>
+      <c r="Q28" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A28,Mesures!$C:$C,Q$21),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -15247,6 +16282,10 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A29,Mesures!$C:$C,P$21),"")</f>
         <v/>
       </c>
+      <c r="Q29" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A29,Mesures!$C:$C,Q$21),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -15314,6 +16353,10 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A30,Mesures!$C:$C,P$21),"")</f>
         <v/>
       </c>
+      <c r="Q30" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A30,Mesures!$C:$C,Q$21),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -15381,6 +16424,10 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A31,Mesures!$C:$C,P$21),"")</f>
         <v/>
       </c>
+      <c r="Q31" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A31,Mesures!$C:$C,Q$21),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -15448,6 +16495,10 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A32,Mesures!$C:$C,P$21),"")</f>
         <v/>
       </c>
+      <c r="Q32" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A32,Mesures!$C:$C,Q$21),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -15515,6 +16566,10 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A33,Mesures!$C:$C,P$21),"")</f>
         <v/>
       </c>
+      <c r="Q33" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A33,Mesures!$C:$C,Q$21),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -15582,6 +16637,10 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A34,Mesures!$C:$C,P$21),"")</f>
         <v/>
       </c>
+      <c r="Q34" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A34,Mesures!$C:$C,Q$21),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -15649,6 +16708,10 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A35,Mesures!$C:$C,P$21),"")</f>
         <v/>
       </c>
+      <c r="Q35" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A35,Mesures!$C:$C,Q$21),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -15716,6 +16779,10 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A36,Mesures!$C:$C,P$21),"")</f>
         <v/>
       </c>
+      <c r="Q36" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A36,Mesures!$C:$C,Q$21),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -15781,6 +16848,10 @@
       </c>
       <c r="P37" s="3">
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A37,Mesures!$C:$C,P$21),"")</f>
+        <v/>
+      </c>
+      <c r="Q37" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A37,Mesures!$C:$C,Q$21),"")</f>
         <v/>
       </c>
     </row>

--- a/lyre-viz/historique_perf.xlsx
+++ b/lyre-viz/historique_perf.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O240"/>
+  <dimension ref="A1:O277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -14362,6 +14362,2198 @@
         </is>
       </c>
     </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:37</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>f23a476+modifs</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>9a. Eau au sol : creux, flaques nettes, variante seche du shader</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide (cas 15-16 : eau 0,8)</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F241" s="2" t="inlineStr">
+        <is>
+          <t>defaut / public</t>
+        </is>
+      </c>
+      <c r="G241" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="H241" s="4">
+        <f>IF(G241&gt;0,1000/G241,"")</f>
+        <v/>
+      </c>
+      <c r="I241" s="3" t="n">
+        <v>7.435</v>
+      </c>
+      <c r="J241" s="3" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="K241" s="3" t="n">
+        <v>1.631</v>
+      </c>
+      <c r="L241" s="3" t="n">
+        <v>1.988</v>
+      </c>
+      <c r="M241" s="3" t="n"/>
+      <c r="N241" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="O241" s="2" t="inlineStr">
+        <is>
+          <t>eau2_B0, eau2_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:37</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>f23a476+modifs</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>9a. Eau au sol : creux, flaques nettes, variante seche du shader</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide (cas 15-16 : eau 0,8)</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F242" s="2" t="inlineStr">
+        <is>
+          <t>defaut / scene</t>
+        </is>
+      </c>
+      <c r="G242" s="3" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="H242" s="4">
+        <f>IF(G242&gt;0,1000/G242,"")</f>
+        <v/>
+      </c>
+      <c r="I242" s="3" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="J242" s="3" t="n">
+        <v>6.865</v>
+      </c>
+      <c r="K242" s="3" t="n">
+        <v>1.579</v>
+      </c>
+      <c r="L242" s="3" t="n">
+        <v>1.954</v>
+      </c>
+      <c r="M242" s="3" t="n"/>
+      <c r="N242" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="O242" s="2" t="inlineStr">
+        <is>
+          <t>eau2_B0, eau2_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:37</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>f23a476+modifs</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>9a. Eau au sol : creux, flaques nettes, variante seche du shader</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide (cas 15-16 : eau 0,8)</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F243" s="2" t="inlineStr">
+        <is>
+          <t>defaut / sous les trusses</t>
+        </is>
+      </c>
+      <c r="G243" s="3" t="n">
+        <v>8.074999999999999</v>
+      </c>
+      <c r="H243" s="4">
+        <f>IF(G243&gt;0,1000/G243,"")</f>
+        <v/>
+      </c>
+      <c r="I243" s="3" t="n">
+        <v>6.475</v>
+      </c>
+      <c r="J243" s="3" t="n">
+        <v>6.125</v>
+      </c>
+      <c r="K243" s="3" t="n">
+        <v>1.131</v>
+      </c>
+      <c r="L243" s="3" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="M243" s="3" t="n"/>
+      <c r="N243" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="O243" s="2" t="inlineStr">
+        <is>
+          <t>eau2_B0, eau2_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:37</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>f23a476+modifs</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>9a. Eau au sol : creux, flaques nettes, variante seche du shader</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide (cas 15-16 : eau 0,8)</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F244" s="2" t="inlineStr">
+        <is>
+          <t>gobo + prisme 8 + zoom 25 / public</t>
+        </is>
+      </c>
+      <c r="G244" s="3" t="n">
+        <v>20.835</v>
+      </c>
+      <c r="H244" s="4">
+        <f>IF(G244&gt;0,1000/G244,"")</f>
+        <v/>
+      </c>
+      <c r="I244" s="3" t="n">
+        <v>19.575</v>
+      </c>
+      <c r="J244" s="3" t="n">
+        <v>19.57</v>
+      </c>
+      <c r="K244" s="3" t="n">
+        <v>7.428</v>
+      </c>
+      <c r="L244" s="3" t="n">
+        <v>6.918</v>
+      </c>
+      <c r="M244" s="3" t="n"/>
+      <c r="N244" s="2" t="n">
+        <v>280</v>
+      </c>
+      <c r="O244" s="2" t="inlineStr">
+        <is>
+          <t>eau2_B0, eau2_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:37</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>f23a476+modifs</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>9a. Eau au sol : creux, flaques nettes, variante seche du shader</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide (cas 15-16 : eau 0,8)</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F245" s="2" t="inlineStr">
+        <is>
+          <t>gobo + prisme 8 + zoom 25 / scene</t>
+        </is>
+      </c>
+      <c r="G245" s="3" t="n">
+        <v>19.185</v>
+      </c>
+      <c r="H245" s="4">
+        <f>IF(G245&gt;0,1000/G245,"")</f>
+        <v/>
+      </c>
+      <c r="I245" s="3" t="n">
+        <v>18.005</v>
+      </c>
+      <c r="J245" s="3" t="n">
+        <v>17.835</v>
+      </c>
+      <c r="K245" s="3" t="n">
+        <v>5.706</v>
+      </c>
+      <c r="L245" s="3" t="n">
+        <v>6.345</v>
+      </c>
+      <c r="M245" s="3" t="n"/>
+      <c r="N245" s="2" t="n">
+        <v>280</v>
+      </c>
+      <c r="O245" s="2" t="inlineStr">
+        <is>
+          <t>eau2_B0, eau2_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:37</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>f23a476+modifs</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>9a. Eau au sol : creux, flaques nettes, variante seche du shader</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide (cas 15-16 : eau 0,8)</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F246" s="2" t="inlineStr">
+        <is>
+          <t>gobo + prisme 8 + zoom 25 / sous les trusses</t>
+        </is>
+      </c>
+      <c r="G246" s="3" t="n">
+        <v>14.61</v>
+      </c>
+      <c r="H246" s="4">
+        <f>IF(G246&gt;0,1000/G246,"")</f>
+        <v/>
+      </c>
+      <c r="I246" s="3" t="n">
+        <v>13.64</v>
+      </c>
+      <c r="J246" s="3" t="n">
+        <v>13.97</v>
+      </c>
+      <c r="K246" s="3" t="n">
+        <v>3.371</v>
+      </c>
+      <c r="L246" s="3" t="n">
+        <v>3.962</v>
+      </c>
+      <c r="M246" s="3" t="n"/>
+      <c r="N246" s="2" t="n">
+        <v>280</v>
+      </c>
+      <c r="O246" s="2" t="inlineStr">
+        <is>
+          <t>eau2_B0, eau2_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:37</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>f23a476+modifs</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>9a. Eau au sol : creux, flaques nettes, variante seche du shader</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide (cas 15-16 : eau 0,8)</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F247" s="2" t="inlineStr">
+        <is>
+          <t>zoom 45 + frost 0.6 / public</t>
+        </is>
+      </c>
+      <c r="G247" s="3" t="n">
+        <v>12.575</v>
+      </c>
+      <c r="H247" s="4">
+        <f>IF(G247&gt;0,1000/G247,"")</f>
+        <v/>
+      </c>
+      <c r="I247" s="3" t="n">
+        <v>11.245</v>
+      </c>
+      <c r="J247" s="3" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="K247" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L247" s="3" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="M247" s="3" t="n"/>
+      <c r="N247" s="2" t="n">
+        <v>887</v>
+      </c>
+      <c r="O247" s="2" t="inlineStr">
+        <is>
+          <t>eau2_B0, eau2_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:37</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>f23a476+modifs</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>9a. Eau au sol : creux, flaques nettes, variante seche du shader</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide (cas 15-16 : eau 0,8)</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F248" s="2" t="inlineStr">
+        <is>
+          <t>zoom 45 + frost 0.6 / scene</t>
+        </is>
+      </c>
+      <c r="G248" s="3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H248" s="4">
+        <f>IF(G248&gt;0,1000/G248,"")</f>
+        <v/>
+      </c>
+      <c r="I248" s="3" t="n">
+        <v>10.98</v>
+      </c>
+      <c r="J248" s="3" t="n">
+        <v>10.115</v>
+      </c>
+      <c r="K248" s="3" t="n">
+        <v>2.965</v>
+      </c>
+      <c r="L248" s="3" t="n">
+        <v>4.127</v>
+      </c>
+      <c r="M248" s="3" t="n"/>
+      <c r="N248" s="2" t="n">
+        <v>887</v>
+      </c>
+      <c r="O248" s="2" t="inlineStr">
+        <is>
+          <t>eau2_B0, eau2_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:37</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>f23a476+modifs</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>9a. Eau au sol : creux, flaques nettes, variante seche du shader</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide (cas 15-16 : eau 0,8)</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F249" s="2" t="inlineStr">
+        <is>
+          <t>zoom 45 + frost 0.6 / sous les trusses</t>
+        </is>
+      </c>
+      <c r="G249" s="3" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="H249" s="4">
+        <f>IF(G249&gt;0,1000/G249,"")</f>
+        <v/>
+      </c>
+      <c r="I249" s="3" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="J249" s="3" t="n">
+        <v>7.685</v>
+      </c>
+      <c r="K249" s="3" t="n">
+        <v>1.527</v>
+      </c>
+      <c r="L249" s="3" t="n">
+        <v>3.239</v>
+      </c>
+      <c r="M249" s="3" t="n"/>
+      <c r="N249" s="2" t="n">
+        <v>887</v>
+      </c>
+      <c r="O249" s="2" t="inlineStr">
+        <is>
+          <t>eau2_B0, eau2_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:37</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>f23a476+modifs</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>9a. Eau au sol : creux, flaques nettes, variante seche du shader</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide (cas 15-16 : eau 0,8)</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F250" s="2" t="inlineStr">
+        <is>
+          <t>sans rebonds (GI)</t>
+        </is>
+      </c>
+      <c r="G250" s="3" t="n">
+        <v>7.805</v>
+      </c>
+      <c r="H250" s="4">
+        <f>IF(G250&gt;0,1000/G250,"")</f>
+        <v/>
+      </c>
+      <c r="I250" s="3" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="J250" s="3" t="n">
+        <v>5.915</v>
+      </c>
+      <c r="K250" s="3" t="n">
+        <v>1.406</v>
+      </c>
+      <c r="L250" s="3" t="n">
+        <v>1.526</v>
+      </c>
+      <c r="M250" s="3" t="n"/>
+      <c r="N250" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="O250" s="2" t="inlineStr">
+        <is>
+          <t>eau2_B0, eau2_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:37</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>f23a476+modifs</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>9a. Eau au sol : creux, flaques nettes, variante seche du shader</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide (cas 15-16 : eau 0,8)</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F251" s="2" t="inlineStr">
+        <is>
+          <t>sans fumee volumetrique</t>
+        </is>
+      </c>
+      <c r="G251" s="3" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="H251" s="4">
+        <f>IF(G251&gt;0,1000/G251,"")</f>
+        <v/>
+      </c>
+      <c r="I251" s="3" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="J251" s="3" t="n">
+        <v>3.215</v>
+      </c>
+      <c r="K251" s="3" t="n">
+        <v>1.663</v>
+      </c>
+      <c r="L251" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M251" s="3" t="n"/>
+      <c r="N251" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="O251" s="2" t="inlineStr">
+        <is>
+          <t>eau2_B0, eau2_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:37</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>f23a476+modifs</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>9a. Eau au sol : creux, flaques nettes, variante seche du shader</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide (cas 15-16 : eau 0,8)</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F252" s="2" t="inlineStr">
+        <is>
+          <t>sans taches sur surfaces</t>
+        </is>
+      </c>
+      <c r="G252" s="3" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="H252" s="4">
+        <f>IF(G252&gt;0,1000/G252,"")</f>
+        <v/>
+      </c>
+      <c r="I252" s="3" t="n">
+        <v>6.585</v>
+      </c>
+      <c r="J252" s="3" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="K252" s="3" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="L252" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M252" s="3" t="n"/>
+      <c r="N252" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="O252" s="2" t="inlineStr">
+        <is>
+          <t>eau2_B0, eau2_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:37</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>f23a476+modifs</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>9a. Eau au sol : creux, flaques nettes, variante seche du shader</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide (cas 15-16 : eau 0,8)</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F253" s="2" t="inlineStr">
+        <is>
+          <t>sans reflets</t>
+        </is>
+      </c>
+      <c r="G253" s="3" t="n">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="H253" s="4">
+        <f>IF(G253&gt;0,1000/G253,"")</f>
+        <v/>
+      </c>
+      <c r="I253" s="3" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="J253" s="3" t="n">
+        <v>7.625</v>
+      </c>
+      <c r="K253" s="3" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="L253" s="3" t="n">
+        <v>2.005</v>
+      </c>
+      <c r="M253" s="3" t="n"/>
+      <c r="N253" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="O253" s="2" t="inlineStr">
+        <is>
+          <t>eau2_B0, eau2_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:37</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>f23a476+modifs</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>9a. Eau au sol : creux, flaques nettes, variante seche du shader</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide (cas 15-16 : eau 0,8)</t>
+        </is>
+      </c>
+      <c r="E254" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F254" s="2" t="inlineStr">
+        <is>
+          <t>sans bloom</t>
+        </is>
+      </c>
+      <c r="G254" s="3" t="n">
+        <v>8.025</v>
+      </c>
+      <c r="H254" s="4">
+        <f>IF(G254&gt;0,1000/G254,"")</f>
+        <v/>
+      </c>
+      <c r="I254" s="3" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="J254" s="3" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="K254" s="3" t="n">
+        <v>1.629</v>
+      </c>
+      <c r="L254" s="3" t="n">
+        <v>1.977</v>
+      </c>
+      <c r="M254" s="3" t="n"/>
+      <c r="N254" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="O254" s="2" t="inlineStr">
+        <is>
+          <t>eau2_B0, eau2_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:37</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>f23a476+modifs</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>9a. Eau au sol : creux, flaques nettes, variante seche du shader</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide (cas 15-16 : eau 0,8)</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F255" s="2" t="inlineStr">
+        <is>
+          <t>sol mouille / public</t>
+        </is>
+      </c>
+      <c r="G255" s="3" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="H255" s="4">
+        <f>IF(G255&gt;0,1000/G255,"")</f>
+        <v/>
+      </c>
+      <c r="I255" s="3" t="n">
+        <v>9.515000000000001</v>
+      </c>
+      <c r="J255" s="3" t="n">
+        <v>9.205</v>
+      </c>
+      <c r="K255" s="3" t="n">
+        <v>2.049</v>
+      </c>
+      <c r="L255" s="3" t="n">
+        <v>2.061</v>
+      </c>
+      <c r="M255" s="3" t="n">
+        <v>0.9389999999999999</v>
+      </c>
+      <c r="N255" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="O255" s="2" t="inlineStr">
+        <is>
+          <t>eau2_B0, eau2_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:37</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>f23a476+modifs</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>9a. Eau au sol : creux, flaques nettes, variante seche du shader</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide (cas 15-16 : eau 0,8)</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F256" s="2" t="inlineStr">
+        <is>
+          <t>sol mouille + gobo + prisme 8 / scene</t>
+        </is>
+      </c>
+      <c r="G256" s="3" t="n">
+        <v>24.49</v>
+      </c>
+      <c r="H256" s="4">
+        <f>IF(G256&gt;0,1000/G256,"")</f>
+        <v/>
+      </c>
+      <c r="I256" s="3" t="n">
+        <v>23.765</v>
+      </c>
+      <c r="J256" s="3" t="n">
+        <v>23.545</v>
+      </c>
+      <c r="K256" s="3" t="n">
+        <v>6.349</v>
+      </c>
+      <c r="L256" s="3" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="M256" s="3" t="n">
+        <v>4.784</v>
+      </c>
+      <c r="N256" s="2" t="n">
+        <v>280</v>
+      </c>
+      <c r="O256" s="2" t="inlineStr">
+        <is>
+          <t>eau2_B0, eau2_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:37</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>f23a476+modifs</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>9b. Eau au sol a 10 %</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide, wet=0.1, 3 cas</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F257" s="2" t="inlineStr">
+        <is>
+          <t>defaut / public</t>
+        </is>
+      </c>
+      <c r="G257" s="3" t="n">
+        <v>10.335</v>
+      </c>
+      <c r="H257" s="4">
+        <f>IF(G257&gt;0,1000/G257,"")</f>
+        <v/>
+      </c>
+      <c r="I257" s="3" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="J257" s="3" t="n">
+        <v>9.205</v>
+      </c>
+      <c r="K257" s="3" t="n">
+        <v>1.978</v>
+      </c>
+      <c r="L257" s="3" t="n">
+        <v>1.968</v>
+      </c>
+      <c r="M257" s="3" t="n">
+        <v>0.903</v>
+      </c>
+      <c r="N257" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="O257" s="2" t="inlineStr">
+        <is>
+          <t>eau2_10_B0, eau2_10_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:37</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>f23a476+modifs</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>9b. Eau au sol a 10 %</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide, wet=0.1, 3 cas</t>
+        </is>
+      </c>
+      <c r="E258" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F258" s="2" t="inlineStr">
+        <is>
+          <t>gobo + prisme 8 + zoom 25 / public</t>
+        </is>
+      </c>
+      <c r="G258" s="3" t="n">
+        <v>26.38</v>
+      </c>
+      <c r="H258" s="4">
+        <f>IF(G258&gt;0,1000/G258,"")</f>
+        <v/>
+      </c>
+      <c r="I258" s="3" t="n">
+        <v>25.65</v>
+      </c>
+      <c r="J258" s="3" t="n">
+        <v>25.275</v>
+      </c>
+      <c r="K258" s="3" t="n">
+        <v>7.163</v>
+      </c>
+      <c r="L258" s="3" t="n">
+        <v>6.729</v>
+      </c>
+      <c r="M258" s="3" t="n">
+        <v>5.549</v>
+      </c>
+      <c r="N258" s="2" t="n">
+        <v>280</v>
+      </c>
+      <c r="O258" s="2" t="inlineStr">
+        <is>
+          <t>eau2_10_B0, eau2_10_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:37</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>f23a476+modifs</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>9b. Eau au sol a 10 %</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide, wet=0.1, 3 cas</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F259" s="2" t="inlineStr">
+        <is>
+          <t>zoom 45 + frost 0.6 / public</t>
+        </is>
+      </c>
+      <c r="G259" s="3" t="n">
+        <v>23.265</v>
+      </c>
+      <c r="H259" s="4">
+        <f>IF(G259&gt;0,1000/G259,"")</f>
+        <v/>
+      </c>
+      <c r="I259" s="3" t="n">
+        <v>21.995</v>
+      </c>
+      <c r="J259" s="3" t="n">
+        <v>21.65</v>
+      </c>
+      <c r="K259" s="3" t="n">
+        <v>3.192</v>
+      </c>
+      <c r="L259" s="3" t="n">
+        <v>3.938</v>
+      </c>
+      <c r="M259" s="3" t="n">
+        <v>10.626</v>
+      </c>
+      <c r="N259" s="2" t="n">
+        <v>887</v>
+      </c>
+      <c r="O259" s="2" t="inlineStr">
+        <is>
+          <t>eau2_10_B0, eau2_10_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:37</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>f23a476+modifs</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>9e. Essai : creux en trilineaire (abandonne)</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide, wet=0.3, 3 cas</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t>defaut / public</t>
+        </is>
+      </c>
+      <c r="G260" s="3" t="n">
+        <v>10.443</v>
+      </c>
+      <c r="H260" s="4">
+        <f>IF(G260&gt;0,1000/G260,"")</f>
+        <v/>
+      </c>
+      <c r="I260" s="3" t="n">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="J260" s="3" t="n">
+        <v>9.167</v>
+      </c>
+      <c r="K260" s="3" t="n">
+        <v>1.981</v>
+      </c>
+      <c r="L260" s="3" t="n">
+        <v>1.977</v>
+      </c>
+      <c r="M260" s="3" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="N260" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="O260" s="2" t="inlineStr">
+        <is>
+          <t>eau3_B0, eau3_B1, eau3_B2</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:37</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>f23a476+modifs</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>9e. Essai : creux en trilineaire (abandonne)</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide, wet=0.3, 3 cas</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F261" s="2" t="inlineStr">
+        <is>
+          <t>gobo + prisme 8 + zoom 25 / public</t>
+        </is>
+      </c>
+      <c r="G261" s="3" t="n">
+        <v>25.493</v>
+      </c>
+      <c r="H261" s="4">
+        <f>IF(G261&gt;0,1000/G261,"")</f>
+        <v/>
+      </c>
+      <c r="I261" s="3" t="n">
+        <v>24.817</v>
+      </c>
+      <c r="J261" s="3" t="n">
+        <v>24.72</v>
+      </c>
+      <c r="K261" s="3" t="n">
+        <v>7.241</v>
+      </c>
+      <c r="L261" s="3" t="n">
+        <v>6.729</v>
+      </c>
+      <c r="M261" s="3" t="n">
+        <v>5.336</v>
+      </c>
+      <c r="N261" s="2" t="n">
+        <v>280</v>
+      </c>
+      <c r="O261" s="2" t="inlineStr">
+        <is>
+          <t>eau3_B0, eau3_B1, eau3_B2</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:37</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>f23a476+modifs</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>9e. Essai : creux en trilineaire (abandonne)</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide, wet=0.3, 3 cas</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F262" s="2" t="inlineStr">
+        <is>
+          <t>zoom 45 + frost 0.6 / public</t>
+        </is>
+      </c>
+      <c r="G262" s="3" t="n">
+        <v>22.373</v>
+      </c>
+      <c r="H262" s="4">
+        <f>IF(G262&gt;0,1000/G262,"")</f>
+        <v/>
+      </c>
+      <c r="I262" s="3" t="n">
+        <v>21.39</v>
+      </c>
+      <c r="J262" s="3" t="n">
+        <v>21.117</v>
+      </c>
+      <c r="K262" s="3" t="n">
+        <v>3.085</v>
+      </c>
+      <c r="L262" s="3" t="n">
+        <v>3.904</v>
+      </c>
+      <c r="M262" s="3" t="n">
+        <v>10.149</v>
+      </c>
+      <c r="N262" s="2" t="n">
+        <v>887</v>
+      </c>
+      <c r="O262" s="2" t="inlineStr">
+        <is>
+          <t>eau3_B0, eau3_B1, eau3_B2</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:55</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>f23a476+modifs</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>10a. Reflet seulement dans l'eau (masque par blocs), eau 0,1</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide, wet=0.1, 3 cas</t>
+        </is>
+      </c>
+      <c r="E263" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F263" s="2" t="inlineStr">
+        <is>
+          <t>defaut / public</t>
+        </is>
+      </c>
+      <c r="G263" s="3" t="n">
+        <v>10.435</v>
+      </c>
+      <c r="H263" s="4">
+        <f>IF(G263&gt;0,1000/G263,"")</f>
+        <v/>
+      </c>
+      <c r="I263" s="3" t="n">
+        <v>9.335000000000001</v>
+      </c>
+      <c r="J263" s="3" t="n">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="K263" s="3" t="n">
+        <v>1.974</v>
+      </c>
+      <c r="L263" s="3" t="n">
+        <v>2.058</v>
+      </c>
+      <c r="M263" s="3" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="N263" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="O263" s="2" t="inlineStr">
+        <is>
+          <t>masque_w01_B0, masque_w01_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:55</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>f23a476+modifs</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>10a. Reflet seulement dans l'eau (masque par blocs), eau 0,1</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide, wet=0.1, 3 cas</t>
+        </is>
+      </c>
+      <c r="E264" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F264" s="2" t="inlineStr">
+        <is>
+          <t>gobo + prisme 8 + zoom 25 / public</t>
+        </is>
+      </c>
+      <c r="G264" s="3" t="n">
+        <v>24.45</v>
+      </c>
+      <c r="H264" s="4">
+        <f>IF(G264&gt;0,1000/G264,"")</f>
+        <v/>
+      </c>
+      <c r="I264" s="3" t="n">
+        <v>23.745</v>
+      </c>
+      <c r="J264" s="3" t="n">
+        <v>23.73</v>
+      </c>
+      <c r="K264" s="3" t="n">
+        <v>7.047</v>
+      </c>
+      <c r="L264" s="3" t="n">
+        <v>6.708</v>
+      </c>
+      <c r="M264" s="3" t="n">
+        <v>4.266</v>
+      </c>
+      <c r="N264" s="2" t="n">
+        <v>280</v>
+      </c>
+      <c r="O264" s="2" t="inlineStr">
+        <is>
+          <t>masque_w01_B0, masque_w01_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:55</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>f23a476+modifs</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>10a. Reflet seulement dans l'eau (masque par blocs), eau 0,1</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide, wet=0.1, 3 cas</t>
+        </is>
+      </c>
+      <c r="E265" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F265" s="2" t="inlineStr">
+        <is>
+          <t>zoom 45 + frost 0.6 / public</t>
+        </is>
+      </c>
+      <c r="G265" s="3" t="n">
+        <v>17.98</v>
+      </c>
+      <c r="H265" s="4">
+        <f>IF(G265&gt;0,1000/G265,"")</f>
+        <v/>
+      </c>
+      <c r="I265" s="3" t="n">
+        <v>17.035</v>
+      </c>
+      <c r="J265" s="3" t="n">
+        <v>17.245</v>
+      </c>
+      <c r="K265" s="3" t="n">
+        <v>3.214</v>
+      </c>
+      <c r="L265" s="3" t="n">
+        <v>4.069</v>
+      </c>
+      <c r="M265" s="3" t="n">
+        <v>5.796</v>
+      </c>
+      <c r="N265" s="2" t="n">
+        <v>887</v>
+      </c>
+      <c r="O265" s="2" t="inlineStr">
+        <is>
+          <t>masque_w01_B0, masque_w01_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:55</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>f23a476+modifs</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>10b. Reflet seulement dans l'eau, eau 0,3</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide, wet=0.3, 3 cas</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F266" s="2" t="inlineStr">
+        <is>
+          <t>defaut / public</t>
+        </is>
+      </c>
+      <c r="G266" s="3" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="H266" s="4">
+        <f>IF(G266&gt;0,1000/G266,"")</f>
+        <v/>
+      </c>
+      <c r="I266" s="3" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="J266" s="3" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="K266" s="3" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="L266" s="3" t="n">
+        <v>2.033</v>
+      </c>
+      <c r="M266" s="3" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="N266" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="O266" s="2" t="inlineStr">
+        <is>
+          <t>masque30d_B0, masque30d_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:55</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>f23a476+modifs</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>10b. Reflet seulement dans l'eau, eau 0,3</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide, wet=0.3, 3 cas</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F267" s="2" t="inlineStr">
+        <is>
+          <t>gobo + prisme 8 + zoom 25 / public</t>
+        </is>
+      </c>
+      <c r="G267" s="3" t="n">
+        <v>24.965</v>
+      </c>
+      <c r="H267" s="4">
+        <f>IF(G267&gt;0,1000/G267,"")</f>
+        <v/>
+      </c>
+      <c r="I267" s="3" t="n">
+        <v>24.46</v>
+      </c>
+      <c r="J267" s="3" t="n">
+        <v>24.39</v>
+      </c>
+      <c r="K267" s="3" t="n">
+        <v>7.035</v>
+      </c>
+      <c r="L267" s="3" t="n">
+        <v>6.774</v>
+      </c>
+      <c r="M267" s="3" t="n">
+        <v>5.058</v>
+      </c>
+      <c r="N267" s="2" t="n">
+        <v>280</v>
+      </c>
+      <c r="O267" s="2" t="inlineStr">
+        <is>
+          <t>masque30d_B0, masque30d_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:55</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>f23a476+modifs</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>10b. Reflet seulement dans l'eau, eau 0,3</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide, wet=0.3, 3 cas</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F268" s="2" t="inlineStr">
+        <is>
+          <t>zoom 45 + frost 0.6 / public</t>
+        </is>
+      </c>
+      <c r="G268" s="3" t="n">
+        <v>20.31</v>
+      </c>
+      <c r="H268" s="4">
+        <f>IF(G268&gt;0,1000/G268,"")</f>
+        <v/>
+      </c>
+      <c r="I268" s="3" t="n">
+        <v>19.29</v>
+      </c>
+      <c r="J268" s="3" t="n">
+        <v>19.255</v>
+      </c>
+      <c r="K268" s="3" t="n">
+        <v>3.122</v>
+      </c>
+      <c r="L268" s="3" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="M268" s="3" t="n">
+        <v>8.183</v>
+      </c>
+      <c r="N268" s="2" t="n">
+        <v>887</v>
+      </c>
+      <c r="O268" s="2" t="inlineStr">
+        <is>
+          <t>masque30d_B0, masque30d_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:55</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>f23a476+modifs</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>10c. Reflet seulement dans l'eau, eau 1</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide, wet=1, 3 cas</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F269" s="2" t="inlineStr">
+        <is>
+          <t>defaut / public</t>
+        </is>
+      </c>
+      <c r="G269" s="3" t="n">
+        <v>10.545</v>
+      </c>
+      <c r="H269" s="4">
+        <f>IF(G269&gt;0,1000/G269,"")</f>
+        <v/>
+      </c>
+      <c r="I269" s="3" t="n">
+        <v>9.395</v>
+      </c>
+      <c r="J269" s="3" t="n">
+        <v>8.895</v>
+      </c>
+      <c r="K269" s="3" t="n">
+        <v>1.987</v>
+      </c>
+      <c r="L269" s="3" t="n">
+        <v>2.047</v>
+      </c>
+      <c r="M269" s="3" t="n">
+        <v>1.036</v>
+      </c>
+      <c r="N269" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="O269" s="2" t="inlineStr">
+        <is>
+          <t>masque_w1_B0, masque_w1_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:55</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>f23a476+modifs</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>10c. Reflet seulement dans l'eau, eau 1</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide, wet=1, 3 cas</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F270" s="2" t="inlineStr">
+        <is>
+          <t>gobo + prisme 8 + zoom 25 / public</t>
+        </is>
+      </c>
+      <c r="G270" s="3" t="n">
+        <v>24.72</v>
+      </c>
+      <c r="H270" s="4">
+        <f>IF(G270&gt;0,1000/G270,"")</f>
+        <v/>
+      </c>
+      <c r="I270" s="3" t="n">
+        <v>24.025</v>
+      </c>
+      <c r="J270" s="3" t="n">
+        <v>23.955</v>
+      </c>
+      <c r="K270" s="3" t="n">
+        <v>6.742</v>
+      </c>
+      <c r="L270" s="3" t="n">
+        <v>6.862</v>
+      </c>
+      <c r="M270" s="3" t="n">
+        <v>4.739</v>
+      </c>
+      <c r="N270" s="2" t="n">
+        <v>280</v>
+      </c>
+      <c r="O270" s="2" t="inlineStr">
+        <is>
+          <t>masque_w1_B0, masque_w1_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:55</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>f23a476+modifs</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>10c. Reflet seulement dans l'eau, eau 1</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide, wet=1, 3 cas</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F271" s="2" t="inlineStr">
+        <is>
+          <t>zoom 45 + frost 0.6 / public</t>
+        </is>
+      </c>
+      <c r="G271" s="3" t="n">
+        <v>22.225</v>
+      </c>
+      <c r="H271" s="4">
+        <f>IF(G271&gt;0,1000/G271,"")</f>
+        <v/>
+      </c>
+      <c r="I271" s="3" t="n">
+        <v>21.025</v>
+      </c>
+      <c r="J271" s="3" t="n">
+        <v>20.725</v>
+      </c>
+      <c r="K271" s="3" t="n">
+        <v>3.311</v>
+      </c>
+      <c r="L271" s="3" t="n">
+        <v>4.068</v>
+      </c>
+      <c r="M271" s="3" t="n">
+        <v>9.781000000000001</v>
+      </c>
+      <c r="N271" s="2" t="n">
+        <v>887</v>
+      </c>
+      <c r="O271" s="2" t="inlineStr">
+        <is>
+          <t>masque_w1_B0, masque_w1_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:55</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>f23a476+modifs</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>10e1. Essai masque : 1 point par pixel du miroir (creux manques)</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide, wet=0.3, 3 cas</t>
+        </is>
+      </c>
+      <c r="E272" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F272" s="2" t="inlineStr">
+        <is>
+          <t>defaut / public</t>
+        </is>
+      </c>
+      <c r="G272" s="3" t="n">
+        <v>10.185</v>
+      </c>
+      <c r="H272" s="4">
+        <f>IF(G272&gt;0,1000/G272,"")</f>
+        <v/>
+      </c>
+      <c r="I272" s="3" t="n">
+        <v>8.275</v>
+      </c>
+      <c r="J272" s="3" t="n">
+        <v>7.925</v>
+      </c>
+      <c r="K272" s="3" t="n">
+        <v>1.976</v>
+      </c>
+      <c r="L272" s="3" t="n">
+        <v>2.026</v>
+      </c>
+      <c r="M272" s="3" t="n">
+        <v>0.706</v>
+      </c>
+      <c r="N272" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="O272" s="2" t="inlineStr">
+        <is>
+          <t>masque30_B0, masque30_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:55</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>f23a476+modifs</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t>10e1. Essai masque : 1 point par pixel du miroir (creux manques)</t>
+        </is>
+      </c>
+      <c r="D273" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide, wet=0.3, 3 cas</t>
+        </is>
+      </c>
+      <c r="E273" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F273" s="2" t="inlineStr">
+        <is>
+          <t>gobo + prisme 8 + zoom 25 / public</t>
+        </is>
+      </c>
+      <c r="G273" s="3" t="n">
+        <v>22.795</v>
+      </c>
+      <c r="H273" s="4">
+        <f>IF(G273&gt;0,1000/G273,"")</f>
+        <v/>
+      </c>
+      <c r="I273" s="3" t="n">
+        <v>22.29</v>
+      </c>
+      <c r="J273" s="3" t="n">
+        <v>22.145</v>
+      </c>
+      <c r="K273" s="3" t="n">
+        <v>6.997</v>
+      </c>
+      <c r="L273" s="3" t="n">
+        <v>6.96</v>
+      </c>
+      <c r="M273" s="3" t="n">
+        <v>3.037</v>
+      </c>
+      <c r="N273" s="2" t="n">
+        <v>280</v>
+      </c>
+      <c r="O273" s="2" t="inlineStr">
+        <is>
+          <t>masque30_B0, masque30_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:55</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>f23a476+modifs</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>10e1. Essai masque : 1 point par pixel du miroir (creux manques)</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide, wet=0.3, 3 cas</t>
+        </is>
+      </c>
+      <c r="E274" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F274" s="2" t="inlineStr">
+        <is>
+          <t>zoom 45 + frost 0.6 / public</t>
+        </is>
+      </c>
+      <c r="G274" s="3" t="n">
+        <v>17.785</v>
+      </c>
+      <c r="H274" s="4">
+        <f>IF(G274&gt;0,1000/G274,"")</f>
+        <v/>
+      </c>
+      <c r="I274" s="3" t="n">
+        <v>17.11</v>
+      </c>
+      <c r="J274" s="3" t="n">
+        <v>16.58</v>
+      </c>
+      <c r="K274" s="3" t="n">
+        <v>3.274</v>
+      </c>
+      <c r="L274" s="3" t="n">
+        <v>4.053</v>
+      </c>
+      <c r="M274" s="3" t="n">
+        <v>6.131</v>
+      </c>
+      <c r="N274" s="2" t="n">
+        <v>887</v>
+      </c>
+      <c r="O274" s="2" t="inlineStr">
+        <is>
+          <t>masque30_B0, masque30_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:55</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="inlineStr">
+        <is>
+          <t>f23a476+modifs</t>
+        </is>
+      </c>
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t>10e3. Essai masque : faisceaux seulement dans les flaques (pores plus sombres)</t>
+        </is>
+      </c>
+      <c r="D275" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide, wet=0.3, 3 cas</t>
+        </is>
+      </c>
+      <c r="E275" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F275" s="2" t="inlineStr">
+        <is>
+          <t>defaut / public</t>
+        </is>
+      </c>
+      <c r="G275" s="3" t="n">
+        <v>10.52</v>
+      </c>
+      <c r="H275" s="4">
+        <f>IF(G275&gt;0,1000/G275,"")</f>
+        <v/>
+      </c>
+      <c r="I275" s="3" t="n">
+        <v>9.07</v>
+      </c>
+      <c r="J275" s="3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="K275" s="3" t="n">
+        <v>1.969</v>
+      </c>
+      <c r="L275" s="3" t="n">
+        <v>2.051</v>
+      </c>
+      <c r="M275" s="3" t="n">
+        <v>0.783</v>
+      </c>
+      <c r="N275" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="O275" s="2" t="inlineStr">
+        <is>
+          <t>masque30c_B0, masque30c_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:55</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>f23a476+modifs</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>10e3. Essai masque : faisceaux seulement dans les flaques (pores plus sombres)</t>
+        </is>
+      </c>
+      <c r="D276" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide, wet=0.3, 3 cas</t>
+        </is>
+      </c>
+      <c r="E276" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F276" s="2" t="inlineStr">
+        <is>
+          <t>gobo + prisme 8 + zoom 25 / public</t>
+        </is>
+      </c>
+      <c r="G276" s="3" t="n">
+        <v>24.63</v>
+      </c>
+      <c r="H276" s="4">
+        <f>IF(G276&gt;0,1000/G276,"")</f>
+        <v/>
+      </c>
+      <c r="I276" s="3" t="n">
+        <v>24.06</v>
+      </c>
+      <c r="J276" s="3" t="n">
+        <v>23.92</v>
+      </c>
+      <c r="K276" s="3" t="n">
+        <v>7.072</v>
+      </c>
+      <c r="L276" s="3" t="n">
+        <v>6.812</v>
+      </c>
+      <c r="M276" s="3" t="n">
+        <v>4.506</v>
+      </c>
+      <c r="N276" s="2" t="n">
+        <v>280</v>
+      </c>
+      <c r="O276" s="2" t="inlineStr">
+        <is>
+          <t>masque30c_B0, masque30c_B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:55</t>
+        </is>
+      </c>
+      <c r="B277" s="2" t="inlineStr">
+        <is>
+          <t>f23a476+modifs</t>
+        </is>
+      </c>
+      <c r="C277" s="2" t="inlineStr">
+        <is>
+          <t>10e3. Essai masque : faisceaux seulement dans les flaques (pores plus sombres)</t>
+        </is>
+      </c>
+      <c r="D277" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide, wet=0.3, 3 cas</t>
+        </is>
+      </c>
+      <c r="E277" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F277" s="2" t="inlineStr">
+        <is>
+          <t>zoom 45 + frost 0.6 / public</t>
+        </is>
+      </c>
+      <c r="G277" s="3" t="n">
+        <v>18.845</v>
+      </c>
+      <c r="H277" s="4">
+        <f>IF(G277&gt;0,1000/G277,"")</f>
+        <v/>
+      </c>
+      <c r="I277" s="3" t="n">
+        <v>18.045</v>
+      </c>
+      <c r="J277" s="3" t="n">
+        <v>18.025</v>
+      </c>
+      <c r="K277" s="3" t="n">
+        <v>3.206</v>
+      </c>
+      <c r="L277" s="3" t="n">
+        <v>4.082</v>
+      </c>
+      <c r="M277" s="3" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="N277" s="2" t="n">
+        <v>887</v>
+      </c>
+      <c r="O277" s="2" t="inlineStr">
+        <is>
+          <t>masque30c_B0, masque30c_B1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14373,7 +16565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q37"/>
+  <dimension ref="A1:Y37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -14393,6 +16585,14 @@
     <col width="16" customWidth="1" min="15" max="15"/>
     <col width="16" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="23" max="23"/>
+    <col width="16" customWidth="1" min="24" max="24"/>
+    <col width="16" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14488,6 +16688,46 @@
           <t>8. Longueur exacte des faisceaux arretes par le sol (bout des taches rasantes)</t>
         </is>
       </c>
+      <c r="R2" s="1" t="inlineStr">
+        <is>
+          <t>9a. Eau au sol : creux, flaques nettes, variante seche du shader</t>
+        </is>
+      </c>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>9b. Eau au sol a 10 %</t>
+        </is>
+      </c>
+      <c r="T2" s="1" t="inlineStr">
+        <is>
+          <t>9e. Essai : creux en trilineaire (abandonne)</t>
+        </is>
+      </c>
+      <c r="U2" s="1" t="inlineStr">
+        <is>
+          <t>10a. Reflet seulement dans l'eau (masque par blocs), eau 0,1</t>
+        </is>
+      </c>
+      <c r="V2" s="1" t="inlineStr">
+        <is>
+          <t>10b. Reflet seulement dans l'eau, eau 0,3</t>
+        </is>
+      </c>
+      <c r="W2" s="1" t="inlineStr">
+        <is>
+          <t>10c. Reflet seulement dans l'eau, eau 1</t>
+        </is>
+      </c>
+      <c r="X2" s="1" t="inlineStr">
+        <is>
+          <t>10e1. Essai masque : 1 point par pixel du miroir (creux manques)</t>
+        </is>
+      </c>
+      <c r="Y2" s="1" t="inlineStr">
+        <is>
+          <t>10e3. Essai masque : faisceaux seulement dans les flaques (pores plus sombres)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -14559,6 +16799,38 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A3,Mesures!$C:$C,Q$2),"")</f>
         <v/>
       </c>
+      <c r="R3" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A3,Mesures!$C:$C,R$2),"")</f>
+        <v/>
+      </c>
+      <c r="S3" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A3,Mesures!$C:$C,S$2),"")</f>
+        <v/>
+      </c>
+      <c r="T3" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A3,Mesures!$C:$C,T$2),"")</f>
+        <v/>
+      </c>
+      <c r="U3" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A3,Mesures!$C:$C,U$2),"")</f>
+        <v/>
+      </c>
+      <c r="V3" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A3,Mesures!$C:$C,V$2),"")</f>
+        <v/>
+      </c>
+      <c r="W3" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A3,Mesures!$C:$C,W$2),"")</f>
+        <v/>
+      </c>
+      <c r="X3" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A3,Mesures!$C:$C,X$2),"")</f>
+        <v/>
+      </c>
+      <c r="Y3" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A3,Mesures!$C:$C,Y$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -14630,6 +16902,38 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A4,Mesures!$C:$C,Q$2),"")</f>
         <v/>
       </c>
+      <c r="R4" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A4,Mesures!$C:$C,R$2),"")</f>
+        <v/>
+      </c>
+      <c r="S4" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A4,Mesures!$C:$C,S$2),"")</f>
+        <v/>
+      </c>
+      <c r="T4" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A4,Mesures!$C:$C,T$2),"")</f>
+        <v/>
+      </c>
+      <c r="U4" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A4,Mesures!$C:$C,U$2),"")</f>
+        <v/>
+      </c>
+      <c r="V4" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A4,Mesures!$C:$C,V$2),"")</f>
+        <v/>
+      </c>
+      <c r="W4" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A4,Mesures!$C:$C,W$2),"")</f>
+        <v/>
+      </c>
+      <c r="X4" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A4,Mesures!$C:$C,X$2),"")</f>
+        <v/>
+      </c>
+      <c r="Y4" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A4,Mesures!$C:$C,Y$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -14701,6 +17005,38 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A5,Mesures!$C:$C,Q$2),"")</f>
         <v/>
       </c>
+      <c r="R5" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A5,Mesures!$C:$C,R$2),"")</f>
+        <v/>
+      </c>
+      <c r="S5" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A5,Mesures!$C:$C,S$2),"")</f>
+        <v/>
+      </c>
+      <c r="T5" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A5,Mesures!$C:$C,T$2),"")</f>
+        <v/>
+      </c>
+      <c r="U5" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A5,Mesures!$C:$C,U$2),"")</f>
+        <v/>
+      </c>
+      <c r="V5" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A5,Mesures!$C:$C,V$2),"")</f>
+        <v/>
+      </c>
+      <c r="W5" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A5,Mesures!$C:$C,W$2),"")</f>
+        <v/>
+      </c>
+      <c r="X5" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A5,Mesures!$C:$C,X$2),"")</f>
+        <v/>
+      </c>
+      <c r="Y5" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A5,Mesures!$C:$C,Y$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -14772,6 +17108,38 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A6,Mesures!$C:$C,Q$2),"")</f>
         <v/>
       </c>
+      <c r="R6" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A6,Mesures!$C:$C,R$2),"")</f>
+        <v/>
+      </c>
+      <c r="S6" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A6,Mesures!$C:$C,S$2),"")</f>
+        <v/>
+      </c>
+      <c r="T6" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A6,Mesures!$C:$C,T$2),"")</f>
+        <v/>
+      </c>
+      <c r="U6" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A6,Mesures!$C:$C,U$2),"")</f>
+        <v/>
+      </c>
+      <c r="V6" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A6,Mesures!$C:$C,V$2),"")</f>
+        <v/>
+      </c>
+      <c r="W6" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A6,Mesures!$C:$C,W$2),"")</f>
+        <v/>
+      </c>
+      <c r="X6" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A6,Mesures!$C:$C,X$2),"")</f>
+        <v/>
+      </c>
+      <c r="Y6" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A6,Mesures!$C:$C,Y$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -14843,6 +17211,38 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A7,Mesures!$C:$C,Q$2),"")</f>
         <v/>
       </c>
+      <c r="R7" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A7,Mesures!$C:$C,R$2),"")</f>
+        <v/>
+      </c>
+      <c r="S7" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A7,Mesures!$C:$C,S$2),"")</f>
+        <v/>
+      </c>
+      <c r="T7" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A7,Mesures!$C:$C,T$2),"")</f>
+        <v/>
+      </c>
+      <c r="U7" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A7,Mesures!$C:$C,U$2),"")</f>
+        <v/>
+      </c>
+      <c r="V7" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A7,Mesures!$C:$C,V$2),"")</f>
+        <v/>
+      </c>
+      <c r="W7" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A7,Mesures!$C:$C,W$2),"")</f>
+        <v/>
+      </c>
+      <c r="X7" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A7,Mesures!$C:$C,X$2),"")</f>
+        <v/>
+      </c>
+      <c r="Y7" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A7,Mesures!$C:$C,Y$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -14914,6 +17314,38 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A8,Mesures!$C:$C,Q$2),"")</f>
         <v/>
       </c>
+      <c r="R8" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A8,Mesures!$C:$C,R$2),"")</f>
+        <v/>
+      </c>
+      <c r="S8" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A8,Mesures!$C:$C,S$2),"")</f>
+        <v/>
+      </c>
+      <c r="T8" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A8,Mesures!$C:$C,T$2),"")</f>
+        <v/>
+      </c>
+      <c r="U8" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A8,Mesures!$C:$C,U$2),"")</f>
+        <v/>
+      </c>
+      <c r="V8" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A8,Mesures!$C:$C,V$2),"")</f>
+        <v/>
+      </c>
+      <c r="W8" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A8,Mesures!$C:$C,W$2),"")</f>
+        <v/>
+      </c>
+      <c r="X8" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A8,Mesures!$C:$C,X$2),"")</f>
+        <v/>
+      </c>
+      <c r="Y8" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A8,Mesures!$C:$C,Y$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -14985,6 +17417,38 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A9,Mesures!$C:$C,Q$2),"")</f>
         <v/>
       </c>
+      <c r="R9" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A9,Mesures!$C:$C,R$2),"")</f>
+        <v/>
+      </c>
+      <c r="S9" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A9,Mesures!$C:$C,S$2),"")</f>
+        <v/>
+      </c>
+      <c r="T9" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A9,Mesures!$C:$C,T$2),"")</f>
+        <v/>
+      </c>
+      <c r="U9" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A9,Mesures!$C:$C,U$2),"")</f>
+        <v/>
+      </c>
+      <c r="V9" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A9,Mesures!$C:$C,V$2),"")</f>
+        <v/>
+      </c>
+      <c r="W9" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A9,Mesures!$C:$C,W$2),"")</f>
+        <v/>
+      </c>
+      <c r="X9" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A9,Mesures!$C:$C,X$2),"")</f>
+        <v/>
+      </c>
+      <c r="Y9" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A9,Mesures!$C:$C,Y$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -15056,6 +17520,38 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A10,Mesures!$C:$C,Q$2),"")</f>
         <v/>
       </c>
+      <c r="R10" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A10,Mesures!$C:$C,R$2),"")</f>
+        <v/>
+      </c>
+      <c r="S10" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A10,Mesures!$C:$C,S$2),"")</f>
+        <v/>
+      </c>
+      <c r="T10" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A10,Mesures!$C:$C,T$2),"")</f>
+        <v/>
+      </c>
+      <c r="U10" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A10,Mesures!$C:$C,U$2),"")</f>
+        <v/>
+      </c>
+      <c r="V10" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A10,Mesures!$C:$C,V$2),"")</f>
+        <v/>
+      </c>
+      <c r="W10" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A10,Mesures!$C:$C,W$2),"")</f>
+        <v/>
+      </c>
+      <c r="X10" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A10,Mesures!$C:$C,X$2),"")</f>
+        <v/>
+      </c>
+      <c r="Y10" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A10,Mesures!$C:$C,Y$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -15127,6 +17623,38 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A11,Mesures!$C:$C,Q$2),"")</f>
         <v/>
       </c>
+      <c r="R11" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A11,Mesures!$C:$C,R$2),"")</f>
+        <v/>
+      </c>
+      <c r="S11" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A11,Mesures!$C:$C,S$2),"")</f>
+        <v/>
+      </c>
+      <c r="T11" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A11,Mesures!$C:$C,T$2),"")</f>
+        <v/>
+      </c>
+      <c r="U11" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A11,Mesures!$C:$C,U$2),"")</f>
+        <v/>
+      </c>
+      <c r="V11" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A11,Mesures!$C:$C,V$2),"")</f>
+        <v/>
+      </c>
+      <c r="W11" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A11,Mesures!$C:$C,W$2),"")</f>
+        <v/>
+      </c>
+      <c r="X11" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A11,Mesures!$C:$C,X$2),"")</f>
+        <v/>
+      </c>
+      <c r="Y11" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A11,Mesures!$C:$C,Y$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -15198,6 +17726,38 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A12,Mesures!$C:$C,Q$2),"")</f>
         <v/>
       </c>
+      <c r="R12" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A12,Mesures!$C:$C,R$2),"")</f>
+        <v/>
+      </c>
+      <c r="S12" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A12,Mesures!$C:$C,S$2),"")</f>
+        <v/>
+      </c>
+      <c r="T12" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A12,Mesures!$C:$C,T$2),"")</f>
+        <v/>
+      </c>
+      <c r="U12" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A12,Mesures!$C:$C,U$2),"")</f>
+        <v/>
+      </c>
+      <c r="V12" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A12,Mesures!$C:$C,V$2),"")</f>
+        <v/>
+      </c>
+      <c r="W12" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A12,Mesures!$C:$C,W$2),"")</f>
+        <v/>
+      </c>
+      <c r="X12" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A12,Mesures!$C:$C,X$2),"")</f>
+        <v/>
+      </c>
+      <c r="Y12" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A12,Mesures!$C:$C,Y$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -15269,6 +17829,38 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A13,Mesures!$C:$C,Q$2),"")</f>
         <v/>
       </c>
+      <c r="R13" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A13,Mesures!$C:$C,R$2),"")</f>
+        <v/>
+      </c>
+      <c r="S13" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A13,Mesures!$C:$C,S$2),"")</f>
+        <v/>
+      </c>
+      <c r="T13" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A13,Mesures!$C:$C,T$2),"")</f>
+        <v/>
+      </c>
+      <c r="U13" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A13,Mesures!$C:$C,U$2),"")</f>
+        <v/>
+      </c>
+      <c r="V13" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A13,Mesures!$C:$C,V$2),"")</f>
+        <v/>
+      </c>
+      <c r="W13" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A13,Mesures!$C:$C,W$2),"")</f>
+        <v/>
+      </c>
+      <c r="X13" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A13,Mesures!$C:$C,X$2),"")</f>
+        <v/>
+      </c>
+      <c r="Y13" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A13,Mesures!$C:$C,Y$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -15340,6 +17932,38 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A14,Mesures!$C:$C,Q$2),"")</f>
         <v/>
       </c>
+      <c r="R14" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A14,Mesures!$C:$C,R$2),"")</f>
+        <v/>
+      </c>
+      <c r="S14" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A14,Mesures!$C:$C,S$2),"")</f>
+        <v/>
+      </c>
+      <c r="T14" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A14,Mesures!$C:$C,T$2),"")</f>
+        <v/>
+      </c>
+      <c r="U14" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A14,Mesures!$C:$C,U$2),"")</f>
+        <v/>
+      </c>
+      <c r="V14" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A14,Mesures!$C:$C,V$2),"")</f>
+        <v/>
+      </c>
+      <c r="W14" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A14,Mesures!$C:$C,W$2),"")</f>
+        <v/>
+      </c>
+      <c r="X14" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A14,Mesures!$C:$C,X$2),"")</f>
+        <v/>
+      </c>
+      <c r="Y14" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A14,Mesures!$C:$C,Y$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -15411,6 +18035,38 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A15,Mesures!$C:$C,Q$2),"")</f>
         <v/>
       </c>
+      <c r="R15" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A15,Mesures!$C:$C,R$2),"")</f>
+        <v/>
+      </c>
+      <c r="S15" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A15,Mesures!$C:$C,S$2),"")</f>
+        <v/>
+      </c>
+      <c r="T15" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A15,Mesures!$C:$C,T$2),"")</f>
+        <v/>
+      </c>
+      <c r="U15" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A15,Mesures!$C:$C,U$2),"")</f>
+        <v/>
+      </c>
+      <c r="V15" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A15,Mesures!$C:$C,V$2),"")</f>
+        <v/>
+      </c>
+      <c r="W15" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A15,Mesures!$C:$C,W$2),"")</f>
+        <v/>
+      </c>
+      <c r="X15" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A15,Mesures!$C:$C,X$2),"")</f>
+        <v/>
+      </c>
+      <c r="Y15" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A15,Mesures!$C:$C,Y$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -15482,6 +18138,38 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A16,Mesures!$C:$C,Q$2),"")</f>
         <v/>
       </c>
+      <c r="R16" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A16,Mesures!$C:$C,R$2),"")</f>
+        <v/>
+      </c>
+      <c r="S16" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A16,Mesures!$C:$C,S$2),"")</f>
+        <v/>
+      </c>
+      <c r="T16" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A16,Mesures!$C:$C,T$2),"")</f>
+        <v/>
+      </c>
+      <c r="U16" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A16,Mesures!$C:$C,U$2),"")</f>
+        <v/>
+      </c>
+      <c r="V16" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A16,Mesures!$C:$C,V$2),"")</f>
+        <v/>
+      </c>
+      <c r="W16" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A16,Mesures!$C:$C,W$2),"")</f>
+        <v/>
+      </c>
+      <c r="X16" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A16,Mesures!$C:$C,X$2),"")</f>
+        <v/>
+      </c>
+      <c r="Y16" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A16,Mesures!$C:$C,Y$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -15553,6 +18241,38 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A17,Mesures!$C:$C,Q$2),"")</f>
         <v/>
       </c>
+      <c r="R17" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A17,Mesures!$C:$C,R$2),"")</f>
+        <v/>
+      </c>
+      <c r="S17" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A17,Mesures!$C:$C,S$2),"")</f>
+        <v/>
+      </c>
+      <c r="T17" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A17,Mesures!$C:$C,T$2),"")</f>
+        <v/>
+      </c>
+      <c r="U17" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A17,Mesures!$C:$C,U$2),"")</f>
+        <v/>
+      </c>
+      <c r="V17" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A17,Mesures!$C:$C,V$2),"")</f>
+        <v/>
+      </c>
+      <c r="W17" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A17,Mesures!$C:$C,W$2),"")</f>
+        <v/>
+      </c>
+      <c r="X17" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A17,Mesures!$C:$C,X$2),"")</f>
+        <v/>
+      </c>
+      <c r="Y17" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A17,Mesures!$C:$C,Y$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -15624,6 +18344,38 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A18,Mesures!$C:$C,Q$2),"")</f>
         <v/>
       </c>
+      <c r="R18" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A18,Mesures!$C:$C,R$2),"")</f>
+        <v/>
+      </c>
+      <c r="S18" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A18,Mesures!$C:$C,S$2),"")</f>
+        <v/>
+      </c>
+      <c r="T18" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A18,Mesures!$C:$C,T$2),"")</f>
+        <v/>
+      </c>
+      <c r="U18" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A18,Mesures!$C:$C,U$2),"")</f>
+        <v/>
+      </c>
+      <c r="V18" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A18,Mesures!$C:$C,V$2),"")</f>
+        <v/>
+      </c>
+      <c r="W18" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A18,Mesures!$C:$C,W$2),"")</f>
+        <v/>
+      </c>
+      <c r="X18" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A18,Mesures!$C:$C,X$2),"")</f>
+        <v/>
+      </c>
+      <c r="Y18" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A18,Mesures!$C:$C,Y$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -15718,6 +18470,46 @@
           <t>8. Longueur exacte des faisceaux arretes par le sol (bout des taches rasantes)</t>
         </is>
       </c>
+      <c r="R21" s="1" t="inlineStr">
+        <is>
+          <t>9a. Eau au sol : creux, flaques nettes, variante seche du shader</t>
+        </is>
+      </c>
+      <c r="S21" s="1" t="inlineStr">
+        <is>
+          <t>9b. Eau au sol a 10 %</t>
+        </is>
+      </c>
+      <c r="T21" s="1" t="inlineStr">
+        <is>
+          <t>9e. Essai : creux en trilineaire (abandonne)</t>
+        </is>
+      </c>
+      <c r="U21" s="1" t="inlineStr">
+        <is>
+          <t>10a. Reflet seulement dans l'eau (masque par blocs), eau 0,1</t>
+        </is>
+      </c>
+      <c r="V21" s="1" t="inlineStr">
+        <is>
+          <t>10b. Reflet seulement dans l'eau, eau 0,3</t>
+        </is>
+      </c>
+      <c r="W21" s="1" t="inlineStr">
+        <is>
+          <t>10c. Reflet seulement dans l'eau, eau 1</t>
+        </is>
+      </c>
+      <c r="X21" s="1" t="inlineStr">
+        <is>
+          <t>10e1. Essai masque : 1 point par pixel du miroir (creux manques)</t>
+        </is>
+      </c>
+      <c r="Y21" s="1" t="inlineStr">
+        <is>
+          <t>10e3. Essai masque : faisceaux seulement dans les flaques (pores plus sombres)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -15789,6 +18581,38 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A22,Mesures!$C:$C,Q$21),"")</f>
         <v/>
       </c>
+      <c r="R22" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A22,Mesures!$C:$C,R$21),"")</f>
+        <v/>
+      </c>
+      <c r="S22" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A22,Mesures!$C:$C,S$21),"")</f>
+        <v/>
+      </c>
+      <c r="T22" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A22,Mesures!$C:$C,T$21),"")</f>
+        <v/>
+      </c>
+      <c r="U22" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A22,Mesures!$C:$C,U$21),"")</f>
+        <v/>
+      </c>
+      <c r="V22" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A22,Mesures!$C:$C,V$21),"")</f>
+        <v/>
+      </c>
+      <c r="W22" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A22,Mesures!$C:$C,W$21),"")</f>
+        <v/>
+      </c>
+      <c r="X22" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A22,Mesures!$C:$C,X$21),"")</f>
+        <v/>
+      </c>
+      <c r="Y22" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A22,Mesures!$C:$C,Y$21),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -15860,6 +18684,38 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A23,Mesures!$C:$C,Q$21),"")</f>
         <v/>
       </c>
+      <c r="R23" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A23,Mesures!$C:$C,R$21),"")</f>
+        <v/>
+      </c>
+      <c r="S23" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A23,Mesures!$C:$C,S$21),"")</f>
+        <v/>
+      </c>
+      <c r="T23" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A23,Mesures!$C:$C,T$21),"")</f>
+        <v/>
+      </c>
+      <c r="U23" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A23,Mesures!$C:$C,U$21),"")</f>
+        <v/>
+      </c>
+      <c r="V23" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A23,Mesures!$C:$C,V$21),"")</f>
+        <v/>
+      </c>
+      <c r="W23" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A23,Mesures!$C:$C,W$21),"")</f>
+        <v/>
+      </c>
+      <c r="X23" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A23,Mesures!$C:$C,X$21),"")</f>
+        <v/>
+      </c>
+      <c r="Y23" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A23,Mesures!$C:$C,Y$21),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -15931,6 +18787,38 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A24,Mesures!$C:$C,Q$21),"")</f>
         <v/>
       </c>
+      <c r="R24" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A24,Mesures!$C:$C,R$21),"")</f>
+        <v/>
+      </c>
+      <c r="S24" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A24,Mesures!$C:$C,S$21),"")</f>
+        <v/>
+      </c>
+      <c r="T24" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A24,Mesures!$C:$C,T$21),"")</f>
+        <v/>
+      </c>
+      <c r="U24" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A24,Mesures!$C:$C,U$21),"")</f>
+        <v/>
+      </c>
+      <c r="V24" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A24,Mesures!$C:$C,V$21),"")</f>
+        <v/>
+      </c>
+      <c r="W24" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A24,Mesures!$C:$C,W$21),"")</f>
+        <v/>
+      </c>
+      <c r="X24" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A24,Mesures!$C:$C,X$21),"")</f>
+        <v/>
+      </c>
+      <c r="Y24" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A24,Mesures!$C:$C,Y$21),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -16002,6 +18890,38 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A25,Mesures!$C:$C,Q$21),"")</f>
         <v/>
       </c>
+      <c r="R25" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A25,Mesures!$C:$C,R$21),"")</f>
+        <v/>
+      </c>
+      <c r="S25" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A25,Mesures!$C:$C,S$21),"")</f>
+        <v/>
+      </c>
+      <c r="T25" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A25,Mesures!$C:$C,T$21),"")</f>
+        <v/>
+      </c>
+      <c r="U25" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A25,Mesures!$C:$C,U$21),"")</f>
+        <v/>
+      </c>
+      <c r="V25" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A25,Mesures!$C:$C,V$21),"")</f>
+        <v/>
+      </c>
+      <c r="W25" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A25,Mesures!$C:$C,W$21),"")</f>
+        <v/>
+      </c>
+      <c r="X25" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A25,Mesures!$C:$C,X$21),"")</f>
+        <v/>
+      </c>
+      <c r="Y25" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A25,Mesures!$C:$C,Y$21),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -16073,6 +18993,38 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A26,Mesures!$C:$C,Q$21),"")</f>
         <v/>
       </c>
+      <c r="R26" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A26,Mesures!$C:$C,R$21),"")</f>
+        <v/>
+      </c>
+      <c r="S26" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A26,Mesures!$C:$C,S$21),"")</f>
+        <v/>
+      </c>
+      <c r="T26" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A26,Mesures!$C:$C,T$21),"")</f>
+        <v/>
+      </c>
+      <c r="U26" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A26,Mesures!$C:$C,U$21),"")</f>
+        <v/>
+      </c>
+      <c r="V26" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A26,Mesures!$C:$C,V$21),"")</f>
+        <v/>
+      </c>
+      <c r="W26" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A26,Mesures!$C:$C,W$21),"")</f>
+        <v/>
+      </c>
+      <c r="X26" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A26,Mesures!$C:$C,X$21),"")</f>
+        <v/>
+      </c>
+      <c r="Y26" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A26,Mesures!$C:$C,Y$21),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -16144,6 +19096,38 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A27,Mesures!$C:$C,Q$21),"")</f>
         <v/>
       </c>
+      <c r="R27" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A27,Mesures!$C:$C,R$21),"")</f>
+        <v/>
+      </c>
+      <c r="S27" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A27,Mesures!$C:$C,S$21),"")</f>
+        <v/>
+      </c>
+      <c r="T27" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A27,Mesures!$C:$C,T$21),"")</f>
+        <v/>
+      </c>
+      <c r="U27" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A27,Mesures!$C:$C,U$21),"")</f>
+        <v/>
+      </c>
+      <c r="V27" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A27,Mesures!$C:$C,V$21),"")</f>
+        <v/>
+      </c>
+      <c r="W27" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A27,Mesures!$C:$C,W$21),"")</f>
+        <v/>
+      </c>
+      <c r="X27" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A27,Mesures!$C:$C,X$21),"")</f>
+        <v/>
+      </c>
+      <c r="Y27" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A27,Mesures!$C:$C,Y$21),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -16215,6 +19199,38 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A28,Mesures!$C:$C,Q$21),"")</f>
         <v/>
       </c>
+      <c r="R28" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A28,Mesures!$C:$C,R$21),"")</f>
+        <v/>
+      </c>
+      <c r="S28" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A28,Mesures!$C:$C,S$21),"")</f>
+        <v/>
+      </c>
+      <c r="T28" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A28,Mesures!$C:$C,T$21),"")</f>
+        <v/>
+      </c>
+      <c r="U28" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A28,Mesures!$C:$C,U$21),"")</f>
+        <v/>
+      </c>
+      <c r="V28" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A28,Mesures!$C:$C,V$21),"")</f>
+        <v/>
+      </c>
+      <c r="W28" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A28,Mesures!$C:$C,W$21),"")</f>
+        <v/>
+      </c>
+      <c r="X28" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A28,Mesures!$C:$C,X$21),"")</f>
+        <v/>
+      </c>
+      <c r="Y28" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A28,Mesures!$C:$C,Y$21),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -16286,6 +19302,38 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A29,Mesures!$C:$C,Q$21),"")</f>
         <v/>
       </c>
+      <c r="R29" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A29,Mesures!$C:$C,R$21),"")</f>
+        <v/>
+      </c>
+      <c r="S29" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A29,Mesures!$C:$C,S$21),"")</f>
+        <v/>
+      </c>
+      <c r="T29" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A29,Mesures!$C:$C,T$21),"")</f>
+        <v/>
+      </c>
+      <c r="U29" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A29,Mesures!$C:$C,U$21),"")</f>
+        <v/>
+      </c>
+      <c r="V29" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A29,Mesures!$C:$C,V$21),"")</f>
+        <v/>
+      </c>
+      <c r="W29" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A29,Mesures!$C:$C,W$21),"")</f>
+        <v/>
+      </c>
+      <c r="X29" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A29,Mesures!$C:$C,X$21),"")</f>
+        <v/>
+      </c>
+      <c r="Y29" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A29,Mesures!$C:$C,Y$21),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -16357,6 +19405,38 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A30,Mesures!$C:$C,Q$21),"")</f>
         <v/>
       </c>
+      <c r="R30" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A30,Mesures!$C:$C,R$21),"")</f>
+        <v/>
+      </c>
+      <c r="S30" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A30,Mesures!$C:$C,S$21),"")</f>
+        <v/>
+      </c>
+      <c r="T30" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A30,Mesures!$C:$C,T$21),"")</f>
+        <v/>
+      </c>
+      <c r="U30" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A30,Mesures!$C:$C,U$21),"")</f>
+        <v/>
+      </c>
+      <c r="V30" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A30,Mesures!$C:$C,V$21),"")</f>
+        <v/>
+      </c>
+      <c r="W30" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A30,Mesures!$C:$C,W$21),"")</f>
+        <v/>
+      </c>
+      <c r="X30" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A30,Mesures!$C:$C,X$21),"")</f>
+        <v/>
+      </c>
+      <c r="Y30" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A30,Mesures!$C:$C,Y$21),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -16428,6 +19508,38 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A31,Mesures!$C:$C,Q$21),"")</f>
         <v/>
       </c>
+      <c r="R31" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A31,Mesures!$C:$C,R$21),"")</f>
+        <v/>
+      </c>
+      <c r="S31" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A31,Mesures!$C:$C,S$21),"")</f>
+        <v/>
+      </c>
+      <c r="T31" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A31,Mesures!$C:$C,T$21),"")</f>
+        <v/>
+      </c>
+      <c r="U31" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A31,Mesures!$C:$C,U$21),"")</f>
+        <v/>
+      </c>
+      <c r="V31" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A31,Mesures!$C:$C,V$21),"")</f>
+        <v/>
+      </c>
+      <c r="W31" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A31,Mesures!$C:$C,W$21),"")</f>
+        <v/>
+      </c>
+      <c r="X31" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A31,Mesures!$C:$C,X$21),"")</f>
+        <v/>
+      </c>
+      <c r="Y31" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A31,Mesures!$C:$C,Y$21),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -16499,6 +19611,38 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A32,Mesures!$C:$C,Q$21),"")</f>
         <v/>
       </c>
+      <c r="R32" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A32,Mesures!$C:$C,R$21),"")</f>
+        <v/>
+      </c>
+      <c r="S32" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A32,Mesures!$C:$C,S$21),"")</f>
+        <v/>
+      </c>
+      <c r="T32" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A32,Mesures!$C:$C,T$21),"")</f>
+        <v/>
+      </c>
+      <c r="U32" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A32,Mesures!$C:$C,U$21),"")</f>
+        <v/>
+      </c>
+      <c r="V32" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A32,Mesures!$C:$C,V$21),"")</f>
+        <v/>
+      </c>
+      <c r="W32" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A32,Mesures!$C:$C,W$21),"")</f>
+        <v/>
+      </c>
+      <c r="X32" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A32,Mesures!$C:$C,X$21),"")</f>
+        <v/>
+      </c>
+      <c r="Y32" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A32,Mesures!$C:$C,Y$21),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -16570,6 +19714,38 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A33,Mesures!$C:$C,Q$21),"")</f>
         <v/>
       </c>
+      <c r="R33" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A33,Mesures!$C:$C,R$21),"")</f>
+        <v/>
+      </c>
+      <c r="S33" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A33,Mesures!$C:$C,S$21),"")</f>
+        <v/>
+      </c>
+      <c r="T33" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A33,Mesures!$C:$C,T$21),"")</f>
+        <v/>
+      </c>
+      <c r="U33" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A33,Mesures!$C:$C,U$21),"")</f>
+        <v/>
+      </c>
+      <c r="V33" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A33,Mesures!$C:$C,V$21),"")</f>
+        <v/>
+      </c>
+      <c r="W33" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A33,Mesures!$C:$C,W$21),"")</f>
+        <v/>
+      </c>
+      <c r="X33" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A33,Mesures!$C:$C,X$21),"")</f>
+        <v/>
+      </c>
+      <c r="Y33" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A33,Mesures!$C:$C,Y$21),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -16641,6 +19817,38 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A34,Mesures!$C:$C,Q$21),"")</f>
         <v/>
       </c>
+      <c r="R34" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A34,Mesures!$C:$C,R$21),"")</f>
+        <v/>
+      </c>
+      <c r="S34" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A34,Mesures!$C:$C,S$21),"")</f>
+        <v/>
+      </c>
+      <c r="T34" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A34,Mesures!$C:$C,T$21),"")</f>
+        <v/>
+      </c>
+      <c r="U34" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A34,Mesures!$C:$C,U$21),"")</f>
+        <v/>
+      </c>
+      <c r="V34" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A34,Mesures!$C:$C,V$21),"")</f>
+        <v/>
+      </c>
+      <c r="W34" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A34,Mesures!$C:$C,W$21),"")</f>
+        <v/>
+      </c>
+      <c r="X34" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A34,Mesures!$C:$C,X$21),"")</f>
+        <v/>
+      </c>
+      <c r="Y34" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A34,Mesures!$C:$C,Y$21),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -16712,6 +19920,38 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A35,Mesures!$C:$C,Q$21),"")</f>
         <v/>
       </c>
+      <c r="R35" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A35,Mesures!$C:$C,R$21),"")</f>
+        <v/>
+      </c>
+      <c r="S35" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A35,Mesures!$C:$C,S$21),"")</f>
+        <v/>
+      </c>
+      <c r="T35" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A35,Mesures!$C:$C,T$21),"")</f>
+        <v/>
+      </c>
+      <c r="U35" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A35,Mesures!$C:$C,U$21),"")</f>
+        <v/>
+      </c>
+      <c r="V35" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A35,Mesures!$C:$C,V$21),"")</f>
+        <v/>
+      </c>
+      <c r="W35" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A35,Mesures!$C:$C,W$21),"")</f>
+        <v/>
+      </c>
+      <c r="X35" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A35,Mesures!$C:$C,X$21),"")</f>
+        <v/>
+      </c>
+      <c r="Y35" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A35,Mesures!$C:$C,Y$21),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -16783,6 +20023,38 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A36,Mesures!$C:$C,Q$21),"")</f>
         <v/>
       </c>
+      <c r="R36" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A36,Mesures!$C:$C,R$21),"")</f>
+        <v/>
+      </c>
+      <c r="S36" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A36,Mesures!$C:$C,S$21),"")</f>
+        <v/>
+      </c>
+      <c r="T36" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A36,Mesures!$C:$C,T$21),"")</f>
+        <v/>
+      </c>
+      <c r="U36" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A36,Mesures!$C:$C,U$21),"")</f>
+        <v/>
+      </c>
+      <c r="V36" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A36,Mesures!$C:$C,V$21),"")</f>
+        <v/>
+      </c>
+      <c r="W36" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A36,Mesures!$C:$C,W$21),"")</f>
+        <v/>
+      </c>
+      <c r="X36" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A36,Mesures!$C:$C,X$21),"")</f>
+        <v/>
+      </c>
+      <c r="Y36" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A36,Mesures!$C:$C,Y$21),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -16852,6 +20124,38 @@
       </c>
       <c r="Q37" s="3">
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A37,Mesures!$C:$C,Q$21),"")</f>
+        <v/>
+      </c>
+      <c r="R37" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A37,Mesures!$C:$C,R$21),"")</f>
+        <v/>
+      </c>
+      <c r="S37" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A37,Mesures!$C:$C,S$21),"")</f>
+        <v/>
+      </c>
+      <c r="T37" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A37,Mesures!$C:$C,T$21),"")</f>
+        <v/>
+      </c>
+      <c r="U37" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A37,Mesures!$C:$C,U$21),"")</f>
+        <v/>
+      </c>
+      <c r="V37" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A37,Mesures!$C:$C,V$21),"")</f>
+        <v/>
+      </c>
+      <c r="W37" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A37,Mesures!$C:$C,W$21),"")</f>
+        <v/>
+      </c>
+      <c r="X37" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A37,Mesures!$C:$C,X$21),"")</f>
+        <v/>
+      </c>
+      <c r="Y37" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A37,Mesures!$C:$C,Y$21),"")</f>
         <v/>
       </c>
     </row>

--- a/lyre-viz/historique_perf.xlsx
+++ b/lyre-viz/historique_perf.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q572"/>
+  <dimension ref="A1:Q678"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -35920,6 +35920,6980 @@
         </is>
       </c>
     </row>
+    <row r="573">
+      <c r="A573" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:16</t>
+        </is>
+      </c>
+      <c r="B573" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C573" s="2" t="inlineStr">
+        <is>
+          <t>21. Lasers : collisions, code present coupe (lasercoll=0)</t>
+        </is>
+      </c>
+      <c r="D573" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, lasercoll=0, immobile, banc rapide, 5 cas</t>
+        </is>
+      </c>
+      <c r="E573" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F573" s="2" t="inlineStr">
+        <is>
+          <t>L1 eventails 200 x 1000 traits / public</t>
+        </is>
+      </c>
+      <c r="G573" s="3" t="n">
+        <v>13.92</v>
+      </c>
+      <c r="H573" s="4">
+        <f>IF(G573&gt;0,1000/G573,"")</f>
+        <v/>
+      </c>
+      <c r="I573" s="3" t="n">
+        <v>13.145</v>
+      </c>
+      <c r="J573" s="3" t="n">
+        <v>12.05</v>
+      </c>
+      <c r="K573" s="3" t="n">
+        <v>0.784</v>
+      </c>
+      <c r="L573" s="3" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="M573" s="3" t="n"/>
+      <c r="N573" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O573" s="2" t="inlineStr">
+        <is>
+          <t>coll_presence2_B0, coll_presence2_B1</t>
+        </is>
+      </c>
+      <c r="P573" s="3" t="n">
+        <v>9.125</v>
+      </c>
+      <c r="Q573" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:16</t>
+        </is>
+      </c>
+      <c r="B574" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C574" s="2" t="inlineStr">
+        <is>
+          <t>21. Lasers : collisions, code present coupe (lasercoll=0)</t>
+        </is>
+      </c>
+      <c r="D574" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, lasercoll=0, immobile, banc rapide, 5 cas</t>
+        </is>
+      </c>
+      <c r="E574" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F574" s="2" t="inlineStr">
+        <is>
+          <t>L2 cones 200 x 32 segments / public</t>
+        </is>
+      </c>
+      <c r="G574" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="H574" s="4">
+        <f>IF(G574&gt;0,1000/G574,"")</f>
+        <v/>
+      </c>
+      <c r="I574" s="3" t="n">
+        <v>17.06</v>
+      </c>
+      <c r="J574" s="3" t="n">
+        <v>16.305</v>
+      </c>
+      <c r="K574" s="3" t="n">
+        <v>0.666</v>
+      </c>
+      <c r="L574" s="3" t="n">
+        <v>0.651</v>
+      </c>
+      <c r="M574" s="3" t="n"/>
+      <c r="N574" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O574" s="2" t="inlineStr">
+        <is>
+          <t>coll_presence2_B0, coll_presence2_B1</t>
+        </is>
+      </c>
+      <c r="P574" s="3" t="n">
+        <v>13.299</v>
+      </c>
+      <c r="Q574" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:16</t>
+        </is>
+      </c>
+      <c r="B575" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C575" s="2" t="inlineStr">
+        <is>
+          <t>21. Lasers : collisions, code present coupe (lasercoll=0)</t>
+        </is>
+      </c>
+      <c r="D575" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, lasercoll=0, immobile, banc rapide, 5 cas</t>
+        </is>
+      </c>
+      <c r="E575" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F575" s="2" t="inlineStr">
+        <is>
+          <t>L3 camera dans les nappes</t>
+        </is>
+      </c>
+      <c r="G575" s="3" t="n">
+        <v>12.775</v>
+      </c>
+      <c r="H575" s="4">
+        <f>IF(G575&gt;0,1000/G575,"")</f>
+        <v/>
+      </c>
+      <c r="I575" s="3" t="n">
+        <v>11.68</v>
+      </c>
+      <c r="J575" s="3" t="n">
+        <v>11.155</v>
+      </c>
+      <c r="K575" s="3" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="L575" s="3" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="M575" s="3" t="n"/>
+      <c r="N575" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O575" s="2" t="inlineStr">
+        <is>
+          <t>coll_presence2_B0, coll_presence2_B1</t>
+        </is>
+      </c>
+      <c r="P575" s="3" t="n">
+        <v>8.233000000000001</v>
+      </c>
+      <c r="Q575" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:16</t>
+        </is>
+      </c>
+      <c r="B576" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C576" s="2" t="inlineStr">
+        <is>
+          <t>21. Lasers : collisions, code present coupe (lasercoll=0)</t>
+        </is>
+      </c>
+      <c r="D576" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, lasercoll=0, immobile, banc rapide, 5 cas</t>
+        </is>
+      </c>
+      <c r="E576" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F576" s="2" t="inlineStr">
+        <is>
+          <t>L4 200 x 8 traits separes / public</t>
+        </is>
+      </c>
+      <c r="G576" s="3" t="n">
+        <v>7.985</v>
+      </c>
+      <c r="H576" s="4">
+        <f>IF(G576&gt;0,1000/G576,"")</f>
+        <v/>
+      </c>
+      <c r="I576" s="3" t="n">
+        <v>6.96</v>
+      </c>
+      <c r="J576" s="3" t="n">
+        <v>6.195</v>
+      </c>
+      <c r="K576" s="3" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="L576" s="3" t="n">
+        <v>2.152</v>
+      </c>
+      <c r="M576" s="3" t="n"/>
+      <c r="N576" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O576" s="2" t="inlineStr">
+        <is>
+          <t>coll_presence2_B0, coll_presence2_B1</t>
+        </is>
+      </c>
+      <c r="P576" s="3" t="n">
+        <v>1.645</v>
+      </c>
+      <c r="Q576" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:16</t>
+        </is>
+      </c>
+      <c r="B577" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C577" s="2" t="inlineStr">
+        <is>
+          <t>21. Lasers : collisions, code present coupe (lasercoll=0)</t>
+        </is>
+      </c>
+      <c r="D577" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, lasercoll=0, immobile, banc rapide, 5 cas</t>
+        </is>
+      </c>
+      <c r="E577" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F577" s="2" t="inlineStr">
+        <is>
+          <t>M1 100 lyres + 100 lasers / public</t>
+        </is>
+      </c>
+      <c r="G577" s="3" t="n">
+        <v>11.405</v>
+      </c>
+      <c r="H577" s="4">
+        <f>IF(G577&gt;0,1000/G577,"")</f>
+        <v/>
+      </c>
+      <c r="I577" s="3" t="n">
+        <v>10.535</v>
+      </c>
+      <c r="J577" s="3" t="n">
+        <v>9.66</v>
+      </c>
+      <c r="K577" s="3" t="n">
+        <v>1.214</v>
+      </c>
+      <c r="L577" s="3" t="n">
+        <v>1.385</v>
+      </c>
+      <c r="M577" s="3" t="n"/>
+      <c r="N577" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="O577" s="2" t="inlineStr">
+        <is>
+          <t>coll_presence2_B0, coll_presence2_B1</t>
+        </is>
+      </c>
+      <c r="P577" s="3" t="n">
+        <v>4.905</v>
+      </c>
+      <c r="Q577" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:16</t>
+        </is>
+      </c>
+      <c r="B578" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C578" s="2" t="inlineStr">
+        <is>
+          <t>21. Lasers : collisions actives (essai, test avec branchement)</t>
+        </is>
+      </c>
+      <c r="D578" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, lasercoll=1, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E578" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F578" s="2" t="inlineStr">
+        <is>
+          <t>L1 eventails 200 x 1000 traits / public</t>
+        </is>
+      </c>
+      <c r="G578" s="3" t="n">
+        <v>13.645</v>
+      </c>
+      <c r="H578" s="4">
+        <f>IF(G578&gt;0,1000/G578,"")</f>
+        <v/>
+      </c>
+      <c r="I578" s="3" t="n">
+        <v>12.765</v>
+      </c>
+      <c r="J578" s="3" t="n">
+        <v>11.895</v>
+      </c>
+      <c r="K578" s="3" t="n">
+        <v>0.663</v>
+      </c>
+      <c r="L578" s="3" t="n">
+        <v>0.647</v>
+      </c>
+      <c r="M578" s="3" t="n"/>
+      <c r="N578" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O578" s="2" t="inlineStr">
+        <is>
+          <t>coll_cout_B0, coll_cout_B1</t>
+        </is>
+      </c>
+      <c r="P578" s="3" t="n">
+        <v>8.965</v>
+      </c>
+      <c r="Q578" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:16</t>
+        </is>
+      </c>
+      <c r="B579" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C579" s="2" t="inlineStr">
+        <is>
+          <t>21. Lasers : collisions actives (essai, test avec branchement)</t>
+        </is>
+      </c>
+      <c r="D579" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, lasercoll=1, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E579" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F579" s="2" t="inlineStr">
+        <is>
+          <t>L1 eventails 200 x 1000 traits / scene</t>
+        </is>
+      </c>
+      <c r="G579" s="3" t="n">
+        <v>12.295</v>
+      </c>
+      <c r="H579" s="4">
+        <f>IF(G579&gt;0,1000/G579,"")</f>
+        <v/>
+      </c>
+      <c r="I579" s="3" t="n">
+        <v>11.735</v>
+      </c>
+      <c r="J579" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="K579" s="3" t="n">
+        <v>0.792</v>
+      </c>
+      <c r="L579" s="3" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="M579" s="3" t="n"/>
+      <c r="N579" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O579" s="2" t="inlineStr">
+        <is>
+          <t>coll_cout_B0, coll_cout_B1</t>
+        </is>
+      </c>
+      <c r="P579" s="3" t="n">
+        <v>8.188000000000001</v>
+      </c>
+      <c r="Q579" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:16</t>
+        </is>
+      </c>
+      <c r="B580" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C580" s="2" t="inlineStr">
+        <is>
+          <t>21. Lasers : collisions actives (essai, test avec branchement)</t>
+        </is>
+      </c>
+      <c r="D580" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, lasercoll=1, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E580" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F580" s="2" t="inlineStr">
+        <is>
+          <t>L1 eventails 200 x 1000 traits / sous les trusses</t>
+        </is>
+      </c>
+      <c r="G580" s="3" t="n">
+        <v>11.64</v>
+      </c>
+      <c r="H580" s="4">
+        <f>IF(G580&gt;0,1000/G580,"")</f>
+        <v/>
+      </c>
+      <c r="I580" s="3" t="n">
+        <v>10.725</v>
+      </c>
+      <c r="J580" s="3" t="n">
+        <v>10.425</v>
+      </c>
+      <c r="K580" s="3" t="n">
+        <v>0.694</v>
+      </c>
+      <c r="L580" s="3" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="M580" s="3" t="n"/>
+      <c r="N580" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O580" s="2" t="inlineStr">
+        <is>
+          <t>coll_cout_B0, coll_cout_B1</t>
+        </is>
+      </c>
+      <c r="P580" s="3" t="n">
+        <v>7.377</v>
+      </c>
+      <c r="Q580" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:16</t>
+        </is>
+      </c>
+      <c r="B581" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C581" s="2" t="inlineStr">
+        <is>
+          <t>21. Lasers : collisions actives (essai, test avec branchement)</t>
+        </is>
+      </c>
+      <c r="D581" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, lasercoll=1, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E581" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F581" s="2" t="inlineStr">
+        <is>
+          <t>L2 cones 200 x 32 segments / public</t>
+        </is>
+      </c>
+      <c r="G581" s="3" t="n">
+        <v>17.835</v>
+      </c>
+      <c r="H581" s="4">
+        <f>IF(G581&gt;0,1000/G581,"")</f>
+        <v/>
+      </c>
+      <c r="I581" s="3" t="n">
+        <v>17.21</v>
+      </c>
+      <c r="J581" s="3" t="n">
+        <v>16.425</v>
+      </c>
+      <c r="K581" s="3" t="n">
+        <v>0.554</v>
+      </c>
+      <c r="L581" s="3" t="n">
+        <v>0.644</v>
+      </c>
+      <c r="M581" s="3" t="n"/>
+      <c r="N581" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O581" s="2" t="inlineStr">
+        <is>
+          <t>coll_cout_B0, coll_cout_B1</t>
+        </is>
+      </c>
+      <c r="P581" s="3" t="n">
+        <v>13.531</v>
+      </c>
+      <c r="Q581" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:16</t>
+        </is>
+      </c>
+      <c r="B582" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C582" s="2" t="inlineStr">
+        <is>
+          <t>21. Lasers : collisions actives (essai, test avec branchement)</t>
+        </is>
+      </c>
+      <c r="D582" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, lasercoll=1, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E582" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F582" s="2" t="inlineStr">
+        <is>
+          <t>L2 cones 200 x 32 segments / scene</t>
+        </is>
+      </c>
+      <c r="G582" s="3" t="n">
+        <v>18.225</v>
+      </c>
+      <c r="H582" s="4">
+        <f>IF(G582&gt;0,1000/G582,"")</f>
+        <v/>
+      </c>
+      <c r="I582" s="3" t="n">
+        <v>17.45</v>
+      </c>
+      <c r="J582" s="3" t="n">
+        <v>16.61</v>
+      </c>
+      <c r="K582" s="3" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="L582" s="3" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M582" s="3" t="n"/>
+      <c r="N582" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O582" s="2" t="inlineStr">
+        <is>
+          <t>coll_cout_B0, coll_cout_B1</t>
+        </is>
+      </c>
+      <c r="P582" s="3" t="n">
+        <v>13.581</v>
+      </c>
+      <c r="Q582" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:16</t>
+        </is>
+      </c>
+      <c r="B583" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C583" s="2" t="inlineStr">
+        <is>
+          <t>21. Lasers : collisions actives (essai, test avec branchement)</t>
+        </is>
+      </c>
+      <c r="D583" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, lasercoll=1, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E583" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F583" s="2" t="inlineStr">
+        <is>
+          <t>L3 camera dans les nappes</t>
+        </is>
+      </c>
+      <c r="G583" s="3" t="n">
+        <v>13.07</v>
+      </c>
+      <c r="H583" s="4">
+        <f>IF(G583&gt;0,1000/G583,"")</f>
+        <v/>
+      </c>
+      <c r="I583" s="3" t="n">
+        <v>12.545</v>
+      </c>
+      <c r="J583" s="3" t="n">
+        <v>11.515</v>
+      </c>
+      <c r="K583" s="3" t="n">
+        <v>0.758</v>
+      </c>
+      <c r="L583" s="3" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="M583" s="3" t="n"/>
+      <c r="N583" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O583" s="2" t="inlineStr">
+        <is>
+          <t>coll_cout_B0, coll_cout_B1</t>
+        </is>
+      </c>
+      <c r="P583" s="3" t="n">
+        <v>8.529</v>
+      </c>
+      <c r="Q583" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:16</t>
+        </is>
+      </c>
+      <c r="B584" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C584" s="2" t="inlineStr">
+        <is>
+          <t>21. Lasers : collisions actives (essai, test avec branchement)</t>
+        </is>
+      </c>
+      <c r="D584" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, lasercoll=1, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E584" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F584" s="2" t="inlineStr">
+        <is>
+          <t>L4 200 x 8 traits separes / public</t>
+        </is>
+      </c>
+      <c r="G584" s="3" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="H584" s="4">
+        <f>IF(G584&gt;0,1000/G584,"")</f>
+        <v/>
+      </c>
+      <c r="I584" s="3" t="n">
+        <v>5.125</v>
+      </c>
+      <c r="J584" s="3" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="K584" s="3" t="n">
+        <v>0.783</v>
+      </c>
+      <c r="L584" s="3" t="n">
+        <v>0.657</v>
+      </c>
+      <c r="M584" s="3" t="n"/>
+      <c r="N584" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O584" s="2" t="inlineStr">
+        <is>
+          <t>coll_cout_B0, coll_cout_B1</t>
+        </is>
+      </c>
+      <c r="P584" s="3" t="n">
+        <v>1.641</v>
+      </c>
+      <c r="Q584" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:16</t>
+        </is>
+      </c>
+      <c r="B585" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C585" s="2" t="inlineStr">
+        <is>
+          <t>21. Lasers : collisions actives (essai, test avec branchement)</t>
+        </is>
+      </c>
+      <c r="D585" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, lasercoll=1, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E585" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F585" s="2" t="inlineStr">
+        <is>
+          <t>L5 nappes en gros plan, fumee epaisse</t>
+        </is>
+      </c>
+      <c r="G585" s="3" t="n">
+        <v>13.22</v>
+      </c>
+      <c r="H585" s="4">
+        <f>IF(G585&gt;0,1000/G585,"")</f>
+        <v/>
+      </c>
+      <c r="I585" s="3" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="J585" s="3" t="n">
+        <v>11.67</v>
+      </c>
+      <c r="K585" s="3" t="n">
+        <v>0.589</v>
+      </c>
+      <c r="L585" s="3" t="n">
+        <v>0.642</v>
+      </c>
+      <c r="M585" s="3" t="n"/>
+      <c r="N585" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O585" s="2" t="inlineStr">
+        <is>
+          <t>coll_cout_B0, coll_cout_B1</t>
+        </is>
+      </c>
+      <c r="P585" s="3" t="n">
+        <v>8.678000000000001</v>
+      </c>
+      <c r="Q585" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:16</t>
+        </is>
+      </c>
+      <c r="B586" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C586" s="2" t="inlineStr">
+        <is>
+          <t>21. Lasers : collisions actives (essai, test avec branchement)</t>
+        </is>
+      </c>
+      <c r="D586" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, lasercoll=1, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E586" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F586" s="2" t="inlineStr">
+        <is>
+          <t>L6 traits vers le sol et les obstacles / public</t>
+        </is>
+      </c>
+      <c r="G586" s="3" t="n">
+        <v>14.875</v>
+      </c>
+      <c r="H586" s="4">
+        <f>IF(G586&gt;0,1000/G586,"")</f>
+        <v/>
+      </c>
+      <c r="I586" s="3" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="J586" s="3" t="n">
+        <v>13.405</v>
+      </c>
+      <c r="K586" s="3" t="n">
+        <v>0.804</v>
+      </c>
+      <c r="L586" s="3" t="n">
+        <v>0.677</v>
+      </c>
+      <c r="M586" s="3" t="n"/>
+      <c r="N586" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O586" s="2" t="inlineStr">
+        <is>
+          <t>coll_cout_B0, coll_cout_B1</t>
+        </is>
+      </c>
+      <c r="P586" s="3" t="n">
+        <v>10.277</v>
+      </c>
+      <c r="Q586" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:16</t>
+        </is>
+      </c>
+      <c r="B587" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C587" s="2" t="inlineStr">
+        <is>
+          <t>21. Lasers : collisions actives (essai, test avec branchement)</t>
+        </is>
+      </c>
+      <c r="D587" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, lasercoll=1, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E587" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F587" s="2" t="inlineStr">
+        <is>
+          <t>M1 100 lyres + 100 lasers / public</t>
+        </is>
+      </c>
+      <c r="G587" s="3" t="n">
+        <v>11.29</v>
+      </c>
+      <c r="H587" s="4">
+        <f>IF(G587&gt;0,1000/G587,"")</f>
+        <v/>
+      </c>
+      <c r="I587" s="3" t="n">
+        <v>10.395</v>
+      </c>
+      <c r="J587" s="3" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="K587" s="3" t="n">
+        <v>1.226</v>
+      </c>
+      <c r="L587" s="3" t="n">
+        <v>1.397</v>
+      </c>
+      <c r="M587" s="3" t="n"/>
+      <c r="N587" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="O587" s="2" t="inlineStr">
+        <is>
+          <t>coll_cout_B0, coll_cout_B1</t>
+        </is>
+      </c>
+      <c r="P587" s="3" t="n">
+        <v>4.948</v>
+      </c>
+      <c r="Q587" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:16</t>
+        </is>
+      </c>
+      <c r="B588" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C588" s="2" t="inlineStr">
+        <is>
+          <t>21. Lasers : collisions actives (essai, test avec branchement)</t>
+        </is>
+      </c>
+      <c r="D588" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, lasercoll=1, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E588" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F588" s="2" t="inlineStr">
+        <is>
+          <t>M1 100 lyres + 100 lasers / scene</t>
+        </is>
+      </c>
+      <c r="G588" s="3" t="n">
+        <v>11.225</v>
+      </c>
+      <c r="H588" s="4">
+        <f>IF(G588&gt;0,1000/G588,"")</f>
+        <v/>
+      </c>
+      <c r="I588" s="3" t="n">
+        <v>10.545</v>
+      </c>
+      <c r="J588" s="3" t="n">
+        <v>8.994999999999999</v>
+      </c>
+      <c r="K588" s="3" t="n">
+        <v>1.165</v>
+      </c>
+      <c r="L588" s="3" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="M588" s="3" t="n"/>
+      <c r="N588" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="O588" s="2" t="inlineStr">
+        <is>
+          <t>coll_cout_B0, coll_cout_B1</t>
+        </is>
+      </c>
+      <c r="P588" s="3" t="n">
+        <v>4.225</v>
+      </c>
+      <c r="Q588" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:16</t>
+        </is>
+      </c>
+      <c r="B589" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C589" s="2" t="inlineStr">
+        <is>
+          <t>21. Lasers : collisions actives (essai, test avec branchement)</t>
+        </is>
+      </c>
+      <c r="D589" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, lasercoll=1, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E589" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F589" s="2" t="inlineStr">
+        <is>
+          <t>M1 100 lyres + 100 lasers / sous les trusses</t>
+        </is>
+      </c>
+      <c r="G589" s="3" t="n">
+        <v>10.325</v>
+      </c>
+      <c r="H589" s="4">
+        <f>IF(G589&gt;0,1000/G589,"")</f>
+        <v/>
+      </c>
+      <c r="I589" s="3" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="J589" s="3" t="n">
+        <v>8.225</v>
+      </c>
+      <c r="K589" s="3" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="L589" s="3" t="n">
+        <v>1.306</v>
+      </c>
+      <c r="M589" s="3" t="n"/>
+      <c r="N589" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="O589" s="2" t="inlineStr">
+        <is>
+          <t>coll_cout_B0, coll_cout_B1</t>
+        </is>
+      </c>
+      <c r="P589" s="3" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="Q589" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:16</t>
+        </is>
+      </c>
+      <c r="B590" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C590" s="2" t="inlineStr">
+        <is>
+          <t>21. Lasers : collisions actives (essai, test avec branchement)</t>
+        </is>
+      </c>
+      <c r="D590" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, lasercoll=1, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E590" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F590" s="2" t="inlineStr">
+        <is>
+          <t>sans lasers (scene seule) / public</t>
+        </is>
+      </c>
+      <c r="G590" s="3" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="H590" s="4">
+        <f>IF(G590&gt;0,1000/G590,"")</f>
+        <v/>
+      </c>
+      <c r="I590" s="3" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="J590" s="3" t="n">
+        <v>2.575</v>
+      </c>
+      <c r="K590" s="3" t="n">
+        <v>0.781</v>
+      </c>
+      <c r="L590" s="3" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="M590" s="3" t="n"/>
+      <c r="N590" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O590" s="2" t="inlineStr">
+        <is>
+          <t>coll_cout_B0, coll_cout_B1</t>
+        </is>
+      </c>
+      <c r="P590" s="3" t="n"/>
+      <c r="Q590" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:16</t>
+        </is>
+      </c>
+      <c r="B591" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C591" s="2" t="inlineStr">
+        <is>
+          <t>21. Lasers : collisions actives (essai, test avec branchement)</t>
+        </is>
+      </c>
+      <c r="D591" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, lasercoll=1, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E591" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F591" s="2" t="inlineStr">
+        <is>
+          <t>L7 programmeur : formes, degrades, effets / public</t>
+        </is>
+      </c>
+      <c r="G591" s="3" t="n">
+        <v>24.575</v>
+      </c>
+      <c r="H591" s="4">
+        <f>IF(G591&gt;0,1000/G591,"")</f>
+        <v/>
+      </c>
+      <c r="I591" s="3" t="n">
+        <v>23.92</v>
+      </c>
+      <c r="J591" s="3" t="n">
+        <v>23.005</v>
+      </c>
+      <c r="K591" s="3" t="n">
+        <v>0.774</v>
+      </c>
+      <c r="L591" s="3" t="n">
+        <v>0.677</v>
+      </c>
+      <c r="M591" s="3" t="n"/>
+      <c r="N591" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O591" s="2" t="inlineStr">
+        <is>
+          <t>coll_cout_B0, coll_cout_B1</t>
+        </is>
+      </c>
+      <c r="P591" s="3" t="n">
+        <v>19.602</v>
+      </c>
+      <c r="Q591" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:16</t>
+        </is>
+      </c>
+      <c r="B592" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C592" s="2" t="inlineStr">
+        <is>
+          <t>21. Lasers : collisions actives (essai, test avec branchement)</t>
+        </is>
+      </c>
+      <c r="D592" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, lasercoll=1, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E592" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F592" s="2" t="inlineStr">
+        <is>
+          <t>I1 ILDA nappes (banque Nappes) / public</t>
+        </is>
+      </c>
+      <c r="G592" s="3" t="n">
+        <v>39.86</v>
+      </c>
+      <c r="H592" s="4">
+        <f>IF(G592&gt;0,1000/G592,"")</f>
+        <v/>
+      </c>
+      <c r="I592" s="3" t="n">
+        <v>39.015</v>
+      </c>
+      <c r="J592" s="3" t="n">
+        <v>38.02</v>
+      </c>
+      <c r="K592" s="3" t="n">
+        <v>0.779</v>
+      </c>
+      <c r="L592" s="3" t="n">
+        <v>0.679</v>
+      </c>
+      <c r="M592" s="3" t="n"/>
+      <c r="N592" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O592" s="2" t="inlineStr">
+        <is>
+          <t>coll_cout_B0, coll_cout_B1</t>
+        </is>
+      </c>
+      <c r="P592" s="3" t="n">
+        <v>34.752</v>
+      </c>
+      <c r="Q592" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:16</t>
+        </is>
+      </c>
+      <c r="B593" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C593" s="2" t="inlineStr">
+        <is>
+          <t>21. Lasers : collisions actives (essai, test avec branchement)</t>
+        </is>
+      </c>
+      <c r="D593" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, lasercoll=1, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E593" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F593" s="2" t="inlineStr">
+        <is>
+          <t>I2 ILDA faisceaux (banque Faisceaux) / public</t>
+        </is>
+      </c>
+      <c r="G593" s="3" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="H593" s="4">
+        <f>IF(G593&gt;0,1000/G593,"")</f>
+        <v/>
+      </c>
+      <c r="I593" s="3" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="J593" s="3" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="K593" s="3" t="n">
+        <v>0.783</v>
+      </c>
+      <c r="L593" s="3" t="n">
+        <v>0.657</v>
+      </c>
+      <c r="M593" s="3" t="n"/>
+      <c r="N593" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O593" s="2" t="inlineStr">
+        <is>
+          <t>coll_cout_B0, coll_cout_B1</t>
+        </is>
+      </c>
+      <c r="P593" s="3" t="n">
+        <v>2.066</v>
+      </c>
+      <c r="Q593" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:16</t>
+        </is>
+      </c>
+      <c r="B594" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C594" s="2" t="inlineStr">
+        <is>
+          <t>21. Lasers : collisions actives (essai, test avec branchement)</t>
+        </is>
+      </c>
+      <c r="D594" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, lasercoll=1, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E594" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F594" s="2" t="inlineStr">
+        <is>
+          <t>I3 ILDA geometrie (banque Geometrie) / public</t>
+        </is>
+      </c>
+      <c r="G594" s="3" t="n">
+        <v>53.53</v>
+      </c>
+      <c r="H594" s="4">
+        <f>IF(G594&gt;0,1000/G594,"")</f>
+        <v/>
+      </c>
+      <c r="I594" s="3" t="n">
+        <v>52.875</v>
+      </c>
+      <c r="J594" s="3" t="n">
+        <v>52.35</v>
+      </c>
+      <c r="K594" s="3" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="L594" s="3" t="n">
+        <v>0.669</v>
+      </c>
+      <c r="M594" s="3" t="n"/>
+      <c r="N594" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O594" s="2" t="inlineStr">
+        <is>
+          <t>coll_cout_B0, coll_cout_B1</t>
+        </is>
+      </c>
+      <c r="P594" s="3" t="n">
+        <v>49.216</v>
+      </c>
+      <c r="Q594" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:16</t>
+        </is>
+      </c>
+      <c r="B595" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C595" s="2" t="inlineStr">
+        <is>
+          <t>21. Lasers : collisions actives (essai, test avec branchement)</t>
+        </is>
+      </c>
+      <c r="D595" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, lasercoll=1, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E595" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F595" s="2" t="inlineStr">
+        <is>
+          <t>I4 ILDA tunnels (banque Tunnels) / public</t>
+        </is>
+      </c>
+      <c r="G595" s="3" t="n">
+        <v>37.365</v>
+      </c>
+      <c r="H595" s="4">
+        <f>IF(G595&gt;0,1000/G595,"")</f>
+        <v/>
+      </c>
+      <c r="I595" s="3" t="n">
+        <v>36.575</v>
+      </c>
+      <c r="J595" s="3" t="n">
+        <v>36.03</v>
+      </c>
+      <c r="K595" s="3" t="n">
+        <v>0.781</v>
+      </c>
+      <c r="L595" s="3" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="M595" s="3" t="n"/>
+      <c r="N595" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O595" s="2" t="inlineStr">
+        <is>
+          <t>coll_cout_B0, coll_cout_B1</t>
+        </is>
+      </c>
+      <c r="P595" s="3" t="n">
+        <v>32.821</v>
+      </c>
+      <c r="Q595" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:16</t>
+        </is>
+      </c>
+      <c r="B596" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C596" s="2" t="inlineStr">
+        <is>
+          <t>21. Lasers : collisions actives (essai, test avec branchement)</t>
+        </is>
+      </c>
+      <c r="D596" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, lasercoll=1, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E596" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F596" s="2" t="inlineStr">
+        <is>
+          <t>L1 en mode ligne (nappes continues) / public</t>
+        </is>
+      </c>
+      <c r="G596" s="3" t="n">
+        <v>12.145</v>
+      </c>
+      <c r="H596" s="4">
+        <f>IF(G596&gt;0,1000/G596,"")</f>
+        <v/>
+      </c>
+      <c r="I596" s="3" t="n">
+        <v>11.365</v>
+      </c>
+      <c r="J596" s="3" t="n">
+        <v>10.965</v>
+      </c>
+      <c r="K596" s="3" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="L596" s="3" t="n">
+        <v>0.669</v>
+      </c>
+      <c r="M596" s="3" t="n"/>
+      <c r="N596" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O596" s="2" t="inlineStr">
+        <is>
+          <t>coll_cout_B0, coll_cout_B1</t>
+        </is>
+      </c>
+      <c r="P596" s="3" t="n">
+        <v>7.96</v>
+      </c>
+      <c r="Q596" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:32</t>
+        </is>
+      </c>
+      <c r="B597" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C597" s="2" t="inlineStr">
+        <is>
+          <t>22. Lasers : impacts coupes (laserimpacts=0)</t>
+        </is>
+      </c>
+      <c r="D597" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, laserimpacts=0, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E597" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F597" s="2" t="inlineStr">
+        <is>
+          <t>L1 eventails 200 x 1000 traits / public</t>
+        </is>
+      </c>
+      <c r="G597" s="3" t="n">
+        <v>13.67</v>
+      </c>
+      <c r="H597" s="4">
+        <f>IF(G597&gt;0,1000/G597,"")</f>
+        <v/>
+      </c>
+      <c r="I597" s="3" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="J597" s="3" t="n">
+        <v>11.935</v>
+      </c>
+      <c r="K597" s="3" t="n">
+        <v>0.541</v>
+      </c>
+      <c r="L597" s="3" t="n">
+        <v>0.653</v>
+      </c>
+      <c r="M597" s="3" t="n"/>
+      <c r="N597" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O597" s="2" t="inlineStr">
+        <is>
+          <t>imp_cout2_A0, imp_cout2_A1</t>
+        </is>
+      </c>
+      <c r="P597" s="3" t="n">
+        <v>8.962</v>
+      </c>
+      <c r="Q597" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:32</t>
+        </is>
+      </c>
+      <c r="B598" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C598" s="2" t="inlineStr">
+        <is>
+          <t>22. Lasers : impacts coupes (laserimpacts=0)</t>
+        </is>
+      </c>
+      <c r="D598" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, laserimpacts=0, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E598" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F598" s="2" t="inlineStr">
+        <is>
+          <t>L1 eventails 200 x 1000 traits / scene</t>
+        </is>
+      </c>
+      <c r="G598" s="3" t="n">
+        <v>12.83</v>
+      </c>
+      <c r="H598" s="4">
+        <f>IF(G598&gt;0,1000/G598,"")</f>
+        <v/>
+      </c>
+      <c r="I598" s="3" t="n">
+        <v>12.01</v>
+      </c>
+      <c r="J598" s="3" t="n">
+        <v>11.095</v>
+      </c>
+      <c r="K598" s="3" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="L598" s="3" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="M598" s="3" t="n"/>
+      <c r="N598" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O598" s="2" t="inlineStr">
+        <is>
+          <t>imp_cout2_A0, imp_cout2_A1</t>
+        </is>
+      </c>
+      <c r="P598" s="3" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="Q598" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:32</t>
+        </is>
+      </c>
+      <c r="B599" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C599" s="2" t="inlineStr">
+        <is>
+          <t>22. Lasers : impacts coupes (laserimpacts=0)</t>
+        </is>
+      </c>
+      <c r="D599" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, laserimpacts=0, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E599" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F599" s="2" t="inlineStr">
+        <is>
+          <t>L1 eventails 200 x 1000 traits / sous les trusses</t>
+        </is>
+      </c>
+      <c r="G599" s="3" t="n">
+        <v>12.05</v>
+      </c>
+      <c r="H599" s="4">
+        <f>IF(G599&gt;0,1000/G599,"")</f>
+        <v/>
+      </c>
+      <c r="I599" s="3" t="n">
+        <v>11.085</v>
+      </c>
+      <c r="J599" s="3" t="n">
+        <v>10.455</v>
+      </c>
+      <c r="K599" s="3" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="L599" s="3" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="M599" s="3" t="n"/>
+      <c r="N599" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O599" s="2" t="inlineStr">
+        <is>
+          <t>imp_cout2_A0, imp_cout2_A1</t>
+        </is>
+      </c>
+      <c r="P599" s="3" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="Q599" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:32</t>
+        </is>
+      </c>
+      <c r="B600" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C600" s="2" t="inlineStr">
+        <is>
+          <t>22. Lasers : impacts coupes (laserimpacts=0)</t>
+        </is>
+      </c>
+      <c r="D600" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, laserimpacts=0, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E600" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F600" s="2" t="inlineStr">
+        <is>
+          <t>L2 cones 200 x 32 segments / public</t>
+        </is>
+      </c>
+      <c r="G600" s="3" t="n">
+        <v>18.28</v>
+      </c>
+      <c r="H600" s="4">
+        <f>IF(G600&gt;0,1000/G600,"")</f>
+        <v/>
+      </c>
+      <c r="I600" s="3" t="n">
+        <v>17.475</v>
+      </c>
+      <c r="J600" s="3" t="n">
+        <v>16.56</v>
+      </c>
+      <c r="K600" s="3" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="L600" s="3" t="n">
+        <v>0.6830000000000001</v>
+      </c>
+      <c r="M600" s="3" t="n"/>
+      <c r="N600" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O600" s="2" t="inlineStr">
+        <is>
+          <t>imp_cout2_A0, imp_cout2_A1</t>
+        </is>
+      </c>
+      <c r="P600" s="3" t="n">
+        <v>13.591</v>
+      </c>
+      <c r="Q600" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:32</t>
+        </is>
+      </c>
+      <c r="B601" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C601" s="2" t="inlineStr">
+        <is>
+          <t>22. Lasers : impacts coupes (laserimpacts=0)</t>
+        </is>
+      </c>
+      <c r="D601" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, laserimpacts=0, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E601" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F601" s="2" t="inlineStr">
+        <is>
+          <t>L2 cones 200 x 32 segments / scene</t>
+        </is>
+      </c>
+      <c r="G601" s="3" t="n">
+        <v>18.14</v>
+      </c>
+      <c r="H601" s="4">
+        <f>IF(G601&gt;0,1000/G601,"")</f>
+        <v/>
+      </c>
+      <c r="I601" s="3" t="n">
+        <v>17.455</v>
+      </c>
+      <c r="J601" s="3" t="n">
+        <v>16.58</v>
+      </c>
+      <c r="K601" s="3" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="L601" s="3" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="M601" s="3" t="n"/>
+      <c r="N601" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O601" s="2" t="inlineStr">
+        <is>
+          <t>imp_cout2_A0, imp_cout2_A1</t>
+        </is>
+      </c>
+      <c r="P601" s="3" t="n">
+        <v>13.35</v>
+      </c>
+      <c r="Q601" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:32</t>
+        </is>
+      </c>
+      <c r="B602" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C602" s="2" t="inlineStr">
+        <is>
+          <t>22. Lasers : impacts coupes (laserimpacts=0)</t>
+        </is>
+      </c>
+      <c r="D602" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, laserimpacts=0, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E602" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F602" s="2" t="inlineStr">
+        <is>
+          <t>L3 camera dans les nappes</t>
+        </is>
+      </c>
+      <c r="G602" s="3" t="n">
+        <v>13.19</v>
+      </c>
+      <c r="H602" s="4">
+        <f>IF(G602&gt;0,1000/G602,"")</f>
+        <v/>
+      </c>
+      <c r="I602" s="3" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="J602" s="3" t="n">
+        <v>11.73</v>
+      </c>
+      <c r="K602" s="3" t="n">
+        <v>0.744</v>
+      </c>
+      <c r="L602" s="3" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="M602" s="3" t="n"/>
+      <c r="N602" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O602" s="2" t="inlineStr">
+        <is>
+          <t>imp_cout2_A0, imp_cout2_A1</t>
+        </is>
+      </c>
+      <c r="P602" s="3" t="n">
+        <v>8.645</v>
+      </c>
+      <c r="Q602" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:32</t>
+        </is>
+      </c>
+      <c r="B603" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C603" s="2" t="inlineStr">
+        <is>
+          <t>22. Lasers : impacts coupes (laserimpacts=0)</t>
+        </is>
+      </c>
+      <c r="D603" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, laserimpacts=0, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E603" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F603" s="2" t="inlineStr">
+        <is>
+          <t>L4 200 x 8 traits separes / public</t>
+        </is>
+      </c>
+      <c r="G603" s="3" t="n">
+        <v>7.735</v>
+      </c>
+      <c r="H603" s="4">
+        <f>IF(G603&gt;0,1000/G603,"")</f>
+        <v/>
+      </c>
+      <c r="I603" s="3" t="n">
+        <v>7.065</v>
+      </c>
+      <c r="J603" s="3" t="n">
+        <v>6.895</v>
+      </c>
+      <c r="K603" s="3" t="n">
+        <v>0.536</v>
+      </c>
+      <c r="L603" s="3" t="n">
+        <v>2.839</v>
+      </c>
+      <c r="M603" s="3" t="n"/>
+      <c r="N603" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O603" s="2" t="inlineStr">
+        <is>
+          <t>imp_cout2_A0, imp_cout2_A1</t>
+        </is>
+      </c>
+      <c r="P603" s="3" t="n">
+        <v>1.635</v>
+      </c>
+      <c r="Q603" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:32</t>
+        </is>
+      </c>
+      <c r="B604" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C604" s="2" t="inlineStr">
+        <is>
+          <t>22. Lasers : impacts coupes (laserimpacts=0)</t>
+        </is>
+      </c>
+      <c r="D604" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, laserimpacts=0, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E604" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F604" s="2" t="inlineStr">
+        <is>
+          <t>L5 nappes en gros plan, fumee epaisse</t>
+        </is>
+      </c>
+      <c r="G604" s="3" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="H604" s="4">
+        <f>IF(G604&gt;0,1000/G604,"")</f>
+        <v/>
+      </c>
+      <c r="I604" s="3" t="n">
+        <v>12.11</v>
+      </c>
+      <c r="J604" s="3" t="n">
+        <v>11.515</v>
+      </c>
+      <c r="K604" s="3" t="n">
+        <v>0.803</v>
+      </c>
+      <c r="L604" s="3" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="M604" s="3" t="n"/>
+      <c r="N604" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O604" s="2" t="inlineStr">
+        <is>
+          <t>imp_cout2_A0, imp_cout2_A1</t>
+        </is>
+      </c>
+      <c r="P604" s="3" t="n">
+        <v>8.544</v>
+      </c>
+      <c r="Q604" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:32</t>
+        </is>
+      </c>
+      <c r="B605" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C605" s="2" t="inlineStr">
+        <is>
+          <t>22. Lasers : impacts coupes (laserimpacts=0)</t>
+        </is>
+      </c>
+      <c r="D605" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, laserimpacts=0, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E605" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F605" s="2" t="inlineStr">
+        <is>
+          <t>L6 traits vers le sol et les obstacles / public</t>
+        </is>
+      </c>
+      <c r="G605" s="3" t="n">
+        <v>15.34</v>
+      </c>
+      <c r="H605" s="4">
+        <f>IF(G605&gt;0,1000/G605,"")</f>
+        <v/>
+      </c>
+      <c r="I605" s="3" t="n">
+        <v>14.465</v>
+      </c>
+      <c r="J605" s="3" t="n">
+        <v>13.055</v>
+      </c>
+      <c r="K605" s="3" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="L605" s="3" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="M605" s="3" t="n"/>
+      <c r="N605" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O605" s="2" t="inlineStr">
+        <is>
+          <t>imp_cout2_A0, imp_cout2_A1</t>
+        </is>
+      </c>
+      <c r="P605" s="3" t="n">
+        <v>10.093</v>
+      </c>
+      <c r="Q605" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:32</t>
+        </is>
+      </c>
+      <c r="B606" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C606" s="2" t="inlineStr">
+        <is>
+          <t>22. Lasers : impacts coupes (laserimpacts=0)</t>
+        </is>
+      </c>
+      <c r="D606" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, laserimpacts=0, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E606" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F606" s="2" t="inlineStr">
+        <is>
+          <t>M1 100 lyres + 100 lasers / public</t>
+        </is>
+      </c>
+      <c r="G606" s="3" t="n">
+        <v>11.605</v>
+      </c>
+      <c r="H606" s="4">
+        <f>IF(G606&gt;0,1000/G606,"")</f>
+        <v/>
+      </c>
+      <c r="I606" s="3" t="n">
+        <v>10.675</v>
+      </c>
+      <c r="J606" s="3" t="n">
+        <v>10.065</v>
+      </c>
+      <c r="K606" s="3" t="n">
+        <v>1.241</v>
+      </c>
+      <c r="L606" s="3" t="n">
+        <v>1.422</v>
+      </c>
+      <c r="M606" s="3" t="n"/>
+      <c r="N606" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="O606" s="2" t="inlineStr">
+        <is>
+          <t>imp_cout2_A0, imp_cout2_A1</t>
+        </is>
+      </c>
+      <c r="P606" s="3" t="n">
+        <v>4.907</v>
+      </c>
+      <c r="Q606" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:32</t>
+        </is>
+      </c>
+      <c r="B607" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C607" s="2" t="inlineStr">
+        <is>
+          <t>22. Lasers : impacts coupes (laserimpacts=0)</t>
+        </is>
+      </c>
+      <c r="D607" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, laserimpacts=0, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E607" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F607" s="2" t="inlineStr">
+        <is>
+          <t>M1 100 lyres + 100 lasers / scene</t>
+        </is>
+      </c>
+      <c r="G607" s="3" t="n">
+        <v>11.485</v>
+      </c>
+      <c r="H607" s="4">
+        <f>IF(G607&gt;0,1000/G607,"")</f>
+        <v/>
+      </c>
+      <c r="I607" s="3" t="n">
+        <v>10.545</v>
+      </c>
+      <c r="J607" s="3" t="n">
+        <v>9.055</v>
+      </c>
+      <c r="K607" s="3" t="n">
+        <v>1.181</v>
+      </c>
+      <c r="L607" s="3" t="n">
+        <v>1.406</v>
+      </c>
+      <c r="M607" s="3" t="n"/>
+      <c r="N607" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="O607" s="2" t="inlineStr">
+        <is>
+          <t>imp_cout2_A0, imp_cout2_A1</t>
+        </is>
+      </c>
+      <c r="P607" s="3" t="n">
+        <v>4.242</v>
+      </c>
+      <c r="Q607" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:32</t>
+        </is>
+      </c>
+      <c r="B608" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C608" s="2" t="inlineStr">
+        <is>
+          <t>22. Lasers : impacts coupes (laserimpacts=0)</t>
+        </is>
+      </c>
+      <c r="D608" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, laserimpacts=0, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E608" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F608" s="2" t="inlineStr">
+        <is>
+          <t>M1 100 lyres + 100 lasers / sous les trusses</t>
+        </is>
+      </c>
+      <c r="G608" s="3" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="H608" s="4">
+        <f>IF(G608&gt;0,1000/G608,"")</f>
+        <v/>
+      </c>
+      <c r="I608" s="3" t="n">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="J608" s="3" t="n">
+        <v>8.195</v>
+      </c>
+      <c r="K608" s="3" t="n">
+        <v>0.914</v>
+      </c>
+      <c r="L608" s="3" t="n">
+        <v>1.315</v>
+      </c>
+      <c r="M608" s="3" t="n"/>
+      <c r="N608" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="O608" s="2" t="inlineStr">
+        <is>
+          <t>imp_cout2_A0, imp_cout2_A1</t>
+        </is>
+      </c>
+      <c r="P608" s="3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Q608" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:32</t>
+        </is>
+      </c>
+      <c r="B609" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C609" s="2" t="inlineStr">
+        <is>
+          <t>22. Lasers : impacts coupes (laserimpacts=0)</t>
+        </is>
+      </c>
+      <c r="D609" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, laserimpacts=0, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E609" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F609" s="2" t="inlineStr">
+        <is>
+          <t>sans lasers (scene seule) / public</t>
+        </is>
+      </c>
+      <c r="G609" s="3" t="n">
+        <v>5.195</v>
+      </c>
+      <c r="H609" s="4">
+        <f>IF(G609&gt;0,1000/G609,"")</f>
+        <v/>
+      </c>
+      <c r="I609" s="3" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="J609" s="3" t="n">
+        <v>2.595</v>
+      </c>
+      <c r="K609" s="3" t="n">
+        <v>0.779</v>
+      </c>
+      <c r="L609" s="3" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="M609" s="3" t="n"/>
+      <c r="N609" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O609" s="2" t="inlineStr">
+        <is>
+          <t>imp_cout2_A0, imp_cout2_A1</t>
+        </is>
+      </c>
+      <c r="P609" s="3" t="n"/>
+      <c r="Q609" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:32</t>
+        </is>
+      </c>
+      <c r="B610" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C610" s="2" t="inlineStr">
+        <is>
+          <t>22. Lasers : impacts coupes (laserimpacts=0)</t>
+        </is>
+      </c>
+      <c r="D610" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, laserimpacts=0, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E610" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F610" s="2" t="inlineStr">
+        <is>
+          <t>L7 programmeur : formes, degrades, effets / public</t>
+        </is>
+      </c>
+      <c r="G610" s="3" t="n">
+        <v>26.85</v>
+      </c>
+      <c r="H610" s="4">
+        <f>IF(G610&gt;0,1000/G610,"")</f>
+        <v/>
+      </c>
+      <c r="I610" s="3" t="n">
+        <v>25.955</v>
+      </c>
+      <c r="J610" s="3" t="n">
+        <v>25.235</v>
+      </c>
+      <c r="K610" s="3" t="n">
+        <v>0.752</v>
+      </c>
+      <c r="L610" s="3" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="M610" s="3" t="n"/>
+      <c r="N610" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O610" s="2" t="inlineStr">
+        <is>
+          <t>imp_cout2_A0, imp_cout2_A1</t>
+        </is>
+      </c>
+      <c r="P610" s="3" t="n">
+        <v>21.937</v>
+      </c>
+      <c r="Q610" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:32</t>
+        </is>
+      </c>
+      <c r="B611" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C611" s="2" t="inlineStr">
+        <is>
+          <t>22. Lasers : impacts coupes (laserimpacts=0)</t>
+        </is>
+      </c>
+      <c r="D611" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, laserimpacts=0, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E611" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F611" s="2" t="inlineStr">
+        <is>
+          <t>I1 ILDA nappes (banque Nappes) / public</t>
+        </is>
+      </c>
+      <c r="G611" s="3" t="n">
+        <v>41.56</v>
+      </c>
+      <c r="H611" s="4">
+        <f>IF(G611&gt;0,1000/G611,"")</f>
+        <v/>
+      </c>
+      <c r="I611" s="3" t="n">
+        <v>40.79</v>
+      </c>
+      <c r="J611" s="3" t="n">
+        <v>40.47</v>
+      </c>
+      <c r="K611" s="3" t="n">
+        <v>0.764</v>
+      </c>
+      <c r="L611" s="3" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="M611" s="3" t="n"/>
+      <c r="N611" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O611" s="2" t="inlineStr">
+        <is>
+          <t>imp_cout2_A0, imp_cout2_A1</t>
+        </is>
+      </c>
+      <c r="P611" s="3" t="n">
+        <v>36.915</v>
+      </c>
+      <c r="Q611" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:32</t>
+        </is>
+      </c>
+      <c r="B612" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C612" s="2" t="inlineStr">
+        <is>
+          <t>22. Lasers : impacts coupes (laserimpacts=0)</t>
+        </is>
+      </c>
+      <c r="D612" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, laserimpacts=0, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E612" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F612" s="2" t="inlineStr">
+        <is>
+          <t>I2 ILDA faisceaux (banque Faisceaux) / public</t>
+        </is>
+      </c>
+      <c r="G612" s="3" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="H612" s="4">
+        <f>IF(G612&gt;0,1000/G612,"")</f>
+        <v/>
+      </c>
+      <c r="I612" s="3" t="n">
+        <v>6.615</v>
+      </c>
+      <c r="J612" s="3" t="n">
+        <v>6.175</v>
+      </c>
+      <c r="K612" s="3" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L612" s="3" t="n">
+        <v>0.591</v>
+      </c>
+      <c r="M612" s="3" t="n"/>
+      <c r="N612" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O612" s="2" t="inlineStr">
+        <is>
+          <t>imp_cout2_A0, imp_cout2_A1</t>
+        </is>
+      </c>
+      <c r="P612" s="3" t="n">
+        <v>2.064</v>
+      </c>
+      <c r="Q612" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:32</t>
+        </is>
+      </c>
+      <c r="B613" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C613" s="2" t="inlineStr">
+        <is>
+          <t>22. Lasers : impacts coupes (laserimpacts=0)</t>
+        </is>
+      </c>
+      <c r="D613" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, laserimpacts=0, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E613" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F613" s="2" t="inlineStr">
+        <is>
+          <t>I3 ILDA geometrie (banque Geometrie) / public</t>
+        </is>
+      </c>
+      <c r="G613" s="3" t="n">
+        <v>57.525</v>
+      </c>
+      <c r="H613" s="4">
+        <f>IF(G613&gt;0,1000/G613,"")</f>
+        <v/>
+      </c>
+      <c r="I613" s="3" t="n">
+        <v>56.66</v>
+      </c>
+      <c r="J613" s="3" t="n">
+        <v>55.835</v>
+      </c>
+      <c r="K613" s="3" t="n">
+        <v>0.726</v>
+      </c>
+      <c r="L613" s="3" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="M613" s="3" t="n"/>
+      <c r="N613" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O613" s="2" t="inlineStr">
+        <is>
+          <t>imp_cout2_A0, imp_cout2_A1</t>
+        </is>
+      </c>
+      <c r="P613" s="3" t="n">
+        <v>52.444</v>
+      </c>
+      <c r="Q613" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:32</t>
+        </is>
+      </c>
+      <c r="B614" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C614" s="2" t="inlineStr">
+        <is>
+          <t>22. Lasers : impacts coupes (laserimpacts=0)</t>
+        </is>
+      </c>
+      <c r="D614" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, laserimpacts=0, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E614" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F614" s="2" t="inlineStr">
+        <is>
+          <t>I4 ILDA tunnels (banque Tunnels) / public</t>
+        </is>
+      </c>
+      <c r="G614" s="3" t="n">
+        <v>39.09</v>
+      </c>
+      <c r="H614" s="4">
+        <f>IF(G614&gt;0,1000/G614,"")</f>
+        <v/>
+      </c>
+      <c r="I614" s="3" t="n">
+        <v>38.42</v>
+      </c>
+      <c r="J614" s="3" t="n">
+        <v>37.93</v>
+      </c>
+      <c r="K614" s="3" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="L614" s="3" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="M614" s="3" t="n"/>
+      <c r="N614" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O614" s="2" t="inlineStr">
+        <is>
+          <t>imp_cout2_A0, imp_cout2_A1</t>
+        </is>
+      </c>
+      <c r="P614" s="3" t="n">
+        <v>34.133</v>
+      </c>
+      <c r="Q614" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:32</t>
+        </is>
+      </c>
+      <c r="B615" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C615" s="2" t="inlineStr">
+        <is>
+          <t>22. Lasers : impacts coupes (laserimpacts=0)</t>
+        </is>
+      </c>
+      <c r="D615" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, laserimpacts=0, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E615" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F615" s="2" t="inlineStr">
+        <is>
+          <t>L1 en mode ligne (nappes continues) / public</t>
+        </is>
+      </c>
+      <c r="G615" s="3" t="n">
+        <v>12.775</v>
+      </c>
+      <c r="H615" s="4">
+        <f>IF(G615&gt;0,1000/G615,"")</f>
+        <v/>
+      </c>
+      <c r="I615" s="3" t="n">
+        <v>12.145</v>
+      </c>
+      <c r="J615" s="3" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="K615" s="3" t="n">
+        <v>0.779</v>
+      </c>
+      <c r="L615" s="3" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="M615" s="3" t="n"/>
+      <c r="N615" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O615" s="2" t="inlineStr">
+        <is>
+          <t>imp_cout2_A0, imp_cout2_A1</t>
+        </is>
+      </c>
+      <c r="P615" s="3" t="n">
+        <v>8.428000000000001</v>
+      </c>
+      <c r="Q615" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:32</t>
+        </is>
+      </c>
+      <c r="B616" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C616" s="2" t="inlineStr">
+        <is>
+          <t>22. Lasers : impacts sur les surfaces</t>
+        </is>
+      </c>
+      <c r="D616" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, laserimpacts=1, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E616" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F616" s="2" t="inlineStr">
+        <is>
+          <t>L1 eventails 200 x 1000 traits / public</t>
+        </is>
+      </c>
+      <c r="G616" s="3" t="n">
+        <v>14.275</v>
+      </c>
+      <c r="H616" s="4">
+        <f>IF(G616&gt;0,1000/G616,"")</f>
+        <v/>
+      </c>
+      <c r="I616" s="3" t="n">
+        <v>13.61</v>
+      </c>
+      <c r="J616" s="3" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="K616" s="3" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="L616" s="3" t="n">
+        <v>0.663</v>
+      </c>
+      <c r="M616" s="3" t="n"/>
+      <c r="N616" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O616" s="2" t="inlineStr">
+        <is>
+          <t>imp_cout2_B0, imp_cout2_B1</t>
+        </is>
+      </c>
+      <c r="P616" s="3" t="n">
+        <v>9.337</v>
+      </c>
+      <c r="Q616" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:32</t>
+        </is>
+      </c>
+      <c r="B617" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C617" s="2" t="inlineStr">
+        <is>
+          <t>22. Lasers : impacts sur les surfaces</t>
+        </is>
+      </c>
+      <c r="D617" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, laserimpacts=1, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E617" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F617" s="2" t="inlineStr">
+        <is>
+          <t>L1 eventails 200 x 1000 traits / scene</t>
+        </is>
+      </c>
+      <c r="G617" s="3" t="n">
+        <v>13.835</v>
+      </c>
+      <c r="H617" s="4">
+        <f>IF(G617&gt;0,1000/G617,"")</f>
+        <v/>
+      </c>
+      <c r="I617" s="3" t="n">
+        <v>12.54</v>
+      </c>
+      <c r="J617" s="3" t="n">
+        <v>12.31</v>
+      </c>
+      <c r="K617" s="3" t="n">
+        <v>0.926</v>
+      </c>
+      <c r="L617" s="3" t="n">
+        <v>0.697</v>
+      </c>
+      <c r="M617" s="3" t="n"/>
+      <c r="N617" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O617" s="2" t="inlineStr">
+        <is>
+          <t>imp_cout2_B0, imp_cout2_B1</t>
+        </is>
+      </c>
+      <c r="P617" s="3" t="n">
+        <v>8.84</v>
+      </c>
+      <c r="Q617" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:32</t>
+        </is>
+      </c>
+      <c r="B618" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C618" s="2" t="inlineStr">
+        <is>
+          <t>22. Lasers : impacts sur les surfaces</t>
+        </is>
+      </c>
+      <c r="D618" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, laserimpacts=1, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E618" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F618" s="2" t="inlineStr">
+        <is>
+          <t>L1 eventails 200 x 1000 traits / sous les trusses</t>
+        </is>
+      </c>
+      <c r="G618" s="3" t="n">
+        <v>12.57</v>
+      </c>
+      <c r="H618" s="4">
+        <f>IF(G618&gt;0,1000/G618,"")</f>
+        <v/>
+      </c>
+      <c r="I618" s="3" t="n">
+        <v>11.93</v>
+      </c>
+      <c r="J618" s="3" t="n">
+        <v>11.64</v>
+      </c>
+      <c r="K618" s="3" t="n">
+        <v>0.798</v>
+      </c>
+      <c r="L618" s="3" t="n">
+        <v>0.798</v>
+      </c>
+      <c r="M618" s="3" t="n"/>
+      <c r="N618" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O618" s="2" t="inlineStr">
+        <is>
+          <t>imp_cout2_B0, imp_cout2_B1</t>
+        </is>
+      </c>
+      <c r="P618" s="3" t="n">
+        <v>8.271000000000001</v>
+      </c>
+      <c r="Q618" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:32</t>
+        </is>
+      </c>
+      <c r="B619" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C619" s="2" t="inlineStr">
+        <is>
+          <t>22. Lasers : impacts sur les surfaces</t>
+        </is>
+      </c>
+      <c r="D619" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, laserimpacts=1, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E619" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F619" s="2" t="inlineStr">
+        <is>
+          <t>L2 cones 200 x 32 segments / public</t>
+        </is>
+      </c>
+      <c r="G619" s="3" t="n">
+        <v>20.115</v>
+      </c>
+      <c r="H619" s="4">
+        <f>IF(G619&gt;0,1000/G619,"")</f>
+        <v/>
+      </c>
+      <c r="I619" s="3" t="n">
+        <v>19.375</v>
+      </c>
+      <c r="J619" s="3" t="n">
+        <v>18.425</v>
+      </c>
+      <c r="K619" s="3" t="n">
+        <v>0.919</v>
+      </c>
+      <c r="L619" s="3" t="n">
+        <v>0.598</v>
+      </c>
+      <c r="M619" s="3" t="n"/>
+      <c r="N619" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O619" s="2" t="inlineStr">
+        <is>
+          <t>imp_cout2_B0, imp_cout2_B1</t>
+        </is>
+      </c>
+      <c r="P619" s="3" t="n">
+        <v>15.095</v>
+      </c>
+      <c r="Q619" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:32</t>
+        </is>
+      </c>
+      <c r="B620" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C620" s="2" t="inlineStr">
+        <is>
+          <t>22. Lasers : impacts sur les surfaces</t>
+        </is>
+      </c>
+      <c r="D620" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, laserimpacts=1, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E620" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F620" s="2" t="inlineStr">
+        <is>
+          <t>L2 cones 200 x 32 segments / scene</t>
+        </is>
+      </c>
+      <c r="G620" s="3" t="n">
+        <v>20.115</v>
+      </c>
+      <c r="H620" s="4">
+        <f>IF(G620&gt;0,1000/G620,"")</f>
+        <v/>
+      </c>
+      <c r="I620" s="3" t="n">
+        <v>19.51</v>
+      </c>
+      <c r="J620" s="3" t="n">
+        <v>18.485</v>
+      </c>
+      <c r="K620" s="3" t="n">
+        <v>0.919</v>
+      </c>
+      <c r="L620" s="3" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="M620" s="3" t="n"/>
+      <c r="N620" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O620" s="2" t="inlineStr">
+        <is>
+          <t>imp_cout2_B0, imp_cout2_B1</t>
+        </is>
+      </c>
+      <c r="P620" s="3" t="n">
+        <v>15.213</v>
+      </c>
+      <c r="Q620" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:32</t>
+        </is>
+      </c>
+      <c r="B621" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C621" s="2" t="inlineStr">
+        <is>
+          <t>22. Lasers : impacts sur les surfaces</t>
+        </is>
+      </c>
+      <c r="D621" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, laserimpacts=1, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E621" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F621" s="2" t="inlineStr">
+        <is>
+          <t>L3 camera dans les nappes</t>
+        </is>
+      </c>
+      <c r="G621" s="3" t="n">
+        <v>14.585</v>
+      </c>
+      <c r="H621" s="4">
+        <f>IF(G621&gt;0,1000/G621,"")</f>
+        <v/>
+      </c>
+      <c r="I621" s="3" t="n">
+        <v>13.64</v>
+      </c>
+      <c r="J621" s="3" t="n">
+        <v>13.725</v>
+      </c>
+      <c r="K621" s="3" t="n">
+        <v>0.747</v>
+      </c>
+      <c r="L621" s="3" t="n">
+        <v>0.602</v>
+      </c>
+      <c r="M621" s="3" t="n"/>
+      <c r="N621" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O621" s="2" t="inlineStr">
+        <is>
+          <t>imp_cout2_B0, imp_cout2_B1</t>
+        </is>
+      </c>
+      <c r="P621" s="3" t="n">
+        <v>10.276</v>
+      </c>
+      <c r="Q621" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:32</t>
+        </is>
+      </c>
+      <c r="B622" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C622" s="2" t="inlineStr">
+        <is>
+          <t>22. Lasers : impacts sur les surfaces</t>
+        </is>
+      </c>
+      <c r="D622" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, laserimpacts=1, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E622" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F622" s="2" t="inlineStr">
+        <is>
+          <t>L4 200 x 8 traits separes / public</t>
+        </is>
+      </c>
+      <c r="G622" s="3" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="H622" s="4">
+        <f>IF(G622&gt;0,1000/G622,"")</f>
+        <v/>
+      </c>
+      <c r="I622" s="3" t="n">
+        <v>5.875</v>
+      </c>
+      <c r="J622" s="3" t="n">
+        <v>6.245</v>
+      </c>
+      <c r="K622" s="3" t="n">
+        <v>0.768</v>
+      </c>
+      <c r="L622" s="3" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="M622" s="3" t="n"/>
+      <c r="N622" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O622" s="2" t="inlineStr">
+        <is>
+          <t>imp_cout2_B0, imp_cout2_B1</t>
+        </is>
+      </c>
+      <c r="P622" s="3" t="n">
+        <v>1.637</v>
+      </c>
+      <c r="Q622" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:32</t>
+        </is>
+      </c>
+      <c r="B623" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C623" s="2" t="inlineStr">
+        <is>
+          <t>22. Lasers : impacts sur les surfaces</t>
+        </is>
+      </c>
+      <c r="D623" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, laserimpacts=1, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E623" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F623" s="2" t="inlineStr">
+        <is>
+          <t>L5 nappes en gros plan, fumee epaisse</t>
+        </is>
+      </c>
+      <c r="G623" s="3" t="n">
+        <v>14.265</v>
+      </c>
+      <c r="H623" s="4">
+        <f>IF(G623&gt;0,1000/G623,"")</f>
+        <v/>
+      </c>
+      <c r="I623" s="3" t="n">
+        <v>13.655</v>
+      </c>
+      <c r="J623" s="3" t="n">
+        <v>13.785</v>
+      </c>
+      <c r="K623" s="3" t="n">
+        <v>0.799</v>
+      </c>
+      <c r="L623" s="3" t="n">
+        <v>0.576</v>
+      </c>
+      <c r="M623" s="3" t="n"/>
+      <c r="N623" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O623" s="2" t="inlineStr">
+        <is>
+          <t>imp_cout2_B0, imp_cout2_B1</t>
+        </is>
+      </c>
+      <c r="P623" s="3" t="n">
+        <v>10.149</v>
+      </c>
+      <c r="Q623" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:32</t>
+        </is>
+      </c>
+      <c r="B624" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C624" s="2" t="inlineStr">
+        <is>
+          <t>22. Lasers : impacts sur les surfaces</t>
+        </is>
+      </c>
+      <c r="D624" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, laserimpacts=1, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E624" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F624" s="2" t="inlineStr">
+        <is>
+          <t>L6 traits vers le sol et les obstacles / public</t>
+        </is>
+      </c>
+      <c r="G624" s="3" t="n">
+        <v>16.64</v>
+      </c>
+      <c r="H624" s="4">
+        <f>IF(G624&gt;0,1000/G624,"")</f>
+        <v/>
+      </c>
+      <c r="I624" s="3" t="n">
+        <v>15.93</v>
+      </c>
+      <c r="J624" s="3" t="n">
+        <v>15.86</v>
+      </c>
+      <c r="K624" s="3" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="L624" s="3" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="M624" s="3" t="n"/>
+      <c r="N624" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O624" s="2" t="inlineStr">
+        <is>
+          <t>imp_cout2_B0, imp_cout2_B1</t>
+        </is>
+      </c>
+      <c r="P624" s="3" t="n">
+        <v>12.532</v>
+      </c>
+      <c r="Q624" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:32</t>
+        </is>
+      </c>
+      <c r="B625" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C625" s="2" t="inlineStr">
+        <is>
+          <t>22. Lasers : impacts sur les surfaces</t>
+        </is>
+      </c>
+      <c r="D625" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, laserimpacts=1, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E625" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F625" s="2" t="inlineStr">
+        <is>
+          <t>M1 100 lyres + 100 lasers / public</t>
+        </is>
+      </c>
+      <c r="G625" s="3" t="n">
+        <v>12.64</v>
+      </c>
+      <c r="H625" s="4">
+        <f>IF(G625&gt;0,1000/G625,"")</f>
+        <v/>
+      </c>
+      <c r="I625" s="3" t="n">
+        <v>11.885</v>
+      </c>
+      <c r="J625" s="3" t="n">
+        <v>11.575</v>
+      </c>
+      <c r="K625" s="3" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="L625" s="3" t="n">
+        <v>1.345</v>
+      </c>
+      <c r="M625" s="3" t="n"/>
+      <c r="N625" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="O625" s="2" t="inlineStr">
+        <is>
+          <t>imp_cout2_B0, imp_cout2_B1</t>
+        </is>
+      </c>
+      <c r="P625" s="3" t="n">
+        <v>6.348</v>
+      </c>
+      <c r="Q625" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:32</t>
+        </is>
+      </c>
+      <c r="B626" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C626" s="2" t="inlineStr">
+        <is>
+          <t>22. Lasers : impacts sur les surfaces</t>
+        </is>
+      </c>
+      <c r="D626" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, laserimpacts=1, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E626" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F626" s="2" t="inlineStr">
+        <is>
+          <t>M1 100 lyres + 100 lasers / scene</t>
+        </is>
+      </c>
+      <c r="G626" s="3" t="n">
+        <v>11.475</v>
+      </c>
+      <c r="H626" s="4">
+        <f>IF(G626&gt;0,1000/G626,"")</f>
+        <v/>
+      </c>
+      <c r="I626" s="3" t="n">
+        <v>10.69</v>
+      </c>
+      <c r="J626" s="3" t="n">
+        <v>10.48</v>
+      </c>
+      <c r="K626" s="3" t="n">
+        <v>1.295</v>
+      </c>
+      <c r="L626" s="3" t="n">
+        <v>1.323</v>
+      </c>
+      <c r="M626" s="3" t="n"/>
+      <c r="N626" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="O626" s="2" t="inlineStr">
+        <is>
+          <t>imp_cout2_B0, imp_cout2_B1</t>
+        </is>
+      </c>
+      <c r="P626" s="3" t="n">
+        <v>5.393</v>
+      </c>
+      <c r="Q626" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:32</t>
+        </is>
+      </c>
+      <c r="B627" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C627" s="2" t="inlineStr">
+        <is>
+          <t>22. Lasers : impacts sur les surfaces</t>
+        </is>
+      </c>
+      <c r="D627" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, laserimpacts=1, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E627" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F627" s="2" t="inlineStr">
+        <is>
+          <t>M1 100 lyres + 100 lasers / sous les trusses</t>
+        </is>
+      </c>
+      <c r="G627" s="3" t="n">
+        <v>11.07</v>
+      </c>
+      <c r="H627" s="4">
+        <f>IF(G627&gt;0,1000/G627,"")</f>
+        <v/>
+      </c>
+      <c r="I627" s="3" t="n">
+        <v>10.245</v>
+      </c>
+      <c r="J627" s="3" t="n">
+        <v>10.025</v>
+      </c>
+      <c r="K627" s="3" t="n">
+        <v>1.108</v>
+      </c>
+      <c r="L627" s="3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M627" s="3" t="n"/>
+      <c r="N627" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="O627" s="2" t="inlineStr">
+        <is>
+          <t>imp_cout2_B0, imp_cout2_B1</t>
+        </is>
+      </c>
+      <c r="P627" s="3" t="n">
+        <v>4.669</v>
+      </c>
+      <c r="Q627" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:32</t>
+        </is>
+      </c>
+      <c r="B628" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C628" s="2" t="inlineStr">
+        <is>
+          <t>22. Lasers : impacts sur les surfaces</t>
+        </is>
+      </c>
+      <c r="D628" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, laserimpacts=1, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E628" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F628" s="2" t="inlineStr">
+        <is>
+          <t>sans lasers (scene seule) / public</t>
+        </is>
+      </c>
+      <c r="G628" s="3" t="n">
+        <v>5.235</v>
+      </c>
+      <c r="H628" s="4">
+        <f>IF(G628&gt;0,1000/G628,"")</f>
+        <v/>
+      </c>
+      <c r="I628" s="3" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="J628" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="K628" s="3" t="n">
+        <v>0.783</v>
+      </c>
+      <c r="L628" s="3" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="M628" s="3" t="n"/>
+      <c r="N628" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O628" s="2" t="inlineStr">
+        <is>
+          <t>imp_cout2_B0, imp_cout2_B1</t>
+        </is>
+      </c>
+      <c r="P628" s="3" t="n"/>
+      <c r="Q628" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:32</t>
+        </is>
+      </c>
+      <c r="B629" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C629" s="2" t="inlineStr">
+        <is>
+          <t>22. Lasers : impacts sur les surfaces</t>
+        </is>
+      </c>
+      <c r="D629" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, laserimpacts=1, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E629" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F629" s="2" t="inlineStr">
+        <is>
+          <t>L7 programmeur : formes, degrades, effets / public</t>
+        </is>
+      </c>
+      <c r="G629" s="3" t="n">
+        <v>29.605</v>
+      </c>
+      <c r="H629" s="4">
+        <f>IF(G629&gt;0,1000/G629,"")</f>
+        <v/>
+      </c>
+      <c r="I629" s="3" t="n">
+        <v>28.83</v>
+      </c>
+      <c r="J629" s="3" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="K629" s="3" t="n">
+        <v>0.917</v>
+      </c>
+      <c r="L629" s="3" t="n">
+        <v>0.574</v>
+      </c>
+      <c r="M629" s="3" t="n"/>
+      <c r="N629" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O629" s="2" t="inlineStr">
+        <is>
+          <t>imp_cout2_B0, imp_cout2_B1</t>
+        </is>
+      </c>
+      <c r="P629" s="3" t="n">
+        <v>24.928</v>
+      </c>
+      <c r="Q629" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:32</t>
+        </is>
+      </c>
+      <c r="B630" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C630" s="2" t="inlineStr">
+        <is>
+          <t>22. Lasers : impacts sur les surfaces</t>
+        </is>
+      </c>
+      <c r="D630" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, laserimpacts=1, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E630" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F630" s="2" t="inlineStr">
+        <is>
+          <t>I1 ILDA nappes (banque Nappes) / public</t>
+        </is>
+      </c>
+      <c r="G630" s="3" t="n">
+        <v>46.35</v>
+      </c>
+      <c r="H630" s="4">
+        <f>IF(G630&gt;0,1000/G630,"")</f>
+        <v/>
+      </c>
+      <c r="I630" s="3" t="n">
+        <v>45.575</v>
+      </c>
+      <c r="J630" s="3" t="n">
+        <v>45.41</v>
+      </c>
+      <c r="K630" s="3" t="n">
+        <v>0.967</v>
+      </c>
+      <c r="L630" s="3" t="n">
+        <v>0.518</v>
+      </c>
+      <c r="M630" s="3" t="n"/>
+      <c r="N630" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O630" s="2" t="inlineStr">
+        <is>
+          <t>imp_cout2_B0, imp_cout2_B1</t>
+        </is>
+      </c>
+      <c r="P630" s="3" t="n">
+        <v>41.604</v>
+      </c>
+      <c r="Q630" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:32</t>
+        </is>
+      </c>
+      <c r="B631" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C631" s="2" t="inlineStr">
+        <is>
+          <t>22. Lasers : impacts sur les surfaces</t>
+        </is>
+      </c>
+      <c r="D631" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, laserimpacts=1, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E631" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F631" s="2" t="inlineStr">
+        <is>
+          <t>I2 ILDA faisceaux (banque Faisceaux) / public</t>
+        </is>
+      </c>
+      <c r="G631" s="3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H631" s="4">
+        <f>IF(G631&gt;0,1000/G631,"")</f>
+        <v/>
+      </c>
+      <c r="I631" s="3" t="n">
+        <v>6.975</v>
+      </c>
+      <c r="J631" s="3" t="n">
+        <v>7.255</v>
+      </c>
+      <c r="K631" s="3" t="n">
+        <v>0.866</v>
+      </c>
+      <c r="L631" s="3" t="n">
+        <v>0.494</v>
+      </c>
+      <c r="M631" s="3" t="n"/>
+      <c r="N631" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O631" s="2" t="inlineStr">
+        <is>
+          <t>imp_cout2_B0, imp_cout2_B1</t>
+        </is>
+      </c>
+      <c r="P631" s="3" t="n">
+        <v>2.934</v>
+      </c>
+      <c r="Q631" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:32</t>
+        </is>
+      </c>
+      <c r="B632" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C632" s="2" t="inlineStr">
+        <is>
+          <t>22. Lasers : impacts sur les surfaces</t>
+        </is>
+      </c>
+      <c r="D632" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, laserimpacts=1, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E632" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F632" s="2" t="inlineStr">
+        <is>
+          <t>I3 ILDA geometrie (banque Geometrie) / public</t>
+        </is>
+      </c>
+      <c r="G632" s="3" t="n">
+        <v>63.13</v>
+      </c>
+      <c r="H632" s="4">
+        <f>IF(G632&gt;0,1000/G632,"")</f>
+        <v/>
+      </c>
+      <c r="I632" s="3" t="n">
+        <v>62.19</v>
+      </c>
+      <c r="J632" s="3" t="n">
+        <v>61.925</v>
+      </c>
+      <c r="K632" s="3" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="L632" s="3" t="n">
+        <v>0.589</v>
+      </c>
+      <c r="M632" s="3" t="n"/>
+      <c r="N632" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O632" s="2" t="inlineStr">
+        <is>
+          <t>imp_cout2_B0, imp_cout2_B1</t>
+        </is>
+      </c>
+      <c r="P632" s="3" t="n">
+        <v>57.98</v>
+      </c>
+      <c r="Q632" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:32</t>
+        </is>
+      </c>
+      <c r="B633" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C633" s="2" t="inlineStr">
+        <is>
+          <t>22. Lasers : impacts sur les surfaces</t>
+        </is>
+      </c>
+      <c r="D633" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, laserimpacts=1, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E633" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F633" s="2" t="inlineStr">
+        <is>
+          <t>I4 ILDA tunnels (banque Tunnels) / public</t>
+        </is>
+      </c>
+      <c r="G633" s="3" t="n">
+        <v>43.97</v>
+      </c>
+      <c r="H633" s="4">
+        <f>IF(G633&gt;0,1000/G633,"")</f>
+        <v/>
+      </c>
+      <c r="I633" s="3" t="n">
+        <v>43.105</v>
+      </c>
+      <c r="J633" s="3" t="n">
+        <v>43.09</v>
+      </c>
+      <c r="K633" s="3" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="L633" s="3" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="M633" s="3" t="n"/>
+      <c r="N633" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O633" s="2" t="inlineStr">
+        <is>
+          <t>imp_cout2_B0, imp_cout2_B1</t>
+        </is>
+      </c>
+      <c r="P633" s="3" t="n">
+        <v>38.578</v>
+      </c>
+      <c r="Q633" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:32</t>
+        </is>
+      </c>
+      <c r="B634" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C634" s="2" t="inlineStr">
+        <is>
+          <t>22. Lasers : impacts sur les surfaces</t>
+        </is>
+      </c>
+      <c r="D634" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, laserimpacts=1, immobile, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E634" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F634" s="2" t="inlineStr">
+        <is>
+          <t>L1 en mode ligne (nappes continues) / public</t>
+        </is>
+      </c>
+      <c r="G634" s="3" t="n">
+        <v>14.555</v>
+      </c>
+      <c r="H634" s="4">
+        <f>IF(G634&gt;0,1000/G634,"")</f>
+        <v/>
+      </c>
+      <c r="I634" s="3" t="n">
+        <v>13.715</v>
+      </c>
+      <c r="J634" s="3" t="n">
+        <v>14.005</v>
+      </c>
+      <c r="K634" s="3" t="n">
+        <v>0.9370000000000001</v>
+      </c>
+      <c r="L634" s="3" t="n">
+        <v>0.657</v>
+      </c>
+      <c r="M634" s="3" t="n"/>
+      <c r="N634" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O634" s="2" t="inlineStr">
+        <is>
+          <t>imp_cout2_B0, imp_cout2_B1</t>
+        </is>
+      </c>
+      <c r="P634" s="3" t="n">
+        <v>9.913</v>
+      </c>
+      <c r="Q634" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:36</t>
+        </is>
+      </c>
+      <c r="B635" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C635" s="2" t="inlineStr">
+        <is>
+          <t>22b. Lasers : etape 5 (collisions + impacts), en mouvement</t>
+        </is>
+      </c>
+      <c r="D635" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E635" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F635" s="2" t="inlineStr">
+        <is>
+          <t>L1 eventails 200 x 1000 traits / public</t>
+        </is>
+      </c>
+      <c r="G635" s="3" t="n">
+        <v>17.19</v>
+      </c>
+      <c r="H635" s="4">
+        <f>IF(G635&gt;0,1000/G635,"")</f>
+        <v/>
+      </c>
+      <c r="I635" s="3" t="n">
+        <v>16.51</v>
+      </c>
+      <c r="J635" s="3" t="n">
+        <v>16.375</v>
+      </c>
+      <c r="K635" s="3" t="n">
+        <v>0.768</v>
+      </c>
+      <c r="L635" s="3" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="M635" s="3" t="n"/>
+      <c r="N635" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O635" s="2" t="inlineStr">
+        <is>
+          <t>e5_complet_B0, e5_complet_B1</t>
+        </is>
+      </c>
+      <c r="P635" s="3" t="n">
+        <v>12.876</v>
+      </c>
+      <c r="Q635" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:36</t>
+        </is>
+      </c>
+      <c r="B636" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C636" s="2" t="inlineStr">
+        <is>
+          <t>22b. Lasers : etape 5 (collisions + impacts), en mouvement</t>
+        </is>
+      </c>
+      <c r="D636" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E636" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F636" s="2" t="inlineStr">
+        <is>
+          <t>L1 eventails 200 x 1000 traits / scene</t>
+        </is>
+      </c>
+      <c r="G636" s="3" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="H636" s="4">
+        <f>IF(G636&gt;0,1000/G636,"")</f>
+        <v/>
+      </c>
+      <c r="I636" s="3" t="n">
+        <v>12.545</v>
+      </c>
+      <c r="J636" s="3" t="n">
+        <v>12.175</v>
+      </c>
+      <c r="K636" s="3" t="n">
+        <v>0.859</v>
+      </c>
+      <c r="L636" s="3" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="M636" s="3" t="n"/>
+      <c r="N636" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O636" s="2" t="inlineStr">
+        <is>
+          <t>e5_complet_B0, e5_complet_B1</t>
+        </is>
+      </c>
+      <c r="P636" s="3" t="n">
+        <v>8.948</v>
+      </c>
+      <c r="Q636" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:36</t>
+        </is>
+      </c>
+      <c r="B637" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C637" s="2" t="inlineStr">
+        <is>
+          <t>22b. Lasers : etape 5 (collisions + impacts), en mouvement</t>
+        </is>
+      </c>
+      <c r="D637" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E637" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F637" s="2" t="inlineStr">
+        <is>
+          <t>L1 eventails 200 x 1000 traits / sous les trusses</t>
+        </is>
+      </c>
+      <c r="G637" s="3" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="H637" s="4">
+        <f>IF(G637&gt;0,1000/G637,"")</f>
+        <v/>
+      </c>
+      <c r="I637" s="3" t="n">
+        <v>12.725</v>
+      </c>
+      <c r="J637" s="3" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="K637" s="3" t="n">
+        <v>0.696</v>
+      </c>
+      <c r="L637" s="3" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="M637" s="3" t="n"/>
+      <c r="N637" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O637" s="2" t="inlineStr">
+        <is>
+          <t>e5_complet_B0, e5_complet_B1</t>
+        </is>
+      </c>
+      <c r="P637" s="3" t="n">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="Q637" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:36</t>
+        </is>
+      </c>
+      <c r="B638" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C638" s="2" t="inlineStr">
+        <is>
+          <t>22b. Lasers : etape 5 (collisions + impacts), en mouvement</t>
+        </is>
+      </c>
+      <c r="D638" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E638" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F638" s="2" t="inlineStr">
+        <is>
+          <t>L2 cones 200 x 32 segments / public</t>
+        </is>
+      </c>
+      <c r="G638" s="3" t="n">
+        <v>19.715</v>
+      </c>
+      <c r="H638" s="4">
+        <f>IF(G638&gt;0,1000/G638,"")</f>
+        <v/>
+      </c>
+      <c r="I638" s="3" t="n">
+        <v>18.94</v>
+      </c>
+      <c r="J638" s="3" t="n">
+        <v>18.64</v>
+      </c>
+      <c r="K638" s="3" t="n">
+        <v>0.821</v>
+      </c>
+      <c r="L638" s="3" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="M638" s="3" t="n"/>
+      <c r="N638" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O638" s="2" t="inlineStr">
+        <is>
+          <t>e5_complet_B0, e5_complet_B1</t>
+        </is>
+      </c>
+      <c r="P638" s="3" t="n">
+        <v>15.533</v>
+      </c>
+      <c r="Q638" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:36</t>
+        </is>
+      </c>
+      <c r="B639" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C639" s="2" t="inlineStr">
+        <is>
+          <t>22b. Lasers : etape 5 (collisions + impacts), en mouvement</t>
+        </is>
+      </c>
+      <c r="D639" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E639" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F639" s="2" t="inlineStr">
+        <is>
+          <t>L2 cones 200 x 32 segments / scene</t>
+        </is>
+      </c>
+      <c r="G639" s="3" t="n">
+        <v>20.675</v>
+      </c>
+      <c r="H639" s="4">
+        <f>IF(G639&gt;0,1000/G639,"")</f>
+        <v/>
+      </c>
+      <c r="I639" s="3" t="n">
+        <v>20.29</v>
+      </c>
+      <c r="J639" s="3" t="n">
+        <v>19.765</v>
+      </c>
+      <c r="K639" s="3" t="n">
+        <v>0.841</v>
+      </c>
+      <c r="L639" s="3" t="n">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="M639" s="3" t="n"/>
+      <c r="N639" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O639" s="2" t="inlineStr">
+        <is>
+          <t>e5_complet_B0, e5_complet_B1</t>
+        </is>
+      </c>
+      <c r="P639" s="3" t="n">
+        <v>16.409</v>
+      </c>
+      <c r="Q639" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:36</t>
+        </is>
+      </c>
+      <c r="B640" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C640" s="2" t="inlineStr">
+        <is>
+          <t>22b. Lasers : etape 5 (collisions + impacts), en mouvement</t>
+        </is>
+      </c>
+      <c r="D640" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E640" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F640" s="2" t="inlineStr">
+        <is>
+          <t>L3 camera dans les nappes</t>
+        </is>
+      </c>
+      <c r="G640" s="3" t="n">
+        <v>13.415</v>
+      </c>
+      <c r="H640" s="4">
+        <f>IF(G640&gt;0,1000/G640,"")</f>
+        <v/>
+      </c>
+      <c r="I640" s="3" t="n">
+        <v>12.53</v>
+      </c>
+      <c r="J640" s="3" t="n">
+        <v>12.395</v>
+      </c>
+      <c r="K640" s="3" t="n">
+        <v>0.824</v>
+      </c>
+      <c r="L640" s="3" t="n">
+        <v>0.606</v>
+      </c>
+      <c r="M640" s="3" t="n"/>
+      <c r="N640" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O640" s="2" t="inlineStr">
+        <is>
+          <t>e5_complet_B0, e5_complet_B1</t>
+        </is>
+      </c>
+      <c r="P640" s="3" t="n">
+        <v>9.010999999999999</v>
+      </c>
+      <c r="Q640" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:36</t>
+        </is>
+      </c>
+      <c r="B641" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C641" s="2" t="inlineStr">
+        <is>
+          <t>22b. Lasers : etape 5 (collisions + impacts), en mouvement</t>
+        </is>
+      </c>
+      <c r="D641" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E641" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F641" s="2" t="inlineStr">
+        <is>
+          <t>L4 200 x 8 traits separes / public</t>
+        </is>
+      </c>
+      <c r="G641" s="3" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="H641" s="4">
+        <f>IF(G641&gt;0,1000/G641,"")</f>
+        <v/>
+      </c>
+      <c r="I641" s="3" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="J641" s="3" t="n">
+        <v>6.075</v>
+      </c>
+      <c r="K641" s="3" t="n">
+        <v>0.966</v>
+      </c>
+      <c r="L641" s="3" t="n">
+        <v>0.669</v>
+      </c>
+      <c r="M641" s="3" t="n"/>
+      <c r="N641" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O641" s="2" t="inlineStr">
+        <is>
+          <t>e5_complet_B0, e5_complet_B1</t>
+        </is>
+      </c>
+      <c r="P641" s="3" t="n">
+        <v>1.854</v>
+      </c>
+      <c r="Q641" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:36</t>
+        </is>
+      </c>
+      <c r="B642" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C642" s="2" t="inlineStr">
+        <is>
+          <t>22b. Lasers : etape 5 (collisions + impacts), en mouvement</t>
+        </is>
+      </c>
+      <c r="D642" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E642" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F642" s="2" t="inlineStr">
+        <is>
+          <t>L5 nappes en gros plan, fumee epaisse</t>
+        </is>
+      </c>
+      <c r="G642" s="3" t="n">
+        <v>15.095</v>
+      </c>
+      <c r="H642" s="4">
+        <f>IF(G642&gt;0,1000/G642,"")</f>
+        <v/>
+      </c>
+      <c r="I642" s="3" t="n">
+        <v>14.495</v>
+      </c>
+      <c r="J642" s="3" t="n">
+        <v>13.77</v>
+      </c>
+      <c r="K642" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L642" s="3" t="n">
+        <v>0.518</v>
+      </c>
+      <c r="M642" s="3" t="n"/>
+      <c r="N642" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O642" s="2" t="inlineStr">
+        <is>
+          <t>e5_complet_B0, e5_complet_B1</t>
+        </is>
+      </c>
+      <c r="P642" s="3" t="n">
+        <v>10.18</v>
+      </c>
+      <c r="Q642" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:36</t>
+        </is>
+      </c>
+      <c r="B643" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C643" s="2" t="inlineStr">
+        <is>
+          <t>22b. Lasers : etape 5 (collisions + impacts), en mouvement</t>
+        </is>
+      </c>
+      <c r="D643" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E643" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F643" s="2" t="inlineStr">
+        <is>
+          <t>L6 traits vers le sol et les obstacles / public</t>
+        </is>
+      </c>
+      <c r="G643" s="3" t="n">
+        <v>17.02</v>
+      </c>
+      <c r="H643" s="4">
+        <f>IF(G643&gt;0,1000/G643,"")</f>
+        <v/>
+      </c>
+      <c r="I643" s="3" t="n">
+        <v>16.23</v>
+      </c>
+      <c r="J643" s="3" t="n">
+        <v>16.11</v>
+      </c>
+      <c r="K643" s="3" t="n">
+        <v>0.787</v>
+      </c>
+      <c r="L643" s="3" t="n">
+        <v>0.518</v>
+      </c>
+      <c r="M643" s="3" t="n"/>
+      <c r="N643" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O643" s="2" t="inlineStr">
+        <is>
+          <t>e5_complet_B0, e5_complet_B1</t>
+        </is>
+      </c>
+      <c r="P643" s="3" t="n">
+        <v>13.095</v>
+      </c>
+      <c r="Q643" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:36</t>
+        </is>
+      </c>
+      <c r="B644" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C644" s="2" t="inlineStr">
+        <is>
+          <t>22b. Lasers : etape 5 (collisions + impacts), en mouvement</t>
+        </is>
+      </c>
+      <c r="D644" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E644" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F644" s="2" t="inlineStr">
+        <is>
+          <t>M1 100 lyres + 100 lasers / public</t>
+        </is>
+      </c>
+      <c r="G644" s="3" t="n">
+        <v>13.185</v>
+      </c>
+      <c r="H644" s="4">
+        <f>IF(G644&gt;0,1000/G644,"")</f>
+        <v/>
+      </c>
+      <c r="I644" s="3" t="n">
+        <v>12.67</v>
+      </c>
+      <c r="J644" s="3" t="n">
+        <v>12.405</v>
+      </c>
+      <c r="K644" s="3" t="n">
+        <v>1.462</v>
+      </c>
+      <c r="L644" s="3" t="n">
+        <v>1.352</v>
+      </c>
+      <c r="M644" s="3" t="n"/>
+      <c r="N644" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="O644" s="2" t="inlineStr">
+        <is>
+          <t>e5_complet_B0, e5_complet_B1</t>
+        </is>
+      </c>
+      <c r="P644" s="3" t="n">
+        <v>6.723</v>
+      </c>
+      <c r="Q644" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:36</t>
+        </is>
+      </c>
+      <c r="B645" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C645" s="2" t="inlineStr">
+        <is>
+          <t>22b. Lasers : etape 5 (collisions + impacts), en mouvement</t>
+        </is>
+      </c>
+      <c r="D645" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E645" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F645" s="2" t="inlineStr">
+        <is>
+          <t>M1 100 lyres + 100 lasers / scene</t>
+        </is>
+      </c>
+      <c r="G645" s="3" t="n">
+        <v>11.15</v>
+      </c>
+      <c r="H645" s="4">
+        <f>IF(G645&gt;0,1000/G645,"")</f>
+        <v/>
+      </c>
+      <c r="I645" s="3" t="n">
+        <v>10.455</v>
+      </c>
+      <c r="J645" s="3" t="n">
+        <v>10.285</v>
+      </c>
+      <c r="K645" s="3" t="n">
+        <v>1.352</v>
+      </c>
+      <c r="L645" s="3" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="M645" s="3" t="n"/>
+      <c r="N645" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="O645" s="2" t="inlineStr">
+        <is>
+          <t>e5_complet_B0, e5_complet_B1</t>
+        </is>
+      </c>
+      <c r="P645" s="3" t="n">
+        <v>4.812</v>
+      </c>
+      <c r="Q645" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:36</t>
+        </is>
+      </c>
+      <c r="B646" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C646" s="2" t="inlineStr">
+        <is>
+          <t>22b. Lasers : etape 5 (collisions + impacts), en mouvement</t>
+        </is>
+      </c>
+      <c r="D646" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E646" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F646" s="2" t="inlineStr">
+        <is>
+          <t>M1 100 lyres + 100 lasers / sous les trusses</t>
+        </is>
+      </c>
+      <c r="G646" s="3" t="n">
+        <v>11.04</v>
+      </c>
+      <c r="H646" s="4">
+        <f>IF(G646&gt;0,1000/G646,"")</f>
+        <v/>
+      </c>
+      <c r="I646" s="3" t="n">
+        <v>10.415</v>
+      </c>
+      <c r="J646" s="3" t="n">
+        <v>10.265</v>
+      </c>
+      <c r="K646" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="L646" s="3" t="n">
+        <v>1.252</v>
+      </c>
+      <c r="M646" s="3" t="n"/>
+      <c r="N646" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="O646" s="2" t="inlineStr">
+        <is>
+          <t>e5_complet_B0, e5_complet_B1</t>
+        </is>
+      </c>
+      <c r="P646" s="3" t="n">
+        <v>5.045</v>
+      </c>
+      <c r="Q646" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:36</t>
+        </is>
+      </c>
+      <c r="B647" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C647" s="2" t="inlineStr">
+        <is>
+          <t>22b. Lasers : etape 5 (collisions + impacts), en mouvement</t>
+        </is>
+      </c>
+      <c r="D647" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E647" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F647" s="2" t="inlineStr">
+        <is>
+          <t>sans lasers (scene seule) / public</t>
+        </is>
+      </c>
+      <c r="G647" s="3" t="n">
+        <v>4.275</v>
+      </c>
+      <c r="H647" s="4">
+        <f>IF(G647&gt;0,1000/G647,"")</f>
+        <v/>
+      </c>
+      <c r="I647" s="3" t="n">
+        <v>2.795</v>
+      </c>
+      <c r="J647" s="3" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="K647" s="3" t="n">
+        <v>0.784</v>
+      </c>
+      <c r="L647" s="3" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="M647" s="3" t="n"/>
+      <c r="N647" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O647" s="2" t="inlineStr">
+        <is>
+          <t>e5_complet_B0, e5_complet_B1</t>
+        </is>
+      </c>
+      <c r="P647" s="3" t="n"/>
+      <c r="Q647" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:36</t>
+        </is>
+      </c>
+      <c r="B648" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C648" s="2" t="inlineStr">
+        <is>
+          <t>22b. Lasers : etape 5 (collisions + impacts), en mouvement</t>
+        </is>
+      </c>
+      <c r="D648" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E648" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F648" s="2" t="inlineStr">
+        <is>
+          <t>L7 programmeur : formes, degrades, effets / public</t>
+        </is>
+      </c>
+      <c r="G648" s="3" t="n">
+        <v>31.455</v>
+      </c>
+      <c r="H648" s="4">
+        <f>IF(G648&gt;0,1000/G648,"")</f>
+        <v/>
+      </c>
+      <c r="I648" s="3" t="n">
+        <v>30.76</v>
+      </c>
+      <c r="J648" s="3" t="n">
+        <v>30.515</v>
+      </c>
+      <c r="K648" s="3" t="n">
+        <v>0.917</v>
+      </c>
+      <c r="L648" s="3" t="n">
+        <v>0.522</v>
+      </c>
+      <c r="M648" s="3" t="n"/>
+      <c r="N648" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O648" s="2" t="inlineStr">
+        <is>
+          <t>e5_complet_B0, e5_complet_B1</t>
+        </is>
+      </c>
+      <c r="P648" s="3" t="n">
+        <v>26.383</v>
+      </c>
+      <c r="Q648" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:36</t>
+        </is>
+      </c>
+      <c r="B649" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C649" s="2" t="inlineStr">
+        <is>
+          <t>22b. Lasers : etape 5 (collisions + impacts), en mouvement</t>
+        </is>
+      </c>
+      <c r="D649" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E649" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F649" s="2" t="inlineStr">
+        <is>
+          <t>I1 ILDA nappes (banque Nappes) / public</t>
+        </is>
+      </c>
+      <c r="G649" s="3" t="n">
+        <v>45.75</v>
+      </c>
+      <c r="H649" s="4">
+        <f>IF(G649&gt;0,1000/G649,"")</f>
+        <v/>
+      </c>
+      <c r="I649" s="3" t="n">
+        <v>45.105</v>
+      </c>
+      <c r="J649" s="3" t="n">
+        <v>44.695</v>
+      </c>
+      <c r="K649" s="3" t="n">
+        <v>0.972</v>
+      </c>
+      <c r="L649" s="3" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="M649" s="3" t="n"/>
+      <c r="N649" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O649" s="2" t="inlineStr">
+        <is>
+          <t>e5_complet_B0, e5_complet_B1</t>
+        </is>
+      </c>
+      <c r="P649" s="3" t="n">
+        <v>40.562</v>
+      </c>
+      <c r="Q649" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:36</t>
+        </is>
+      </c>
+      <c r="B650" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C650" s="2" t="inlineStr">
+        <is>
+          <t>22b. Lasers : etape 5 (collisions + impacts), en mouvement</t>
+        </is>
+      </c>
+      <c r="D650" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E650" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F650" s="2" t="inlineStr">
+        <is>
+          <t>I2 ILDA faisceaux (banque Faisceaux) / public</t>
+        </is>
+      </c>
+      <c r="G650" s="3" t="n">
+        <v>8.045</v>
+      </c>
+      <c r="H650" s="4">
+        <f>IF(G650&gt;0,1000/G650,"")</f>
+        <v/>
+      </c>
+      <c r="I650" s="3" t="n">
+        <v>6.835</v>
+      </c>
+      <c r="J650" s="3" t="n">
+        <v>6.925</v>
+      </c>
+      <c r="K650" s="3" t="n">
+        <v>0.967</v>
+      </c>
+      <c r="L650" s="3" t="n">
+        <v>0.663</v>
+      </c>
+      <c r="M650" s="3" t="n"/>
+      <c r="N650" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O650" s="2" t="inlineStr">
+        <is>
+          <t>e5_complet_B0, e5_complet_B1</t>
+        </is>
+      </c>
+      <c r="P650" s="3" t="n">
+        <v>2.784</v>
+      </c>
+      <c r="Q650" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:36</t>
+        </is>
+      </c>
+      <c r="B651" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C651" s="2" t="inlineStr">
+        <is>
+          <t>22b. Lasers : etape 5 (collisions + impacts), en mouvement</t>
+        </is>
+      </c>
+      <c r="D651" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E651" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F651" s="2" t="inlineStr">
+        <is>
+          <t>I3 ILDA geometrie (banque Geometrie) / public</t>
+        </is>
+      </c>
+      <c r="G651" s="3" t="n">
+        <v>61.845</v>
+      </c>
+      <c r="H651" s="4">
+        <f>IF(G651&gt;0,1000/G651,"")</f>
+        <v/>
+      </c>
+      <c r="I651" s="3" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="J651" s="3" t="n">
+        <v>61.61</v>
+      </c>
+      <c r="K651" s="3" t="n">
+        <v>0.986</v>
+      </c>
+      <c r="L651" s="3" t="n">
+        <v>0.591</v>
+      </c>
+      <c r="M651" s="3" t="n"/>
+      <c r="N651" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O651" s="2" t="inlineStr">
+        <is>
+          <t>e5_complet_B0, e5_complet_B1</t>
+        </is>
+      </c>
+      <c r="P651" s="3" t="n">
+        <v>57.426</v>
+      </c>
+      <c r="Q651" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:36</t>
+        </is>
+      </c>
+      <c r="B652" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C652" s="2" t="inlineStr">
+        <is>
+          <t>22b. Lasers : etape 5 (collisions + impacts), en mouvement</t>
+        </is>
+      </c>
+      <c r="D652" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E652" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F652" s="2" t="inlineStr">
+        <is>
+          <t>I4 ILDA tunnels (banque Tunnels) / public</t>
+        </is>
+      </c>
+      <c r="G652" s="3" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="H652" s="4">
+        <f>IF(G652&gt;0,1000/G652,"")</f>
+        <v/>
+      </c>
+      <c r="I652" s="3" t="n">
+        <v>45.915</v>
+      </c>
+      <c r="J652" s="3" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="K652" s="3" t="n">
+        <v>0.977</v>
+      </c>
+      <c r="L652" s="3" t="n">
+        <v>0.581</v>
+      </c>
+      <c r="M652" s="3" t="n"/>
+      <c r="N652" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O652" s="2" t="inlineStr">
+        <is>
+          <t>e5_complet_B0, e5_complet_B1</t>
+        </is>
+      </c>
+      <c r="P652" s="3" t="n">
+        <v>41.915</v>
+      </c>
+      <c r="Q652" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:36</t>
+        </is>
+      </c>
+      <c r="B653" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C653" s="2" t="inlineStr">
+        <is>
+          <t>22b. Lasers : etape 5 (collisions + impacts), en mouvement</t>
+        </is>
+      </c>
+      <c r="D653" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, en mouvement, banc rapide, 19 cas</t>
+        </is>
+      </c>
+      <c r="E653" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F653" s="2" t="inlineStr">
+        <is>
+          <t>L1 en mode ligne (nappes continues) / public</t>
+        </is>
+      </c>
+      <c r="G653" s="3" t="n">
+        <v>15.76</v>
+      </c>
+      <c r="H653" s="4">
+        <f>IF(G653&gt;0,1000/G653,"")</f>
+        <v/>
+      </c>
+      <c r="I653" s="3" t="n">
+        <v>15.125</v>
+      </c>
+      <c r="J653" s="3" t="n">
+        <v>15.19</v>
+      </c>
+      <c r="K653" s="3" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="L653" s="3" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="M653" s="3" t="n"/>
+      <c r="N653" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O653" s="2" t="inlineStr">
+        <is>
+          <t>e5_complet_B0, e5_complet_B1</t>
+        </is>
+      </c>
+      <c r="P653" s="3" t="n">
+        <v>11.181</v>
+      </c>
+      <c r="Q653" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:36</t>
+        </is>
+      </c>
+      <c r="B654" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C654" s="2" t="inlineStr">
+        <is>
+          <t>22b. Lyres : etape 5 (inchange)</t>
+        </is>
+      </c>
+      <c r="D654" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide, 3 cas</t>
+        </is>
+      </c>
+      <c r="E654" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F654" s="2" t="inlineStr">
+        <is>
+          <t>defaut / public</t>
+        </is>
+      </c>
+      <c r="G654" s="3" t="n">
+        <v>7.925</v>
+      </c>
+      <c r="H654" s="4">
+        <f>IF(G654&gt;0,1000/G654,"")</f>
+        <v/>
+      </c>
+      <c r="I654" s="3" t="n">
+        <v>7.165</v>
+      </c>
+      <c r="J654" s="3" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="K654" s="3" t="n">
+        <v>1.607</v>
+      </c>
+      <c r="L654" s="3" t="n">
+        <v>2.055</v>
+      </c>
+      <c r="M654" s="3" t="n"/>
+      <c r="N654" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="O654" s="2" t="inlineStr">
+        <is>
+          <t>e5_lyres_B0, e5_lyres_B1</t>
+        </is>
+      </c>
+      <c r="P654" s="3" t="n"/>
+      <c r="Q654" s="2" t="inlineStr">
+        <is>
+          <t>lyres</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:36</t>
+        </is>
+      </c>
+      <c r="B655" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C655" s="2" t="inlineStr">
+        <is>
+          <t>22b. Lyres : etape 5 (inchange)</t>
+        </is>
+      </c>
+      <c r="D655" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide, 3 cas</t>
+        </is>
+      </c>
+      <c r="E655" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F655" s="2" t="inlineStr">
+        <is>
+          <t>gobo + prisme 8 + zoom 25 / public</t>
+        </is>
+      </c>
+      <c r="G655" s="3" t="n">
+        <v>17.175</v>
+      </c>
+      <c r="H655" s="4">
+        <f>IF(G655&gt;0,1000/G655,"")</f>
+        <v/>
+      </c>
+      <c r="I655" s="3" t="n">
+        <v>16.585</v>
+      </c>
+      <c r="J655" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="K655" s="3" t="n">
+        <v>5.938</v>
+      </c>
+      <c r="L655" s="3" t="n">
+        <v>6.788</v>
+      </c>
+      <c r="M655" s="3" t="n"/>
+      <c r="N655" s="2" t="n">
+        <v>280</v>
+      </c>
+      <c r="O655" s="2" t="inlineStr">
+        <is>
+          <t>e5_lyres_B0, e5_lyres_B1</t>
+        </is>
+      </c>
+      <c r="P655" s="3" t="n"/>
+      <c r="Q655" s="2" t="inlineStr">
+        <is>
+          <t>lyres</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:36</t>
+        </is>
+      </c>
+      <c r="B656" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec +modifs</t>
+        </is>
+      </c>
+      <c r="C656" s="2" t="inlineStr">
+        <is>
+          <t>22b. Lyres : etape 5 (inchange)</t>
+        </is>
+      </c>
+      <c r="D656" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide, 3 cas</t>
+        </is>
+      </c>
+      <c r="E656" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F656" s="2" t="inlineStr">
+        <is>
+          <t>zoom 45 + frost 0.6 / public</t>
+        </is>
+      </c>
+      <c r="G656" s="3" t="n">
+        <v>11.585</v>
+      </c>
+      <c r="H656" s="4">
+        <f>IF(G656&gt;0,1000/G656,"")</f>
+        <v/>
+      </c>
+      <c r="I656" s="3" t="n">
+        <v>11.125</v>
+      </c>
+      <c r="J656" s="3" t="n">
+        <v>9.914999999999999</v>
+      </c>
+      <c r="K656" s="3" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="L656" s="3" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="M656" s="3" t="n"/>
+      <c r="N656" s="2" t="n">
+        <v>887</v>
+      </c>
+      <c r="O656" s="2" t="inlineStr">
+        <is>
+          <t>e5_lyres_B0, e5_lyres_B1</t>
+        </is>
+      </c>
+      <c r="P656" s="3" t="n"/>
+      <c r="Q656" s="2" t="inlineStr">
+        <is>
+          <t>lyres</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 16:32</t>
+        </is>
+      </c>
+      <c r="B657" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec+</t>
+        </is>
+      </c>
+      <c r="C657" s="2" t="inlineStr">
+        <is>
+          <t>23. arcs : silhouettes adoucies, pyramide coupee a l'ecran et aux parois, passe des arcs a part</t>
+        </is>
+      </c>
+      <c r="D657" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide (lasers complet)</t>
+        </is>
+      </c>
+      <c r="E657" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F657" s="2" t="inlineStr">
+        <is>
+          <t>L1 eventails 200 x 1000 traits / public</t>
+        </is>
+      </c>
+      <c r="G657" s="3" t="n">
+        <v>14.56</v>
+      </c>
+      <c r="H657" s="4">
+        <f>IF(G657&gt;0,1000/G657,"")</f>
+        <v/>
+      </c>
+      <c r="I657" s="3" t="n">
+        <v>13.885</v>
+      </c>
+      <c r="J657" s="3" t="n">
+        <v>12.865</v>
+      </c>
+      <c r="K657" s="3" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="L657" s="3" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="M657" s="3" t="n"/>
+      <c r="N657" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O657" s="2" t="inlineStr">
+        <is>
+          <t>arcs4_B0, arcs4_B1</t>
+        </is>
+      </c>
+      <c r="P657" s="3" t="n">
+        <v>9.534000000000001</v>
+      </c>
+      <c r="Q657" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 16:32</t>
+        </is>
+      </c>
+      <c r="B658" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec+</t>
+        </is>
+      </c>
+      <c r="C658" s="2" t="inlineStr">
+        <is>
+          <t>23. arcs : silhouettes adoucies, pyramide coupee a l'ecran et aux parois, passe des arcs a part</t>
+        </is>
+      </c>
+      <c r="D658" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide (lasers complet)</t>
+        </is>
+      </c>
+      <c r="E658" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F658" s="2" t="inlineStr">
+        <is>
+          <t>L1 eventails 200 x 1000 traits / scene</t>
+        </is>
+      </c>
+      <c r="G658" s="3" t="n">
+        <v>13.54</v>
+      </c>
+      <c r="H658" s="4">
+        <f>IF(G658&gt;0,1000/G658,"")</f>
+        <v/>
+      </c>
+      <c r="I658" s="3" t="n">
+        <v>12.555</v>
+      </c>
+      <c r="J658" s="3" t="n">
+        <v>11.585</v>
+      </c>
+      <c r="K658" s="3" t="n">
+        <v>0.9389999999999999</v>
+      </c>
+      <c r="L658" s="3" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="M658" s="3" t="n"/>
+      <c r="N658" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O658" s="2" t="inlineStr">
+        <is>
+          <t>arcs4_B0, arcs4_B1</t>
+        </is>
+      </c>
+      <c r="P658" s="3" t="n">
+        <v>8.317</v>
+      </c>
+      <c r="Q658" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 16:32</t>
+        </is>
+      </c>
+      <c r="B659" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec+</t>
+        </is>
+      </c>
+      <c r="C659" s="2" t="inlineStr">
+        <is>
+          <t>23. arcs : silhouettes adoucies, pyramide coupee a l'ecran et aux parois, passe des arcs a part</t>
+        </is>
+      </c>
+      <c r="D659" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide (lasers complet)</t>
+        </is>
+      </c>
+      <c r="E659" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F659" s="2" t="inlineStr">
+        <is>
+          <t>L1 eventails 200 x 1000 traits / sous les trusses</t>
+        </is>
+      </c>
+      <c r="G659" s="3" t="n">
+        <v>12.595</v>
+      </c>
+      <c r="H659" s="4">
+        <f>IF(G659&gt;0,1000/G659,"")</f>
+        <v/>
+      </c>
+      <c r="I659" s="3" t="n">
+        <v>11.72</v>
+      </c>
+      <c r="J659" s="3" t="n">
+        <v>10.92</v>
+      </c>
+      <c r="K659" s="3" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="L659" s="3" t="n">
+        <v>0.803</v>
+      </c>
+      <c r="M659" s="3" t="n"/>
+      <c r="N659" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O659" s="2" t="inlineStr">
+        <is>
+          <t>arcs4_B0, arcs4_B1</t>
+        </is>
+      </c>
+      <c r="P659" s="3" t="n">
+        <v>7.747</v>
+      </c>
+      <c r="Q659" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 16:32</t>
+        </is>
+      </c>
+      <c r="B660" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec+</t>
+        </is>
+      </c>
+      <c r="C660" s="2" t="inlineStr">
+        <is>
+          <t>23. arcs : silhouettes adoucies, pyramide coupee a l'ecran et aux parois, passe des arcs a part</t>
+        </is>
+      </c>
+      <c r="D660" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide (lasers complet)</t>
+        </is>
+      </c>
+      <c r="E660" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F660" s="2" t="inlineStr">
+        <is>
+          <t>L2 cones 200 x 32 segments / public</t>
+        </is>
+      </c>
+      <c r="G660" s="3" t="n">
+        <v>20.01</v>
+      </c>
+      <c r="H660" s="4">
+        <f>IF(G660&gt;0,1000/G660,"")</f>
+        <v/>
+      </c>
+      <c r="I660" s="3" t="n">
+        <v>19.315</v>
+      </c>
+      <c r="J660" s="3" t="n">
+        <v>18.68</v>
+      </c>
+      <c r="K660" s="3" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="L660" s="3" t="n">
+        <v>0.669</v>
+      </c>
+      <c r="M660" s="3" t="n"/>
+      <c r="N660" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O660" s="2" t="inlineStr">
+        <is>
+          <t>arcs4_B0, arcs4_B1</t>
+        </is>
+      </c>
+      <c r="P660" s="3" t="n">
+        <v>15.387</v>
+      </c>
+      <c r="Q660" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 16:32</t>
+        </is>
+      </c>
+      <c r="B661" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec+</t>
+        </is>
+      </c>
+      <c r="C661" s="2" t="inlineStr">
+        <is>
+          <t>23. arcs : silhouettes adoucies, pyramide coupee a l'ecran et aux parois, passe des arcs a part</t>
+        </is>
+      </c>
+      <c r="D661" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide (lasers complet)</t>
+        </is>
+      </c>
+      <c r="E661" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F661" s="2" t="inlineStr">
+        <is>
+          <t>L2 cones 200 x 32 segments / scene</t>
+        </is>
+      </c>
+      <c r="G661" s="3" t="n">
+        <v>20.18</v>
+      </c>
+      <c r="H661" s="4">
+        <f>IF(G661&gt;0,1000/G661,"")</f>
+        <v/>
+      </c>
+      <c r="I661" s="3" t="n">
+        <v>19.355</v>
+      </c>
+      <c r="J661" s="3" t="n">
+        <v>19.01</v>
+      </c>
+      <c r="K661" s="3" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="L661" s="3" t="n">
+        <v>0.744</v>
+      </c>
+      <c r="M661" s="3" t="n"/>
+      <c r="N661" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O661" s="2" t="inlineStr">
+        <is>
+          <t>arcs4_B0, arcs4_B1</t>
+        </is>
+      </c>
+      <c r="P661" s="3" t="n">
+        <v>15.024</v>
+      </c>
+      <c r="Q661" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 16:32</t>
+        </is>
+      </c>
+      <c r="B662" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec+</t>
+        </is>
+      </c>
+      <c r="C662" s="2" t="inlineStr">
+        <is>
+          <t>23. arcs : silhouettes adoucies, pyramide coupee a l'ecran et aux parois, passe des arcs a part</t>
+        </is>
+      </c>
+      <c r="D662" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide (lasers complet)</t>
+        </is>
+      </c>
+      <c r="E662" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F662" s="2" t="inlineStr">
+        <is>
+          <t>L3 camera dans les nappes</t>
+        </is>
+      </c>
+      <c r="G662" s="3" t="n">
+        <v>13.56</v>
+      </c>
+      <c r="H662" s="4">
+        <f>IF(G662&gt;0,1000/G662,"")</f>
+        <v/>
+      </c>
+      <c r="I662" s="3" t="n">
+        <v>12.525</v>
+      </c>
+      <c r="J662" s="3" t="n">
+        <v>11.605</v>
+      </c>
+      <c r="K662" s="3" t="n">
+        <v>0.8129999999999999</v>
+      </c>
+      <c r="L662" s="3" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="M662" s="3" t="n"/>
+      <c r="N662" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O662" s="2" t="inlineStr">
+        <is>
+          <t>arcs4_B0, arcs4_B1</t>
+        </is>
+      </c>
+      <c r="P662" s="3" t="n">
+        <v>8.417</v>
+      </c>
+      <c r="Q662" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 16:32</t>
+        </is>
+      </c>
+      <c r="B663" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec+</t>
+        </is>
+      </c>
+      <c r="C663" s="2" t="inlineStr">
+        <is>
+          <t>23. arcs : silhouettes adoucies, pyramide coupee a l'ecran et aux parois, passe des arcs a part</t>
+        </is>
+      </c>
+      <c r="D663" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide (lasers complet)</t>
+        </is>
+      </c>
+      <c r="E663" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F663" s="2" t="inlineStr">
+        <is>
+          <t>L4 200 x 8 traits separes / public</t>
+        </is>
+      </c>
+      <c r="G663" s="3" t="n">
+        <v>7.295</v>
+      </c>
+      <c r="H663" s="4">
+        <f>IF(G663&gt;0,1000/G663,"")</f>
+        <v/>
+      </c>
+      <c r="I663" s="3" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="J663" s="3" t="n">
+        <v>4.815</v>
+      </c>
+      <c r="K663" s="3" t="n">
+        <v>0.871</v>
+      </c>
+      <c r="L663" s="3" t="n">
+        <v>0.661</v>
+      </c>
+      <c r="M663" s="3" t="n"/>
+      <c r="N663" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O663" s="2" t="inlineStr">
+        <is>
+          <t>arcs4_B0, arcs4_B1</t>
+        </is>
+      </c>
+      <c r="P663" s="3" t="n">
+        <v>1.702</v>
+      </c>
+      <c r="Q663" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 16:32</t>
+        </is>
+      </c>
+      <c r="B664" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec+</t>
+        </is>
+      </c>
+      <c r="C664" s="2" t="inlineStr">
+        <is>
+          <t>23. arcs : silhouettes adoucies, pyramide coupee a l'ecran et aux parois, passe des arcs a part</t>
+        </is>
+      </c>
+      <c r="D664" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide (lasers complet)</t>
+        </is>
+      </c>
+      <c r="E664" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F664" s="2" t="inlineStr">
+        <is>
+          <t>L5 nappes en gros plan, fumee epaisse</t>
+        </is>
+      </c>
+      <c r="G664" s="3" t="n">
+        <v>13.605</v>
+      </c>
+      <c r="H664" s="4">
+        <f>IF(G664&gt;0,1000/G664,"")</f>
+        <v/>
+      </c>
+      <c r="I664" s="3" t="n">
+        <v>12.765</v>
+      </c>
+      <c r="J664" s="3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="K664" s="3" t="n">
+        <v>0.804</v>
+      </c>
+      <c r="L664" s="3" t="n">
+        <v>0.671</v>
+      </c>
+      <c r="M664" s="3" t="n"/>
+      <c r="N664" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O664" s="2" t="inlineStr">
+        <is>
+          <t>arcs4_B0, arcs4_B1</t>
+        </is>
+      </c>
+      <c r="P664" s="3" t="n">
+        <v>8.497</v>
+      </c>
+      <c r="Q664" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 16:32</t>
+        </is>
+      </c>
+      <c r="B665" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec+</t>
+        </is>
+      </c>
+      <c r="C665" s="2" t="inlineStr">
+        <is>
+          <t>23. arcs : silhouettes adoucies, pyramide coupee a l'ecran et aux parois, passe des arcs a part</t>
+        </is>
+      </c>
+      <c r="D665" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide (lasers complet)</t>
+        </is>
+      </c>
+      <c r="E665" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F665" s="2" t="inlineStr">
+        <is>
+          <t>L6 traits vers le sol et les obstacles / public</t>
+        </is>
+      </c>
+      <c r="G665" s="3" t="n">
+        <v>15.72</v>
+      </c>
+      <c r="H665" s="4">
+        <f>IF(G665&gt;0,1000/G665,"")</f>
+        <v/>
+      </c>
+      <c r="I665" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="J665" s="3" t="n">
+        <v>14.52</v>
+      </c>
+      <c r="K665" s="3" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="L665" s="3" t="n">
+        <v>0.696</v>
+      </c>
+      <c r="M665" s="3" t="n"/>
+      <c r="N665" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O665" s="2" t="inlineStr">
+        <is>
+          <t>arcs4_B0, arcs4_B1</t>
+        </is>
+      </c>
+      <c r="P665" s="3" t="n">
+        <v>10.954</v>
+      </c>
+      <c r="Q665" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 16:32</t>
+        </is>
+      </c>
+      <c r="B666" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec+</t>
+        </is>
+      </c>
+      <c r="C666" s="2" t="inlineStr">
+        <is>
+          <t>23. arcs : silhouettes adoucies, pyramide coupee a l'ecran et aux parois, passe des arcs a part</t>
+        </is>
+      </c>
+      <c r="D666" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide (lasers complet)</t>
+        </is>
+      </c>
+      <c r="E666" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F666" s="2" t="inlineStr">
+        <is>
+          <t>M1 100 lyres + 100 lasers / public</t>
+        </is>
+      </c>
+      <c r="G666" s="3" t="n">
+        <v>11.79</v>
+      </c>
+      <c r="H666" s="4">
+        <f>IF(G666&gt;0,1000/G666,"")</f>
+        <v/>
+      </c>
+      <c r="I666" s="3" t="n">
+        <v>10.96</v>
+      </c>
+      <c r="J666" s="3" t="n">
+        <v>10.595</v>
+      </c>
+      <c r="K666" s="3" t="n">
+        <v>1.533</v>
+      </c>
+      <c r="L666" s="3" t="n">
+        <v>1.399</v>
+      </c>
+      <c r="M666" s="3" t="n"/>
+      <c r="N666" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="O666" s="2" t="inlineStr">
+        <is>
+          <t>arcs4_B0, arcs4_B1</t>
+        </is>
+      </c>
+      <c r="P666" s="3" t="n">
+        <v>5.281</v>
+      </c>
+      <c r="Q666" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 16:32</t>
+        </is>
+      </c>
+      <c r="B667" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec+</t>
+        </is>
+      </c>
+      <c r="C667" s="2" t="inlineStr">
+        <is>
+          <t>23. arcs : silhouettes adoucies, pyramide coupee a l'ecran et aux parois, passe des arcs a part</t>
+        </is>
+      </c>
+      <c r="D667" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide (lasers complet)</t>
+        </is>
+      </c>
+      <c r="E667" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F667" s="2" t="inlineStr">
+        <is>
+          <t>M1 100 lyres + 100 lasers / scene</t>
+        </is>
+      </c>
+      <c r="G667" s="3" t="n">
+        <v>11.465</v>
+      </c>
+      <c r="H667" s="4">
+        <f>IF(G667&gt;0,1000/G667,"")</f>
+        <v/>
+      </c>
+      <c r="I667" s="3" t="n">
+        <v>10.515</v>
+      </c>
+      <c r="J667" s="3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="K667" s="3" t="n">
+        <v>1.438</v>
+      </c>
+      <c r="L667" s="3" t="n">
+        <v>1.381</v>
+      </c>
+      <c r="M667" s="3" t="n"/>
+      <c r="N667" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="O667" s="2" t="inlineStr">
+        <is>
+          <t>arcs4_B0, arcs4_B1</t>
+        </is>
+      </c>
+      <c r="P667" s="3" t="n">
+        <v>4.345</v>
+      </c>
+      <c r="Q667" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 16:32</t>
+        </is>
+      </c>
+      <c r="B668" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec+</t>
+        </is>
+      </c>
+      <c r="C668" s="2" t="inlineStr">
+        <is>
+          <t>23. arcs : silhouettes adoucies, pyramide coupee a l'ecran et aux parois, passe des arcs a part</t>
+        </is>
+      </c>
+      <c r="D668" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide (lasers complet)</t>
+        </is>
+      </c>
+      <c r="E668" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F668" s="2" t="inlineStr">
+        <is>
+          <t>M1 100 lyres + 100 lasers / sous les trusses</t>
+        </is>
+      </c>
+      <c r="G668" s="3" t="n">
+        <v>11.415</v>
+      </c>
+      <c r="H668" s="4">
+        <f>IF(G668&gt;0,1000/G668,"")</f>
+        <v/>
+      </c>
+      <c r="I668" s="3" t="n">
+        <v>10.425</v>
+      </c>
+      <c r="J668" s="3" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="K668" s="3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="L668" s="3" t="n">
+        <v>1.294</v>
+      </c>
+      <c r="M668" s="3" t="n"/>
+      <c r="N668" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="O668" s="2" t="inlineStr">
+        <is>
+          <t>arcs4_B0, arcs4_B1</t>
+        </is>
+      </c>
+      <c r="P668" s="3" t="n">
+        <v>4.229</v>
+      </c>
+      <c r="Q668" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 16:32</t>
+        </is>
+      </c>
+      <c r="B669" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec+</t>
+        </is>
+      </c>
+      <c r="C669" s="2" t="inlineStr">
+        <is>
+          <t>23. arcs : silhouettes adoucies, pyramide coupee a l'ecran et aux parois, passe des arcs a part</t>
+        </is>
+      </c>
+      <c r="D669" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide (lasers complet)</t>
+        </is>
+      </c>
+      <c r="E669" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F669" s="2" t="inlineStr">
+        <is>
+          <t>sans lasers (scene seule) / public</t>
+        </is>
+      </c>
+      <c r="G669" s="3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H669" s="4">
+        <f>IF(G669&gt;0,1000/G669,"")</f>
+        <v/>
+      </c>
+      <c r="I669" s="3" t="n">
+        <v>2.675</v>
+      </c>
+      <c r="J669" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="K669" s="3" t="n">
+        <v>0.783</v>
+      </c>
+      <c r="L669" s="3" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="M669" s="3" t="n"/>
+      <c r="N669" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O669" s="2" t="inlineStr">
+        <is>
+          <t>arcs4_B0, arcs4_B1</t>
+        </is>
+      </c>
+      <c r="P669" s="3" t="n"/>
+      <c r="Q669" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 16:32</t>
+        </is>
+      </c>
+      <c r="B670" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec+</t>
+        </is>
+      </c>
+      <c r="C670" s="2" t="inlineStr">
+        <is>
+          <t>23. arcs : silhouettes adoucies, pyramide coupee a l'ecran et aux parois, passe des arcs a part</t>
+        </is>
+      </c>
+      <c r="D670" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide (lasers complet)</t>
+        </is>
+      </c>
+      <c r="E670" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F670" s="2" t="inlineStr">
+        <is>
+          <t>L7 programmeur : formes, degrades, effets / public</t>
+        </is>
+      </c>
+      <c r="G670" s="3" t="n">
+        <v>29.205</v>
+      </c>
+      <c r="H670" s="4">
+        <f>IF(G670&gt;0,1000/G670,"")</f>
+        <v/>
+      </c>
+      <c r="I670" s="3" t="n">
+        <v>28.34</v>
+      </c>
+      <c r="J670" s="3" t="n">
+        <v>27.935</v>
+      </c>
+      <c r="K670" s="3" t="n">
+        <v>0.924</v>
+      </c>
+      <c r="L670" s="3" t="n">
+        <v>0.669</v>
+      </c>
+      <c r="M670" s="3" t="n"/>
+      <c r="N670" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O670" s="2" t="inlineStr">
+        <is>
+          <t>arcs4_B0, arcs4_B1</t>
+        </is>
+      </c>
+      <c r="P670" s="3" t="n">
+        <v>24.295</v>
+      </c>
+      <c r="Q670" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 16:32</t>
+        </is>
+      </c>
+      <c r="B671" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec+</t>
+        </is>
+      </c>
+      <c r="C671" s="2" t="inlineStr">
+        <is>
+          <t>23. arcs : silhouettes adoucies, pyramide coupee a l'ecran et aux parois, passe des arcs a part</t>
+        </is>
+      </c>
+      <c r="D671" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide (lasers complet)</t>
+        </is>
+      </c>
+      <c r="E671" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F671" s="2" t="inlineStr">
+        <is>
+          <t>I1 ILDA nappes (banque Nappes) / public</t>
+        </is>
+      </c>
+      <c r="G671" s="3" t="n">
+        <v>40.935</v>
+      </c>
+      <c r="H671" s="4">
+        <f>IF(G671&gt;0,1000/G671,"")</f>
+        <v/>
+      </c>
+      <c r="I671" s="3" t="n">
+        <v>40.18</v>
+      </c>
+      <c r="J671" s="3" t="n">
+        <v>40.14</v>
+      </c>
+      <c r="K671" s="3" t="n">
+        <v>1.024</v>
+      </c>
+      <c r="L671" s="3" t="n">
+        <v>0.704</v>
+      </c>
+      <c r="M671" s="3" t="n"/>
+      <c r="N671" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O671" s="2" t="inlineStr">
+        <is>
+          <t>arcs4_B0, arcs4_B1</t>
+        </is>
+      </c>
+      <c r="P671" s="3" t="n">
+        <v>36.163</v>
+      </c>
+      <c r="Q671" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 16:32</t>
+        </is>
+      </c>
+      <c r="B672" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec+</t>
+        </is>
+      </c>
+      <c r="C672" s="2" t="inlineStr">
+        <is>
+          <t>23. arcs : silhouettes adoucies, pyramide coupee a l'ecran et aux parois, passe des arcs a part</t>
+        </is>
+      </c>
+      <c r="D672" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide (lasers complet)</t>
+        </is>
+      </c>
+      <c r="E672" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F672" s="2" t="inlineStr">
+        <is>
+          <t>I2 ILDA faisceaux (banque Faisceaux) / public</t>
+        </is>
+      </c>
+      <c r="G672" s="3" t="n">
+        <v>8.645</v>
+      </c>
+      <c r="H672" s="4">
+        <f>IF(G672&gt;0,1000/G672,"")</f>
+        <v/>
+      </c>
+      <c r="I672" s="3" t="n">
+        <v>6.855</v>
+      </c>
+      <c r="J672" s="3" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="K672" s="3" t="n">
+        <v>0.962</v>
+      </c>
+      <c r="L672" s="3" t="n">
+        <v>0.657</v>
+      </c>
+      <c r="M672" s="3" t="n"/>
+      <c r="N672" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O672" s="2" t="inlineStr">
+        <is>
+          <t>arcs4_B0, arcs4_B1</t>
+        </is>
+      </c>
+      <c r="P672" s="3" t="n">
+        <v>2.894</v>
+      </c>
+      <c r="Q672" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 16:32</t>
+        </is>
+      </c>
+      <c r="B673" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec+</t>
+        </is>
+      </c>
+      <c r="C673" s="2" t="inlineStr">
+        <is>
+          <t>23. arcs : silhouettes adoucies, pyramide coupee a l'ecran et aux parois, passe des arcs a part</t>
+        </is>
+      </c>
+      <c r="D673" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide (lasers complet)</t>
+        </is>
+      </c>
+      <c r="E673" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F673" s="2" t="inlineStr">
+        <is>
+          <t>I3 ILDA geometrie (banque Geometrie) / public</t>
+        </is>
+      </c>
+      <c r="G673" s="3" t="n">
+        <v>54.705</v>
+      </c>
+      <c r="H673" s="4">
+        <f>IF(G673&gt;0,1000/G673,"")</f>
+        <v/>
+      </c>
+      <c r="I673" s="3" t="n">
+        <v>53.605</v>
+      </c>
+      <c r="J673" s="3" t="n">
+        <v>53.255</v>
+      </c>
+      <c r="K673" s="3" t="n">
+        <v>0.978</v>
+      </c>
+      <c r="L673" s="3" t="n">
+        <v>0.6830000000000001</v>
+      </c>
+      <c r="M673" s="3" t="n"/>
+      <c r="N673" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O673" s="2" t="inlineStr">
+        <is>
+          <t>arcs4_B0, arcs4_B1</t>
+        </is>
+      </c>
+      <c r="P673" s="3" t="n">
+        <v>48.822</v>
+      </c>
+      <c r="Q673" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 16:32</t>
+        </is>
+      </c>
+      <c r="B674" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec+</t>
+        </is>
+      </c>
+      <c r="C674" s="2" t="inlineStr">
+        <is>
+          <t>23. arcs : silhouettes adoucies, pyramide coupee a l'ecran et aux parois, passe des arcs a part</t>
+        </is>
+      </c>
+      <c r="D674" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide (lasers complet)</t>
+        </is>
+      </c>
+      <c r="E674" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F674" s="2" t="inlineStr">
+        <is>
+          <t>I4 ILDA tunnels (banque Tunnels) / public</t>
+        </is>
+      </c>
+      <c r="G674" s="3" t="n">
+        <v>38.64</v>
+      </c>
+      <c r="H674" s="4">
+        <f>IF(G674&gt;0,1000/G674,"")</f>
+        <v/>
+      </c>
+      <c r="I674" s="3" t="n">
+        <v>37.86</v>
+      </c>
+      <c r="J674" s="3" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="K674" s="3" t="n">
+        <v>1.045</v>
+      </c>
+      <c r="L674" s="3" t="n">
+        <v>0.704</v>
+      </c>
+      <c r="M674" s="3" t="n"/>
+      <c r="N674" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O674" s="2" t="inlineStr">
+        <is>
+          <t>arcs4_B0, arcs4_B1</t>
+        </is>
+      </c>
+      <c r="P674" s="3" t="n">
+        <v>33.206</v>
+      </c>
+      <c r="Q674" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 16:32</t>
+        </is>
+      </c>
+      <c r="B675" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec+</t>
+        </is>
+      </c>
+      <c r="C675" s="2" t="inlineStr">
+        <is>
+          <t>23. arcs : silhouettes adoucies, pyramide coupee a l'ecran et aux parois, passe des arcs a part</t>
+        </is>
+      </c>
+      <c r="D675" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide (lasers complet)</t>
+        </is>
+      </c>
+      <c r="E675" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F675" s="2" t="inlineStr">
+        <is>
+          <t>L1 en mode ligne (nappes continues) / public</t>
+        </is>
+      </c>
+      <c r="G675" s="3" t="n">
+        <v>13.735</v>
+      </c>
+      <c r="H675" s="4">
+        <f>IF(G675&gt;0,1000/G675,"")</f>
+        <v/>
+      </c>
+      <c r="I675" s="3" t="n">
+        <v>12.905</v>
+      </c>
+      <c r="J675" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="K675" s="3" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="L675" s="3" t="n">
+        <v>0.6909999999999999</v>
+      </c>
+      <c r="M675" s="3" t="n"/>
+      <c r="N675" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O675" s="2" t="inlineStr">
+        <is>
+          <t>arcs4_B0, arcs4_B1</t>
+        </is>
+      </c>
+      <c r="P675" s="3" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="Q675" s="2" t="inlineStr">
+        <is>
+          <t>lasers</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 16:32</t>
+        </is>
+      </c>
+      <c r="B676" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec+</t>
+        </is>
+      </c>
+      <c r="C676" s="2" t="inlineStr">
+        <is>
+          <t>23. arcs : silhouettes adoucies, pyramide coupee a l'ecran et aux parois, passe des arcs a part</t>
+        </is>
+      </c>
+      <c r="D676" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide (lyres)</t>
+        </is>
+      </c>
+      <c r="E676" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F676" s="2" t="inlineStr">
+        <is>
+          <t>defaut / public</t>
+        </is>
+      </c>
+      <c r="G676" s="3" t="n">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="H676" s="4">
+        <f>IF(G676&gt;0,1000/G676,"")</f>
+        <v/>
+      </c>
+      <c r="I676" s="3" t="n">
+        <v>6.785</v>
+      </c>
+      <c r="J676" s="3" t="n">
+        <v>6.085</v>
+      </c>
+      <c r="K676" s="3" t="n">
+        <v>1.626</v>
+      </c>
+      <c r="L676" s="3" t="n">
+        <v>2.055</v>
+      </c>
+      <c r="M676" s="3" t="n"/>
+      <c r="N676" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="O676" s="2" t="inlineStr">
+        <is>
+          <t>arcs4ly_B0, arcs4ly_B1</t>
+        </is>
+      </c>
+      <c r="P676" s="3" t="n"/>
+      <c r="Q676" s="2" t="inlineStr">
+        <is>
+          <t>lyres</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 16:32</t>
+        </is>
+      </c>
+      <c r="B677" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec+</t>
+        </is>
+      </c>
+      <c r="C677" s="2" t="inlineStr">
+        <is>
+          <t>23. arcs : silhouettes adoucies, pyramide coupee a l'ecran et aux parois, passe des arcs a part</t>
+        </is>
+      </c>
+      <c r="D677" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide (lyres)</t>
+        </is>
+      </c>
+      <c r="E677" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F677" s="2" t="inlineStr">
+        <is>
+          <t>gobo + prisme 8 + zoom 25 / public</t>
+        </is>
+      </c>
+      <c r="G677" s="3" t="n">
+        <v>17.805</v>
+      </c>
+      <c r="H677" s="4">
+        <f>IF(G677&gt;0,1000/G677,"")</f>
+        <v/>
+      </c>
+      <c r="I677" s="3" t="n">
+        <v>16.915</v>
+      </c>
+      <c r="J677" s="3" t="n">
+        <v>16.845</v>
+      </c>
+      <c r="K677" s="3" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="L677" s="3" t="n">
+        <v>6.838</v>
+      </c>
+      <c r="M677" s="3" t="n"/>
+      <c r="N677" s="2" t="n">
+        <v>280</v>
+      </c>
+      <c r="O677" s="2" t="inlineStr">
+        <is>
+          <t>arcs4ly_B0, arcs4ly_B1</t>
+        </is>
+      </c>
+      <c r="P677" s="3" t="n"/>
+      <c r="Q677" s="2" t="inlineStr">
+        <is>
+          <t>lyres</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 16:32</t>
+        </is>
+      </c>
+      <c r="B678" s="2" t="inlineStr">
+        <is>
+          <t>eb108ec+</t>
+        </is>
+      </c>
+      <c r="C678" s="2" t="inlineStr">
+        <is>
+          <t>23. arcs : silhouettes adoucies, pyramide coupee a l'ecran et aux parois, passe des arcs a part</t>
+        </is>
+      </c>
+      <c r="D678" s="2" t="inlineStr">
+        <is>
+          <t>adaptive=0, immobile, banc rapide (lyres)</t>
+        </is>
+      </c>
+      <c r="E678" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F678" s="2" t="inlineStr">
+        <is>
+          <t>zoom 45 + frost 0.6 / public</t>
+        </is>
+      </c>
+      <c r="G678" s="3" t="n">
+        <v>11.635</v>
+      </c>
+      <c r="H678" s="4">
+        <f>IF(G678&gt;0,1000/G678,"")</f>
+        <v/>
+      </c>
+      <c r="I678" s="3" t="n">
+        <v>10.725</v>
+      </c>
+      <c r="J678" s="3" t="n">
+        <v>10.215</v>
+      </c>
+      <c r="K678" s="3" t="n">
+        <v>3.405</v>
+      </c>
+      <c r="L678" s="3" t="n">
+        <v>4.174</v>
+      </c>
+      <c r="M678" s="3" t="n"/>
+      <c r="N678" s="2" t="n">
+        <v>887</v>
+      </c>
+      <c r="O678" s="2" t="inlineStr">
+        <is>
+          <t>arcs4ly_B0, arcs4ly_B1</t>
+        </is>
+      </c>
+      <c r="P678" s="3" t="n"/>
+      <c r="Q678" s="2" t="inlineStr">
+        <is>
+          <t>lyres</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -35931,7 +42905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY75"/>
+  <dimension ref="A1:BF75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -35985,6 +42959,13 @@
     <col width="16" customWidth="1" min="49" max="49"/>
     <col width="16" customWidth="1" min="50" max="50"/>
     <col width="16" customWidth="1" min="51" max="51"/>
+    <col width="16" customWidth="1" min="52" max="52"/>
+    <col width="16" customWidth="1" min="53" max="53"/>
+    <col width="16" customWidth="1" min="54" max="54"/>
+    <col width="16" customWidth="1" min="55" max="55"/>
+    <col width="16" customWidth="1" min="56" max="56"/>
+    <col width="16" customWidth="1" min="57" max="57"/>
+    <col width="16" customWidth="1" min="58" max="58"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -36250,6 +43231,41 @@
           <t>20. Lyres : lecture ILDA (inchange)</t>
         </is>
       </c>
+      <c r="AZ2" s="1" t="inlineStr">
+        <is>
+          <t>21. Lasers : collisions, code present coupe (lasercoll=0)</t>
+        </is>
+      </c>
+      <c r="BA2" s="1" t="inlineStr">
+        <is>
+          <t>21. Lasers : collisions actives (essai, test avec branchement)</t>
+        </is>
+      </c>
+      <c r="BB2" s="1" t="inlineStr">
+        <is>
+          <t>22. Lasers : impacts coupes (laserimpacts=0)</t>
+        </is>
+      </c>
+      <c r="BC2" s="1" t="inlineStr">
+        <is>
+          <t>22. Lasers : impacts sur les surfaces</t>
+        </is>
+      </c>
+      <c r="BD2" s="1" t="inlineStr">
+        <is>
+          <t>22b. Lasers : etape 5 (collisions + impacts), en mouvement</t>
+        </is>
+      </c>
+      <c r="BE2" s="1" t="inlineStr">
+        <is>
+          <t>22b. Lyres : etape 5 (inchange)</t>
+        </is>
+      </c>
+      <c r="BF2" s="1" t="inlineStr">
+        <is>
+          <t>23. arcs : silhouettes adoucies, pyramide coupee a l'ecran et aux parois, passe des arcs a part</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -36457,6 +43473,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A3,Mesures!$C:$C,AY$2),"")</f>
         <v/>
       </c>
+      <c r="AZ3" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A3,Mesures!$C:$C,AZ$2),"")</f>
+        <v/>
+      </c>
+      <c r="BA3" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A3,Mesures!$C:$C,BA$2),"")</f>
+        <v/>
+      </c>
+      <c r="BB3" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A3,Mesures!$C:$C,BB$2),"")</f>
+        <v/>
+      </c>
+      <c r="BC3" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A3,Mesures!$C:$C,BC$2),"")</f>
+        <v/>
+      </c>
+      <c r="BD3" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A3,Mesures!$C:$C,BD$2),"")</f>
+        <v/>
+      </c>
+      <c r="BE3" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A3,Mesures!$C:$C,BE$2),"")</f>
+        <v/>
+      </c>
+      <c r="BF3" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A3,Mesures!$C:$C,BF$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -36664,6 +43708,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A4,Mesures!$C:$C,AY$2),"")</f>
         <v/>
       </c>
+      <c r="AZ4" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A4,Mesures!$C:$C,AZ$2),"")</f>
+        <v/>
+      </c>
+      <c r="BA4" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A4,Mesures!$C:$C,BA$2),"")</f>
+        <v/>
+      </c>
+      <c r="BB4" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A4,Mesures!$C:$C,BB$2),"")</f>
+        <v/>
+      </c>
+      <c r="BC4" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A4,Mesures!$C:$C,BC$2),"")</f>
+        <v/>
+      </c>
+      <c r="BD4" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A4,Mesures!$C:$C,BD$2),"")</f>
+        <v/>
+      </c>
+      <c r="BE4" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A4,Mesures!$C:$C,BE$2),"")</f>
+        <v/>
+      </c>
+      <c r="BF4" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A4,Mesures!$C:$C,BF$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -36871,6 +43943,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A5,Mesures!$C:$C,AY$2),"")</f>
         <v/>
       </c>
+      <c r="AZ5" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A5,Mesures!$C:$C,AZ$2),"")</f>
+        <v/>
+      </c>
+      <c r="BA5" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A5,Mesures!$C:$C,BA$2),"")</f>
+        <v/>
+      </c>
+      <c r="BB5" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A5,Mesures!$C:$C,BB$2),"")</f>
+        <v/>
+      </c>
+      <c r="BC5" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A5,Mesures!$C:$C,BC$2),"")</f>
+        <v/>
+      </c>
+      <c r="BD5" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A5,Mesures!$C:$C,BD$2),"")</f>
+        <v/>
+      </c>
+      <c r="BE5" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A5,Mesures!$C:$C,BE$2),"")</f>
+        <v/>
+      </c>
+      <c r="BF5" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A5,Mesures!$C:$C,BF$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -37078,6 +44178,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A6,Mesures!$C:$C,AY$2),"")</f>
         <v/>
       </c>
+      <c r="AZ6" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A6,Mesures!$C:$C,AZ$2),"")</f>
+        <v/>
+      </c>
+      <c r="BA6" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A6,Mesures!$C:$C,BA$2),"")</f>
+        <v/>
+      </c>
+      <c r="BB6" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A6,Mesures!$C:$C,BB$2),"")</f>
+        <v/>
+      </c>
+      <c r="BC6" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A6,Mesures!$C:$C,BC$2),"")</f>
+        <v/>
+      </c>
+      <c r="BD6" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A6,Mesures!$C:$C,BD$2),"")</f>
+        <v/>
+      </c>
+      <c r="BE6" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A6,Mesures!$C:$C,BE$2),"")</f>
+        <v/>
+      </c>
+      <c r="BF6" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A6,Mesures!$C:$C,BF$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -37285,6 +44413,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A7,Mesures!$C:$C,AY$2),"")</f>
         <v/>
       </c>
+      <c r="AZ7" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A7,Mesures!$C:$C,AZ$2),"")</f>
+        <v/>
+      </c>
+      <c r="BA7" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A7,Mesures!$C:$C,BA$2),"")</f>
+        <v/>
+      </c>
+      <c r="BB7" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A7,Mesures!$C:$C,BB$2),"")</f>
+        <v/>
+      </c>
+      <c r="BC7" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A7,Mesures!$C:$C,BC$2),"")</f>
+        <v/>
+      </c>
+      <c r="BD7" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A7,Mesures!$C:$C,BD$2),"")</f>
+        <v/>
+      </c>
+      <c r="BE7" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A7,Mesures!$C:$C,BE$2),"")</f>
+        <v/>
+      </c>
+      <c r="BF7" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A7,Mesures!$C:$C,BF$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -37492,6 +44648,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A8,Mesures!$C:$C,AY$2),"")</f>
         <v/>
       </c>
+      <c r="AZ8" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A8,Mesures!$C:$C,AZ$2),"")</f>
+        <v/>
+      </c>
+      <c r="BA8" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A8,Mesures!$C:$C,BA$2),"")</f>
+        <v/>
+      </c>
+      <c r="BB8" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A8,Mesures!$C:$C,BB$2),"")</f>
+        <v/>
+      </c>
+      <c r="BC8" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A8,Mesures!$C:$C,BC$2),"")</f>
+        <v/>
+      </c>
+      <c r="BD8" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A8,Mesures!$C:$C,BD$2),"")</f>
+        <v/>
+      </c>
+      <c r="BE8" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A8,Mesures!$C:$C,BE$2),"")</f>
+        <v/>
+      </c>
+      <c r="BF8" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A8,Mesures!$C:$C,BF$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -37699,6 +44883,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A9,Mesures!$C:$C,AY$2),"")</f>
         <v/>
       </c>
+      <c r="AZ9" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A9,Mesures!$C:$C,AZ$2),"")</f>
+        <v/>
+      </c>
+      <c r="BA9" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A9,Mesures!$C:$C,BA$2),"")</f>
+        <v/>
+      </c>
+      <c r="BB9" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A9,Mesures!$C:$C,BB$2),"")</f>
+        <v/>
+      </c>
+      <c r="BC9" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A9,Mesures!$C:$C,BC$2),"")</f>
+        <v/>
+      </c>
+      <c r="BD9" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A9,Mesures!$C:$C,BD$2),"")</f>
+        <v/>
+      </c>
+      <c r="BE9" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A9,Mesures!$C:$C,BE$2),"")</f>
+        <v/>
+      </c>
+      <c r="BF9" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A9,Mesures!$C:$C,BF$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -37906,6 +45118,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A10,Mesures!$C:$C,AY$2),"")</f>
         <v/>
       </c>
+      <c r="AZ10" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A10,Mesures!$C:$C,AZ$2),"")</f>
+        <v/>
+      </c>
+      <c r="BA10" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A10,Mesures!$C:$C,BA$2),"")</f>
+        <v/>
+      </c>
+      <c r="BB10" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A10,Mesures!$C:$C,BB$2),"")</f>
+        <v/>
+      </c>
+      <c r="BC10" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A10,Mesures!$C:$C,BC$2),"")</f>
+        <v/>
+      </c>
+      <c r="BD10" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A10,Mesures!$C:$C,BD$2),"")</f>
+        <v/>
+      </c>
+      <c r="BE10" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A10,Mesures!$C:$C,BE$2),"")</f>
+        <v/>
+      </c>
+      <c r="BF10" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A10,Mesures!$C:$C,BF$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -38113,6 +45353,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A11,Mesures!$C:$C,AY$2),"")</f>
         <v/>
       </c>
+      <c r="AZ11" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A11,Mesures!$C:$C,AZ$2),"")</f>
+        <v/>
+      </c>
+      <c r="BA11" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A11,Mesures!$C:$C,BA$2),"")</f>
+        <v/>
+      </c>
+      <c r="BB11" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A11,Mesures!$C:$C,BB$2),"")</f>
+        <v/>
+      </c>
+      <c r="BC11" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A11,Mesures!$C:$C,BC$2),"")</f>
+        <v/>
+      </c>
+      <c r="BD11" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A11,Mesures!$C:$C,BD$2),"")</f>
+        <v/>
+      </c>
+      <c r="BE11" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A11,Mesures!$C:$C,BE$2),"")</f>
+        <v/>
+      </c>
+      <c r="BF11" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A11,Mesures!$C:$C,BF$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -38320,6 +45588,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A12,Mesures!$C:$C,AY$2),"")</f>
         <v/>
       </c>
+      <c r="AZ12" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A12,Mesures!$C:$C,AZ$2),"")</f>
+        <v/>
+      </c>
+      <c r="BA12" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A12,Mesures!$C:$C,BA$2),"")</f>
+        <v/>
+      </c>
+      <c r="BB12" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A12,Mesures!$C:$C,BB$2),"")</f>
+        <v/>
+      </c>
+      <c r="BC12" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A12,Mesures!$C:$C,BC$2),"")</f>
+        <v/>
+      </c>
+      <c r="BD12" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A12,Mesures!$C:$C,BD$2),"")</f>
+        <v/>
+      </c>
+      <c r="BE12" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A12,Mesures!$C:$C,BE$2),"")</f>
+        <v/>
+      </c>
+      <c r="BF12" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A12,Mesures!$C:$C,BF$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -38527,6 +45823,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A13,Mesures!$C:$C,AY$2),"")</f>
         <v/>
       </c>
+      <c r="AZ13" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A13,Mesures!$C:$C,AZ$2),"")</f>
+        <v/>
+      </c>
+      <c r="BA13" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A13,Mesures!$C:$C,BA$2),"")</f>
+        <v/>
+      </c>
+      <c r="BB13" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A13,Mesures!$C:$C,BB$2),"")</f>
+        <v/>
+      </c>
+      <c r="BC13" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A13,Mesures!$C:$C,BC$2),"")</f>
+        <v/>
+      </c>
+      <c r="BD13" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A13,Mesures!$C:$C,BD$2),"")</f>
+        <v/>
+      </c>
+      <c r="BE13" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A13,Mesures!$C:$C,BE$2),"")</f>
+        <v/>
+      </c>
+      <c r="BF13" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A13,Mesures!$C:$C,BF$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -38734,6 +46058,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A14,Mesures!$C:$C,AY$2),"")</f>
         <v/>
       </c>
+      <c r="AZ14" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A14,Mesures!$C:$C,AZ$2),"")</f>
+        <v/>
+      </c>
+      <c r="BA14" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A14,Mesures!$C:$C,BA$2),"")</f>
+        <v/>
+      </c>
+      <c r="BB14" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A14,Mesures!$C:$C,BB$2),"")</f>
+        <v/>
+      </c>
+      <c r="BC14" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A14,Mesures!$C:$C,BC$2),"")</f>
+        <v/>
+      </c>
+      <c r="BD14" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A14,Mesures!$C:$C,BD$2),"")</f>
+        <v/>
+      </c>
+      <c r="BE14" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A14,Mesures!$C:$C,BE$2),"")</f>
+        <v/>
+      </c>
+      <c r="BF14" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A14,Mesures!$C:$C,BF$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -38941,6 +46293,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A15,Mesures!$C:$C,AY$2),"")</f>
         <v/>
       </c>
+      <c r="AZ15" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A15,Mesures!$C:$C,AZ$2),"")</f>
+        <v/>
+      </c>
+      <c r="BA15" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A15,Mesures!$C:$C,BA$2),"")</f>
+        <v/>
+      </c>
+      <c r="BB15" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A15,Mesures!$C:$C,BB$2),"")</f>
+        <v/>
+      </c>
+      <c r="BC15" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A15,Mesures!$C:$C,BC$2),"")</f>
+        <v/>
+      </c>
+      <c r="BD15" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A15,Mesures!$C:$C,BD$2),"")</f>
+        <v/>
+      </c>
+      <c r="BE15" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A15,Mesures!$C:$C,BE$2),"")</f>
+        <v/>
+      </c>
+      <c r="BF15" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A15,Mesures!$C:$C,BF$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -39148,6 +46528,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A16,Mesures!$C:$C,AY$2),"")</f>
         <v/>
       </c>
+      <c r="AZ16" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A16,Mesures!$C:$C,AZ$2),"")</f>
+        <v/>
+      </c>
+      <c r="BA16" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A16,Mesures!$C:$C,BA$2),"")</f>
+        <v/>
+      </c>
+      <c r="BB16" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A16,Mesures!$C:$C,BB$2),"")</f>
+        <v/>
+      </c>
+      <c r="BC16" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A16,Mesures!$C:$C,BC$2),"")</f>
+        <v/>
+      </c>
+      <c r="BD16" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A16,Mesures!$C:$C,BD$2),"")</f>
+        <v/>
+      </c>
+      <c r="BE16" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A16,Mesures!$C:$C,BE$2),"")</f>
+        <v/>
+      </c>
+      <c r="BF16" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A16,Mesures!$C:$C,BF$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -39355,6 +46763,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A17,Mesures!$C:$C,AY$2),"")</f>
         <v/>
       </c>
+      <c r="AZ17" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A17,Mesures!$C:$C,AZ$2),"")</f>
+        <v/>
+      </c>
+      <c r="BA17" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A17,Mesures!$C:$C,BA$2),"")</f>
+        <v/>
+      </c>
+      <c r="BB17" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A17,Mesures!$C:$C,BB$2),"")</f>
+        <v/>
+      </c>
+      <c r="BC17" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A17,Mesures!$C:$C,BC$2),"")</f>
+        <v/>
+      </c>
+      <c r="BD17" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A17,Mesures!$C:$C,BD$2),"")</f>
+        <v/>
+      </c>
+      <c r="BE17" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A17,Mesures!$C:$C,BE$2),"")</f>
+        <v/>
+      </c>
+      <c r="BF17" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A17,Mesures!$C:$C,BF$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -39562,6 +46998,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A18,Mesures!$C:$C,AY$2),"")</f>
         <v/>
       </c>
+      <c r="AZ18" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A18,Mesures!$C:$C,AZ$2),"")</f>
+        <v/>
+      </c>
+      <c r="BA18" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A18,Mesures!$C:$C,BA$2),"")</f>
+        <v/>
+      </c>
+      <c r="BB18" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A18,Mesures!$C:$C,BB$2),"")</f>
+        <v/>
+      </c>
+      <c r="BC18" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A18,Mesures!$C:$C,BC$2),"")</f>
+        <v/>
+      </c>
+      <c r="BD18" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A18,Mesures!$C:$C,BD$2),"")</f>
+        <v/>
+      </c>
+      <c r="BE18" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A18,Mesures!$C:$C,BE$2),"")</f>
+        <v/>
+      </c>
+      <c r="BF18" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A18,Mesures!$C:$C,BF$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -39769,6 +47233,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A19,Mesures!$C:$C,AY$2),"")</f>
         <v/>
       </c>
+      <c r="AZ19" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A19,Mesures!$C:$C,AZ$2),"")</f>
+        <v/>
+      </c>
+      <c r="BA19" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A19,Mesures!$C:$C,BA$2),"")</f>
+        <v/>
+      </c>
+      <c r="BB19" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A19,Mesures!$C:$C,BB$2),"")</f>
+        <v/>
+      </c>
+      <c r="BC19" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A19,Mesures!$C:$C,BC$2),"")</f>
+        <v/>
+      </c>
+      <c r="BD19" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A19,Mesures!$C:$C,BD$2),"")</f>
+        <v/>
+      </c>
+      <c r="BE19" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A19,Mesures!$C:$C,BE$2),"")</f>
+        <v/>
+      </c>
+      <c r="BF19" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A19,Mesures!$C:$C,BF$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -39976,6 +47468,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A20,Mesures!$C:$C,AY$2),"")</f>
         <v/>
       </c>
+      <c r="AZ20" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A20,Mesures!$C:$C,AZ$2),"")</f>
+        <v/>
+      </c>
+      <c r="BA20" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A20,Mesures!$C:$C,BA$2),"")</f>
+        <v/>
+      </c>
+      <c r="BB20" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A20,Mesures!$C:$C,BB$2),"")</f>
+        <v/>
+      </c>
+      <c r="BC20" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A20,Mesures!$C:$C,BC$2),"")</f>
+        <v/>
+      </c>
+      <c r="BD20" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A20,Mesures!$C:$C,BD$2),"")</f>
+        <v/>
+      </c>
+      <c r="BE20" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A20,Mesures!$C:$C,BE$2),"")</f>
+        <v/>
+      </c>
+      <c r="BF20" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A20,Mesures!$C:$C,BF$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -40183,6 +47703,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A21,Mesures!$C:$C,AY$2),"")</f>
         <v/>
       </c>
+      <c r="AZ21" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A21,Mesures!$C:$C,AZ$2),"")</f>
+        <v/>
+      </c>
+      <c r="BA21" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A21,Mesures!$C:$C,BA$2),"")</f>
+        <v/>
+      </c>
+      <c r="BB21" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A21,Mesures!$C:$C,BB$2),"")</f>
+        <v/>
+      </c>
+      <c r="BC21" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A21,Mesures!$C:$C,BC$2),"")</f>
+        <v/>
+      </c>
+      <c r="BD21" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A21,Mesures!$C:$C,BD$2),"")</f>
+        <v/>
+      </c>
+      <c r="BE21" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A21,Mesures!$C:$C,BE$2),"")</f>
+        <v/>
+      </c>
+      <c r="BF21" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A21,Mesures!$C:$C,BF$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -40390,6 +47938,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A22,Mesures!$C:$C,AY$2),"")</f>
         <v/>
       </c>
+      <c r="AZ22" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A22,Mesures!$C:$C,AZ$2),"")</f>
+        <v/>
+      </c>
+      <c r="BA22" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A22,Mesures!$C:$C,BA$2),"")</f>
+        <v/>
+      </c>
+      <c r="BB22" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A22,Mesures!$C:$C,BB$2),"")</f>
+        <v/>
+      </c>
+      <c r="BC22" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A22,Mesures!$C:$C,BC$2),"")</f>
+        <v/>
+      </c>
+      <c r="BD22" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A22,Mesures!$C:$C,BD$2),"")</f>
+        <v/>
+      </c>
+      <c r="BE22" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A22,Mesures!$C:$C,BE$2),"")</f>
+        <v/>
+      </c>
+      <c r="BF22" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A22,Mesures!$C:$C,BF$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -40597,6 +48173,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A23,Mesures!$C:$C,AY$2),"")</f>
         <v/>
       </c>
+      <c r="AZ23" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A23,Mesures!$C:$C,AZ$2),"")</f>
+        <v/>
+      </c>
+      <c r="BA23" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A23,Mesures!$C:$C,BA$2),"")</f>
+        <v/>
+      </c>
+      <c r="BB23" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A23,Mesures!$C:$C,BB$2),"")</f>
+        <v/>
+      </c>
+      <c r="BC23" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A23,Mesures!$C:$C,BC$2),"")</f>
+        <v/>
+      </c>
+      <c r="BD23" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A23,Mesures!$C:$C,BD$2),"")</f>
+        <v/>
+      </c>
+      <c r="BE23" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A23,Mesures!$C:$C,BE$2),"")</f>
+        <v/>
+      </c>
+      <c r="BF23" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A23,Mesures!$C:$C,BF$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -40804,6 +48408,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A24,Mesures!$C:$C,AY$2),"")</f>
         <v/>
       </c>
+      <c r="AZ24" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A24,Mesures!$C:$C,AZ$2),"")</f>
+        <v/>
+      </c>
+      <c r="BA24" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A24,Mesures!$C:$C,BA$2),"")</f>
+        <v/>
+      </c>
+      <c r="BB24" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A24,Mesures!$C:$C,BB$2),"")</f>
+        <v/>
+      </c>
+      <c r="BC24" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A24,Mesures!$C:$C,BC$2),"")</f>
+        <v/>
+      </c>
+      <c r="BD24" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A24,Mesures!$C:$C,BD$2),"")</f>
+        <v/>
+      </c>
+      <c r="BE24" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A24,Mesures!$C:$C,BE$2),"")</f>
+        <v/>
+      </c>
+      <c r="BF24" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A24,Mesures!$C:$C,BF$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -41011,6 +48643,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A25,Mesures!$C:$C,AY$2),"")</f>
         <v/>
       </c>
+      <c r="AZ25" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A25,Mesures!$C:$C,AZ$2),"")</f>
+        <v/>
+      </c>
+      <c r="BA25" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A25,Mesures!$C:$C,BA$2),"")</f>
+        <v/>
+      </c>
+      <c r="BB25" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A25,Mesures!$C:$C,BB$2),"")</f>
+        <v/>
+      </c>
+      <c r="BC25" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A25,Mesures!$C:$C,BC$2),"")</f>
+        <v/>
+      </c>
+      <c r="BD25" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A25,Mesures!$C:$C,BD$2),"")</f>
+        <v/>
+      </c>
+      <c r="BE25" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A25,Mesures!$C:$C,BE$2),"")</f>
+        <v/>
+      </c>
+      <c r="BF25" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A25,Mesures!$C:$C,BF$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -41218,6 +48878,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A26,Mesures!$C:$C,AY$2),"")</f>
         <v/>
       </c>
+      <c r="AZ26" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A26,Mesures!$C:$C,AZ$2),"")</f>
+        <v/>
+      </c>
+      <c r="BA26" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A26,Mesures!$C:$C,BA$2),"")</f>
+        <v/>
+      </c>
+      <c r="BB26" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A26,Mesures!$C:$C,BB$2),"")</f>
+        <v/>
+      </c>
+      <c r="BC26" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A26,Mesures!$C:$C,BC$2),"")</f>
+        <v/>
+      </c>
+      <c r="BD26" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A26,Mesures!$C:$C,BD$2),"")</f>
+        <v/>
+      </c>
+      <c r="BE26" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A26,Mesures!$C:$C,BE$2),"")</f>
+        <v/>
+      </c>
+      <c r="BF26" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A26,Mesures!$C:$C,BF$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -41425,6 +49113,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A27,Mesures!$C:$C,AY$2),"")</f>
         <v/>
       </c>
+      <c r="AZ27" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A27,Mesures!$C:$C,AZ$2),"")</f>
+        <v/>
+      </c>
+      <c r="BA27" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A27,Mesures!$C:$C,BA$2),"")</f>
+        <v/>
+      </c>
+      <c r="BB27" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A27,Mesures!$C:$C,BB$2),"")</f>
+        <v/>
+      </c>
+      <c r="BC27" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A27,Mesures!$C:$C,BC$2),"")</f>
+        <v/>
+      </c>
+      <c r="BD27" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A27,Mesures!$C:$C,BD$2),"")</f>
+        <v/>
+      </c>
+      <c r="BE27" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A27,Mesures!$C:$C,BE$2),"")</f>
+        <v/>
+      </c>
+      <c r="BF27" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A27,Mesures!$C:$C,BF$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -41632,6 +49348,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A28,Mesures!$C:$C,AY$2),"")</f>
         <v/>
       </c>
+      <c r="AZ28" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A28,Mesures!$C:$C,AZ$2),"")</f>
+        <v/>
+      </c>
+      <c r="BA28" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A28,Mesures!$C:$C,BA$2),"")</f>
+        <v/>
+      </c>
+      <c r="BB28" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A28,Mesures!$C:$C,BB$2),"")</f>
+        <v/>
+      </c>
+      <c r="BC28" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A28,Mesures!$C:$C,BC$2),"")</f>
+        <v/>
+      </c>
+      <c r="BD28" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A28,Mesures!$C:$C,BD$2),"")</f>
+        <v/>
+      </c>
+      <c r="BE28" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A28,Mesures!$C:$C,BE$2),"")</f>
+        <v/>
+      </c>
+      <c r="BF28" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A28,Mesures!$C:$C,BF$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -41839,6 +49583,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A29,Mesures!$C:$C,AY$2),"")</f>
         <v/>
       </c>
+      <c r="AZ29" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A29,Mesures!$C:$C,AZ$2),"")</f>
+        <v/>
+      </c>
+      <c r="BA29" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A29,Mesures!$C:$C,BA$2),"")</f>
+        <v/>
+      </c>
+      <c r="BB29" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A29,Mesures!$C:$C,BB$2),"")</f>
+        <v/>
+      </c>
+      <c r="BC29" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A29,Mesures!$C:$C,BC$2),"")</f>
+        <v/>
+      </c>
+      <c r="BD29" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A29,Mesures!$C:$C,BD$2),"")</f>
+        <v/>
+      </c>
+      <c r="BE29" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A29,Mesures!$C:$C,BE$2),"")</f>
+        <v/>
+      </c>
+      <c r="BF29" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A29,Mesures!$C:$C,BF$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -42046,6 +49818,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A30,Mesures!$C:$C,AY$2),"")</f>
         <v/>
       </c>
+      <c r="AZ30" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A30,Mesures!$C:$C,AZ$2),"")</f>
+        <v/>
+      </c>
+      <c r="BA30" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A30,Mesures!$C:$C,BA$2),"")</f>
+        <v/>
+      </c>
+      <c r="BB30" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A30,Mesures!$C:$C,BB$2),"")</f>
+        <v/>
+      </c>
+      <c r="BC30" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A30,Mesures!$C:$C,BC$2),"")</f>
+        <v/>
+      </c>
+      <c r="BD30" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A30,Mesures!$C:$C,BD$2),"")</f>
+        <v/>
+      </c>
+      <c r="BE30" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A30,Mesures!$C:$C,BE$2),"")</f>
+        <v/>
+      </c>
+      <c r="BF30" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A30,Mesures!$C:$C,BF$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -42253,6 +50053,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A31,Mesures!$C:$C,AY$2),"")</f>
         <v/>
       </c>
+      <c r="AZ31" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A31,Mesures!$C:$C,AZ$2),"")</f>
+        <v/>
+      </c>
+      <c r="BA31" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A31,Mesures!$C:$C,BA$2),"")</f>
+        <v/>
+      </c>
+      <c r="BB31" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A31,Mesures!$C:$C,BB$2),"")</f>
+        <v/>
+      </c>
+      <c r="BC31" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A31,Mesures!$C:$C,BC$2),"")</f>
+        <v/>
+      </c>
+      <c r="BD31" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A31,Mesures!$C:$C,BD$2),"")</f>
+        <v/>
+      </c>
+      <c r="BE31" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A31,Mesures!$C:$C,BE$2),"")</f>
+        <v/>
+      </c>
+      <c r="BF31" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A31,Mesures!$C:$C,BF$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -42460,6 +50288,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A32,Mesures!$C:$C,AY$2),"")</f>
         <v/>
       </c>
+      <c r="AZ32" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A32,Mesures!$C:$C,AZ$2),"")</f>
+        <v/>
+      </c>
+      <c r="BA32" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A32,Mesures!$C:$C,BA$2),"")</f>
+        <v/>
+      </c>
+      <c r="BB32" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A32,Mesures!$C:$C,BB$2),"")</f>
+        <v/>
+      </c>
+      <c r="BC32" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A32,Mesures!$C:$C,BC$2),"")</f>
+        <v/>
+      </c>
+      <c r="BD32" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A32,Mesures!$C:$C,BD$2),"")</f>
+        <v/>
+      </c>
+      <c r="BE32" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A32,Mesures!$C:$C,BE$2),"")</f>
+        <v/>
+      </c>
+      <c r="BF32" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A32,Mesures!$C:$C,BF$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -42667,6 +50523,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A33,Mesures!$C:$C,AY$2),"")</f>
         <v/>
       </c>
+      <c r="AZ33" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A33,Mesures!$C:$C,AZ$2),"")</f>
+        <v/>
+      </c>
+      <c r="BA33" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A33,Mesures!$C:$C,BA$2),"")</f>
+        <v/>
+      </c>
+      <c r="BB33" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A33,Mesures!$C:$C,BB$2),"")</f>
+        <v/>
+      </c>
+      <c r="BC33" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A33,Mesures!$C:$C,BC$2),"")</f>
+        <v/>
+      </c>
+      <c r="BD33" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A33,Mesures!$C:$C,BD$2),"")</f>
+        <v/>
+      </c>
+      <c r="BE33" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A33,Mesures!$C:$C,BE$2),"")</f>
+        <v/>
+      </c>
+      <c r="BF33" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A33,Mesures!$C:$C,BF$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -42874,6 +50758,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A34,Mesures!$C:$C,AY$2),"")</f>
         <v/>
       </c>
+      <c r="AZ34" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A34,Mesures!$C:$C,AZ$2),"")</f>
+        <v/>
+      </c>
+      <c r="BA34" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A34,Mesures!$C:$C,BA$2),"")</f>
+        <v/>
+      </c>
+      <c r="BB34" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A34,Mesures!$C:$C,BB$2),"")</f>
+        <v/>
+      </c>
+      <c r="BC34" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A34,Mesures!$C:$C,BC$2),"")</f>
+        <v/>
+      </c>
+      <c r="BD34" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A34,Mesures!$C:$C,BD$2),"")</f>
+        <v/>
+      </c>
+      <c r="BE34" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A34,Mesures!$C:$C,BE$2),"")</f>
+        <v/>
+      </c>
+      <c r="BF34" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A34,Mesures!$C:$C,BF$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -43081,6 +50993,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A35,Mesures!$C:$C,AY$2),"")</f>
         <v/>
       </c>
+      <c r="AZ35" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A35,Mesures!$C:$C,AZ$2),"")</f>
+        <v/>
+      </c>
+      <c r="BA35" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A35,Mesures!$C:$C,BA$2),"")</f>
+        <v/>
+      </c>
+      <c r="BB35" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A35,Mesures!$C:$C,BB$2),"")</f>
+        <v/>
+      </c>
+      <c r="BC35" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A35,Mesures!$C:$C,BC$2),"")</f>
+        <v/>
+      </c>
+      <c r="BD35" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A35,Mesures!$C:$C,BD$2),"")</f>
+        <v/>
+      </c>
+      <c r="BE35" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A35,Mesures!$C:$C,BE$2),"")</f>
+        <v/>
+      </c>
+      <c r="BF35" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A35,Mesures!$C:$C,BF$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -43288,6 +51228,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A36,Mesures!$C:$C,AY$2),"")</f>
         <v/>
       </c>
+      <c r="AZ36" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A36,Mesures!$C:$C,AZ$2),"")</f>
+        <v/>
+      </c>
+      <c r="BA36" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A36,Mesures!$C:$C,BA$2),"")</f>
+        <v/>
+      </c>
+      <c r="BB36" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A36,Mesures!$C:$C,BB$2),"")</f>
+        <v/>
+      </c>
+      <c r="BC36" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A36,Mesures!$C:$C,BC$2),"")</f>
+        <v/>
+      </c>
+      <c r="BD36" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A36,Mesures!$C:$C,BD$2),"")</f>
+        <v/>
+      </c>
+      <c r="BE36" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A36,Mesures!$C:$C,BE$2),"")</f>
+        <v/>
+      </c>
+      <c r="BF36" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A36,Mesures!$C:$C,BF$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -43495,6 +51463,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A37,Mesures!$C:$C,AY$2),"")</f>
         <v/>
       </c>
+      <c r="AZ37" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A37,Mesures!$C:$C,AZ$2),"")</f>
+        <v/>
+      </c>
+      <c r="BA37" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A37,Mesures!$C:$C,BA$2),"")</f>
+        <v/>
+      </c>
+      <c r="BB37" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A37,Mesures!$C:$C,BB$2),"")</f>
+        <v/>
+      </c>
+      <c r="BC37" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A37,Mesures!$C:$C,BC$2),"")</f>
+        <v/>
+      </c>
+      <c r="BD37" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A37,Mesures!$C:$C,BD$2),"")</f>
+        <v/>
+      </c>
+      <c r="BE37" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A37,Mesures!$C:$C,BE$2),"")</f>
+        <v/>
+      </c>
+      <c r="BF37" s="4">
+        <f>IFERROR(AVERAGEIFS(Mesures!$H:$H,Mesures!$F:$F,$A37,Mesures!$C:$C,BF$2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -43759,6 +51755,41 @@
           <t>20. Lyres : lecture ILDA (inchange)</t>
         </is>
       </c>
+      <c r="AZ40" s="1" t="inlineStr">
+        <is>
+          <t>21. Lasers : collisions, code present coupe (lasercoll=0)</t>
+        </is>
+      </c>
+      <c r="BA40" s="1" t="inlineStr">
+        <is>
+          <t>21. Lasers : collisions actives (essai, test avec branchement)</t>
+        </is>
+      </c>
+      <c r="BB40" s="1" t="inlineStr">
+        <is>
+          <t>22. Lasers : impacts coupes (laserimpacts=0)</t>
+        </is>
+      </c>
+      <c r="BC40" s="1" t="inlineStr">
+        <is>
+          <t>22. Lasers : impacts sur les surfaces</t>
+        </is>
+      </c>
+      <c r="BD40" s="1" t="inlineStr">
+        <is>
+          <t>22b. Lasers : etape 5 (collisions + impacts), en mouvement</t>
+        </is>
+      </c>
+      <c r="BE40" s="1" t="inlineStr">
+        <is>
+          <t>22b. Lyres : etape 5 (inchange)</t>
+        </is>
+      </c>
+      <c r="BF40" s="1" t="inlineStr">
+        <is>
+          <t>23. arcs : silhouettes adoucies, pyramide coupee a l'ecran et aux parois, passe des arcs a part</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -43966,6 +51997,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A41,Mesures!$C:$C,AY$40),"")</f>
         <v/>
       </c>
+      <c r="AZ41" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A41,Mesures!$C:$C,AZ$40),"")</f>
+        <v/>
+      </c>
+      <c r="BA41" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A41,Mesures!$C:$C,BA$40),"")</f>
+        <v/>
+      </c>
+      <c r="BB41" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A41,Mesures!$C:$C,BB$40),"")</f>
+        <v/>
+      </c>
+      <c r="BC41" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A41,Mesures!$C:$C,BC$40),"")</f>
+        <v/>
+      </c>
+      <c r="BD41" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A41,Mesures!$C:$C,BD$40),"")</f>
+        <v/>
+      </c>
+      <c r="BE41" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A41,Mesures!$C:$C,BE$40),"")</f>
+        <v/>
+      </c>
+      <c r="BF41" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A41,Mesures!$C:$C,BF$40),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -44173,6 +52232,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A42,Mesures!$C:$C,AY$40),"")</f>
         <v/>
       </c>
+      <c r="AZ42" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A42,Mesures!$C:$C,AZ$40),"")</f>
+        <v/>
+      </c>
+      <c r="BA42" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A42,Mesures!$C:$C,BA$40),"")</f>
+        <v/>
+      </c>
+      <c r="BB42" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A42,Mesures!$C:$C,BB$40),"")</f>
+        <v/>
+      </c>
+      <c r="BC42" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A42,Mesures!$C:$C,BC$40),"")</f>
+        <v/>
+      </c>
+      <c r="BD42" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A42,Mesures!$C:$C,BD$40),"")</f>
+        <v/>
+      </c>
+      <c r="BE42" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A42,Mesures!$C:$C,BE$40),"")</f>
+        <v/>
+      </c>
+      <c r="BF42" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A42,Mesures!$C:$C,BF$40),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -44380,6 +52467,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A43,Mesures!$C:$C,AY$40),"")</f>
         <v/>
       </c>
+      <c r="AZ43" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A43,Mesures!$C:$C,AZ$40),"")</f>
+        <v/>
+      </c>
+      <c r="BA43" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A43,Mesures!$C:$C,BA$40),"")</f>
+        <v/>
+      </c>
+      <c r="BB43" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A43,Mesures!$C:$C,BB$40),"")</f>
+        <v/>
+      </c>
+      <c r="BC43" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A43,Mesures!$C:$C,BC$40),"")</f>
+        <v/>
+      </c>
+      <c r="BD43" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A43,Mesures!$C:$C,BD$40),"")</f>
+        <v/>
+      </c>
+      <c r="BE43" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A43,Mesures!$C:$C,BE$40),"")</f>
+        <v/>
+      </c>
+      <c r="BF43" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A43,Mesures!$C:$C,BF$40),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -44587,6 +52702,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A44,Mesures!$C:$C,AY$40),"")</f>
         <v/>
       </c>
+      <c r="AZ44" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A44,Mesures!$C:$C,AZ$40),"")</f>
+        <v/>
+      </c>
+      <c r="BA44" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A44,Mesures!$C:$C,BA$40),"")</f>
+        <v/>
+      </c>
+      <c r="BB44" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A44,Mesures!$C:$C,BB$40),"")</f>
+        <v/>
+      </c>
+      <c r="BC44" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A44,Mesures!$C:$C,BC$40),"")</f>
+        <v/>
+      </c>
+      <c r="BD44" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A44,Mesures!$C:$C,BD$40),"")</f>
+        <v/>
+      </c>
+      <c r="BE44" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A44,Mesures!$C:$C,BE$40),"")</f>
+        <v/>
+      </c>
+      <c r="BF44" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A44,Mesures!$C:$C,BF$40),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -44794,6 +52937,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A45,Mesures!$C:$C,AY$40),"")</f>
         <v/>
       </c>
+      <c r="AZ45" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A45,Mesures!$C:$C,AZ$40),"")</f>
+        <v/>
+      </c>
+      <c r="BA45" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A45,Mesures!$C:$C,BA$40),"")</f>
+        <v/>
+      </c>
+      <c r="BB45" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A45,Mesures!$C:$C,BB$40),"")</f>
+        <v/>
+      </c>
+      <c r="BC45" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A45,Mesures!$C:$C,BC$40),"")</f>
+        <v/>
+      </c>
+      <c r="BD45" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A45,Mesures!$C:$C,BD$40),"")</f>
+        <v/>
+      </c>
+      <c r="BE45" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A45,Mesures!$C:$C,BE$40),"")</f>
+        <v/>
+      </c>
+      <c r="BF45" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A45,Mesures!$C:$C,BF$40),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -45001,6 +53172,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A46,Mesures!$C:$C,AY$40),"")</f>
         <v/>
       </c>
+      <c r="AZ46" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A46,Mesures!$C:$C,AZ$40),"")</f>
+        <v/>
+      </c>
+      <c r="BA46" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A46,Mesures!$C:$C,BA$40),"")</f>
+        <v/>
+      </c>
+      <c r="BB46" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A46,Mesures!$C:$C,BB$40),"")</f>
+        <v/>
+      </c>
+      <c r="BC46" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A46,Mesures!$C:$C,BC$40),"")</f>
+        <v/>
+      </c>
+      <c r="BD46" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A46,Mesures!$C:$C,BD$40),"")</f>
+        <v/>
+      </c>
+      <c r="BE46" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A46,Mesures!$C:$C,BE$40),"")</f>
+        <v/>
+      </c>
+      <c r="BF46" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A46,Mesures!$C:$C,BF$40),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -45208,6 +53407,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A47,Mesures!$C:$C,AY$40),"")</f>
         <v/>
       </c>
+      <c r="AZ47" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A47,Mesures!$C:$C,AZ$40),"")</f>
+        <v/>
+      </c>
+      <c r="BA47" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A47,Mesures!$C:$C,BA$40),"")</f>
+        <v/>
+      </c>
+      <c r="BB47" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A47,Mesures!$C:$C,BB$40),"")</f>
+        <v/>
+      </c>
+      <c r="BC47" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A47,Mesures!$C:$C,BC$40),"")</f>
+        <v/>
+      </c>
+      <c r="BD47" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A47,Mesures!$C:$C,BD$40),"")</f>
+        <v/>
+      </c>
+      <c r="BE47" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A47,Mesures!$C:$C,BE$40),"")</f>
+        <v/>
+      </c>
+      <c r="BF47" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A47,Mesures!$C:$C,BF$40),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -45415,6 +53642,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A48,Mesures!$C:$C,AY$40),"")</f>
         <v/>
       </c>
+      <c r="AZ48" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A48,Mesures!$C:$C,AZ$40),"")</f>
+        <v/>
+      </c>
+      <c r="BA48" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A48,Mesures!$C:$C,BA$40),"")</f>
+        <v/>
+      </c>
+      <c r="BB48" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A48,Mesures!$C:$C,BB$40),"")</f>
+        <v/>
+      </c>
+      <c r="BC48" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A48,Mesures!$C:$C,BC$40),"")</f>
+        <v/>
+      </c>
+      <c r="BD48" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A48,Mesures!$C:$C,BD$40),"")</f>
+        <v/>
+      </c>
+      <c r="BE48" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A48,Mesures!$C:$C,BE$40),"")</f>
+        <v/>
+      </c>
+      <c r="BF48" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A48,Mesures!$C:$C,BF$40),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -45622,6 +53877,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A49,Mesures!$C:$C,AY$40),"")</f>
         <v/>
       </c>
+      <c r="AZ49" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A49,Mesures!$C:$C,AZ$40),"")</f>
+        <v/>
+      </c>
+      <c r="BA49" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A49,Mesures!$C:$C,BA$40),"")</f>
+        <v/>
+      </c>
+      <c r="BB49" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A49,Mesures!$C:$C,BB$40),"")</f>
+        <v/>
+      </c>
+      <c r="BC49" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A49,Mesures!$C:$C,BC$40),"")</f>
+        <v/>
+      </c>
+      <c r="BD49" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A49,Mesures!$C:$C,BD$40),"")</f>
+        <v/>
+      </c>
+      <c r="BE49" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A49,Mesures!$C:$C,BE$40),"")</f>
+        <v/>
+      </c>
+      <c r="BF49" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A49,Mesures!$C:$C,BF$40),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -45829,6 +54112,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A50,Mesures!$C:$C,AY$40),"")</f>
         <v/>
       </c>
+      <c r="AZ50" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A50,Mesures!$C:$C,AZ$40),"")</f>
+        <v/>
+      </c>
+      <c r="BA50" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A50,Mesures!$C:$C,BA$40),"")</f>
+        <v/>
+      </c>
+      <c r="BB50" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A50,Mesures!$C:$C,BB$40),"")</f>
+        <v/>
+      </c>
+      <c r="BC50" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A50,Mesures!$C:$C,BC$40),"")</f>
+        <v/>
+      </c>
+      <c r="BD50" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A50,Mesures!$C:$C,BD$40),"")</f>
+        <v/>
+      </c>
+      <c r="BE50" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A50,Mesures!$C:$C,BE$40),"")</f>
+        <v/>
+      </c>
+      <c r="BF50" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A50,Mesures!$C:$C,BF$40),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -46036,6 +54347,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A51,Mesures!$C:$C,AY$40),"")</f>
         <v/>
       </c>
+      <c r="AZ51" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A51,Mesures!$C:$C,AZ$40),"")</f>
+        <v/>
+      </c>
+      <c r="BA51" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A51,Mesures!$C:$C,BA$40),"")</f>
+        <v/>
+      </c>
+      <c r="BB51" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A51,Mesures!$C:$C,BB$40),"")</f>
+        <v/>
+      </c>
+      <c r="BC51" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A51,Mesures!$C:$C,BC$40),"")</f>
+        <v/>
+      </c>
+      <c r="BD51" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A51,Mesures!$C:$C,BD$40),"")</f>
+        <v/>
+      </c>
+      <c r="BE51" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A51,Mesures!$C:$C,BE$40),"")</f>
+        <v/>
+      </c>
+      <c r="BF51" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A51,Mesures!$C:$C,BF$40),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -46243,6 +54582,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A52,Mesures!$C:$C,AY$40),"")</f>
         <v/>
       </c>
+      <c r="AZ52" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A52,Mesures!$C:$C,AZ$40),"")</f>
+        <v/>
+      </c>
+      <c r="BA52" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A52,Mesures!$C:$C,BA$40),"")</f>
+        <v/>
+      </c>
+      <c r="BB52" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A52,Mesures!$C:$C,BB$40),"")</f>
+        <v/>
+      </c>
+      <c r="BC52" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A52,Mesures!$C:$C,BC$40),"")</f>
+        <v/>
+      </c>
+      <c r="BD52" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A52,Mesures!$C:$C,BD$40),"")</f>
+        <v/>
+      </c>
+      <c r="BE52" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A52,Mesures!$C:$C,BE$40),"")</f>
+        <v/>
+      </c>
+      <c r="BF52" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A52,Mesures!$C:$C,BF$40),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -46450,6 +54817,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A53,Mesures!$C:$C,AY$40),"")</f>
         <v/>
       </c>
+      <c r="AZ53" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A53,Mesures!$C:$C,AZ$40),"")</f>
+        <v/>
+      </c>
+      <c r="BA53" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A53,Mesures!$C:$C,BA$40),"")</f>
+        <v/>
+      </c>
+      <c r="BB53" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A53,Mesures!$C:$C,BB$40),"")</f>
+        <v/>
+      </c>
+      <c r="BC53" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A53,Mesures!$C:$C,BC$40),"")</f>
+        <v/>
+      </c>
+      <c r="BD53" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A53,Mesures!$C:$C,BD$40),"")</f>
+        <v/>
+      </c>
+      <c r="BE53" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A53,Mesures!$C:$C,BE$40),"")</f>
+        <v/>
+      </c>
+      <c r="BF53" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A53,Mesures!$C:$C,BF$40),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -46657,6 +55052,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A54,Mesures!$C:$C,AY$40),"")</f>
         <v/>
       </c>
+      <c r="AZ54" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A54,Mesures!$C:$C,AZ$40),"")</f>
+        <v/>
+      </c>
+      <c r="BA54" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A54,Mesures!$C:$C,BA$40),"")</f>
+        <v/>
+      </c>
+      <c r="BB54" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A54,Mesures!$C:$C,BB$40),"")</f>
+        <v/>
+      </c>
+      <c r="BC54" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A54,Mesures!$C:$C,BC$40),"")</f>
+        <v/>
+      </c>
+      <c r="BD54" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A54,Mesures!$C:$C,BD$40),"")</f>
+        <v/>
+      </c>
+      <c r="BE54" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A54,Mesures!$C:$C,BE$40),"")</f>
+        <v/>
+      </c>
+      <c r="BF54" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A54,Mesures!$C:$C,BF$40),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -46864,6 +55287,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A55,Mesures!$C:$C,AY$40),"")</f>
         <v/>
       </c>
+      <c r="AZ55" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A55,Mesures!$C:$C,AZ$40),"")</f>
+        <v/>
+      </c>
+      <c r="BA55" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A55,Mesures!$C:$C,BA$40),"")</f>
+        <v/>
+      </c>
+      <c r="BB55" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A55,Mesures!$C:$C,BB$40),"")</f>
+        <v/>
+      </c>
+      <c r="BC55" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A55,Mesures!$C:$C,BC$40),"")</f>
+        <v/>
+      </c>
+      <c r="BD55" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A55,Mesures!$C:$C,BD$40),"")</f>
+        <v/>
+      </c>
+      <c r="BE55" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A55,Mesures!$C:$C,BE$40),"")</f>
+        <v/>
+      </c>
+      <c r="BF55" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A55,Mesures!$C:$C,BF$40),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -47071,6 +55522,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A56,Mesures!$C:$C,AY$40),"")</f>
         <v/>
       </c>
+      <c r="AZ56" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A56,Mesures!$C:$C,AZ$40),"")</f>
+        <v/>
+      </c>
+      <c r="BA56" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A56,Mesures!$C:$C,BA$40),"")</f>
+        <v/>
+      </c>
+      <c r="BB56" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A56,Mesures!$C:$C,BB$40),"")</f>
+        <v/>
+      </c>
+      <c r="BC56" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A56,Mesures!$C:$C,BC$40),"")</f>
+        <v/>
+      </c>
+      <c r="BD56" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A56,Mesures!$C:$C,BD$40),"")</f>
+        <v/>
+      </c>
+      <c r="BE56" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A56,Mesures!$C:$C,BE$40),"")</f>
+        <v/>
+      </c>
+      <c r="BF56" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A56,Mesures!$C:$C,BF$40),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -47278,6 +55757,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A57,Mesures!$C:$C,AY$40),"")</f>
         <v/>
       </c>
+      <c r="AZ57" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A57,Mesures!$C:$C,AZ$40),"")</f>
+        <v/>
+      </c>
+      <c r="BA57" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A57,Mesures!$C:$C,BA$40),"")</f>
+        <v/>
+      </c>
+      <c r="BB57" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A57,Mesures!$C:$C,BB$40),"")</f>
+        <v/>
+      </c>
+      <c r="BC57" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A57,Mesures!$C:$C,BC$40),"")</f>
+        <v/>
+      </c>
+      <c r="BD57" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A57,Mesures!$C:$C,BD$40),"")</f>
+        <v/>
+      </c>
+      <c r="BE57" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A57,Mesures!$C:$C,BE$40),"")</f>
+        <v/>
+      </c>
+      <c r="BF57" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A57,Mesures!$C:$C,BF$40),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -47485,6 +55992,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A58,Mesures!$C:$C,AY$40),"")</f>
         <v/>
       </c>
+      <c r="AZ58" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A58,Mesures!$C:$C,AZ$40),"")</f>
+        <v/>
+      </c>
+      <c r="BA58" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A58,Mesures!$C:$C,BA$40),"")</f>
+        <v/>
+      </c>
+      <c r="BB58" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A58,Mesures!$C:$C,BB$40),"")</f>
+        <v/>
+      </c>
+      <c r="BC58" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A58,Mesures!$C:$C,BC$40),"")</f>
+        <v/>
+      </c>
+      <c r="BD58" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A58,Mesures!$C:$C,BD$40),"")</f>
+        <v/>
+      </c>
+      <c r="BE58" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A58,Mesures!$C:$C,BE$40),"")</f>
+        <v/>
+      </c>
+      <c r="BF58" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A58,Mesures!$C:$C,BF$40),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -47692,6 +56227,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A59,Mesures!$C:$C,AY$40),"")</f>
         <v/>
       </c>
+      <c r="AZ59" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A59,Mesures!$C:$C,AZ$40),"")</f>
+        <v/>
+      </c>
+      <c r="BA59" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A59,Mesures!$C:$C,BA$40),"")</f>
+        <v/>
+      </c>
+      <c r="BB59" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A59,Mesures!$C:$C,BB$40),"")</f>
+        <v/>
+      </c>
+      <c r="BC59" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A59,Mesures!$C:$C,BC$40),"")</f>
+        <v/>
+      </c>
+      <c r="BD59" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A59,Mesures!$C:$C,BD$40),"")</f>
+        <v/>
+      </c>
+      <c r="BE59" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A59,Mesures!$C:$C,BE$40),"")</f>
+        <v/>
+      </c>
+      <c r="BF59" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A59,Mesures!$C:$C,BF$40),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -47899,6 +56462,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A60,Mesures!$C:$C,AY$40),"")</f>
         <v/>
       </c>
+      <c r="AZ60" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A60,Mesures!$C:$C,AZ$40),"")</f>
+        <v/>
+      </c>
+      <c r="BA60" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A60,Mesures!$C:$C,BA$40),"")</f>
+        <v/>
+      </c>
+      <c r="BB60" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A60,Mesures!$C:$C,BB$40),"")</f>
+        <v/>
+      </c>
+      <c r="BC60" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A60,Mesures!$C:$C,BC$40),"")</f>
+        <v/>
+      </c>
+      <c r="BD60" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A60,Mesures!$C:$C,BD$40),"")</f>
+        <v/>
+      </c>
+      <c r="BE60" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A60,Mesures!$C:$C,BE$40),"")</f>
+        <v/>
+      </c>
+      <c r="BF60" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A60,Mesures!$C:$C,BF$40),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -48106,6 +56697,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A61,Mesures!$C:$C,AY$40),"")</f>
         <v/>
       </c>
+      <c r="AZ61" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A61,Mesures!$C:$C,AZ$40),"")</f>
+        <v/>
+      </c>
+      <c r="BA61" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A61,Mesures!$C:$C,BA$40),"")</f>
+        <v/>
+      </c>
+      <c r="BB61" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A61,Mesures!$C:$C,BB$40),"")</f>
+        <v/>
+      </c>
+      <c r="BC61" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A61,Mesures!$C:$C,BC$40),"")</f>
+        <v/>
+      </c>
+      <c r="BD61" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A61,Mesures!$C:$C,BD$40),"")</f>
+        <v/>
+      </c>
+      <c r="BE61" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A61,Mesures!$C:$C,BE$40),"")</f>
+        <v/>
+      </c>
+      <c r="BF61" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A61,Mesures!$C:$C,BF$40),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -48313,6 +56932,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A62,Mesures!$C:$C,AY$40),"")</f>
         <v/>
       </c>
+      <c r="AZ62" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A62,Mesures!$C:$C,AZ$40),"")</f>
+        <v/>
+      </c>
+      <c r="BA62" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A62,Mesures!$C:$C,BA$40),"")</f>
+        <v/>
+      </c>
+      <c r="BB62" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A62,Mesures!$C:$C,BB$40),"")</f>
+        <v/>
+      </c>
+      <c r="BC62" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A62,Mesures!$C:$C,BC$40),"")</f>
+        <v/>
+      </c>
+      <c r="BD62" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A62,Mesures!$C:$C,BD$40),"")</f>
+        <v/>
+      </c>
+      <c r="BE62" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A62,Mesures!$C:$C,BE$40),"")</f>
+        <v/>
+      </c>
+      <c r="BF62" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A62,Mesures!$C:$C,BF$40),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -48520,6 +57167,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A63,Mesures!$C:$C,AY$40),"")</f>
         <v/>
       </c>
+      <c r="AZ63" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A63,Mesures!$C:$C,AZ$40),"")</f>
+        <v/>
+      </c>
+      <c r="BA63" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A63,Mesures!$C:$C,BA$40),"")</f>
+        <v/>
+      </c>
+      <c r="BB63" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A63,Mesures!$C:$C,BB$40),"")</f>
+        <v/>
+      </c>
+      <c r="BC63" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A63,Mesures!$C:$C,BC$40),"")</f>
+        <v/>
+      </c>
+      <c r="BD63" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A63,Mesures!$C:$C,BD$40),"")</f>
+        <v/>
+      </c>
+      <c r="BE63" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A63,Mesures!$C:$C,BE$40),"")</f>
+        <v/>
+      </c>
+      <c r="BF63" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A63,Mesures!$C:$C,BF$40),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -48727,6 +57402,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A64,Mesures!$C:$C,AY$40),"")</f>
         <v/>
       </c>
+      <c r="AZ64" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A64,Mesures!$C:$C,AZ$40),"")</f>
+        <v/>
+      </c>
+      <c r="BA64" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A64,Mesures!$C:$C,BA$40),"")</f>
+        <v/>
+      </c>
+      <c r="BB64" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A64,Mesures!$C:$C,BB$40),"")</f>
+        <v/>
+      </c>
+      <c r="BC64" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A64,Mesures!$C:$C,BC$40),"")</f>
+        <v/>
+      </c>
+      <c r="BD64" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A64,Mesures!$C:$C,BD$40),"")</f>
+        <v/>
+      </c>
+      <c r="BE64" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A64,Mesures!$C:$C,BE$40),"")</f>
+        <v/>
+      </c>
+      <c r="BF64" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A64,Mesures!$C:$C,BF$40),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -48934,6 +57637,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A65,Mesures!$C:$C,AY$40),"")</f>
         <v/>
       </c>
+      <c r="AZ65" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A65,Mesures!$C:$C,AZ$40),"")</f>
+        <v/>
+      </c>
+      <c r="BA65" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A65,Mesures!$C:$C,BA$40),"")</f>
+        <v/>
+      </c>
+      <c r="BB65" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A65,Mesures!$C:$C,BB$40),"")</f>
+        <v/>
+      </c>
+      <c r="BC65" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A65,Mesures!$C:$C,BC$40),"")</f>
+        <v/>
+      </c>
+      <c r="BD65" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A65,Mesures!$C:$C,BD$40),"")</f>
+        <v/>
+      </c>
+      <c r="BE65" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A65,Mesures!$C:$C,BE$40),"")</f>
+        <v/>
+      </c>
+      <c r="BF65" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A65,Mesures!$C:$C,BF$40),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -49141,6 +57872,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A66,Mesures!$C:$C,AY$40),"")</f>
         <v/>
       </c>
+      <c r="AZ66" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A66,Mesures!$C:$C,AZ$40),"")</f>
+        <v/>
+      </c>
+      <c r="BA66" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A66,Mesures!$C:$C,BA$40),"")</f>
+        <v/>
+      </c>
+      <c r="BB66" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A66,Mesures!$C:$C,BB$40),"")</f>
+        <v/>
+      </c>
+      <c r="BC66" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A66,Mesures!$C:$C,BC$40),"")</f>
+        <v/>
+      </c>
+      <c r="BD66" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A66,Mesures!$C:$C,BD$40),"")</f>
+        <v/>
+      </c>
+      <c r="BE66" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A66,Mesures!$C:$C,BE$40),"")</f>
+        <v/>
+      </c>
+      <c r="BF66" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A66,Mesures!$C:$C,BF$40),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -49348,6 +58107,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A67,Mesures!$C:$C,AY$40),"")</f>
         <v/>
       </c>
+      <c r="AZ67" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A67,Mesures!$C:$C,AZ$40),"")</f>
+        <v/>
+      </c>
+      <c r="BA67" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A67,Mesures!$C:$C,BA$40),"")</f>
+        <v/>
+      </c>
+      <c r="BB67" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A67,Mesures!$C:$C,BB$40),"")</f>
+        <v/>
+      </c>
+      <c r="BC67" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A67,Mesures!$C:$C,BC$40),"")</f>
+        <v/>
+      </c>
+      <c r="BD67" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A67,Mesures!$C:$C,BD$40),"")</f>
+        <v/>
+      </c>
+      <c r="BE67" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A67,Mesures!$C:$C,BE$40),"")</f>
+        <v/>
+      </c>
+      <c r="BF67" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A67,Mesures!$C:$C,BF$40),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -49555,6 +58342,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A68,Mesures!$C:$C,AY$40),"")</f>
         <v/>
       </c>
+      <c r="AZ68" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A68,Mesures!$C:$C,AZ$40),"")</f>
+        <v/>
+      </c>
+      <c r="BA68" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A68,Mesures!$C:$C,BA$40),"")</f>
+        <v/>
+      </c>
+      <c r="BB68" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A68,Mesures!$C:$C,BB$40),"")</f>
+        <v/>
+      </c>
+      <c r="BC68" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A68,Mesures!$C:$C,BC$40),"")</f>
+        <v/>
+      </c>
+      <c r="BD68" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A68,Mesures!$C:$C,BD$40),"")</f>
+        <v/>
+      </c>
+      <c r="BE68" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A68,Mesures!$C:$C,BE$40),"")</f>
+        <v/>
+      </c>
+      <c r="BF68" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A68,Mesures!$C:$C,BF$40),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -49762,6 +58577,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A69,Mesures!$C:$C,AY$40),"")</f>
         <v/>
       </c>
+      <c r="AZ69" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A69,Mesures!$C:$C,AZ$40),"")</f>
+        <v/>
+      </c>
+      <c r="BA69" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A69,Mesures!$C:$C,BA$40),"")</f>
+        <v/>
+      </c>
+      <c r="BB69" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A69,Mesures!$C:$C,BB$40),"")</f>
+        <v/>
+      </c>
+      <c r="BC69" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A69,Mesures!$C:$C,BC$40),"")</f>
+        <v/>
+      </c>
+      <c r="BD69" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A69,Mesures!$C:$C,BD$40),"")</f>
+        <v/>
+      </c>
+      <c r="BE69" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A69,Mesures!$C:$C,BE$40),"")</f>
+        <v/>
+      </c>
+      <c r="BF69" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A69,Mesures!$C:$C,BF$40),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -49969,6 +58812,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A70,Mesures!$C:$C,AY$40),"")</f>
         <v/>
       </c>
+      <c r="AZ70" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A70,Mesures!$C:$C,AZ$40),"")</f>
+        <v/>
+      </c>
+      <c r="BA70" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A70,Mesures!$C:$C,BA$40),"")</f>
+        <v/>
+      </c>
+      <c r="BB70" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A70,Mesures!$C:$C,BB$40),"")</f>
+        <v/>
+      </c>
+      <c r="BC70" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A70,Mesures!$C:$C,BC$40),"")</f>
+        <v/>
+      </c>
+      <c r="BD70" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A70,Mesures!$C:$C,BD$40),"")</f>
+        <v/>
+      </c>
+      <c r="BE70" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A70,Mesures!$C:$C,BE$40),"")</f>
+        <v/>
+      </c>
+      <c r="BF70" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A70,Mesures!$C:$C,BF$40),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -50176,6 +59047,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A71,Mesures!$C:$C,AY$40),"")</f>
         <v/>
       </c>
+      <c r="AZ71" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A71,Mesures!$C:$C,AZ$40),"")</f>
+        <v/>
+      </c>
+      <c r="BA71" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A71,Mesures!$C:$C,BA$40),"")</f>
+        <v/>
+      </c>
+      <c r="BB71" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A71,Mesures!$C:$C,BB$40),"")</f>
+        <v/>
+      </c>
+      <c r="BC71" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A71,Mesures!$C:$C,BC$40),"")</f>
+        <v/>
+      </c>
+      <c r="BD71" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A71,Mesures!$C:$C,BD$40),"")</f>
+        <v/>
+      </c>
+      <c r="BE71" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A71,Mesures!$C:$C,BE$40),"")</f>
+        <v/>
+      </c>
+      <c r="BF71" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A71,Mesures!$C:$C,BF$40),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -50383,6 +59282,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A72,Mesures!$C:$C,AY$40),"")</f>
         <v/>
       </c>
+      <c r="AZ72" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A72,Mesures!$C:$C,AZ$40),"")</f>
+        <v/>
+      </c>
+      <c r="BA72" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A72,Mesures!$C:$C,BA$40),"")</f>
+        <v/>
+      </c>
+      <c r="BB72" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A72,Mesures!$C:$C,BB$40),"")</f>
+        <v/>
+      </c>
+      <c r="BC72" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A72,Mesures!$C:$C,BC$40),"")</f>
+        <v/>
+      </c>
+      <c r="BD72" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A72,Mesures!$C:$C,BD$40),"")</f>
+        <v/>
+      </c>
+      <c r="BE72" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A72,Mesures!$C:$C,BE$40),"")</f>
+        <v/>
+      </c>
+      <c r="BF72" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A72,Mesures!$C:$C,BF$40),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -50590,6 +59517,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A73,Mesures!$C:$C,AY$40),"")</f>
         <v/>
       </c>
+      <c r="AZ73" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A73,Mesures!$C:$C,AZ$40),"")</f>
+        <v/>
+      </c>
+      <c r="BA73" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A73,Mesures!$C:$C,BA$40),"")</f>
+        <v/>
+      </c>
+      <c r="BB73" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A73,Mesures!$C:$C,BB$40),"")</f>
+        <v/>
+      </c>
+      <c r="BC73" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A73,Mesures!$C:$C,BC$40),"")</f>
+        <v/>
+      </c>
+      <c r="BD73" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A73,Mesures!$C:$C,BD$40),"")</f>
+        <v/>
+      </c>
+      <c r="BE73" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A73,Mesures!$C:$C,BE$40),"")</f>
+        <v/>
+      </c>
+      <c r="BF73" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A73,Mesures!$C:$C,BF$40),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -50797,6 +59752,34 @@
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A74,Mesures!$C:$C,AY$40),"")</f>
         <v/>
       </c>
+      <c r="AZ74" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A74,Mesures!$C:$C,AZ$40),"")</f>
+        <v/>
+      </c>
+      <c r="BA74" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A74,Mesures!$C:$C,BA$40),"")</f>
+        <v/>
+      </c>
+      <c r="BB74" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A74,Mesures!$C:$C,BB$40),"")</f>
+        <v/>
+      </c>
+      <c r="BC74" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A74,Mesures!$C:$C,BC$40),"")</f>
+        <v/>
+      </c>
+      <c r="BD74" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A74,Mesures!$C:$C,BD$40),"")</f>
+        <v/>
+      </c>
+      <c r="BE74" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A74,Mesures!$C:$C,BE$40),"")</f>
+        <v/>
+      </c>
+      <c r="BF74" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A74,Mesures!$C:$C,BF$40),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -51002,6 +59985,34 @@
       </c>
       <c r="AY75" s="3">
         <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A75,Mesures!$C:$C,AY$40),"")</f>
+        <v/>
+      </c>
+      <c r="AZ75" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A75,Mesures!$C:$C,AZ$40),"")</f>
+        <v/>
+      </c>
+      <c r="BA75" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A75,Mesures!$C:$C,BA$40),"")</f>
+        <v/>
+      </c>
+      <c r="BB75" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A75,Mesures!$C:$C,BB$40),"")</f>
+        <v/>
+      </c>
+      <c r="BC75" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A75,Mesures!$C:$C,BC$40),"")</f>
+        <v/>
+      </c>
+      <c r="BD75" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A75,Mesures!$C:$C,BD$40),"")</f>
+        <v/>
+      </c>
+      <c r="BE75" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A75,Mesures!$C:$C,BE$40),"")</f>
+        <v/>
+      </c>
+      <c r="BF75" s="3">
+        <f>IFERROR(AVERAGEIFS(Mesures!$I:$I,Mesures!$F:$F,$A75,Mesures!$C:$C,BF$40),"")</f>
         <v/>
       </c>
     </row>
